--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77314</v>
+        <v>76721</v>
       </c>
       <c r="F2" t="n">
-        <v>1552722866590</v>
+        <v>1540822738759</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>28639817629</v>
+        <v>15423566617</v>
       </c>
       <c r="I2" t="n">
-        <v>79607</v>
+        <v>77479</v>
       </c>
       <c r="J2" t="n">
-        <v>76952</v>
+        <v>76516</v>
       </c>
       <c r="K2" t="n">
-        <v>-262.4575759976724</v>
+        <v>-567.5499394721992</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.40435</v>
+        <v>-0.73433</v>
       </c>
       <c r="M2" t="n">
-        <v>20083262</v>
+        <v>20083712</v>
       </c>
       <c r="N2" t="n">
-        <v>20083312</v>
+        <v>20083803</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2534.68</v>
+        <v>2475.01</v>
       </c>
       <c r="F3" t="n">
-        <v>309335837072</v>
+        <v>302065765195</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>21125178458</v>
+        <v>8681587348</v>
       </c>
       <c r="I3" t="n">
-        <v>2647.68</v>
+        <v>2543.69</v>
       </c>
       <c r="J3" t="n">
-        <v>2492.31</v>
+        <v>2470.18</v>
       </c>
       <c r="K3" t="n">
-        <v>40.13</v>
+        <v>-63.41930568684711</v>
       </c>
       <c r="L3" t="n">
-        <v>1.54763</v>
+        <v>-2.49837</v>
       </c>
       <c r="M3" t="n">
-        <v>122041373.1030534</v>
+        <v>122044301.968694</v>
       </c>
       <c r="N3" t="n">
-        <v>122041373.1030533</v>
+        <v>122044301.968694</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99981</v>
+        <v>0.9997549999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183482230974</v>
+        <v>183471976747</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>59719219122</v>
+        <v>31189029121</v>
       </c>
       <c r="I4" t="n">
-        <v>0.99993</v>
+        <v>0.9999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999562</v>
+        <v>0.999673</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00025862</v>
+        <v>-2.4432368397109e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02306</v>
+        <v>-0.00244</v>
       </c>
       <c r="M4" t="n">
         <v>183517171052.1943</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>736.4299999999999</v>
+        <v>715.63</v>
       </c>
       <c r="F5" t="n">
-        <v>98062399038</v>
+        <v>95291988111</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1194854270</v>
+        <v>729267845</v>
       </c>
       <c r="I5" t="n">
-        <v>740.12</v>
+        <v>736.9</v>
       </c>
       <c r="J5" t="n">
-        <v>717.4400000000001</v>
+        <v>714.33</v>
       </c>
       <c r="K5" t="n">
-        <v>14.67</v>
+        <v>-20.34689269518844</v>
       </c>
       <c r="L5" t="n">
-        <v>1.99022</v>
+        <v>-2.76462</v>
       </c>
       <c r="M5" t="n">
-        <v>133161036.91</v>
+        <v>133160976.96</v>
       </c>
       <c r="N5" t="n">
-        <v>133161033.96</v>
+        <v>133160976.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="F6" t="n">
-        <v>86186130739</v>
+        <v>84099500734</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2258448691</v>
+        <v>926219439</v>
       </c>
       <c r="I6" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0121198</v>
+        <v>-0.02964740290489787</v>
       </c>
       <c r="L6" t="n">
-        <v>0.73402</v>
+        <v>-2.16849</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999865</v>
+        <v>0.999803</v>
       </c>
       <c r="F7" t="n">
-        <v>74337600627</v>
+        <v>74215368644</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>15757949678</v>
+        <v>6204149731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999952</v>
+        <v>0.999961</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999771</v>
+        <v>0.999717</v>
       </c>
       <c r="K7" t="n">
-        <v>7.379e-05</v>
+        <v>-2.497102552268e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00401</v>
+        <v>-0.0025</v>
       </c>
       <c r="M7" t="n">
-        <v>74347671861.2077</v>
+        <v>74230204758.1429</v>
       </c>
       <c r="N7" t="n">
-        <v>74349866797.12619</v>
+        <v>74232084708.50609</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.26</v>
+        <v>99.78</v>
       </c>
       <c r="F8" t="n">
-        <v>59986196956</v>
+        <v>58544716598</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4038038163</v>
+        <v>1835705498</v>
       </c>
       <c r="I8" t="n">
-        <v>105.42</v>
+        <v>102.3</v>
       </c>
       <c r="J8" t="n">
-        <v>100.64</v>
+        <v>99.45</v>
       </c>
       <c r="K8" t="n">
-        <v>1.29</v>
+        <v>-2.106818682073197</v>
       </c>
       <c r="L8" t="n">
-        <v>1.16766</v>
+        <v>-2.06771</v>
       </c>
       <c r="M8" t="n">
-        <v>586632914.9787524</v>
+        <v>586731099.4701495</v>
       </c>
       <c r="N8" t="n">
-        <v>633924207.4848769</v>
+        <v>634018355.2162156</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.341025</v>
+        <v>0.340537</v>
       </c>
       <c r="F9" t="n">
-        <v>32378541531</v>
+        <v>32326642058</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>521177154</v>
+        <v>340530028</v>
       </c>
       <c r="I9" t="n">
-        <v>0.344079</v>
+        <v>0.341069</v>
       </c>
       <c r="J9" t="n">
-        <v>0.335532</v>
+        <v>0.339263</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00460594</v>
+        <v>0.00014634</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36849</v>
+        <v>0.04299</v>
       </c>
       <c r="M9" t="n">
         <v>94944652948.92628</v>
       </c>
       <c r="N9" t="n">
-        <v>94946361438.41998</v>
+        <v>94948611026.79419</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.016</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>22870501626</v>
+        <v>22551817529</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>60215308</v>
+        <v>50043</v>
       </c>
       <c r="I10" t="n">
-        <v>1.036</v>
+        <v>1.044</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.0185665039219145</v>
+        <v>-0.01618492385492987</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.79099</v>
+        <v>-1.59239</v>
       </c>
       <c r="M10" t="n">
-        <v>22502232981.668</v>
+        <v>22547102017.768</v>
       </c>
       <c r="N10" t="n">
-        <v>22502232981.668</v>
+        <v>22552850918.668</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T01:20:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1158.26</v>
+        <v>1087.03</v>
       </c>
       <c r="F11" t="n">
-        <v>19604336005</v>
+        <v>18394302590</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H11" t="n">
-        <v>1665786195</v>
+        <v>1165436311</v>
       </c>
       <c r="I11" t="n">
-        <v>1215.61</v>
+        <v>1154.85</v>
       </c>
       <c r="J11" t="n">
-        <v>1121.91</v>
+        <v>1075.39</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.629609895717067</v>
+        <v>-67.91789754973047</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1411</v>
+        <v>-5.88059</v>
       </c>
       <c r="M11" t="n">
         <v>16925695.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16928367.3530448</v>
+        <v>16930195.4780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.31999999999999</v>
+        <v>77.36</v>
       </c>
       <c r="F12" t="n">
-        <v>17867396242</v>
+        <v>17208887027</v>
       </c>
       <c r="G12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H12" t="n">
-        <v>1071366521</v>
+        <v>575492758</v>
       </c>
       <c r="I12" t="n">
-        <v>83.63</v>
+        <v>80.77</v>
       </c>
       <c r="J12" t="n">
-        <v>78.41</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.044752684165488</v>
+        <v>-2.878903719731241</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.36165</v>
+        <v>-3.58773</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.085033</v>
+        <v>0.08321099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13255413715</v>
+        <v>12972524811</v>
       </c>
       <c r="G13" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="n">
-        <v>651168802</v>
+        <v>331894085</v>
       </c>
       <c r="I13" t="n">
-        <v>0.087898</v>
+        <v>0.085325</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08368</v>
+        <v>0.08315699999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00046809</v>
+        <v>-0.001738211689757158</v>
       </c>
       <c r="L13" t="n">
-        <v>0.50806</v>
+        <v>-2.04618</v>
       </c>
       <c r="M13" t="n">
-        <v>155884756383.7052</v>
+        <v>155898206383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155884476383.7052</v>
+        <v>171610343126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,31 +1305,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01512165</v>
+        <v>0.01525428</v>
       </c>
       <c r="F14" t="n">
-        <v>10724534145</v>
+        <v>10818364725</v>
       </c>
       <c r="G14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H14" t="n">
-        <v>38289961</v>
+        <v>34695409</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01626765</v>
+        <v>0.01589978</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01509086</v>
+        <v>0.01503352</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000651524093373202</v>
+        <v>0.00017217</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.09935</v>
+        <v>1.14158</v>
       </c>
       <c r="M14" t="n">
-        <v>709217602168.6873</v>
+        <v>709218381891.3804</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.46</v>
+        <v>529.33</v>
       </c>
       <c r="F15" t="n">
-        <v>9955702220</v>
+        <v>9952232995</v>
       </c>
       <c r="G15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H15" t="n">
-        <v>123793672</v>
+        <v>97785882</v>
       </c>
       <c r="I15" t="n">
-        <v>546.62</v>
+        <v>543.63</v>
       </c>
       <c r="J15" t="n">
-        <v>509.38</v>
+        <v>524.34</v>
       </c>
       <c r="K15" t="n">
-        <v>16.48</v>
+        <v>-1.876506267517925</v>
       </c>
       <c r="L15" t="n">
-        <v>3.27851</v>
+        <v>-0.35326</v>
       </c>
       <c r="M15" t="n">
-        <v>18803665.4396461</v>
+        <v>18804107.03109685</v>
       </c>
       <c r="N15" t="n">
-        <v>18803679.83773144</v>
+        <v>18804122.63109685</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999871</v>
+        <v>0.999763</v>
       </c>
       <c r="F16" t="n">
-        <v>9804836648</v>
+        <v>9846306603</v>
       </c>
       <c r="G16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H16" t="n">
-        <v>169068394</v>
+        <v>69915065</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.999937</v>
       </c>
       <c r="J16" t="n">
         <v>0.999626</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00020096</v>
+        <v>1.663e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00217</v>
+        <v>0.00166</v>
       </c>
       <c r="M16" t="n">
-        <v>9806099950.497782</v>
+        <v>9849589553.751617</v>
       </c>
       <c r="N16" t="n">
-        <v>9806099950.497782</v>
+        <v>9848763608.199549</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.37</v>
+        <v>79.53</v>
       </c>
       <c r="F17" t="n">
-        <v>9474296952</v>
+        <v>9375103870</v>
       </c>
       <c r="G17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H17" t="n">
-        <v>120604559</v>
+        <v>29764166</v>
       </c>
       <c r="I17" t="n">
-        <v>83.22</v>
+        <v>80.62</v>
       </c>
       <c r="J17" t="n">
-        <v>80</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.054638</v>
+        <v>-0.8357182138967261</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.18838</v>
+        <v>-1.03986</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.57</v>
+        <v>11.24</v>
       </c>
       <c r="F18" t="n">
-        <v>8653159423</v>
+        <v>8409875424</v>
       </c>
       <c r="G18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H18" t="n">
-        <v>449714905</v>
+        <v>217162086</v>
       </c>
       <c r="I18" t="n">
-        <v>12.17</v>
+        <v>11.62</v>
       </c>
       <c r="J18" t="n">
-        <v>11.46</v>
+        <v>11.24</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02458788</v>
+        <v>-0.3109450215767513</v>
       </c>
       <c r="L18" t="n">
-        <v>0.05704</v>
+        <v>-2.69148</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.109999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="F19" t="n">
-        <v>8383078709</v>
+        <v>8329317905</v>
       </c>
       <c r="G19" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H19" t="n">
-        <v>119813</v>
+        <v>253370</v>
       </c>
       <c r="I19" t="n">
-        <v>9.16</v>
+        <v>9.15</v>
       </c>
       <c r="J19" t="n">
-        <v>9.1</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.03313417990051093</v>
+        <v>-0.06044450122227296</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.36101</v>
+        <v>-0.6631</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.208994</v>
+        <v>0.20505</v>
       </c>
       <c r="F20" t="n">
-        <v>7840773190</v>
+        <v>7692716004</v>
       </c>
       <c r="G20" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H20" t="n">
-        <v>484036030</v>
+        <v>203748626</v>
       </c>
       <c r="I20" t="n">
-        <v>0.215743</v>
+        <v>0.209134</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203215</v>
+        <v>0.203378</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00173125</v>
+        <v>-0.003357533117483491</v>
       </c>
       <c r="L20" t="n">
-        <v>0.54303</v>
+        <v>-1.61104</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260912T124740Z-cfa561</t>
+          <t>20260913T134525Z-2ca65f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.181899</v>
+        <v>0.178693</v>
       </c>
       <c r="F21" t="n">
-        <v>6336215728</v>
+        <v>6224230152</v>
       </c>
       <c r="G21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H21" t="n">
-        <v>152590419</v>
+        <v>77381146</v>
       </c>
       <c r="I21" t="n">
-        <v>0.184869</v>
+        <v>0.182593</v>
       </c>
       <c r="J21" t="n">
-        <v>0.177114</v>
+        <v>0.177194</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00402238</v>
+        <v>-0.002332784981005254</v>
       </c>
       <c r="L21" t="n">
-        <v>2.13215</v>
+        <v>-1.28865</v>
       </c>
       <c r="M21" t="n">
-        <v>34833772973.98598</v>
+        <v>34833765117.35425</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-12T12:44:20.000Z</t>
+          <t>2026-09-13T13:42:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76721</v>
+        <v>78362</v>
       </c>
       <c r="F2" t="n">
-        <v>1540822738759</v>
+        <v>1573986553774</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>15423566617</v>
+        <v>25984289979</v>
       </c>
       <c r="I2" t="n">
-        <v>77479</v>
+        <v>78630</v>
       </c>
       <c r="J2" t="n">
-        <v>76516</v>
+        <v>76439</v>
       </c>
       <c r="K2" t="n">
-        <v>-567.5499394721992</v>
+        <v>1231.1</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.73433</v>
+        <v>1.60581</v>
       </c>
       <c r="M2" t="n">
-        <v>20083712</v>
+        <v>20084256</v>
       </c>
       <c r="N2" t="n">
-        <v>20083803</v>
+        <v>20084296</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2475.01</v>
+        <v>2504.03</v>
       </c>
       <c r="F3" t="n">
-        <v>302065765195</v>
+        <v>305633502308</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8681587348</v>
+        <v>12681366507</v>
       </c>
       <c r="I3" t="n">
-        <v>2543.69</v>
+        <v>2531.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2470.18</v>
+        <v>2467.86</v>
       </c>
       <c r="K3" t="n">
-        <v>-63.41930568684711</v>
+        <v>14.1</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.49837</v>
+        <v>0.55974</v>
       </c>
       <c r="M3" t="n">
-        <v>122044301.968694</v>
+        <v>122047243.4940371</v>
       </c>
       <c r="N3" t="n">
-        <v>122044301.968694</v>
+        <v>122047243.4940371</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9997549999999999</v>
+        <v>0.999729</v>
       </c>
       <c r="F4" t="n">
-        <v>183471976747</v>
+        <v>183381380503</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>31189029121</v>
+        <v>47887967714</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9999</v>
+        <v>0.999795</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999673</v>
+        <v>0.999546</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.4432368397109e-05</v>
+        <v>-3.1522703644593e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00244</v>
+        <v>-0.00331</v>
       </c>
       <c r="M4" t="n">
-        <v>183517171052.1943</v>
+        <v>183430992297.9018</v>
       </c>
       <c r="N4" t="n">
-        <v>188984116915.3062</v>
+        <v>188897938202.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>715.63</v>
+        <v>721.51</v>
       </c>
       <c r="F5" t="n">
-        <v>95291988111</v>
+        <v>96081461908</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>729267845</v>
+        <v>887352635</v>
       </c>
       <c r="I5" t="n">
-        <v>736.9</v>
+        <v>727.36</v>
       </c>
       <c r="J5" t="n">
-        <v>714.33</v>
+        <v>714.28</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.34689269518844</v>
+        <v>2.66</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.76462</v>
+        <v>0.3615</v>
       </c>
       <c r="M5" t="n">
-        <v>133160976.96</v>
+        <v>133160863.85</v>
       </c>
       <c r="N5" t="n">
-        <v>133160976.96</v>
+        <v>133160863.85</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>84099500734</v>
+        <v>88060370043</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>926219439</v>
+        <v>2415726593</v>
       </c>
       <c r="I6" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
         <v>1.34</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02964740290489787</v>
+        <v>0.056142</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.16849</v>
+        <v>4.18102</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999803</v>
+        <v>0.999841</v>
       </c>
       <c r="F7" t="n">
-        <v>74215368644</v>
+        <v>74142138897</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6204149731</v>
+        <v>13799048631</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999961</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999717</v>
+        <v>0.999711</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.497102552268e-05</v>
+        <v>-2.1127436362067e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0025</v>
+        <v>-0.00261</v>
       </c>
       <c r="M7" t="n">
-        <v>74230204758.1429</v>
+        <v>74153956598.56355</v>
       </c>
       <c r="N7" t="n">
-        <v>74232084708.50609</v>
+        <v>74236759977.72971</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>99.78</v>
+        <v>101.84</v>
       </c>
       <c r="F8" t="n">
-        <v>58544716598</v>
+        <v>59767609118</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1835705498</v>
+        <v>2729178439</v>
       </c>
       <c r="I8" t="n">
-        <v>102.3</v>
+        <v>102.21</v>
       </c>
       <c r="J8" t="n">
-        <v>99.45</v>
+        <v>99.03</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.106818682073197</v>
+        <v>1.51</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.06771</v>
+        <v>1.50505</v>
       </c>
       <c r="M8" t="n">
-        <v>586731099.4701495</v>
+        <v>586892648.6679221</v>
       </c>
       <c r="N8" t="n">
-        <v>634018355.2162156</v>
+        <v>634017381.8979012</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.340537</v>
+        <v>0.340552</v>
       </c>
       <c r="F9" t="n">
-        <v>32326642058</v>
+        <v>32338144917</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>340530028</v>
+        <v>363419765</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341069</v>
+        <v>0.341529</v>
       </c>
       <c r="J9" t="n">
-        <v>0.339263</v>
+        <v>0.337711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00014634</v>
+        <v>-0.000581742705109523</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04299</v>
+        <v>-0.15732</v>
       </c>
       <c r="M9" t="n">
-        <v>94944652948.92628</v>
+        <v>94950123551.61649</v>
       </c>
       <c r="N9" t="n">
-        <v>94948611026.79419</v>
+        <v>94950129154.07608</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>1.046</v>
       </c>
       <c r="F10" t="n">
-        <v>22551817529</v>
+        <v>23593992468</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>50043</v>
+        <v>958374</v>
       </c>
       <c r="I10" t="n">
-        <v>1.044</v>
+        <v>1.042</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-0.01618492385492987</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-1.59239</v>
-      </c>
+        <v>1.006</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>22547102017.768</v>
+        <v>22558008629.268</v>
       </c>
       <c r="N10" t="n">
-        <v>22552850918.668</v>
+        <v>22558008629.268</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-13T01:20:10.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1087.03</v>
+        <v>1135.01</v>
       </c>
       <c r="F11" t="n">
-        <v>18394302590</v>
+        <v>19206090756</v>
       </c>
       <c r="G11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1165436311</v>
+        <v>1142157231</v>
       </c>
       <c r="I11" t="n">
-        <v>1154.85</v>
+        <v>1155.3</v>
       </c>
       <c r="J11" t="n">
-        <v>1075.39</v>
+        <v>1048.58</v>
       </c>
       <c r="K11" t="n">
-        <v>-67.91789754973047</v>
+        <v>46.32</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.88059</v>
+        <v>4.11852</v>
       </c>
       <c r="M11" t="n">
-        <v>16925695.4780448</v>
+        <v>16930431.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>16930195.4780448</v>
+        <v>16932228.2905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>77.36</v>
+        <v>79.87</v>
       </c>
       <c r="F12" t="n">
-        <v>17208887027</v>
+        <v>17767318483</v>
       </c>
       <c r="G12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>575492758</v>
+        <v>722094725</v>
       </c>
       <c r="I12" t="n">
-        <v>80.77</v>
+        <v>80.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>77.09999999999999</v>
+        <v>77.01000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.878903719731241</v>
+        <v>1.74</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.58773</v>
+        <v>2.18041</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08321099999999999</v>
+        <v>0.08391800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12972524811</v>
+        <v>13084729747</v>
       </c>
       <c r="G13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>331894085</v>
+        <v>582797744</v>
       </c>
       <c r="I13" t="n">
-        <v>0.085325</v>
+        <v>0.084753</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08315699999999999</v>
+        <v>0.08204</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001738211689757158</v>
+        <v>0.00034659</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.04618</v>
+        <v>0.35787</v>
       </c>
       <c r="M13" t="n">
-        <v>155898206383.7052</v>
+        <v>155910866383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171610343126.579</v>
+        <v>155913316383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,31 +1301,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01525428</v>
+        <v>0.01437241</v>
       </c>
       <c r="F14" t="n">
-        <v>10818364725</v>
+        <v>10194077797</v>
       </c>
       <c r="G14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>34695409</v>
+        <v>23950993</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01589978</v>
+        <v>0.01539524</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01503352</v>
+        <v>0.01471193</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00017217</v>
+        <v>-0.000917734779514243</v>
       </c>
       <c r="L14" t="n">
-        <v>1.14158</v>
+        <v>-5.95737</v>
       </c>
       <c r="M14" t="n">
-        <v>709218381891.3804</v>
+        <v>709219646352.0608</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1344,144 +1340,144 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.33</v>
+        <v>0.999728</v>
       </c>
       <c r="F15" t="n">
-        <v>9952232995</v>
+        <v>9822164283</v>
       </c>
       <c r="G15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>97785882</v>
+        <v>103418986</v>
       </c>
       <c r="I15" t="n">
-        <v>543.63</v>
+        <v>0.999883</v>
       </c>
       <c r="J15" t="n">
-        <v>524.34</v>
+        <v>0.99953</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.876506267517925</v>
+        <v>-5.1109509834446e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.35326</v>
+        <v>-0.00638</v>
       </c>
       <c r="M15" t="n">
-        <v>18804107.03109685</v>
+        <v>9825388957.758593</v>
       </c>
       <c r="N15" t="n">
-        <v>18804122.63109685</v>
+        <v>9825388957.758593</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999763</v>
+        <v>513.16</v>
       </c>
       <c r="F16" t="n">
-        <v>9846306603</v>
+        <v>9650985830</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>69915065</v>
+        <v>120076787</v>
       </c>
       <c r="I16" t="n">
-        <v>0.999937</v>
+        <v>537.77</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999626</v>
+        <v>502.91</v>
       </c>
       <c r="K16" t="n">
-        <v>1.663e-05</v>
+        <v>-22.04391946356634</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00166</v>
+        <v>-4.24549</v>
       </c>
       <c r="M16" t="n">
-        <v>9849589553.751617</v>
+        <v>18804596.02384349</v>
       </c>
       <c r="N16" t="n">
-        <v>9848763608.199549</v>
+        <v>18804629.02373879</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>79.53</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9375103870</v>
+        <v>9541965154</v>
       </c>
       <c r="G17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>29764166</v>
+        <v>103097807</v>
       </c>
       <c r="I17" t="n">
-        <v>80.62</v>
+        <v>81.25</v>
       </c>
       <c r="J17" t="n">
-        <v>79.31999999999999</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8357182138967261</v>
+        <v>1.063</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.03986</v>
+        <v>1.3493</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.24</v>
+        <v>11.43</v>
       </c>
       <c r="F18" t="n">
-        <v>8409875424</v>
+        <v>8547956810</v>
       </c>
       <c r="G18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>217162086</v>
+        <v>351732452</v>
       </c>
       <c r="I18" t="n">
-        <v>11.62</v>
+        <v>11.49</v>
       </c>
       <c r="J18" t="n">
-        <v>11.24</v>
+        <v>11.14</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3109450215767513</v>
+        <v>0.167787</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.69148</v>
+        <v>1.4751</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.06</v>
+        <v>8.99</v>
       </c>
       <c r="F19" t="n">
-        <v>8329317905</v>
+        <v>8265020156</v>
       </c>
       <c r="G19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>253370</v>
+        <v>146114</v>
       </c>
       <c r="I19" t="n">
-        <v>9.15</v>
+        <v>9.08</v>
       </c>
       <c r="J19" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06044450122227296</v>
+        <v>-0.06750082080595554</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6631</v>
+        <v>-0.7448900000000001</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.20505</v>
+        <v>0.208339</v>
       </c>
       <c r="F20" t="n">
-        <v>7692716004</v>
+        <v>7816066705</v>
       </c>
       <c r="G20" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>203748626</v>
+        <v>352248691</v>
       </c>
       <c r="I20" t="n">
-        <v>0.209134</v>
+        <v>0.212356</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203378</v>
+        <v>0.202412</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.003357533117483491</v>
+        <v>0.00229722</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.61104</v>
+        <v>1.0824</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1734,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260913T134525Z-2ca65f</t>
+          <t>20260914T155014Z-854b8f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178693</v>
+        <v>0.192245</v>
       </c>
       <c r="F21" t="n">
-        <v>6224230152</v>
+        <v>6698510243</v>
       </c>
       <c r="G21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>77381146</v>
+        <v>232181544</v>
       </c>
       <c r="I21" t="n">
-        <v>0.182593</v>
+        <v>0.193471</v>
       </c>
       <c r="J21" t="n">
-        <v>0.177194</v>
+        <v>0.176496</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.002332784981005254</v>
+        <v>0.01369287</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.28865</v>
+        <v>7.59998</v>
       </c>
       <c r="M21" t="n">
-        <v>34833765117.35425</v>
+        <v>34833755724.17101</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-13T13:42:20.000Z</t>
+          <t>2026-09-14T15:47:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78362</v>
+        <v>77928</v>
       </c>
       <c r="F2" t="n">
-        <v>1573986553774</v>
+        <v>1565278264656</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>25984289979</v>
+        <v>32481754899</v>
       </c>
       <c r="I2" t="n">
-        <v>78630</v>
+        <v>79530</v>
       </c>
       <c r="J2" t="n">
-        <v>76439</v>
+        <v>77010</v>
       </c>
       <c r="K2" t="n">
-        <v>1231.1</v>
+        <v>1192.34</v>
       </c>
       <c r="L2" t="n">
-        <v>1.60581</v>
+        <v>1.55383</v>
       </c>
       <c r="M2" t="n">
-        <v>20084256</v>
+        <v>20084421</v>
       </c>
       <c r="N2" t="n">
-        <v>20084296</v>
+        <v>20084481</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2504.03</v>
+        <v>2512.93</v>
       </c>
       <c r="F3" t="n">
-        <v>305633502308</v>
+        <v>306704123966</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12681366507</v>
+        <v>16310732511</v>
       </c>
       <c r="I3" t="n">
-        <v>2531.64</v>
+        <v>2607.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2467.86</v>
+        <v>2489.59</v>
       </c>
       <c r="K3" t="n">
-        <v>14.1</v>
+        <v>33.64</v>
       </c>
       <c r="L3" t="n">
-        <v>0.55974</v>
+        <v>1.35678</v>
       </c>
       <c r="M3" t="n">
         <v>122047243.4940371</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999729</v>
+        <v>0.9998359999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183381380503</v>
+        <v>183404017289</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>47887967714</v>
+        <v>58316519980</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999795</v>
+        <v>0.999954</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999546</v>
+        <v>0.999563</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.1522703644593e-05</v>
+        <v>0.00017816</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00331</v>
+        <v>0.01782</v>
       </c>
       <c r="M4" t="n">
-        <v>183430992297.9018</v>
+        <v>183431197333.8773</v>
       </c>
       <c r="N4" t="n">
-        <v>188897938202.3062</v>
+        <v>188898143247.2662</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>721.51</v>
+        <v>719.73</v>
       </c>
       <c r="F5" t="n">
-        <v>96081461908</v>
+        <v>95843853248</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>887352635</v>
+        <v>1013896622</v>
       </c>
       <c r="I5" t="n">
-        <v>727.36</v>
+        <v>732.8</v>
       </c>
       <c r="J5" t="n">
-        <v>714.28</v>
+        <v>717.26</v>
       </c>
       <c r="K5" t="n">
-        <v>2.66</v>
+        <v>3.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3615</v>
+        <v>0.46471</v>
       </c>
       <c r="M5" t="n">
-        <v>133160863.85</v>
+        <v>133160833.09</v>
       </c>
       <c r="N5" t="n">
-        <v>133160863.85</v>
+        <v>133160833.09</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="F6" t="n">
-        <v>88060370043</v>
+        <v>89328302982</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2415726593</v>
+        <v>3988480517</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>0.056142</v>
+        <v>0.07849299999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>4.18102</v>
+        <v>5.84888</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999841</v>
+        <v>0.999866</v>
       </c>
       <c r="F7" t="n">
-        <v>74142138897</v>
+        <v>74355972434</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13799048631</v>
+        <v>18147169260</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
@@ -868,16 +868,16 @@
         <v>0.999711</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.1127436362067e-05</v>
+        <v>3.435e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00261</v>
+        <v>0.00344</v>
       </c>
       <c r="M7" t="n">
-        <v>74153956598.56355</v>
+        <v>74364752733.23085</v>
       </c>
       <c r="N7" t="n">
-        <v>74236759977.72971</v>
+        <v>74371126949.03763</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.84</v>
+        <v>102.33</v>
       </c>
       <c r="F8" t="n">
-        <v>59767609118</v>
+        <v>60071914459</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2729178439</v>
+        <v>3391879841</v>
       </c>
       <c r="I8" t="n">
-        <v>102.21</v>
+        <v>104.76</v>
       </c>
       <c r="J8" t="n">
-        <v>99.03</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>1.51</v>
+        <v>2.95</v>
       </c>
       <c r="L8" t="n">
-        <v>1.50505</v>
+        <v>2.96946</v>
       </c>
       <c r="M8" t="n">
-        <v>586892648.6679221</v>
+        <v>587028564.7667522</v>
       </c>
       <c r="N8" t="n">
-        <v>634017381.8979012</v>
+        <v>634017029.7664536</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.340552</v>
+        <v>0.337933</v>
       </c>
       <c r="F9" t="n">
-        <v>32338144917</v>
+        <v>32085906398</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>363419765</v>
+        <v>459700901</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341529</v>
+        <v>0.342048</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337711</v>
+        <v>0.33736</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000581742705109523</v>
+        <v>-0.000482044361519829</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.15732</v>
+        <v>-0.14244</v>
       </c>
       <c r="M9" t="n">
-        <v>94950123551.61649</v>
+        <v>94950365063.49529</v>
       </c>
       <c r="N9" t="n">
-        <v>94950129154.07608</v>
+        <v>94950919109.75899</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,19 +1045,19 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.046</v>
+        <v>1.028</v>
       </c>
       <c r="F10" t="n">
-        <v>23593992468</v>
+        <v>23190254032</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>958374</v>
+        <v>26456887</v>
       </c>
       <c r="I10" t="n">
-        <v>1.042</v>
+        <v>1.048</v>
       </c>
       <c r="J10" t="n">
         <v>1.006</v>
@@ -1080,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1135.01</v>
+        <v>1156.87</v>
       </c>
       <c r="F11" t="n">
-        <v>19206090756</v>
+        <v>19585748329</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1142157231</v>
+        <v>1339721891</v>
       </c>
       <c r="I11" t="n">
-        <v>1155.3</v>
+        <v>1222.73</v>
       </c>
       <c r="J11" t="n">
-        <v>1048.58</v>
+        <v>1072.1</v>
       </c>
       <c r="K11" t="n">
-        <v>46.32</v>
+        <v>95.72</v>
       </c>
       <c r="L11" t="n">
-        <v>4.11852</v>
+        <v>9.020440000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>16930431.4155448</v>
+        <v>16932570.4780448</v>
       </c>
       <c r="N11" t="n">
-        <v>16932228.2905448</v>
+        <v>16932909.5405448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>79.87</v>
+        <v>80.2</v>
       </c>
       <c r="F12" t="n">
-        <v>17767318483</v>
+        <v>17841668216</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>722094725</v>
+        <v>820683271</v>
       </c>
       <c r="I12" t="n">
-        <v>80.98999999999999</v>
+        <v>82.38</v>
       </c>
       <c r="J12" t="n">
-        <v>77.01000000000001</v>
+        <v>78.05</v>
       </c>
       <c r="K12" t="n">
-        <v>1.74</v>
+        <v>2.51</v>
       </c>
       <c r="L12" t="n">
-        <v>2.18041</v>
+        <v>3.22502</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08391800000000001</v>
+        <v>0.083762</v>
       </c>
       <c r="F13" t="n">
-        <v>13084729747</v>
+        <v>13061146331</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>582797744</v>
+        <v>623849039</v>
       </c>
       <c r="I13" t="n">
-        <v>0.084753</v>
+        <v>0.086033</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08204</v>
+        <v>0.083028</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00034659</v>
+        <v>0.00124728</v>
       </c>
       <c r="L13" t="n">
-        <v>0.35787</v>
+        <v>1.51158</v>
       </c>
       <c r="M13" t="n">
-        <v>155910866383.7052</v>
+        <v>155919246383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155913316383.7052</v>
+        <v>171630873126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,31 +1301,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01437241</v>
+        <v>0.01423283</v>
       </c>
       <c r="F14" t="n">
-        <v>10194077797</v>
+        <v>10097241960</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>23950993</v>
+        <v>27250626</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01539524</v>
+        <v>0.01529975</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01471193</v>
+        <v>0.01423111</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000917734779514243</v>
+        <v>-0.000917806640155248</v>
       </c>
       <c r="L14" t="n">
-        <v>-5.95737</v>
+        <v>-6.05787</v>
       </c>
       <c r="M14" t="n">
-        <v>709219646352.0608</v>
+        <v>709219950838.6726</v>
       </c>
       <c r="N14" t="n">
         <v>1142408526965.963</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999728</v>
+        <v>0.999815</v>
       </c>
       <c r="F15" t="n">
-        <v>9822164283</v>
+        <v>9841412373</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>103418986</v>
+        <v>128014911</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999883</v>
+        <v>0.999922</v>
       </c>
       <c r="J15" t="n">
         <v>0.99953</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.1109509834446e-05</v>
+        <v>4.974e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00638</v>
+        <v>0.00497</v>
       </c>
       <c r="M15" t="n">
-        <v>9825388957.758593</v>
+        <v>9843079519.306154</v>
       </c>
       <c r="N15" t="n">
-        <v>9825388957.758593</v>
+        <v>9859445986.033854</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,34 +1431,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>513.16</v>
+        <v>517.35</v>
       </c>
       <c r="F16" t="n">
-        <v>9650985830</v>
+        <v>9729591804</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>120076787</v>
+        <v>144582594</v>
       </c>
       <c r="I16" t="n">
-        <v>537.77</v>
+        <v>526.9</v>
       </c>
       <c r="J16" t="n">
         <v>502.91</v>
       </c>
       <c r="K16" t="n">
-        <v>-22.04391946356634</v>
+        <v>4.44</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.24549</v>
+        <v>0.86522</v>
       </c>
       <c r="M16" t="n">
-        <v>18804596.02384349</v>
+        <v>18804748.99981384</v>
       </c>
       <c r="N16" t="n">
-        <v>18804629.02373879</v>
+        <v>18804784.39672368</v>
       </c>
       <c r="O16" t="n">
         <v>797.73</v>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.93000000000001</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9541965154</v>
+        <v>9508070993</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>103097807</v>
+        <v>124952764</v>
       </c>
       <c r="I17" t="n">
-        <v>81.25</v>
+        <v>82.67</v>
       </c>
       <c r="J17" t="n">
-        <v>79.23999999999999</v>
+        <v>79.78</v>
       </c>
       <c r="K17" t="n">
-        <v>1.063</v>
+        <v>1.11</v>
       </c>
       <c r="L17" t="n">
-        <v>1.3493</v>
+        <v>1.40009</v>
       </c>
       <c r="M17" t="n">
         <v>117882016</v>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.43</v>
+        <v>11.57</v>
       </c>
       <c r="F18" t="n">
-        <v>8547956810</v>
+        <v>8656632447</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>351732452</v>
+        <v>378630111</v>
       </c>
       <c r="I18" t="n">
-        <v>11.49</v>
+        <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>11.14</v>
+        <v>11.25</v>
       </c>
       <c r="K18" t="n">
-        <v>0.167787</v>
+        <v>0.331506</v>
       </c>
       <c r="L18" t="n">
-        <v>1.4751</v>
+        <v>2.94987</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.99</v>
+        <v>8.98</v>
       </c>
       <c r="F19" t="n">
-        <v>8265020156</v>
+        <v>8262550568</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>146114</v>
+        <v>119220</v>
       </c>
       <c r="I19" t="n">
-        <v>9.08</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J19" t="n">
         <v>8.949999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06750082080595554</v>
+        <v>-0.05097400490951998</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.7448900000000001</v>
+        <v>-0.56428</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.208339</v>
+        <v>0.207943</v>
       </c>
       <c r="F20" t="n">
-        <v>7816066705</v>
+        <v>7803954887</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>352248691</v>
+        <v>399285548</v>
       </c>
       <c r="I20" t="n">
-        <v>0.212356</v>
+        <v>0.215603</v>
       </c>
       <c r="J20" t="n">
-        <v>0.202412</v>
+        <v>0.204682</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00229722</v>
+        <v>0.00435576</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0824</v>
+        <v>2.1395</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260914T155014Z-854b8f</t>
+          <t>20260915T014026Z-a7c3b0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192245</v>
+        <v>0.192906</v>
       </c>
       <c r="F21" t="n">
-        <v>6698510243</v>
+        <v>6720183097</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>232181544</v>
+        <v>352873849</v>
       </c>
       <c r="I21" t="n">
-        <v>0.193471</v>
+        <v>0.196711</v>
       </c>
       <c r="J21" t="n">
-        <v>0.176496</v>
+        <v>0.178695</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01369287</v>
+        <v>0.01534281</v>
       </c>
       <c r="L21" t="n">
-        <v>7.59998</v>
+        <v>8.640750000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>34833755724.17101</v>
+        <v>34835002057.12234</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-14T15:47:20.000Z</t>
+          <t>2026-09-15T01:37:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77928</v>
+        <v>76381</v>
       </c>
       <c r="F2" t="n">
-        <v>1565278264656</v>
+        <v>1534205559019</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32481754899</v>
+        <v>32859344708</v>
       </c>
       <c r="I2" t="n">
         <v>79530</v>
       </c>
       <c r="J2" t="n">
-        <v>77010</v>
+        <v>76142</v>
       </c>
       <c r="K2" t="n">
-        <v>1192.34</v>
+        <v>-2095.025691471383</v>
       </c>
       <c r="L2" t="n">
-        <v>1.55383</v>
+        <v>-2.67474</v>
       </c>
       <c r="M2" t="n">
-        <v>20084421</v>
+        <v>20084731</v>
       </c>
       <c r="N2" t="n">
-        <v>20084481</v>
+        <v>20084753</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2512.93</v>
+        <v>2447.41</v>
       </c>
       <c r="F3" t="n">
-        <v>306704123966</v>
+        <v>298739245343</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16310732511</v>
+        <v>16736514590</v>
       </c>
       <c r="I3" t="n">
         <v>2607.56</v>
       </c>
       <c r="J3" t="n">
-        <v>2489.59</v>
+        <v>2440.21</v>
       </c>
       <c r="K3" t="n">
-        <v>33.64</v>
+        <v>-65.88360726961491</v>
       </c>
       <c r="L3" t="n">
-        <v>1.35678</v>
+        <v>-2.62877</v>
       </c>
       <c r="M3" t="n">
-        <v>122047243.4940371</v>
+        <v>122050160.8356428</v>
       </c>
       <c r="N3" t="n">
-        <v>122047243.4940371</v>
+        <v>122050160.8356428</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9998359999999999</v>
+        <v>0.999597</v>
       </c>
       <c r="F4" t="n">
-        <v>183404017289</v>
+        <v>183354416193</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58316519980</v>
+        <v>58445617168</v>
       </c>
       <c r="I4" t="n">
         <v>0.999954</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999563</v>
+        <v>0.999574</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00017816</v>
+        <v>-6.3166689663885e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01782</v>
+        <v>-0.00637</v>
       </c>
       <c r="M4" t="n">
         <v>183431197333.8773</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>719.73</v>
+        <v>719.6900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>95843853248</v>
+        <v>95838645444</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1013896622</v>
+        <v>918308118</v>
       </c>
       <c r="I5" t="n">
         <v>732.8</v>
       </c>
       <c r="J5" t="n">
-        <v>717.26</v>
+        <v>714.1900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>3.33</v>
+        <v>-2.763283885708461</v>
       </c>
       <c r="L5" t="n">
-        <v>0.46471</v>
+        <v>-0.38611</v>
       </c>
       <c r="M5" t="n">
-        <v>133160833.09</v>
+        <v>133160762.8</v>
       </c>
       <c r="N5" t="n">
-        <v>133160833.09</v>
+        <v>133160756.43</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>89328302982</v>
+        <v>88748268343</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3988480517</v>
+        <v>4262068843</v>
       </c>
       <c r="I6" t="n">
         <v>1.49</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07849299999999999</v>
+        <v>0.009628629999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>5.84888</v>
+        <v>0.71812</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999866</v>
+        <v>0.999758</v>
       </c>
       <c r="F7" t="n">
-        <v>74355972434</v>
+        <v>74113425015</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>18147169260</v>
+        <v>17704315342</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9999980000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999711</v>
+        <v>0.999376</v>
       </c>
       <c r="K7" t="n">
-        <v>3.435e-05</v>
+        <v>-3.6659991143884e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00344</v>
+        <v>-0.00376</v>
       </c>
       <c r="M7" t="n">
-        <v>74364752733.23085</v>
+        <v>74132157601.51918</v>
       </c>
       <c r="N7" t="n">
-        <v>74371126949.03763</v>
+        <v>74178971119.97899</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.33</v>
+        <v>100.3</v>
       </c>
       <c r="F8" t="n">
-        <v>60071914459</v>
+        <v>58889059739</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3391879841</v>
+        <v>3215127218</v>
       </c>
       <c r="I8" t="n">
         <v>104.76</v>
       </c>
       <c r="J8" t="n">
-        <v>99.95999999999999</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>2.95</v>
+        <v>-1.508608506609704</v>
       </c>
       <c r="L8" t="n">
-        <v>2.96946</v>
+        <v>-1.50767</v>
       </c>
       <c r="M8" t="n">
-        <v>587028564.7667522</v>
+        <v>587027977.1330632</v>
       </c>
       <c r="N8" t="n">
-        <v>634017029.7664536</v>
+        <v>634111537.8744141</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337933</v>
+        <v>0.337441</v>
       </c>
       <c r="F9" t="n">
-        <v>32085906398</v>
+        <v>32042437914</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>459700901</v>
+        <v>439649621</v>
       </c>
       <c r="I9" t="n">
         <v>0.342048</v>
@@ -998,16 +998,16 @@
         <v>0.33736</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000482044361519829</v>
+        <v>-0.003462706707822782</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.14244</v>
+        <v>-1.02556</v>
       </c>
       <c r="M9" t="n">
-        <v>94950365063.49529</v>
+        <v>94951106760.14119</v>
       </c>
       <c r="N9" t="n">
-        <v>94950919109.75899</v>
+        <v>94951113668.88469</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,30 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.028</v>
+        <v>1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>23190254032</v>
+        <v>23203168550</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>26456887</v>
+        <v>26481105</v>
       </c>
       <c r="I10" t="n">
         <v>1.048</v>
       </c>
       <c r="J10" t="n">
-        <v>1.006</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.008</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.01315564104259104</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.26266</v>
+      </c>
       <c r="M10" t="n">
         <v>22558008629.268</v>
       </c>
       <c r="N10" t="n">
-        <v>22558008629.268</v>
+        <v>22624876494.218</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1156.87</v>
+        <v>1131</v>
       </c>
       <c r="F11" t="n">
-        <v>19585748329</v>
+        <v>19189557969</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1339721891</v>
+        <v>911698850</v>
       </c>
       <c r="I11" t="n">
         <v>1222.73</v>
       </c>
       <c r="J11" t="n">
-        <v>1072.1</v>
+        <v>1121.6</v>
       </c>
       <c r="K11" t="n">
-        <v>95.72</v>
+        <v>-21.47479087819488</v>
       </c>
       <c r="L11" t="n">
-        <v>9.020440000000001</v>
+        <v>-1.9864</v>
       </c>
       <c r="M11" t="n">
-        <v>16932570.4780448</v>
+        <v>16933759.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16932909.5405448</v>
+        <v>16933876.7280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.2</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>17841668216</v>
+        <v>17472789844</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>820683271</v>
+        <v>701147955</v>
       </c>
       <c r="I12" t="n">
         <v>82.38</v>
       </c>
       <c r="J12" t="n">
-        <v>78.05</v>
+        <v>78.53</v>
       </c>
       <c r="K12" t="n">
-        <v>2.51</v>
+        <v>-2.33141737096723</v>
       </c>
       <c r="L12" t="n">
-        <v>3.22502</v>
+        <v>-2.94723</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.083762</v>
+        <v>0.08265599999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>13061146331</v>
+        <v>12888618761</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>623849039</v>
+        <v>577108242</v>
       </c>
       <c r="I13" t="n">
         <v>0.086033</v>
       </c>
       <c r="J13" t="n">
-        <v>0.083028</v>
+        <v>0.08219799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00124728</v>
+        <v>-0.001444614891101273</v>
       </c>
       <c r="L13" t="n">
-        <v>1.51158</v>
+        <v>-1.74714</v>
       </c>
       <c r="M13" t="n">
-        <v>155919246383.7052</v>
+        <v>155926276383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171630873126.579</v>
+        <v>171638413126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,274 +1279,274 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.01423283</v>
+        <v>0.999568</v>
       </c>
       <c r="F14" t="n">
-        <v>10097241960</v>
+        <v>9854320658</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>27250626</v>
+        <v>147515323</v>
       </c>
       <c r="I14" t="n">
-        <v>0.01529975</v>
+        <v>0.999922</v>
       </c>
       <c r="J14" t="n">
-        <v>0.01423111</v>
+        <v>0.999566</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000917806640155248</v>
+        <v>-8.5224967625419e-05</v>
       </c>
       <c r="L14" t="n">
-        <v>-6.05787</v>
+        <v>-0.00975</v>
       </c>
       <c r="M14" t="n">
-        <v>709219950838.6726</v>
+        <v>9858747591.389191</v>
       </c>
       <c r="N14" t="n">
-        <v>1142408526965.963</v>
+        <v>9841353158.538542</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999815</v>
+        <v>518.12</v>
       </c>
       <c r="F15" t="n">
-        <v>9841412373</v>
+        <v>9747395293</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>128014911</v>
+        <v>120378755</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999922</v>
+        <v>519.62</v>
       </c>
       <c r="J15" t="n">
-        <v>0.99953</v>
+        <v>509.39</v>
       </c>
       <c r="K15" t="n">
-        <v>4.974e-05</v>
+        <v>5.25</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00497</v>
+        <v>1.05346</v>
       </c>
       <c r="M15" t="n">
-        <v>9843079519.306154</v>
+        <v>18804964.99452248</v>
       </c>
       <c r="N15" t="n">
-        <v>9859445986.033854</v>
+        <v>18804999.79259193</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>517.35</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9729591804</v>
+        <v>9307310396</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>144582594</v>
+        <v>111976919</v>
       </c>
       <c r="I16" t="n">
-        <v>526.9</v>
+        <v>82.67</v>
       </c>
       <c r="J16" t="n">
-        <v>502.91</v>
+        <v>78.73999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>4.44</v>
+        <v>-2.1789629554996</v>
       </c>
       <c r="L16" t="n">
-        <v>0.86522</v>
+        <v>-2.71408</v>
       </c>
       <c r="M16" t="n">
-        <v>18804748.99981384</v>
+        <v>117882016</v>
       </c>
       <c r="N16" t="n">
-        <v>18804784.39672368</v>
+        <v>293532015</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>83.22</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2026-09-11T14:03:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.65000000000001</v>
+        <v>0.01303906</v>
       </c>
       <c r="F17" t="n">
-        <v>9508070993</v>
+        <v>9248658690</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>124952764</v>
+        <v>22655688</v>
       </c>
       <c r="I17" t="n">
-        <v>82.67</v>
+        <v>0.01474682</v>
       </c>
       <c r="J17" t="n">
-        <v>79.78</v>
+        <v>0.01303694</v>
       </c>
       <c r="K17" t="n">
-        <v>1.11</v>
+        <v>-0.001979134494756592</v>
       </c>
       <c r="L17" t="n">
-        <v>1.40009</v>
+        <v>-13.1993</v>
       </c>
       <c r="M17" t="n">
-        <v>117882016</v>
+        <v>709230388026.6638</v>
       </c>
       <c r="N17" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O17" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-11T14:03:10.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.57</v>
+        <v>11.33</v>
       </c>
       <c r="F18" t="n">
-        <v>8656632447</v>
+        <v>8476405612</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>378630111</v>
+        <v>354920743</v>
       </c>
       <c r="I18" t="n">
         <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>11.25</v>
+        <v>11.3</v>
       </c>
       <c r="K18" t="n">
-        <v>0.331506</v>
+        <v>-0.09682141799737742</v>
       </c>
       <c r="L18" t="n">
-        <v>2.94987</v>
+        <v>-0.88814</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.98</v>
+        <v>8.76</v>
       </c>
       <c r="F19" t="n">
-        <v>8262550568</v>
+        <v>8058856074</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>119220</v>
+        <v>310469</v>
       </c>
       <c r="I19" t="n">
-        <v>9.050000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="J19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.92</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.05097400490951998</v>
+        <v>-0.2049368320736651</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.56428</v>
+        <v>-2.28863</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.207943</v>
+        <v>0.20469</v>
       </c>
       <c r="F20" t="n">
-        <v>7803954887</v>
+        <v>7681523043</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>399285548</v>
+        <v>364530117</v>
       </c>
       <c r="I20" t="n">
         <v>0.215603</v>
       </c>
       <c r="J20" t="n">
-        <v>0.204682</v>
+        <v>0.203227</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00435576</v>
+        <v>-0.005640167035805999</v>
       </c>
       <c r="L20" t="n">
-        <v>2.1395</v>
+        <v>-2.66892</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260915T014026Z-a7c3b0</t>
+          <t>20260915T141638Z-e5fbce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192906</v>
+        <v>0.196107</v>
       </c>
       <c r="F21" t="n">
-        <v>6720183097</v>
+        <v>6829435123</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>352873849</v>
+        <v>381135110</v>
       </c>
       <c r="I21" t="n">
-        <v>0.196711</v>
+        <v>0.198377</v>
       </c>
       <c r="J21" t="n">
-        <v>0.178695</v>
+        <v>0.189175</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01534281</v>
+        <v>0.00446452</v>
       </c>
       <c r="L21" t="n">
-        <v>8.640750000000001</v>
+        <v>2.34329</v>
       </c>
       <c r="M21" t="n">
-        <v>34835002057.12234</v>
+        <v>34840249441.93312</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70248</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-15T01:37:20.000Z</t>
+          <t>2026-09-15T14:13:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76381</v>
+        <v>75575</v>
       </c>
       <c r="F2" t="n">
-        <v>1534205559019</v>
+        <v>1516961178908</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32859344708</v>
+        <v>36368251316</v>
       </c>
       <c r="I2" t="n">
-        <v>79530</v>
+        <v>77146</v>
       </c>
       <c r="J2" t="n">
-        <v>76142</v>
+        <v>75038</v>
       </c>
       <c r="K2" t="n">
-        <v>-2095.025691471383</v>
+        <v>-769.8386863019696</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.67474</v>
+        <v>-0.95843</v>
       </c>
       <c r="M2" t="n">
-        <v>20084731</v>
+        <v>20085225</v>
       </c>
       <c r="N2" t="n">
-        <v>20084753</v>
+        <v>20085256</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2447.41</v>
+        <v>2391.27</v>
       </c>
       <c r="F3" t="n">
-        <v>298739245343</v>
+        <v>291683286516</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16736514590</v>
+        <v>17993150906</v>
       </c>
       <c r="I3" t="n">
-        <v>2607.56</v>
+        <v>2445.14</v>
       </c>
       <c r="J3" t="n">
-        <v>2440.21</v>
+        <v>2361.16</v>
       </c>
       <c r="K3" t="n">
-        <v>-65.88360726961491</v>
+        <v>-56.62823994185237</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.62877</v>
+        <v>-2.27435</v>
       </c>
       <c r="M3" t="n">
-        <v>122050160.8356428</v>
+        <v>122053082.6997495</v>
       </c>
       <c r="N3" t="n">
-        <v>122050160.8356428</v>
+        <v>122053082.6997494</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999597</v>
+        <v>0.999375</v>
       </c>
       <c r="F4" t="n">
-        <v>183354416193</v>
+        <v>183321762724</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>58445617168</v>
+        <v>64865798573</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999954</v>
+        <v>0.999575</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999574</v>
+        <v>0.999246</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.3166689663885e-05</v>
+        <v>-0.000230253735472474</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00637</v>
+        <v>-0.02245</v>
       </c>
       <c r="M4" t="n">
-        <v>183431197333.8773</v>
+        <v>183442587855.5799</v>
       </c>
       <c r="N4" t="n">
-        <v>188898143247.2662</v>
+        <v>188909533773.7262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>719.6900000000001</v>
+        <v>709.98</v>
       </c>
       <c r="F5" t="n">
-        <v>95838645444</v>
+        <v>94483713743</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>918308118</v>
+        <v>962279454</v>
       </c>
       <c r="I5" t="n">
-        <v>732.8</v>
+        <v>723.8200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>714.1900000000001</v>
+        <v>704.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.763283885708461</v>
+        <v>-9.017519857691013</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.38611</v>
+        <v>-1.23775</v>
       </c>
       <c r="M5" t="n">
-        <v>133160762.8</v>
+        <v>133160634.98</v>
       </c>
       <c r="N5" t="n">
-        <v>133160756.43</v>
+        <v>133160630.47</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="F6" t="n">
-        <v>88748268343</v>
+        <v>79971731012</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4262068843</v>
+        <v>5372201415</v>
       </c>
       <c r="I6" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>0.009628629999999999</v>
+        <v>-0.135845277811097</v>
       </c>
       <c r="L6" t="n">
-        <v>0.71812</v>
+        <v>-9.61839</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999758</v>
+        <v>0.999722</v>
       </c>
       <c r="F7" t="n">
-        <v>74113425015</v>
+        <v>73642078830</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17704315342</v>
+        <v>19054647817</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9999980000000001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999376</v>
+        <v>0.999605</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.6659991143884e-05</v>
+        <v>-4.6245719710569e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00376</v>
+        <v>-0.0043</v>
       </c>
       <c r="M7" t="n">
-        <v>74132157601.51918</v>
+        <v>73664812907.1277</v>
       </c>
       <c r="N7" t="n">
-        <v>74178971119.97899</v>
+        <v>73653551003.2375</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.3</v>
+        <v>97</v>
       </c>
       <c r="F8" t="n">
-        <v>58889059739</v>
+        <v>56905505779</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3215127218</v>
+        <v>3795321892</v>
       </c>
       <c r="I8" t="n">
-        <v>104.76</v>
+        <v>100.54</v>
       </c>
       <c r="J8" t="n">
-        <v>99.90000000000001</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.508608506609704</v>
+        <v>-3.282241035908527</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.50767</v>
+        <v>-3.20872</v>
       </c>
       <c r="M8" t="n">
-        <v>587027977.1330632</v>
+        <v>587064549.8169115</v>
       </c>
       <c r="N8" t="n">
-        <v>634111537.8744141</v>
+        <v>634110600.7933525</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337441</v>
+        <v>0.334519</v>
       </c>
       <c r="F9" t="n">
-        <v>32042437914</v>
+        <v>31757981216</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>439649621</v>
+        <v>506942384</v>
       </c>
       <c r="I9" t="n">
-        <v>0.342048</v>
+        <v>0.336594</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33736</v>
+        <v>0.331863</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003462706707822782</v>
+        <v>-0.002960896167564342</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.02556</v>
+        <v>-0.8641</v>
       </c>
       <c r="M9" t="n">
-        <v>94951106760.14119</v>
+        <v>94952171628.92049</v>
       </c>
       <c r="N9" t="n">
-        <v>94951113668.88469</v>
+        <v>94952166580.72699</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.029</v>
+        <v>1.003</v>
       </c>
       <c r="F10" t="n">
-        <v>23203168550</v>
+        <v>22696694484</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>26481105</v>
+        <v>786631020</v>
       </c>
       <c r="I10" t="n">
-        <v>1.048</v>
+        <v>1.047</v>
       </c>
       <c r="J10" t="n">
-        <v>1.008</v>
+        <v>1.003</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01315564104259104</v>
+        <v>-0.02554960894943803</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.26266</v>
+        <v>-2.48407</v>
       </c>
       <c r="M10" t="n">
-        <v>22558008629.268</v>
+        <v>22624876494.218</v>
       </c>
       <c r="N10" t="n">
-        <v>22624876494.218</v>
+        <v>22598468218.548</v>
       </c>
       <c r="O10" t="n">
         <v>1.061</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1131</v>
+        <v>1247.89</v>
       </c>
       <c r="F11" t="n">
-        <v>19189557969</v>
+        <v>21100710958</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>911698850</v>
+        <v>1521322408</v>
       </c>
       <c r="I11" t="n">
-        <v>1222.73</v>
+        <v>1268.97</v>
       </c>
       <c r="J11" t="n">
-        <v>1121.6</v>
+        <v>1088.87</v>
       </c>
       <c r="K11" t="n">
-        <v>-21.47479087819488</v>
+        <v>114.82</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.9864</v>
+        <v>10.09064</v>
       </c>
       <c r="M11" t="n">
         <v>16933759.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16933876.7280448</v>
+        <v>16935675.1655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.54000000000001</v>
+        <v>78.44</v>
       </c>
       <c r="F12" t="n">
-        <v>17472789844</v>
+        <v>17440527363</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>701147955</v>
+        <v>931340877</v>
       </c>
       <c r="I12" t="n">
-        <v>82.38</v>
+        <v>79.58</v>
       </c>
       <c r="J12" t="n">
-        <v>78.53</v>
+        <v>75.27</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.33141737096723</v>
+        <v>-0.3175158379041818</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.94723</v>
+        <v>-0.40749</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08265599999999999</v>
+        <v>0.07914300000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12888618761</v>
+        <v>12328095249</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>577108242</v>
+        <v>845852778</v>
       </c>
       <c r="I13" t="n">
-        <v>0.086033</v>
+        <v>0.082368</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08219799999999999</v>
+        <v>0.078671</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001444614891101273</v>
+        <v>-0.003420279153313957</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.74714</v>
+        <v>-4.14377</v>
       </c>
       <c r="M13" t="n">
-        <v>155926276383.7052</v>
+        <v>155939426383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171638413126.579</v>
+        <v>171651883126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999568</v>
+        <v>0.999362</v>
       </c>
       <c r="F14" t="n">
-        <v>9854320658</v>
+        <v>9577947441</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>147515323</v>
+        <v>218091969</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999922</v>
+        <v>0.999655</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999566</v>
+        <v>0.999215</v>
       </c>
       <c r="K14" t="n">
-        <v>-8.5224967625419e-05</v>
+        <v>-0.000261162282703786</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.00975</v>
+        <v>-0.02601</v>
       </c>
       <c r="M14" t="n">
-        <v>9858747591.389191</v>
+        <v>9583931558.104593</v>
       </c>
       <c r="N14" t="n">
-        <v>9841353158.538542</v>
+        <v>9577504586.820999</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,339 +1344,339 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>518.12</v>
+        <v>0.01321058</v>
       </c>
       <c r="F15" t="n">
-        <v>9747395293</v>
+        <v>9373518968</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120378755</v>
+        <v>26286505</v>
       </c>
       <c r="I15" t="n">
-        <v>519.62</v>
+        <v>0.01451168</v>
       </c>
       <c r="J15" t="n">
-        <v>509.39</v>
+        <v>0.01254013</v>
       </c>
       <c r="K15" t="n">
-        <v>5.25</v>
+        <v>0.00014604</v>
       </c>
       <c r="L15" t="n">
-        <v>1.05346</v>
+        <v>1.13872</v>
       </c>
       <c r="M15" t="n">
-        <v>18804964.99452248</v>
+        <v>709233397159.627</v>
       </c>
       <c r="N15" t="n">
-        <v>18804999.79259193</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>0.01946402</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>78.95999999999999</v>
+        <v>494.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9307310396</v>
+        <v>9317262109</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>111976919</v>
+        <v>110227395</v>
       </c>
       <c r="I16" t="n">
-        <v>82.67</v>
+        <v>517.62</v>
       </c>
       <c r="J16" t="n">
-        <v>78.73999999999999</v>
+        <v>494.65</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.1789629554996</v>
+        <v>-21.99978176566327</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.71408</v>
+        <v>-4.26237</v>
       </c>
       <c r="M16" t="n">
-        <v>117882016</v>
+        <v>18805370.55291757</v>
       </c>
       <c r="N16" t="n">
-        <v>293532015</v>
+        <v>18805423.95177342</v>
       </c>
       <c r="O16" t="n">
-        <v>83.22</v>
+        <v>797.73</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-11T14:03:10.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01303906</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9248658690</v>
+        <v>9153123057</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>22655688</v>
+        <v>163351294</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01474682</v>
+        <v>79.44</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01303694</v>
+        <v>77.27</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.001979134494756592</v>
+        <v>-1.220355107256495</v>
       </c>
       <c r="L17" t="n">
-        <v>-13.1993</v>
+        <v>-1.53926</v>
       </c>
       <c r="M17" t="n">
-        <v>709230388026.6638</v>
+        <v>117882016</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>293532015</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>83.22</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2026-09-11T14:03:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.33</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>8476405612</v>
+        <v>8163877232</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>354920743</v>
+        <v>319807</v>
       </c>
       <c r="I18" t="n">
-        <v>11.95</v>
+        <v>8.91</v>
       </c>
       <c r="J18" t="n">
-        <v>11.3</v>
+        <v>8.73</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.09682141799737742</v>
+        <v>0.11644</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.88814</v>
+        <v>1.32755</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.76</v>
+        <v>10.69</v>
       </c>
       <c r="F19" t="n">
-        <v>8058856074</v>
+        <v>7986538864</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>310469</v>
+        <v>450558976</v>
       </c>
       <c r="I19" t="n">
-        <v>9.02</v>
+        <v>11.38</v>
       </c>
       <c r="J19" t="n">
-        <v>8.92</v>
+        <v>10.68</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.2049368320736651</v>
+        <v>-0.6460806364119609</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.28863</v>
+        <v>-5.68476</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.20469</v>
+        <v>0.191834</v>
       </c>
       <c r="F20" t="n">
-        <v>7681523043</v>
+        <v>7189370215</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>364530117</v>
+        <v>466275840</v>
       </c>
       <c r="I20" t="n">
-        <v>0.215603</v>
+        <v>0.204209</v>
       </c>
       <c r="J20" t="n">
-        <v>0.203227</v>
+        <v>0.191485</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.005640167035805999</v>
+        <v>-0.01285599910683713</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.66892</v>
+        <v>-6.26884</v>
       </c>
       <c r="M20" t="n">
         <v>37516725700.17653</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260915T141638Z-e5fbce</t>
+          <t>20260916T140843Z-21c472</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.196107</v>
+        <v>0.174197</v>
       </c>
       <c r="F21" t="n">
-        <v>6829435123</v>
+        <v>6061365830</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>381135110</v>
+        <v>350153192</v>
       </c>
       <c r="I21" t="n">
-        <v>0.198377</v>
+        <v>0.193982</v>
       </c>
       <c r="J21" t="n">
-        <v>0.189175</v>
+        <v>0.173614</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00446452</v>
+        <v>-0.02132487491538929</v>
       </c>
       <c r="L21" t="n">
-        <v>2.34329</v>
+        <v>-10.8698</v>
       </c>
       <c r="M21" t="n">
-        <v>34840249441.93312</v>
+        <v>34842263125.93008</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70248</v>
+        <v>50001786839.70148</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-15T14:13:20.000Z</t>
+          <t>2026-09-16T14:05:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>75575</v>
+        <v>76644</v>
       </c>
       <c r="F2" t="n">
-        <v>1516961178908</v>
+        <v>1539320607676</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>36368251316</v>
+        <v>30133625120</v>
       </c>
       <c r="I2" t="n">
-        <v>77146</v>
+        <v>77024</v>
       </c>
       <c r="J2" t="n">
-        <v>75038</v>
+        <v>75161</v>
       </c>
       <c r="K2" t="n">
-        <v>-769.8386863019696</v>
+        <v>1202.29</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.95843</v>
+        <v>1.59367</v>
       </c>
       <c r="M2" t="n">
-        <v>20085225</v>
+        <v>20085603</v>
       </c>
       <c r="N2" t="n">
-        <v>20085256</v>
+        <v>20085665</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2391.27</v>
+        <v>2463.87</v>
       </c>
       <c r="F3" t="n">
-        <v>291683286516</v>
+        <v>300760183438</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17993150906</v>
+        <v>15874627280</v>
       </c>
       <c r="I3" t="n">
-        <v>2445.14</v>
+        <v>2473.53</v>
       </c>
       <c r="J3" t="n">
-        <v>2361.16</v>
+        <v>2371.36</v>
       </c>
       <c r="K3" t="n">
-        <v>-56.62823994185237</v>
+        <v>79.62</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.27435</v>
+        <v>3.33959</v>
       </c>
       <c r="M3" t="n">
-        <v>122053082.6997495</v>
+        <v>122056009.605603</v>
       </c>
       <c r="N3" t="n">
-        <v>122053082.6997494</v>
+        <v>122056009.605603</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999375</v>
+        <v>0.99915</v>
       </c>
       <c r="F4" t="n">
-        <v>183321762724</v>
+        <v>183284327911</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>64865798573</v>
+        <v>61718644343</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999575</v>
+        <v>0.999539</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999246</v>
+        <v>0.999112</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000230253735472474</v>
+        <v>-0.000238099616719611</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02245</v>
+        <v>-0.02382</v>
       </c>
       <c r="M4" t="n">
         <v>183442587855.5799</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>709.98</v>
+        <v>726.74</v>
       </c>
       <c r="F5" t="n">
-        <v>94483713743</v>
+        <v>96755073209</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>962279454</v>
+        <v>1032713365</v>
       </c>
       <c r="I5" t="n">
-        <v>723.8200000000001</v>
+        <v>731.53</v>
       </c>
       <c r="J5" t="n">
-        <v>704.22</v>
+        <v>708.73</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.017519857691013</v>
+        <v>17.6</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.23775</v>
+        <v>2.4826</v>
       </c>
       <c r="M5" t="n">
-        <v>133160634.98</v>
+        <v>133160558.5</v>
       </c>
       <c r="N5" t="n">
-        <v>133160630.47</v>
+        <v>133160532.83</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>79971731012</v>
+        <v>82009347142</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>5372201415</v>
+        <v>3625730823</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.135845277811097</v>
+        <v>0.03567597</v>
       </c>
       <c r="L6" t="n">
-        <v>-9.61839</v>
+        <v>2.81145</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999722</v>
+        <v>0.999571</v>
       </c>
       <c r="F7" t="n">
-        <v>73642078830</v>
+        <v>73555159854</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19054647817</v>
+        <v>19170526434</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999802</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999605</v>
+        <v>0.999055</v>
       </c>
       <c r="K7" t="n">
-        <v>-4.6245719710569e-05</v>
+        <v>-0.000145914927842328</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0043</v>
+        <v>-0.0146</v>
       </c>
       <c r="M7" t="n">
-        <v>73664812907.1277</v>
+        <v>73587375656.46214</v>
       </c>
       <c r="N7" t="n">
-        <v>73653551003.2375</v>
+        <v>73590256479.63303</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>97</v>
+        <v>100.77</v>
       </c>
       <c r="F8" t="n">
-        <v>56905505779</v>
+        <v>59152011113</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3795321892</v>
+        <v>3739451532</v>
       </c>
       <c r="I8" t="n">
-        <v>100.54</v>
+        <v>101.24</v>
       </c>
       <c r="J8" t="n">
-        <v>96.06999999999999</v>
+        <v>96.11</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.282241035908527</v>
+        <v>4.05</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.20872</v>
+        <v>4.18322</v>
       </c>
       <c r="M8" t="n">
-        <v>587064549.8169115</v>
+        <v>587212147.1182363</v>
       </c>
       <c r="N8" t="n">
-        <v>634110600.7933525</v>
+        <v>634204567.4934224</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334519</v>
+        <v>0.334283</v>
       </c>
       <c r="F9" t="n">
-        <v>31757981216</v>
+        <v>31742370925</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>506942384</v>
+        <v>342292091</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336594</v>
+        <v>0.336124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.331863</v>
+        <v>0.334217</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002960896167564342</v>
+        <v>-0.000219834965064225</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8641</v>
+        <v>-0.06572</v>
       </c>
       <c r="M9" t="n">
-        <v>94952171628.92049</v>
+        <v>94953504416.74518</v>
       </c>
       <c r="N9" t="n">
-        <v>94952166580.72699</v>
+        <v>94953498011.30618</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,144 +1019,144 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>figure-heloc</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>figr_heloc</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Figure Heloc</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.003</v>
+        <v>1405.63</v>
       </c>
       <c r="F10" t="n">
-        <v>22696694484</v>
+        <v>23797511040</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>786631020</v>
+        <v>2809381550</v>
       </c>
       <c r="I10" t="n">
-        <v>1.047</v>
+        <v>1388.42</v>
       </c>
       <c r="J10" t="n">
-        <v>1.003</v>
+        <v>1235.16</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02554960894943803</v>
+        <v>157.34</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.48407</v>
+        <v>12.60406</v>
       </c>
       <c r="M10" t="n">
-        <v>22624876494.218</v>
+        <v>16937203.2905448</v>
       </c>
       <c r="N10" t="n">
-        <v>22598468218.548</v>
+        <v>16937454.8530448</v>
       </c>
       <c r="O10" t="n">
-        <v>1.061</v>
+        <v>3191.93</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-08-03T14:19:20.000Z</t>
+          <t>2016-10-28T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>figure-heloc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>figr_heloc</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Figure Heloc</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1247.89</v>
+        <v>1.03</v>
       </c>
       <c r="F11" t="n">
-        <v>21100710958</v>
+        <v>23270039358</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1521322408</v>
+        <v>98622645</v>
       </c>
       <c r="I11" t="n">
-        <v>1268.97</v>
+        <v>1.03</v>
       </c>
       <c r="J11" t="n">
-        <v>1088.87</v>
+        <v>1.001</v>
       </c>
       <c r="K11" t="n">
-        <v>114.82</v>
+        <v>0.02657361</v>
       </c>
       <c r="L11" t="n">
-        <v>10.09064</v>
+        <v>2.64907</v>
       </c>
       <c r="M11" t="n">
-        <v>16933759.5405448</v>
+        <v>22598468218.548</v>
       </c>
       <c r="N11" t="n">
-        <v>16935675.1655448</v>
+        <v>22598468218.548</v>
       </c>
       <c r="O11" t="n">
-        <v>3191.93</v>
+        <v>1.061</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2016-10-28T16:00:00.000Z</t>
+          <t>2026-08-03T14:19:20.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.44</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17440527363</v>
+        <v>18231266029</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>931340877</v>
+        <v>1146341296</v>
       </c>
       <c r="I12" t="n">
-        <v>79.58</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>75.27</v>
+        <v>77.19</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3175158379041818</v>
+        <v>3.78</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.40749</v>
+        <v>4.83726</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07914300000000001</v>
+        <v>0.08157399999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12328095249</v>
+        <v>12717767225</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>845852778</v>
+        <v>729261588</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082368</v>
+        <v>0.08165500000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.078671</v>
+        <v>0.07836799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003420279153313957</v>
+        <v>0.00275889</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.14377</v>
+        <v>3.50047</v>
       </c>
       <c r="M13" t="n">
-        <v>155939426383.7052</v>
+        <v>155951756383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171651883126.579</v>
+        <v>171665603126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999362</v>
+        <v>0.999765</v>
       </c>
       <c r="F14" t="n">
-        <v>9577947441</v>
+        <v>9555093003</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>218091969</v>
+        <v>234322913</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999655</v>
+        <v>0.999879</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999215</v>
+        <v>0.999135</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000261162282703786</v>
+        <v>0.00034214</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.02601</v>
+        <v>0.03423</v>
       </c>
       <c r="M14" t="n">
-        <v>9583931558.104593</v>
+        <v>9556951530.004086</v>
       </c>
       <c r="N14" t="n">
-        <v>9577504586.820999</v>
+        <v>9558143909.30253</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,339 +1344,339 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.01321058</v>
+        <v>505.06</v>
       </c>
       <c r="F15" t="n">
-        <v>9373518968</v>
+        <v>9497377500</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>26286505</v>
+        <v>117728327</v>
       </c>
       <c r="I15" t="n">
-        <v>0.01451168</v>
+        <v>504.23</v>
       </c>
       <c r="J15" t="n">
-        <v>0.01254013</v>
+        <v>485.12</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00014604</v>
+        <v>9.43</v>
       </c>
       <c r="L15" t="n">
-        <v>1.13872</v>
+        <v>1.90225</v>
       </c>
       <c r="M15" t="n">
-        <v>709233397159.627</v>
+        <v>18805792.94955427</v>
       </c>
       <c r="N15" t="n">
-        <v>1142408526965.963</v>
+        <v>18805870.34941343</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01946402</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>494.91</v>
+        <v>79.05</v>
       </c>
       <c r="F16" t="n">
-        <v>9317262109</v>
+        <v>9318236388</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>110227395</v>
+        <v>156128201</v>
       </c>
       <c r="I16" t="n">
-        <v>517.62</v>
+        <v>79.44</v>
       </c>
       <c r="J16" t="n">
-        <v>494.65</v>
+        <v>77.11</v>
       </c>
       <c r="K16" t="n">
-        <v>-21.99978176566327</v>
+        <v>1.51</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.26237</v>
+        <v>1.94453</v>
       </c>
       <c r="M16" t="n">
-        <v>18805370.55291757</v>
+        <v>117882016</v>
       </c>
       <c r="N16" t="n">
-        <v>18805423.95177342</v>
+        <v>293532015</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>83.22</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2026-09-11T14:03:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>77.68000000000001</v>
+        <v>0.01306588</v>
       </c>
       <c r="F17" t="n">
-        <v>9153123057</v>
+        <v>9257577125</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>163351294</v>
+        <v>21935510</v>
       </c>
       <c r="I17" t="n">
-        <v>79.44</v>
+        <v>0.01345016</v>
       </c>
       <c r="J17" t="n">
-        <v>77.27</v>
+        <v>0.01191321</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.220355107256495</v>
+        <v>-0.00015046852519901</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.53926</v>
+        <v>-1.1385</v>
       </c>
       <c r="M17" t="n">
-        <v>117882016</v>
+        <v>709233558707.1311</v>
       </c>
       <c r="N17" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O17" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-11T14:03:10.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.880000000000001</v>
+        <v>11.31</v>
       </c>
       <c r="F18" t="n">
-        <v>8163877232</v>
+        <v>8462869436</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>319807</v>
+        <v>441283863</v>
       </c>
       <c r="I18" t="n">
-        <v>8.91</v>
+        <v>11.32</v>
       </c>
       <c r="J18" t="n">
-        <v>8.73</v>
+        <v>10.62</v>
       </c>
       <c r="K18" t="n">
-        <v>0.11644</v>
+        <v>0.661099</v>
       </c>
       <c r="L18" t="n">
-        <v>1.32755</v>
+        <v>6.20719</v>
       </c>
       <c r="M18" t="n">
-        <v>919857851.9</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>10.69</v>
+        <v>8.92</v>
       </c>
       <c r="F19" t="n">
-        <v>7986538864</v>
+        <v>8202960071</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>450558976</v>
+        <v>156127</v>
       </c>
       <c r="I19" t="n">
-        <v>11.38</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>10.68</v>
+        <v>8.83</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6460806364119609</v>
+        <v>0.04280543</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.68476</v>
+        <v>0.48232</v>
       </c>
       <c r="M19" t="n">
-        <v>748099970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.191834</v>
+        <v>0.201196</v>
       </c>
       <c r="F20" t="n">
-        <v>7189370215</v>
+        <v>7544303914</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>466275840</v>
+        <v>438569875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.204209</v>
+        <v>0.201745</v>
       </c>
       <c r="J20" t="n">
-        <v>0.191485</v>
+        <v>0.190464</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01285599910683713</v>
+        <v>0.00979934</v>
       </c>
       <c r="L20" t="n">
-        <v>-6.26884</v>
+        <v>5.1199</v>
       </c>
       <c r="M20" t="n">
-        <v>37516725700.17653</v>
+        <v>37522923322.16203</v>
       </c>
       <c r="N20" t="n">
         <v>45000000000</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260916T140843Z-21c472</t>
+          <t>20260917T141415Z-294653</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.174197</v>
+        <v>0.184749</v>
       </c>
       <c r="F21" t="n">
-        <v>6061365830</v>
+        <v>6432935996</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>350153192</v>
+        <v>253193320</v>
       </c>
       <c r="I21" t="n">
-        <v>0.193982</v>
+        <v>0.186542</v>
       </c>
       <c r="J21" t="n">
-        <v>0.173614</v>
+        <v>0.172569</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.02132487491538929</v>
+        <v>0.01109385</v>
       </c>
       <c r="L21" t="n">
-        <v>-10.8698</v>
+        <v>6.38843</v>
       </c>
       <c r="M21" t="n">
-        <v>34842263125.93008</v>
+        <v>34845006961.13458</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-16T14:05:10.000Z</t>
+          <t>2026-09-17T14:11:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>76644</v>
+        <v>78107</v>
       </c>
       <c r="F2" t="n">
-        <v>1539320607676</v>
+        <v>1568598802085</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>30133625120</v>
+        <v>29746226629</v>
       </c>
       <c r="I2" t="n">
-        <v>77024</v>
+        <v>78372</v>
       </c>
       <c r="J2" t="n">
-        <v>75161</v>
+        <v>76205</v>
       </c>
       <c r="K2" t="n">
-        <v>1202.29</v>
+        <v>1623.81</v>
       </c>
       <c r="L2" t="n">
-        <v>1.59367</v>
+        <v>2.12309</v>
       </c>
       <c r="M2" t="n">
-        <v>20085603</v>
+        <v>20086075</v>
       </c>
       <c r="N2" t="n">
-        <v>20085665</v>
+        <v>20086075</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2463.87</v>
+        <v>2504.2</v>
       </c>
       <c r="F3" t="n">
-        <v>300760183438</v>
+        <v>305590691965</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15874627280</v>
+        <v>15043114849</v>
       </c>
       <c r="I3" t="n">
-        <v>2473.53</v>
+        <v>2518</v>
       </c>
       <c r="J3" t="n">
-        <v>2371.36</v>
+        <v>2435.96</v>
       </c>
       <c r="K3" t="n">
-        <v>79.62</v>
+        <v>52.04</v>
       </c>
       <c r="L3" t="n">
-        <v>3.33959</v>
+        <v>2.12207</v>
       </c>
       <c r="M3" t="n">
-        <v>122056009.605603</v>
+        <v>122058930.7915531</v>
       </c>
       <c r="N3" t="n">
-        <v>122056009.605603</v>
+        <v>122058930.7915531</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99915</v>
+        <v>0.9991640000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>183284327911</v>
+        <v>183289006638</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>61718644343</v>
+        <v>61371983187</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999539</v>
+        <v>0.9993610000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999112</v>
+        <v>0.999089</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000238099616719611</v>
+        <v>-2.8548222514524e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02382</v>
+        <v>-0.00286</v>
       </c>
       <c r="M4" t="n">
         <v>183442587855.5799</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>726.74</v>
+        <v>750.21</v>
       </c>
       <c r="F5" t="n">
-        <v>96755073209</v>
+        <v>99874497337</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1032713365</v>
+        <v>1327798862</v>
       </c>
       <c r="I5" t="n">
-        <v>731.53</v>
+        <v>758.16</v>
       </c>
       <c r="J5" t="n">
-        <v>708.73</v>
+        <v>724.1900000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>17.6</v>
+        <v>23.05</v>
       </c>
       <c r="L5" t="n">
-        <v>2.4826</v>
+        <v>3.1697</v>
       </c>
       <c r="M5" t="n">
-        <v>133160558.5</v>
+        <v>133160438.17</v>
       </c>
       <c r="N5" t="n">
-        <v>133160532.83</v>
+        <v>133160429.28</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="F6" t="n">
-        <v>82009347142</v>
+        <v>83325852293</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3625730823</v>
+        <v>2693394422</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03567597</v>
+        <v>0.02428641</v>
       </c>
       <c r="L6" t="n">
-        <v>2.81145</v>
+        <v>1.8667</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999571</v>
+        <v>0.999514</v>
       </c>
       <c r="F7" t="n">
-        <v>73555159854</v>
+        <v>73773705191</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19170526434</v>
+        <v>16804878019</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999802</v>
+        <v>0.999703</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999055</v>
+        <v>0.999464</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000145914927842328</v>
+        <v>-7.1772637548539e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0146</v>
+        <v>-0.00718</v>
       </c>
       <c r="M7" t="n">
-        <v>73587375656.46214</v>
+        <v>73809548950.31921</v>
       </c>
       <c r="N7" t="n">
-        <v>73590256479.63303</v>
+        <v>73809465033.80299</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.77</v>
+        <v>105.87</v>
       </c>
       <c r="F8" t="n">
-        <v>59152011113</v>
+        <v>62173407445</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3739451532</v>
+        <v>4336330927</v>
       </c>
       <c r="I8" t="n">
-        <v>101.24</v>
+        <v>106.53</v>
       </c>
       <c r="J8" t="n">
-        <v>96.11</v>
+        <v>100.11</v>
       </c>
       <c r="K8" t="n">
-        <v>4.05</v>
+        <v>5.5</v>
       </c>
       <c r="L8" t="n">
-        <v>4.18322</v>
+        <v>5.47797</v>
       </c>
       <c r="M8" t="n">
-        <v>587212147.1182363</v>
+        <v>587297218.9841995</v>
       </c>
       <c r="N8" t="n">
-        <v>634204567.4934224</v>
+        <v>634298467.6716927</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334283</v>
+        <v>0.338083</v>
       </c>
       <c r="F9" t="n">
-        <v>31742370925</v>
+        <v>32101739690</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>342292091</v>
+        <v>387644195</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336124</v>
+        <v>0.337939</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334217</v>
+        <v>0.333425</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000219834965064225</v>
+        <v>0.00335145</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.06572</v>
+        <v>1.00124</v>
       </c>
       <c r="M9" t="n">
-        <v>94953504416.74518</v>
+        <v>94954902669.86409</v>
       </c>
       <c r="N9" t="n">
-        <v>94953498011.30618</v>
+        <v>94954901666.17758</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1405.63</v>
+        <v>1467.74</v>
       </c>
       <c r="F10" t="n">
-        <v>23797511040</v>
+        <v>24865345606</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2809381550</v>
+        <v>2178796951</v>
       </c>
       <c r="I10" t="n">
-        <v>1388.42</v>
+        <v>1526.56</v>
       </c>
       <c r="J10" t="n">
-        <v>1235.16</v>
+        <v>1370.29</v>
       </c>
       <c r="K10" t="n">
-        <v>157.34</v>
+        <v>105.04</v>
       </c>
       <c r="L10" t="n">
-        <v>12.60406</v>
+        <v>7.70855</v>
       </c>
       <c r="M10" t="n">
-        <v>16937203.2905448</v>
+        <v>16938925.1655448</v>
       </c>
       <c r="N10" t="n">
-        <v>16937454.8530448</v>
+        <v>16939175.1655448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.03</v>
+        <v>1.028</v>
       </c>
       <c r="F11" t="n">
-        <v>23270039358</v>
+        <v>23301466219</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>98622645</v>
+        <v>209412055</v>
       </c>
       <c r="I11" t="n">
-        <v>1.03</v>
+        <v>1.035</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001</v>
+        <v>1.004</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02657361</v>
+        <v>-0.001618662688462669</v>
       </c>
       <c r="L11" t="n">
-        <v>2.64907</v>
+        <v>-0.1572</v>
       </c>
       <c r="M11" t="n">
-        <v>22598468218.548</v>
+        <v>22665434312.548</v>
       </c>
       <c r="N11" t="n">
-        <v>22598468218.548</v>
+        <v>22665434312.548</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.98999999999999</v>
+        <v>91.27</v>
       </c>
       <c r="F12" t="n">
-        <v>18231266029</v>
+        <v>20297028307</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1146341296</v>
+        <v>1618650214</v>
       </c>
       <c r="I12" t="n">
-        <v>82.70999999999999</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>77.19</v>
+        <v>81.5</v>
       </c>
       <c r="K12" t="n">
-        <v>3.78</v>
+        <v>9.19</v>
       </c>
       <c r="L12" t="n">
-        <v>4.83726</v>
+        <v>11.19346</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1205,23 +1205,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>89.59999999999999</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-06T12:28:40.000Z</t>
+          <t>2026-09-18T12:39:40.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08157399999999999</v>
+        <v>0.085364</v>
       </c>
       <c r="F13" t="n">
-        <v>12717767225</v>
+        <v>13314001045</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>729261588</v>
+        <v>877130041</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08165500000000001</v>
+        <v>0.08678</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07836799999999999</v>
+        <v>0.081105</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00275889</v>
+        <v>0.00417871</v>
       </c>
       <c r="L13" t="n">
-        <v>3.50047</v>
+        <v>5.14712</v>
       </c>
       <c r="M13" t="n">
-        <v>155951756383.7052</v>
+        <v>155966856383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171665603126.5791</v>
+        <v>155966926383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,144 +1279,144 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999765</v>
+        <v>531.61</v>
       </c>
       <c r="F14" t="n">
-        <v>9555093003</v>
+        <v>9993028627</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>234322913</v>
+        <v>138577997</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999879</v>
+        <v>544.41</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999135</v>
+        <v>502.16</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00034214</v>
+        <v>29.06</v>
       </c>
       <c r="L14" t="n">
-        <v>0.03423</v>
+        <v>5.78332</v>
       </c>
       <c r="M14" t="n">
-        <v>9556951530.004086</v>
+        <v>18806245.33931784</v>
       </c>
       <c r="N14" t="n">
-        <v>9558143909.30253</v>
+        <v>18806257.93928528</v>
       </c>
       <c r="O14" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>505.06</v>
+        <v>0.999767</v>
       </c>
       <c r="F15" t="n">
-        <v>9497377500</v>
+        <v>9562217003</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>117728327</v>
+        <v>141420739</v>
       </c>
       <c r="I15" t="n">
-        <v>504.23</v>
+        <v>0.999965</v>
       </c>
       <c r="J15" t="n">
-        <v>485.12</v>
+        <v>0.999596</v>
       </c>
       <c r="K15" t="n">
-        <v>9.43</v>
+        <v>9.39e-06</v>
       </c>
       <c r="L15" t="n">
-        <v>1.90225</v>
+        <v>0.00094</v>
       </c>
       <c r="M15" t="n">
-        <v>18805792.94955427</v>
+        <v>9564389019.369761</v>
       </c>
       <c r="N15" t="n">
-        <v>18805870.34941343</v>
+        <v>9565459355.707329</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.05</v>
+        <v>80.44</v>
       </c>
       <c r="F16" t="n">
-        <v>9318236388</v>
+        <v>9482447599</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>156128201</v>
+        <v>112012858</v>
       </c>
       <c r="I16" t="n">
-        <v>79.44</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>77.11</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="L16" t="n">
-        <v>1.94453</v>
+        <v>1.97292</v>
       </c>
       <c r="M16" t="n">
         <v>117882016</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,31 +1500,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01306588</v>
+        <v>0.01278862</v>
       </c>
       <c r="F17" t="n">
-        <v>9257577125</v>
+        <v>9073126084</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>21935510</v>
+        <v>27820992</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01345016</v>
+        <v>0.01310816</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01191321</v>
+        <v>0.01260467</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.00015046852519901</v>
+        <v>-0.000263625237508211</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.1385</v>
+        <v>-2.01977</v>
       </c>
       <c r="M17" t="n">
-        <v>709233558707.1311</v>
+        <v>709234074452.8706</v>
       </c>
       <c r="N17" t="n">
         <v>1142408526965.963</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.31</v>
+        <v>11.82</v>
       </c>
       <c r="F18" t="n">
-        <v>8462869436</v>
+        <v>8843197796</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>441283863</v>
+        <v>465095252</v>
       </c>
       <c r="I18" t="n">
-        <v>11.32</v>
+        <v>11.95</v>
       </c>
       <c r="J18" t="n">
-        <v>10.62</v>
+        <v>11.22</v>
       </c>
       <c r="K18" t="n">
-        <v>0.661099</v>
+        <v>0.575928</v>
       </c>
       <c r="L18" t="n">
-        <v>6.20719</v>
+        <v>5.12126</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.92</v>
+        <v>8.9</v>
       </c>
       <c r="F19" t="n">
-        <v>8202960071</v>
+        <v>8184667580</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>156127</v>
+        <v>76720</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="J19" t="n">
-        <v>8.83</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04280543</v>
+        <v>-0.01999754405595056</v>
       </c>
       <c r="L19" t="n">
-        <v>0.48232</v>
+        <v>-0.22424</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.201196</v>
+        <v>0.21587</v>
       </c>
       <c r="F20" t="n">
-        <v>7544303914</v>
+        <v>8101095616</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>438569875</v>
+        <v>552742767</v>
       </c>
       <c r="I20" t="n">
-        <v>0.201745</v>
+        <v>0.216996</v>
       </c>
       <c r="J20" t="n">
-        <v>0.190464</v>
+        <v>0.199529</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00979934</v>
+        <v>0.01551854</v>
       </c>
       <c r="L20" t="n">
-        <v>5.1199</v>
+        <v>7.74566</v>
       </c>
       <c r="M20" t="n">
         <v>37522923322.16203</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260917T141415Z-294653</t>
+          <t>20260918T133226Z-aef8f8</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.184749</v>
+        <v>0.186694</v>
       </c>
       <c r="F21" t="n">
-        <v>6432935996</v>
+        <v>6499674331</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>253193320</v>
+        <v>190708288</v>
       </c>
       <c r="I21" t="n">
-        <v>0.186542</v>
+        <v>0.18919</v>
       </c>
       <c r="J21" t="n">
-        <v>0.172569</v>
+        <v>0.182408</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01109385</v>
+        <v>0.00268673</v>
       </c>
       <c r="L21" t="n">
-        <v>6.38843</v>
+        <v>1.46012</v>
       </c>
       <c r="M21" t="n">
-        <v>34845006961.13458</v>
+        <v>34845172352.88166</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-17T14:11:10.000Z</t>
+          <t>2026-09-18T13:29:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>78107</v>
+        <v>81303</v>
       </c>
       <c r="F2" t="n">
-        <v>1568598802085</v>
+        <v>1633087433036</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29746226629</v>
+        <v>39046726177</v>
       </c>
       <c r="I2" t="n">
-        <v>78372</v>
+        <v>81675</v>
       </c>
       <c r="J2" t="n">
-        <v>76205</v>
+        <v>80014</v>
       </c>
       <c r="K2" t="n">
-        <v>1623.81</v>
+        <v>3308.3</v>
       </c>
       <c r="L2" t="n">
-        <v>2.12309</v>
+        <v>4.27011</v>
       </c>
       <c r="M2" t="n">
-        <v>20086075</v>
+        <v>20086521</v>
       </c>
       <c r="N2" t="n">
-        <v>20086075</v>
+        <v>20086553</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2504.2</v>
+        <v>2640.53</v>
       </c>
       <c r="F3" t="n">
-        <v>305590691965</v>
+        <v>322307862116</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15043114849</v>
+        <v>20959346820</v>
       </c>
       <c r="I3" t="n">
-        <v>2518</v>
+        <v>2655.71</v>
       </c>
       <c r="J3" t="n">
-        <v>2435.96</v>
+        <v>2552.3</v>
       </c>
       <c r="K3" t="n">
-        <v>52.04</v>
+        <v>140.11</v>
       </c>
       <c r="L3" t="n">
-        <v>2.12207</v>
+        <v>5.64929</v>
       </c>
       <c r="M3" t="n">
-        <v>122058930.7915531</v>
+        <v>122061836.5153193</v>
       </c>
       <c r="N3" t="n">
-        <v>122058930.7915531</v>
+        <v>122061836.5153193</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9991640000000001</v>
+        <v>0.999655</v>
       </c>
       <c r="F4" t="n">
-        <v>183289006638</v>
+        <v>183321470793</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>61371983187</v>
+        <v>73806318083</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9993610000000001</v>
+        <v>0.999786</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999089</v>
+        <v>0.999212</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.8548222514524e-05</v>
+        <v>0.00048018</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00286</v>
+        <v>0.04844</v>
       </c>
       <c r="M4" t="n">
-        <v>183442587855.5799</v>
+        <v>183384649794.4283</v>
       </c>
       <c r="N4" t="n">
-        <v>188909533773.7262</v>
+        <v>188851595759.0362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.21</v>
+        <v>771.92</v>
       </c>
       <c r="F5" t="n">
-        <v>99874497337</v>
+        <v>102788869489</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1327798862</v>
+        <v>1257822052</v>
       </c>
       <c r="I5" t="n">
-        <v>758.16</v>
+        <v>769.3200000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>724.1900000000001</v>
+        <v>754.7</v>
       </c>
       <c r="K5" t="n">
-        <v>23.05</v>
+        <v>25.56</v>
       </c>
       <c r="L5" t="n">
-        <v>3.1697</v>
+        <v>3.48143</v>
       </c>
       <c r="M5" t="n">
-        <v>133160438.17</v>
+        <v>133160340.96</v>
       </c>
       <c r="N5" t="n">
-        <v>133160429.28</v>
+        <v>133160340.96</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>83325852293</v>
+        <v>89964077796</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2693394422</v>
+        <v>4324462181</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02428641</v>
+        <v>0.108094</v>
       </c>
       <c r="L6" t="n">
-        <v>1.8667</v>
+        <v>8.24385</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999514</v>
+        <v>0.99977</v>
       </c>
       <c r="F7" t="n">
-        <v>73773705191</v>
+        <v>74243970808</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16804878019</v>
+        <v>19667075261</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999703</v>
+        <v>0.999862</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999464</v>
+        <v>0.999515</v>
       </c>
       <c r="K7" t="n">
-        <v>-7.1772637548539e-05</v>
+        <v>0.00024919</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00718</v>
+        <v>0.02565</v>
       </c>
       <c r="M7" t="n">
-        <v>73809548950.31921</v>
+        <v>74260936982.90303</v>
       </c>
       <c r="N7" t="n">
-        <v>73809465033.80299</v>
+        <v>74261085155.35321</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105.87</v>
+        <v>111.73</v>
       </c>
       <c r="F8" t="n">
-        <v>62173407445</v>
+        <v>65619505724</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4336330927</v>
+        <v>5307023206</v>
       </c>
       <c r="I8" t="n">
-        <v>106.53</v>
+        <v>114.14</v>
       </c>
       <c r="J8" t="n">
-        <v>100.11</v>
+        <v>108.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.5</v>
+        <v>6.04</v>
       </c>
       <c r="L8" t="n">
-        <v>5.47797</v>
+        <v>5.75077</v>
       </c>
       <c r="M8" t="n">
-        <v>587297218.9841995</v>
+        <v>587296224.8630985</v>
       </c>
       <c r="N8" t="n">
-        <v>634298467.6716927</v>
+        <v>634297490.1327897</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338083</v>
+        <v>0.338162</v>
       </c>
       <c r="F9" t="n">
-        <v>32101739690</v>
+        <v>32110527640</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>387644195</v>
+        <v>444297894</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337939</v>
+        <v>0.339776</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333425</v>
+        <v>0.337075</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00335145</v>
+        <v>0.00045238</v>
       </c>
       <c r="L9" t="n">
-        <v>1.00124</v>
+        <v>0.13803</v>
       </c>
       <c r="M9" t="n">
-        <v>94954902669.86409</v>
+        <v>94955991096.57959</v>
       </c>
       <c r="N9" t="n">
-        <v>94954901666.17758</v>
+        <v>94956666619.81319</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1467.74</v>
+        <v>1534.88</v>
       </c>
       <c r="F10" t="n">
-        <v>24865345606</v>
+        <v>26001228471</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2178796951</v>
+        <v>1664369969</v>
       </c>
       <c r="I10" t="n">
-        <v>1526.56</v>
+        <v>1590.8</v>
       </c>
       <c r="J10" t="n">
-        <v>1370.29</v>
+        <v>1437.73</v>
       </c>
       <c r="K10" t="n">
-        <v>105.04</v>
+        <v>74.98</v>
       </c>
       <c r="L10" t="n">
-        <v>7.70855</v>
+        <v>5.09457</v>
       </c>
       <c r="M10" t="n">
-        <v>16938925.1655448</v>
+        <v>16940251.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16939175.1655448</v>
+        <v>16940898.6030448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.028</v>
+        <v>1.03</v>
       </c>
       <c r="F11" t="n">
-        <v>23301466219</v>
+        <v>23389434218</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>209412055</v>
+        <v>52721291</v>
       </c>
       <c r="I11" t="n">
-        <v>1.035</v>
+        <v>1.034</v>
       </c>
       <c r="J11" t="n">
-        <v>1.004</v>
+        <v>1.027</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.001618662688462669</v>
+        <v>0.00207246</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1572</v>
+        <v>0.20108</v>
       </c>
       <c r="M11" t="n">
-        <v>22665434312.548</v>
+        <v>22705389532.338</v>
       </c>
       <c r="N11" t="n">
-        <v>22665434312.548</v>
+        <v>22705389532.338</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.27</v>
+        <v>92.44</v>
       </c>
       <c r="F12" t="n">
-        <v>20297028307</v>
+        <v>20562860000</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1618650214</v>
+        <v>1445408936</v>
       </c>
       <c r="I12" t="n">
-        <v>91.79000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="J12" t="n">
-        <v>81.5</v>
+        <v>90.36</v>
       </c>
       <c r="K12" t="n">
-        <v>9.19</v>
+        <v>1.25</v>
       </c>
       <c r="L12" t="n">
-        <v>11.19346</v>
+        <v>1.50458</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1205,23 +1205,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>91.79000000000001</v>
+        <v>94.48</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-18T12:39:40.000Z</t>
+          <t>2026-09-19T03:05:00.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.085364</v>
+        <v>0.088697</v>
       </c>
       <c r="F13" t="n">
-        <v>13314001045</v>
+        <v>13834995349</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>877130041</v>
+        <v>1053761028</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08678</v>
+        <v>0.08876100000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.081105</v>
+        <v>0.08651</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00417871</v>
+        <v>0.00331129</v>
       </c>
       <c r="L13" t="n">
-        <v>5.14712</v>
+        <v>3.91707</v>
       </c>
       <c r="M13" t="n">
-        <v>155966856383.7052</v>
+        <v>155979846383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>155966926383.7052</v>
+        <v>171691843126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>531.61</v>
+        <v>582.04</v>
       </c>
       <c r="F14" t="n">
-        <v>9993028627</v>
+        <v>10946267634</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>138577997</v>
+        <v>213999830</v>
       </c>
       <c r="I14" t="n">
-        <v>544.41</v>
+        <v>605</v>
       </c>
       <c r="J14" t="n">
-        <v>502.16</v>
+        <v>537.42</v>
       </c>
       <c r="K14" t="n">
-        <v>29.06</v>
+        <v>47.71</v>
       </c>
       <c r="L14" t="n">
-        <v>5.78332</v>
+        <v>8.926119999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>18806245.33931784</v>
+        <v>18806665.92890474</v>
       </c>
       <c r="N14" t="n">
-        <v>18806257.93928528</v>
+        <v>18806692.32885915</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,209 +1344,209 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999767</v>
+        <v>83.14</v>
       </c>
       <c r="F15" t="n">
-        <v>9562217003</v>
+        <v>9884929159</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>141420739</v>
+        <v>129651249</v>
       </c>
       <c r="I15" t="n">
-        <v>0.999965</v>
+        <v>83.64</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999596</v>
+        <v>82.25</v>
       </c>
       <c r="K15" t="n">
-        <v>9.39e-06</v>
+        <v>2.81</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00094</v>
+        <v>3.54404</v>
       </c>
       <c r="M15" t="n">
-        <v>9564389019.369761</v>
+        <v>118887984</v>
       </c>
       <c r="N15" t="n">
-        <v>9565459355.707329</v>
+        <v>293457483</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>83.64</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-09-18T19:49:00.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80.44</v>
+        <v>0.01392643</v>
       </c>
       <c r="F16" t="n">
-        <v>9482447599</v>
+        <v>9877121902</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>112012858</v>
+        <v>24502476</v>
       </c>
       <c r="I16" t="n">
-        <v>80.70999999999999</v>
+        <v>0.01403534</v>
       </c>
       <c r="J16" t="n">
-        <v>78.51000000000001</v>
+        <v>0.01258685</v>
       </c>
       <c r="K16" t="n">
-        <v>1.56</v>
+        <v>0.00113075</v>
       </c>
       <c r="L16" t="n">
-        <v>1.97292</v>
+        <v>8.83832</v>
       </c>
       <c r="M16" t="n">
-        <v>117882016</v>
+        <v>709234380366.2201</v>
       </c>
       <c r="N16" t="n">
-        <v>293532015</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O16" t="n">
-        <v>83.22</v>
+        <v>0.01946402</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-11T14:03:10.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01278862</v>
+        <v>0.999902</v>
       </c>
       <c r="F17" t="n">
-        <v>9073126084</v>
+        <v>9594602900</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>27820992</v>
+        <v>135400991</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01310816</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01260467</v>
+        <v>0.9997779999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000263625237508211</v>
+        <v>0.00012737</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.01977</v>
+        <v>0.01791</v>
       </c>
       <c r="M17" t="n">
-        <v>709234074452.8706</v>
+        <v>9595541701.9596</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>9593827178.349619</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.82</v>
+        <v>12.52</v>
       </c>
       <c r="F18" t="n">
-        <v>8843197796</v>
+        <v>9366762678</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>465095252</v>
+        <v>519635409</v>
       </c>
       <c r="I18" t="n">
-        <v>11.95</v>
+        <v>12.6</v>
       </c>
       <c r="J18" t="n">
-        <v>11.22</v>
+        <v>11.99</v>
       </c>
       <c r="K18" t="n">
-        <v>0.575928</v>
+        <v>0.708727</v>
       </c>
       <c r="L18" t="n">
-        <v>5.12126</v>
+        <v>6.05539</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,144 +1604,144 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.9</v>
+        <v>0.226696</v>
       </c>
       <c r="F19" t="n">
-        <v>8184667580</v>
+        <v>8506282135</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>76720</v>
+        <v>663518519</v>
       </c>
       <c r="I19" t="n">
-        <v>8.93</v>
+        <v>0.234678</v>
       </c>
       <c r="J19" t="n">
-        <v>8.890000000000001</v>
+        <v>0.216904</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01999754405595056</v>
+        <v>0.01201744</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.22424</v>
+        <v>5.67518</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>37522923322.16203</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.21587</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8101095616</v>
+        <v>8172462611</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>552742767</v>
+        <v>53547</v>
       </c>
       <c r="I20" t="n">
-        <v>0.216996</v>
+        <v>8.92</v>
       </c>
       <c r="J20" t="n">
-        <v>0.199529</v>
+        <v>8.81</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01551854</v>
+        <v>-0.01326123114329647</v>
       </c>
       <c r="L20" t="n">
-        <v>7.74566</v>
+        <v>-0.14903</v>
       </c>
       <c r="M20" t="n">
-        <v>37522923322.16203</v>
+        <v>919857851.9</v>
       </c>
       <c r="N20" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O20" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260918T133226Z-aef8f8</t>
+          <t>20260919T130131Z-9f3deb</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.186694</v>
+        <v>0.199434</v>
       </c>
       <c r="F21" t="n">
-        <v>6499674331</v>
+        <v>6953702577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>190708288</v>
+        <v>273347233</v>
       </c>
       <c r="I21" t="n">
-        <v>0.18919</v>
+        <v>0.196206</v>
       </c>
       <c r="J21" t="n">
-        <v>0.182408</v>
+        <v>0.189492</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00268673</v>
+        <v>0.01351744</v>
       </c>
       <c r="L21" t="n">
-        <v>1.46012</v>
+        <v>7.31125</v>
       </c>
       <c r="M21" t="n">
-        <v>34845172352.88166</v>
+        <v>34867269295.95199</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-18T13:29:20.000Z</t>
+          <t>2026-09-19T12:59:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81303</v>
+        <v>80495</v>
       </c>
       <c r="F2" t="n">
-        <v>1633087433036</v>
+        <v>1616935563111</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>39046726177</v>
+        <v>23866467100</v>
       </c>
       <c r="I2" t="n">
-        <v>81675</v>
+        <v>81864</v>
       </c>
       <c r="J2" t="n">
-        <v>80014</v>
+        <v>80155</v>
       </c>
       <c r="K2" t="n">
-        <v>3308.3</v>
+        <v>-716.1132064880803</v>
       </c>
       <c r="L2" t="n">
-        <v>4.27011</v>
+        <v>-0.88179</v>
       </c>
       <c r="M2" t="n">
-        <v>20086521</v>
+        <v>20086925</v>
       </c>
       <c r="N2" t="n">
-        <v>20086553</v>
+        <v>20086940</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2640.53</v>
+        <v>2580.2</v>
       </c>
       <c r="F3" t="n">
-        <v>322307862116</v>
+        <v>314968305243</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>20959346820</v>
+        <v>9962778525</v>
       </c>
       <c r="I3" t="n">
-        <v>2655.71</v>
+        <v>2655.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2552.3</v>
+        <v>2568.1</v>
       </c>
       <c r="K3" t="n">
-        <v>140.11</v>
+        <v>-52.42004059185319</v>
       </c>
       <c r="L3" t="n">
-        <v>5.64929</v>
+        <v>-1.99117</v>
       </c>
       <c r="M3" t="n">
-        <v>122061836.5153193</v>
+        <v>122064744.0690741</v>
       </c>
       <c r="N3" t="n">
-        <v>122061836.5153193</v>
+        <v>122064744.0690741</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999655</v>
+        <v>0.999618</v>
       </c>
       <c r="F4" t="n">
-        <v>183321470793</v>
+        <v>183316154408</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>73806318083</v>
+        <v>47434232181</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999786</v>
+        <v>0.999725</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999212</v>
+        <v>0.9993649999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00048018</v>
+        <v>-5.0405962333966e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04844</v>
+        <v>-0.00504</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649794.4283</v>
+        <v>183384649789.2811</v>
       </c>
       <c r="N4" t="n">
         <v>188851595759.0362</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>771.92</v>
+        <v>751.14</v>
       </c>
       <c r="F5" t="n">
-        <v>102788869489</v>
+        <v>100013527800</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1257822052</v>
+        <v>925413271</v>
       </c>
       <c r="I5" t="n">
-        <v>769.3200000000001</v>
+        <v>772.55</v>
       </c>
       <c r="J5" t="n">
-        <v>754.7</v>
+        <v>746.64</v>
       </c>
       <c r="K5" t="n">
-        <v>25.56</v>
+        <v>-17.74319357724983</v>
       </c>
       <c r="L5" t="n">
-        <v>3.48143</v>
+        <v>-2.30766</v>
       </c>
       <c r="M5" t="n">
-        <v>133160340.96</v>
+        <v>133160261.42</v>
       </c>
       <c r="N5" t="n">
-        <v>133160340.96</v>
+        <v>133160255.08</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>89964077796</v>
+        <v>86599821752</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4324462181</v>
+        <v>2615052383</v>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="K6" t="n">
-        <v>0.108094</v>
+        <v>-0.05751144693811527</v>
       </c>
       <c r="L6" t="n">
-        <v>8.24385</v>
+        <v>-4.00873</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99977</v>
+        <v>0.999739</v>
       </c>
       <c r="F7" t="n">
-        <v>74243970808</v>
+        <v>74195791330</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19667075261</v>
+        <v>11424902046</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999862</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999515</v>
+        <v>0.9994690000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00024919</v>
+        <v>-1.7217957993698e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02565</v>
+        <v>-0.00172</v>
       </c>
       <c r="M7" t="n">
-        <v>74260936982.90303</v>
+        <v>74214798719.86125</v>
       </c>
       <c r="N7" t="n">
-        <v>74261085155.35321</v>
+        <v>74213440603.05618</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>111.73</v>
+        <v>108.19</v>
       </c>
       <c r="F8" t="n">
-        <v>65619505724</v>
+        <v>63553214540</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5307023206</v>
+        <v>2831986860</v>
       </c>
       <c r="I8" t="n">
-        <v>114.14</v>
+        <v>112.21</v>
       </c>
       <c r="J8" t="n">
-        <v>108.45</v>
+        <v>107.5</v>
       </c>
       <c r="K8" t="n">
-        <v>6.04</v>
+        <v>-3.282472112539367</v>
       </c>
       <c r="L8" t="n">
-        <v>5.75077</v>
+        <v>-2.94473</v>
       </c>
       <c r="M8" t="n">
-        <v>587296224.8630985</v>
+        <v>587366825.3628587</v>
       </c>
       <c r="N8" t="n">
-        <v>634297490.1327897</v>
+        <v>634375499.6096436</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338162</v>
+        <v>0.342134</v>
       </c>
       <c r="F9" t="n">
-        <v>32110527640</v>
+        <v>32482355042</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>444297894</v>
+        <v>373296960</v>
       </c>
       <c r="I9" t="n">
-        <v>0.339776</v>
+        <v>0.342855</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337075</v>
+        <v>0.337711</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00045238</v>
+        <v>0.0043126</v>
       </c>
       <c r="L9" t="n">
-        <v>0.13803</v>
+        <v>1.27659</v>
       </c>
       <c r="M9" t="n">
         <v>94955991096.57959</v>
       </c>
       <c r="N9" t="n">
-        <v>94956666619.81319</v>
+        <v>94958776822.35458</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1534.88</v>
+        <v>1449.06</v>
       </c>
       <c r="F10" t="n">
-        <v>26001228471</v>
+        <v>24547629301</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1664369969</v>
+        <v>1070998386</v>
       </c>
       <c r="I10" t="n">
-        <v>1590.8</v>
+        <v>1532.34</v>
       </c>
       <c r="J10" t="n">
-        <v>1437.73</v>
+        <v>1429.69</v>
       </c>
       <c r="K10" t="n">
-        <v>74.98</v>
+        <v>-86.56531411476908</v>
       </c>
       <c r="L10" t="n">
-        <v>5.09457</v>
+        <v>-5.63715</v>
       </c>
       <c r="M10" t="n">
-        <v>16940251.7280448</v>
+        <v>16942351.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16940898.6030448</v>
+        <v>16942756.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.03</v>
+        <v>1.017</v>
       </c>
       <c r="F11" t="n">
-        <v>23389434218</v>
+        <v>23140466333</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>52721291</v>
+        <v>345014</v>
       </c>
       <c r="I11" t="n">
-        <v>1.034</v>
+        <v>1.044</v>
       </c>
       <c r="J11" t="n">
-        <v>1.027</v>
+        <v>1.001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00207246</v>
+        <v>-0.01372322010803706</v>
       </c>
       <c r="L11" t="n">
-        <v>0.20108</v>
+        <v>-1.3316</v>
       </c>
       <c r="M11" t="n">
-        <v>22705389532.338</v>
+        <v>22756817018.848</v>
       </c>
       <c r="N11" t="n">
-        <v>22705389532.338</v>
+        <v>22756817018.848</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-19T21:24:00.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.44</v>
+        <v>91.02</v>
       </c>
       <c r="F12" t="n">
-        <v>20562860000</v>
+        <v>20248590427</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1445408936</v>
+        <v>816678542</v>
       </c>
       <c r="I12" t="n">
-        <v>94.48</v>
+        <v>93.34</v>
       </c>
       <c r="J12" t="n">
-        <v>90.36</v>
+        <v>89.91</v>
       </c>
       <c r="K12" t="n">
-        <v>1.25</v>
+        <v>-1.201150679321842</v>
       </c>
       <c r="L12" t="n">
-        <v>1.50458</v>
+        <v>-1.30245</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.088697</v>
+        <v>0.084982</v>
       </c>
       <c r="F13" t="n">
-        <v>13834995349</v>
+        <v>13258401671</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1053761028</v>
+        <v>957418339</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08876100000000001</v>
+        <v>0.09105199999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08651</v>
+        <v>0.084508</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00331129</v>
+        <v>-0.003840532751950301</v>
       </c>
       <c r="L13" t="n">
-        <v>3.91707</v>
+        <v>-4.32382</v>
       </c>
       <c r="M13" t="n">
-        <v>155979846383.7052</v>
+        <v>155990666383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171691843126.579</v>
+        <v>155993876383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>582.04</v>
+        <v>535.58</v>
       </c>
       <c r="F14" t="n">
-        <v>10946267634</v>
+        <v>10061624614</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>213999830</v>
+        <v>131885688</v>
       </c>
       <c r="I14" t="n">
-        <v>605</v>
+        <v>579.76</v>
       </c>
       <c r="J14" t="n">
-        <v>537.42</v>
+        <v>518.29</v>
       </c>
       <c r="K14" t="n">
-        <v>47.71</v>
+        <v>-42.40255239524106</v>
       </c>
       <c r="L14" t="n">
-        <v>8.926119999999999</v>
+        <v>-7.33635</v>
       </c>
       <c r="M14" t="n">
-        <v>18806665.92890474</v>
+        <v>18807107.52726052</v>
       </c>
       <c r="N14" t="n">
-        <v>18806692.32885915</v>
+        <v>18807145.32714538</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>83.14</v>
+        <v>81.87</v>
       </c>
       <c r="F15" t="n">
-        <v>9884929159</v>
+        <v>9729647899</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>129651249</v>
+        <v>66922631</v>
       </c>
       <c r="I15" t="n">
-        <v>83.64</v>
+        <v>83.58</v>
       </c>
       <c r="J15" t="n">
-        <v>82.25</v>
+        <v>81.56</v>
       </c>
       <c r="K15" t="n">
-        <v>2.81</v>
+        <v>-1.16256627545016</v>
       </c>
       <c r="L15" t="n">
-        <v>3.54404</v>
+        <v>-1.4002</v>
       </c>
       <c r="M15" t="n">
         <v>118887984</v>
@@ -1409,144 +1409,144 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01392643</v>
+        <v>0.999799</v>
       </c>
       <c r="F16" t="n">
-        <v>9877121902</v>
+        <v>9594177187</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>24502476</v>
+        <v>73095244</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01403534</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01258685</v>
+        <v>0.999555</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00113075</v>
+        <v>-0.000212149564497666</v>
       </c>
       <c r="L16" t="n">
-        <v>8.83832</v>
+        <v>-0.02121</v>
       </c>
       <c r="M16" t="n">
-        <v>709234380366.2201</v>
+        <v>9596506299.314947</v>
       </c>
       <c r="N16" t="n">
-        <v>1142408526965.963</v>
+        <v>9615952659.618965</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01946402</v>
+        <v>1.057</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999902</v>
+        <v>0.01319963</v>
       </c>
       <c r="F17" t="n">
-        <v>9594602900</v>
+        <v>9360305215</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>135400991</v>
+        <v>22251262</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>0.01400625</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9997779999999999</v>
+        <v>0.01315802</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00012737</v>
+        <v>-0.000716285644190382</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01791</v>
+        <v>-5.14724</v>
       </c>
       <c r="M17" t="n">
-        <v>9595541701.9596</v>
+        <v>709239215179.4515</v>
       </c>
       <c r="N17" t="n">
-        <v>9593827178.349619</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O17" t="n">
-        <v>1.057</v>
+        <v>0.01946402</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.52</v>
+        <v>12.1</v>
       </c>
       <c r="F18" t="n">
-        <v>9366762678</v>
+        <v>9051969224</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>519635409</v>
+        <v>444890857</v>
       </c>
       <c r="I18" t="n">
-        <v>12.6</v>
+        <v>12.67</v>
       </c>
       <c r="J18" t="n">
-        <v>11.99</v>
+        <v>11.92</v>
       </c>
       <c r="K18" t="n">
-        <v>0.708727</v>
+        <v>-0.3614832084632802</v>
       </c>
       <c r="L18" t="n">
-        <v>6.05539</v>
+        <v>-2.90074</v>
       </c>
       <c r="M18" t="n">
         <v>748099970.424884</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.226696</v>
+        <v>0.221201</v>
       </c>
       <c r="F19" t="n">
-        <v>8506282135</v>
+        <v>8300217493</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>663518519</v>
+        <v>422086912</v>
       </c>
       <c r="I19" t="n">
-        <v>0.234678</v>
+        <v>0.231163</v>
       </c>
       <c r="J19" t="n">
-        <v>0.216904</v>
+        <v>0.218425</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01201744</v>
+        <v>-0.005928161879755561</v>
       </c>
       <c r="L19" t="n">
-        <v>5.67518</v>
+        <v>-2.61004</v>
       </c>
       <c r="M19" t="n">
         <v>37522923322.16203</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.93</v>
       </c>
       <c r="F20" t="n">
-        <v>8172462611</v>
+        <v>8218224663</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>53547</v>
+        <v>163463</v>
       </c>
       <c r="I20" t="n">
-        <v>8.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>8.81</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01326123114329647</v>
+        <v>0.04202022</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.14903</v>
+        <v>0.47255</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260919T130131Z-9f3deb</t>
+          <t>20260920T133239Z-3ba0f1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.199434</v>
+        <v>0.190217</v>
       </c>
       <c r="F21" t="n">
-        <v>6953702577</v>
+        <v>6633745483</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>273347233</v>
+        <v>209188054</v>
       </c>
       <c r="I21" t="n">
-        <v>0.196206</v>
+        <v>0.202311</v>
       </c>
       <c r="J21" t="n">
-        <v>0.189492</v>
+        <v>0.188682</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01351744</v>
+        <v>-0.01022295789780794</v>
       </c>
       <c r="L21" t="n">
-        <v>7.31125</v>
+        <v>-5.10025</v>
       </c>
       <c r="M21" t="n">
-        <v>34867269295.95199</v>
+        <v>34867261640.33779</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-19T12:59:10.000Z</t>
+          <t>2026-09-20T13:30:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80495</v>
+        <v>86124</v>
       </c>
       <c r="F2" t="n">
-        <v>1616935563111</v>
+        <v>1728665546532</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>23866467100</v>
+        <v>53399664432</v>
       </c>
       <c r="I2" t="n">
-        <v>81864</v>
+        <v>86048</v>
       </c>
       <c r="J2" t="n">
-        <v>80155</v>
+        <v>80631</v>
       </c>
       <c r="K2" t="n">
-        <v>-716.1132064880803</v>
+        <v>5263.94</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.88179</v>
+        <v>6.50996</v>
       </c>
       <c r="M2" t="n">
-        <v>20086925</v>
+        <v>20087478</v>
       </c>
       <c r="N2" t="n">
-        <v>20086940</v>
+        <v>20087478</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2580.2</v>
+        <v>2750.02</v>
       </c>
       <c r="F3" t="n">
-        <v>314968305243</v>
+        <v>335133212622</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9962778525</v>
+        <v>24352107151</v>
       </c>
       <c r="I3" t="n">
-        <v>2655.64</v>
+        <v>2751.07</v>
       </c>
       <c r="J3" t="n">
-        <v>2568.1</v>
+        <v>2607</v>
       </c>
       <c r="K3" t="n">
-        <v>-52.42004059185319</v>
+        <v>144.87</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.99117</v>
+        <v>5.56097</v>
       </c>
       <c r="M3" t="n">
-        <v>122064744.0690741</v>
+        <v>122067645.9189046</v>
       </c>
       <c r="N3" t="n">
-        <v>122064744.0690741</v>
+        <v>122067645.9189046</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999618</v>
+        <v>0.999874</v>
       </c>
       <c r="F4" t="n">
-        <v>183316154408</v>
+        <v>183365978384</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>47434232181</v>
+        <v>93897835021</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999725</v>
+        <v>0.999816</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9993649999999999</v>
+        <v>0.999577</v>
       </c>
       <c r="K4" t="n">
-        <v>-5.0405962333966e-05</v>
+        <v>0.00023771</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00504</v>
+        <v>0.02378</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649789.2811</v>
+        <v>183384649781.6938</v>
       </c>
       <c r="N4" t="n">
         <v>188851595759.0362</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>751.14</v>
+        <v>805.13</v>
       </c>
       <c r="F5" t="n">
-        <v>100013527800</v>
+        <v>107128051029</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>925413271</v>
+        <v>1861840599</v>
       </c>
       <c r="I5" t="n">
-        <v>772.55</v>
+        <v>798.53</v>
       </c>
       <c r="J5" t="n">
-        <v>746.64</v>
+        <v>756.27</v>
       </c>
       <c r="K5" t="n">
-        <v>-17.74319357724983</v>
+        <v>48.91</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.30766</v>
+        <v>6.46797</v>
       </c>
       <c r="M5" t="n">
-        <v>133160261.42</v>
+        <v>133160157.48</v>
       </c>
       <c r="N5" t="n">
-        <v>133160255.08</v>
+        <v>133160152.56</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>86599821752</v>
+        <v>94051358788</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2615052383</v>
+        <v>4723578943</v>
       </c>
       <c r="I6" t="n">
-        <v>1.45</v>
+        <v>1.51</v>
       </c>
       <c r="J6" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05751144693811527</v>
+        <v>0.112485</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.00873</v>
+        <v>8.11206</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999739</v>
+        <v>0.9999169999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>74195791330</v>
+        <v>74231800122</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>11424902046</v>
+        <v>24254647063</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>0.9998629999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9994690000000001</v>
+        <v>0.999598</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7217957993698e-05</v>
+        <v>0.00021933</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00172</v>
+        <v>0.02194</v>
       </c>
       <c r="M7" t="n">
-        <v>74214798719.86125</v>
+        <v>74237004006.76027</v>
       </c>
       <c r="N7" t="n">
-        <v>74213440603.05618</v>
+        <v>74254811731.89992</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>108.19</v>
+        <v>118.05</v>
       </c>
       <c r="F8" t="n">
-        <v>63553214540</v>
+        <v>69255259901</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2831986860</v>
+        <v>6440764344</v>
       </c>
       <c r="I8" t="n">
-        <v>112.21</v>
+        <v>118.69</v>
       </c>
       <c r="J8" t="n">
-        <v>107.5</v>
+        <v>108.51</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.282472112539367</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.94473</v>
+        <v>8.87163</v>
       </c>
       <c r="M8" t="n">
-        <v>587366825.3628587</v>
+        <v>587437261.0683235</v>
       </c>
       <c r="N8" t="n">
-        <v>634375499.6096436</v>
+        <v>634453375.546979</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.342134</v>
+        <v>0.345544</v>
       </c>
       <c r="F9" t="n">
-        <v>32482355042</v>
+        <v>32816706862</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>373296960</v>
+        <v>440937993</v>
       </c>
       <c r="I9" t="n">
-        <v>0.342855</v>
+        <v>0.345088</v>
       </c>
       <c r="J9" t="n">
-        <v>0.337711</v>
+        <v>0.342488</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0043126</v>
+        <v>0.00109724</v>
       </c>
       <c r="L9" t="n">
-        <v>1.27659</v>
+        <v>0.31855</v>
       </c>
       <c r="M9" t="n">
-        <v>94955991096.57959</v>
+        <v>94960364758.90469</v>
       </c>
       <c r="N9" t="n">
-        <v>94958776822.35458</v>
+        <v>94960365761.90469</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1449.06</v>
+        <v>1495.75</v>
       </c>
       <c r="F10" t="n">
-        <v>24547629301</v>
+        <v>25309984948</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1070998386</v>
+        <v>1431547468</v>
       </c>
       <c r="I10" t="n">
-        <v>1532.34</v>
+        <v>1568.53</v>
       </c>
       <c r="J10" t="n">
-        <v>1429.69</v>
+        <v>1439.75</v>
       </c>
       <c r="K10" t="n">
-        <v>-86.56531411476908</v>
+        <v>53.35</v>
       </c>
       <c r="L10" t="n">
-        <v>-5.63715</v>
+        <v>3.69892</v>
       </c>
       <c r="M10" t="n">
         <v>16942351.7280448</v>
       </c>
       <c r="N10" t="n">
-        <v>16942756.4155448</v>
+        <v>16944709.5405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.017</v>
+        <v>1.04</v>
       </c>
       <c r="F11" t="n">
-        <v>23140466333</v>
+        <v>23664863580</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>345014</v>
+        <v>16837398</v>
       </c>
       <c r="I11" t="n">
-        <v>1.044</v>
+        <v>1.021</v>
       </c>
       <c r="J11" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="K11" t="n">
-        <v>-0.01372322010803706</v>
-      </c>
-      <c r="L11" t="n">
-        <v>-1.3316</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>22756817018.848</v>
+        <v>22764228455.528</v>
       </c>
       <c r="N11" t="n">
-        <v>22756817018.848</v>
+        <v>22764228455.528</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-19T21:24:00.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.02</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>20248590427</v>
+        <v>20757345051</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>816678542</v>
+        <v>1256686450</v>
       </c>
       <c r="I12" t="n">
-        <v>93.34</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.91</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.201150679321842</v>
+        <v>1.53</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.30245</v>
+        <v>1.66271</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1205,23 +1201,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>94.48</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-19T03:05:00.000Z</t>
+          <t>2026-09-21T11:21:00.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.084982</v>
+        <v>0.097469</v>
       </c>
       <c r="F13" t="n">
-        <v>13258401671</v>
+        <v>15181065525</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>957418339</v>
+        <v>1882978328</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09105199999999999</v>
+        <v>0.095163</v>
       </c>
       <c r="J13" t="n">
-        <v>0.084508</v>
+        <v>0.085616</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003840532751950301</v>
+        <v>0.01187787</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.32382</v>
+        <v>13.87742</v>
       </c>
       <c r="M13" t="n">
-        <v>155990666383.7052</v>
+        <v>156008016383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>155993876383.7052</v>
+        <v>156008916383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>535.58</v>
+        <v>572.01</v>
       </c>
       <c r="F14" t="n">
-        <v>10061624614</v>
+        <v>10738217262</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131885688</v>
+        <v>235272967</v>
       </c>
       <c r="I14" t="n">
-        <v>579.76</v>
+        <v>630.51</v>
       </c>
       <c r="J14" t="n">
-        <v>518.29</v>
+        <v>540.97</v>
       </c>
       <c r="K14" t="n">
-        <v>-42.40255239524106</v>
+        <v>29.3</v>
       </c>
       <c r="L14" t="n">
-        <v>-7.33635</v>
+        <v>5.39931</v>
       </c>
       <c r="M14" t="n">
-        <v>18807107.52726052</v>
+        <v>18807603.12217533</v>
       </c>
       <c r="N14" t="n">
-        <v>18807145.32714538</v>
+        <v>18807625.32201612</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,28 +1366,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>81.87</v>
+        <v>86.64</v>
       </c>
       <c r="F15" t="n">
-        <v>9729647899</v>
+        <v>10291846518</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>66922631</v>
+        <v>215315698</v>
       </c>
       <c r="I15" t="n">
-        <v>83.58</v>
+        <v>86.64</v>
       </c>
       <c r="J15" t="n">
-        <v>81.56</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.16256627545016</v>
+        <v>4.33</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.4002</v>
+        <v>5.26004</v>
       </c>
       <c r="M15" t="n">
         <v>118887984</v>
@@ -1400,218 +1396,218 @@
         <v>293457483</v>
       </c>
       <c r="O15" t="n">
-        <v>83.64</v>
+        <v>86.8</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-18T19:49:00.000Z</t>
+          <t>2026-09-21T15:13:20.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999799</v>
+        <v>0.01414863</v>
       </c>
       <c r="F16" t="n">
-        <v>9594177187</v>
+        <v>10032920141</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>73095244</v>
+        <v>29041461</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>0.01427443</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999555</v>
+        <v>0.01325824</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.000212149564497666</v>
+        <v>0.00097359</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.02121</v>
+        <v>7.38968</v>
       </c>
       <c r="M16" t="n">
-        <v>9596506299.314947</v>
+        <v>709239296767.5244</v>
       </c>
       <c r="N16" t="n">
-        <v>9615952659.618965</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>0.01946402</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.01319963</v>
+        <v>13.03</v>
       </c>
       <c r="F17" t="n">
-        <v>9360305215</v>
+        <v>9741654136</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>22251262</v>
+        <v>695570017</v>
       </c>
       <c r="I17" t="n">
-        <v>0.01400625</v>
+        <v>13.16</v>
       </c>
       <c r="J17" t="n">
-        <v>0.01315802</v>
+        <v>12.32</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000716285644190382</v>
+        <v>0.717199</v>
       </c>
       <c r="L17" t="n">
-        <v>-5.14724</v>
+        <v>5.82362</v>
       </c>
       <c r="M17" t="n">
-        <v>709239215179.4515</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>1142408526965.963</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01946402</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>12.1</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
-        <v>9051969224</v>
+        <v>9595586523</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>444890857</v>
+        <v>196078899</v>
       </c>
       <c r="I18" t="n">
-        <v>12.67</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>11.92</v>
+        <v>0.999754</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3614832084632802</v>
+        <v>0.00015973</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.90074</v>
+        <v>0.01598</v>
       </c>
       <c r="M18" t="n">
-        <v>748099970.424884</v>
+        <v>9594149705.433596</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>9594892921.253408</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.221201</v>
+        <v>0.245391</v>
       </c>
       <c r="F19" t="n">
-        <v>8300217493</v>
+        <v>9197046672</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>422086912</v>
+        <v>826630614</v>
       </c>
       <c r="I19" t="n">
-        <v>0.231163</v>
+        <v>0.248479</v>
       </c>
       <c r="J19" t="n">
-        <v>0.218425</v>
+        <v>0.22404</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.005928161879755561</v>
+        <v>0.02123083</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.61004</v>
+        <v>9.471270000000001</v>
       </c>
       <c r="M19" t="n">
         <v>37522923322.16203</v>
@@ -1669,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
       <c r="F20" t="n">
-        <v>8218224663</v>
+        <v>8205789399</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>163463</v>
+        <v>45234</v>
       </c>
       <c r="I20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="J20" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04202022</v>
+        <v>-0.01354870721141488</v>
       </c>
       <c r="L20" t="n">
-        <v>0.47255</v>
+        <v>-0.15166</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260920T133239Z-3ba0f1</t>
+          <t>20260921T155008Z-610504</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.190217</v>
+        <v>0.210781</v>
       </c>
       <c r="F21" t="n">
-        <v>6633745483</v>
+        <v>7340660289</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>209188054</v>
+        <v>385358090</v>
       </c>
       <c r="I21" t="n">
-        <v>0.202311</v>
+        <v>0.212907</v>
       </c>
       <c r="J21" t="n">
-        <v>0.188682</v>
+        <v>0.193655</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01022295789780794</v>
+        <v>0.01715873</v>
       </c>
       <c r="L21" t="n">
-        <v>-5.10025</v>
+        <v>8.861940000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>34867261640.33779</v>
+        <v>34882253227.52757</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-20T13:30:20.000Z</t>
+          <t>2026-09-21T15:47:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86124</v>
+        <v>86132</v>
       </c>
       <c r="F2" t="n">
-        <v>1728665546532</v>
+        <v>1730358233094</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>53399664432</v>
+        <v>49306386707</v>
       </c>
       <c r="I2" t="n">
-        <v>86048</v>
+        <v>87330</v>
       </c>
       <c r="J2" t="n">
-        <v>80631</v>
+        <v>85098</v>
       </c>
       <c r="K2" t="n">
-        <v>5263.94</v>
+        <v>592.03</v>
       </c>
       <c r="L2" t="n">
-        <v>6.50996</v>
+        <v>0.69211</v>
       </c>
       <c r="M2" t="n">
-        <v>20087478</v>
+        <v>20087871</v>
       </c>
       <c r="N2" t="n">
-        <v>20087478</v>
+        <v>20087940</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2750.02</v>
+        <v>2754.3</v>
       </c>
       <c r="F3" t="n">
-        <v>335133212622</v>
+        <v>336292649409</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>24352107151</v>
+        <v>19972791098</v>
       </c>
       <c r="I3" t="n">
-        <v>2751.07</v>
+        <v>2804.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2607</v>
+        <v>2714.5</v>
       </c>
       <c r="K3" t="n">
-        <v>144.87</v>
+        <v>19.06</v>
       </c>
       <c r="L3" t="n">
-        <v>5.56097</v>
+        <v>0.6967</v>
       </c>
       <c r="M3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930826</v>
       </c>
       <c r="N3" t="n">
-        <v>122067645.9189046</v>
+        <v>122070499.1930825</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999874</v>
+        <v>0.999735</v>
       </c>
       <c r="F4" t="n">
-        <v>183365978384</v>
+        <v>183336508352</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>93897835021</v>
+        <v>87755318333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999816</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999577</v>
+        <v>0.9996080000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00023771</v>
+        <v>9.564999999999999e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02378</v>
+        <v>0.00957</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>805.13</v>
+        <v>789.84</v>
       </c>
       <c r="F5" t="n">
-        <v>107128051029</v>
+        <v>105180447721</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1861840599</v>
+        <v>1606078435</v>
       </c>
       <c r="I5" t="n">
-        <v>798.53</v>
+        <v>806.75</v>
       </c>
       <c r="J5" t="n">
-        <v>756.27</v>
+        <v>783.38</v>
       </c>
       <c r="K5" t="n">
-        <v>48.91</v>
+        <v>-4.924875956322353</v>
       </c>
       <c r="L5" t="n">
-        <v>6.46797</v>
+        <v>-0.61966</v>
       </c>
       <c r="M5" t="n">
-        <v>133160157.48</v>
+        <v>133160075.87</v>
       </c>
       <c r="N5" t="n">
-        <v>133160152.56</v>
+        <v>133160072.53</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="F6" t="n">
-        <v>94051358788</v>
+        <v>99065321389</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4723578943</v>
+        <v>6307464848</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>0.112485</v>
+        <v>0.089047</v>
       </c>
       <c r="L6" t="n">
-        <v>8.11206</v>
+        <v>5.97063</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9999169999999999</v>
+        <v>0.99983</v>
       </c>
       <c r="F7" t="n">
-        <v>74231800122</v>
+        <v>74582091668</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24254647063</v>
+        <v>23229656383</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9998629999999999</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999598</v>
+        <v>0.999694</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00021933</v>
+        <v>0.00012216</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02194</v>
+        <v>0.01222</v>
       </c>
       <c r="M7" t="n">
-        <v>74237004006.76027</v>
+        <v>74594529696.15031</v>
       </c>
       <c r="N7" t="n">
-        <v>74254811731.89992</v>
+        <v>74599622744.57069</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.05</v>
+        <v>117.61</v>
       </c>
       <c r="F8" t="n">
-        <v>69255259901</v>
+        <v>69106453195</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>6440764344</v>
+        <v>5533889889</v>
       </c>
       <c r="I8" t="n">
-        <v>118.69</v>
+        <v>119.9</v>
       </c>
       <c r="J8" t="n">
-        <v>108.51</v>
+        <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>9.619999999999999</v>
+        <v>-0.5882841268877286</v>
       </c>
       <c r="L8" t="n">
-        <v>8.87163</v>
+        <v>-0.49769</v>
       </c>
       <c r="M8" t="n">
-        <v>587437261.0683235</v>
+        <v>587507739.1137596</v>
       </c>
       <c r="N8" t="n">
-        <v>634453375.546979</v>
+        <v>634531389.3135934</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.345544</v>
+        <v>0.342896</v>
       </c>
       <c r="F9" t="n">
-        <v>32816706862</v>
+        <v>32558762440</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>440937993</v>
+        <v>611135640</v>
       </c>
       <c r="I9" t="n">
-        <v>0.345088</v>
+        <v>0.349178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.342488</v>
+        <v>0.343759</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00109724</v>
+        <v>-0.001853093714661691</v>
       </c>
       <c r="L9" t="n">
-        <v>0.31855</v>
+        <v>-0.53752</v>
       </c>
       <c r="M9" t="n">
-        <v>94960364758.90469</v>
+        <v>94961752942.69308</v>
       </c>
       <c r="N9" t="n">
-        <v>94960365761.90469</v>
+        <v>94961735259.42459</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1495.75</v>
+        <v>1515.29</v>
       </c>
       <c r="F10" t="n">
-        <v>25309984948</v>
+        <v>25679897777</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1431547468</v>
+        <v>1439199278</v>
       </c>
       <c r="I10" t="n">
-        <v>1568.53</v>
+        <v>1540.34</v>
       </c>
       <c r="J10" t="n">
-        <v>1439.75</v>
+        <v>1444.17</v>
       </c>
       <c r="K10" t="n">
-        <v>53.35</v>
+        <v>-22.07724586670861</v>
       </c>
       <c r="L10" t="n">
-        <v>3.69892</v>
+        <v>-1.43604</v>
       </c>
       <c r="M10" t="n">
-        <v>16942351.7280448</v>
+        <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16944709.5405448</v>
+        <v>16946415.7905448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,30 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.04</v>
+        <v>1.013</v>
       </c>
       <c r="F11" t="n">
-        <v>23664863580</v>
+        <v>23062335218</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>16837398</v>
+        <v>55232417</v>
       </c>
       <c r="I11" t="n">
-        <v>1.021</v>
+        <v>1.04</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>1.012</v>
+      </c>
+      <c r="K11" t="n">
+        <v>-0.006103827815765017</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-0.59888</v>
+      </c>
       <c r="M11" t="n">
         <v>22764228455.528</v>
       </c>
       <c r="N11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93.40000000000001</v>
+        <v>95.36</v>
       </c>
       <c r="F12" t="n">
-        <v>20757345051</v>
+        <v>21211241880</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1256686450</v>
+        <v>1293604135</v>
       </c>
       <c r="I12" t="n">
-        <v>95.98999999999999</v>
+        <v>95.88</v>
       </c>
       <c r="J12" t="n">
-        <v>91.90000000000001</v>
+        <v>92.06</v>
       </c>
       <c r="K12" t="n">
-        <v>1.53</v>
+        <v>0.44987</v>
       </c>
       <c r="L12" t="n">
-        <v>1.66271</v>
+        <v>0.47398</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097469</v>
+        <v>0.100752</v>
       </c>
       <c r="F13" t="n">
-        <v>15181065525</v>
+        <v>15718592446</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1882978328</v>
+        <v>3160716957</v>
       </c>
       <c r="I13" t="n">
-        <v>0.095163</v>
+        <v>0.105575</v>
       </c>
       <c r="J13" t="n">
-        <v>0.085616</v>
+        <v>0.09251</v>
       </c>
       <c r="K13" t="n">
-        <v>0.01187787</v>
+        <v>0.00726657</v>
       </c>
       <c r="L13" t="n">
-        <v>13.87742</v>
+        <v>7.77292</v>
       </c>
       <c r="M13" t="n">
-        <v>156008016383.7053</v>
+        <v>156021246383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156008916383.7052</v>
+        <v>171733843126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>572.01</v>
+        <v>572.97</v>
       </c>
       <c r="F14" t="n">
-        <v>10738217262</v>
+        <v>10785142460</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>235272967</v>
+        <v>183437802</v>
       </c>
       <c r="I14" t="n">
-        <v>630.51</v>
+        <v>601.01</v>
       </c>
       <c r="J14" t="n">
-        <v>540.97</v>
+        <v>552.66</v>
       </c>
       <c r="K14" t="n">
-        <v>29.3</v>
+        <v>-2.374429859507018</v>
       </c>
       <c r="L14" t="n">
-        <v>5.39931</v>
+        <v>-0.4127</v>
       </c>
       <c r="M14" t="n">
-        <v>18807603.12217533</v>
+        <v>18808007.51155922</v>
       </c>
       <c r="N14" t="n">
-        <v>18807625.32201612</v>
+        <v>18808040.5111969</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,248 +1370,248 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.64</v>
+        <v>86.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10291846518</v>
+        <v>10299673248</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>215315698</v>
+        <v>176791671</v>
       </c>
       <c r="I15" t="n">
-        <v>86.64</v>
+        <v>87.91</v>
       </c>
       <c r="J15" t="n">
-        <v>82.23999999999999</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>4.33</v>
+        <v>0.492012</v>
       </c>
       <c r="L15" t="n">
-        <v>5.26004</v>
+        <v>0.57098</v>
       </c>
       <c r="M15" t="n">
-        <v>118887984</v>
+        <v>118852171</v>
       </c>
       <c r="N15" t="n">
-        <v>293457483</v>
+        <v>293421670</v>
       </c>
       <c r="O15" t="n">
-        <v>86.8</v>
+        <v>87.91</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-21T15:13:20.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.01414863</v>
+        <v>13.06</v>
       </c>
       <c r="F16" t="n">
-        <v>10032920141</v>
+        <v>9773544357</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>29041461</v>
+        <v>684922983</v>
       </c>
       <c r="I16" t="n">
-        <v>0.01427443</v>
+        <v>13.26</v>
       </c>
       <c r="J16" t="n">
-        <v>0.01325824</v>
+        <v>12.76</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00097359</v>
+        <v>0.009376229999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>7.38968</v>
+        <v>0.07183</v>
       </c>
       <c r="M16" t="n">
-        <v>709239296767.5244</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>1142408526965.963</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01946402</v>
+        <v>52.7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>13.03</v>
+        <v>0.9998939999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>9741654136</v>
+        <v>9583360912</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>695570017</v>
+        <v>238853572</v>
       </c>
       <c r="I17" t="n">
-        <v>13.16</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>12.32</v>
+        <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>0.717199</v>
+        <v>7.478999999999999e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>5.82362</v>
+        <v>0.00748</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>9583873777.059114</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>9576750341.247417</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0.01348809</v>
       </c>
       <c r="F18" t="n">
-        <v>9595586523</v>
+        <v>9559476072</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>196078899</v>
+        <v>17859980</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.01420135</v>
       </c>
       <c r="J18" t="n">
-        <v>0.999754</v>
+        <v>0.01343954</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00015973</v>
+        <v>-0.000638838496365042</v>
       </c>
       <c r="L18" t="n">
-        <v>0.01598</v>
+        <v>-4.52213</v>
       </c>
       <c r="M18" t="n">
-        <v>9594149705.433596</v>
+        <v>709239700254.0453</v>
       </c>
       <c r="N18" t="n">
-        <v>9594892921.253408</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O18" t="n">
-        <v>1.057</v>
+        <v>0.01946402</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.245391</v>
+        <v>0.252441</v>
       </c>
       <c r="F19" t="n">
-        <v>9197046672</v>
+        <v>9470964968</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>826630614</v>
+        <v>838000406</v>
       </c>
       <c r="I19" t="n">
-        <v>0.248479</v>
+        <v>0.251521</v>
       </c>
       <c r="J19" t="n">
-        <v>0.22404</v>
+        <v>0.240416</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02123083</v>
+        <v>0.007827020000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>9.471270000000001</v>
+        <v>3.19974</v>
       </c>
       <c r="M19" t="n">
-        <v>37522923322.16203</v>
+        <v>37529061988.53558</v>
       </c>
       <c r="N19" t="n">
         <v>45000000000</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.92</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8205789399</v>
+        <v>8251314793</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>45234</v>
+        <v>157365</v>
       </c>
       <c r="I20" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01354870721141488</v>
+        <v>-0.01618964306871185</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.15166</v>
+        <v>-0.18016</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260921T155008Z-610504</t>
+          <t>20260922T135928Z-22f6ba</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.210781</v>
+        <v>0.214975</v>
       </c>
       <c r="F21" t="n">
-        <v>7340660289</v>
+        <v>7505565898</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>385358090</v>
+        <v>450679611</v>
       </c>
       <c r="I21" t="n">
-        <v>0.212907</v>
+        <v>0.219762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.193655</v>
+        <v>0.206236</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01715873</v>
+        <v>0.00500717</v>
       </c>
       <c r="L21" t="n">
-        <v>8.861940000000001</v>
+        <v>2.38473</v>
       </c>
       <c r="M21" t="n">
-        <v>34882253227.52757</v>
+        <v>34931879410.76893</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-21T15:47:10.000Z</t>
+          <t>2026-09-22T13:56:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86132</v>
+        <v>86238</v>
       </c>
       <c r="F2" t="n">
-        <v>1730358233094</v>
+        <v>1732793991467</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>49306386707</v>
+        <v>43485131868</v>
       </c>
       <c r="I2" t="n">
-        <v>87330</v>
+        <v>86722</v>
       </c>
       <c r="J2" t="n">
-        <v>85098</v>
+        <v>85107</v>
       </c>
       <c r="K2" t="n">
-        <v>592.03</v>
+        <v>-377.4880582667683</v>
       </c>
       <c r="L2" t="n">
-        <v>0.69211</v>
+        <v>-0.42991</v>
       </c>
       <c r="M2" t="n">
-        <v>20087871</v>
+        <v>20088034</v>
       </c>
       <c r="N2" t="n">
-        <v>20087940</v>
+        <v>20088056</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2754.3</v>
+        <v>2748.95</v>
       </c>
       <c r="F3" t="n">
-        <v>336292649409</v>
+        <v>335700394407</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>19972791098</v>
+        <v>16208315503</v>
       </c>
       <c r="I3" t="n">
-        <v>2804.42</v>
+        <v>2786.01</v>
       </c>
       <c r="J3" t="n">
-        <v>2714.5</v>
+        <v>2716.11</v>
       </c>
       <c r="K3" t="n">
-        <v>19.06</v>
+        <v>-21.36690103358978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6967</v>
+        <v>-0.75097</v>
       </c>
       <c r="M3" t="n">
         <v>122070499.1930826</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999735</v>
+        <v>0.999898</v>
       </c>
       <c r="F4" t="n">
-        <v>183336508352</v>
+        <v>183363689877</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>87755318333</v>
+        <v>78958984976</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9996080000000001</v>
+        <v>0.999627</v>
       </c>
       <c r="K4" t="n">
-        <v>9.564999999999999e-05</v>
+        <v>6.751e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00957</v>
+        <v>0.00721</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>789.84</v>
+        <v>784.49</v>
       </c>
       <c r="F5" t="n">
-        <v>105180447721</v>
+        <v>104509508003</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1606078435</v>
+        <v>1338733134</v>
       </c>
       <c r="I5" t="n">
         <v>806.75</v>
       </c>
       <c r="J5" t="n">
-        <v>783.38</v>
+        <v>781.83</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.924875956322353</v>
+        <v>-20.06454466473849</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.61966</v>
+        <v>-2.48689</v>
       </c>
       <c r="M5" t="n">
-        <v>133160075.87</v>
+        <v>133160045.24</v>
       </c>
       <c r="N5" t="n">
-        <v>133160072.53</v>
+        <v>133160043.94</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="F6" t="n">
-        <v>99065321389</v>
+        <v>98935861541</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6307464848</v>
+        <v>6013941970</v>
       </c>
       <c r="I6" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="J6" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.089047</v>
+        <v>0.02050936</v>
       </c>
       <c r="L6" t="n">
-        <v>5.97063</v>
+        <v>1.26594</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99983</v>
+        <v>0.999892</v>
       </c>
       <c r="F7" t="n">
-        <v>74582091668</v>
+        <v>75082614224</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>23229656383</v>
+        <v>20211770616</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999694</v>
+        <v>0.999695</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00012216</v>
+        <v>8.51e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01222</v>
+        <v>0.00201</v>
       </c>
       <c r="M7" t="n">
-        <v>74594529696.15031</v>
+        <v>75091582641.99438</v>
       </c>
       <c r="N7" t="n">
-        <v>74599622744.57069</v>
+        <v>75091431783.64163</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>117.61</v>
+        <v>118.13</v>
       </c>
       <c r="F8" t="n">
-        <v>69106453195</v>
+        <v>69442081520</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5533889889</v>
+        <v>4713073391</v>
       </c>
       <c r="I8" t="n">
-        <v>119.9</v>
+        <v>119.82</v>
       </c>
       <c r="J8" t="n">
         <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5882841268877286</v>
+        <v>-1.022544647266727</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.49769</v>
+        <v>-0.84705</v>
       </c>
       <c r="M8" t="n">
-        <v>587507739.1137596</v>
+        <v>587507395.8954812</v>
       </c>
       <c r="N8" t="n">
-        <v>634531389.3135934</v>
+        <v>634531021.326126</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.342896</v>
+        <v>0.34165</v>
       </c>
       <c r="F9" t="n">
-        <v>32558762440</v>
+        <v>32442198365</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>611135640</v>
+        <v>605341752</v>
       </c>
       <c r="I9" t="n">
         <v>0.349178</v>
       </c>
       <c r="J9" t="n">
-        <v>0.343759</v>
+        <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001853093714661691</v>
+        <v>-0.002637683000221824</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.53752</v>
+        <v>-0.75484</v>
       </c>
       <c r="M9" t="n">
-        <v>94961752942.69308</v>
+        <v>94961729708.24278</v>
       </c>
       <c r="N9" t="n">
-        <v>94961735259.42459</v>
+        <v>94962102587.18929</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1515.29</v>
+        <v>1518.81</v>
       </c>
       <c r="F10" t="n">
-        <v>25679897777</v>
+        <v>25756147448</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1439199278</v>
+        <v>1389815932</v>
       </c>
       <c r="I10" t="n">
-        <v>1540.34</v>
+        <v>1562.57</v>
       </c>
       <c r="J10" t="n">
-        <v>1444.17</v>
+        <v>1445.89</v>
       </c>
       <c r="K10" t="n">
-        <v>-22.07724586670861</v>
+        <v>56.04</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.43604</v>
+        <v>3.7356</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16946415.7905448</v>
+        <v>16946950.1655448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,31 +1110,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.013</v>
+        <v>1.039</v>
       </c>
       <c r="F11" t="n">
-        <v>23062335218</v>
+        <v>23858934286</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>55232417</v>
+        <v>83847558</v>
       </c>
       <c r="I11" t="n">
-        <v>1.04</v>
+        <v>1.043</v>
       </c>
       <c r="J11" t="n">
-        <v>1.012</v>
+        <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.006103827815765017</v>
+        <v>0.0261228</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.59888</v>
+        <v>2.57897</v>
       </c>
       <c r="M11" t="n">
-        <v>22764228455.528</v>
+        <v>22966221270.418</v>
       </c>
       <c r="N11" t="n">
         <v>22966221270.418</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>95.36</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>21211241880</v>
+        <v>21655414643</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1293604135</v>
+        <v>1249913907</v>
       </c>
       <c r="I12" t="n">
-        <v>95.88</v>
+        <v>96.87</v>
       </c>
       <c r="J12" t="n">
-        <v>92.06</v>
+        <v>92.19</v>
       </c>
       <c r="K12" t="n">
-        <v>0.44987</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.47398</v>
+        <v>4.26103</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1205,23 +1205,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>95.98999999999999</v>
+        <v>97.72</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-21T11:21:00.000Z</t>
+          <t>2026-09-22T21:54:40.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.100752</v>
+        <v>0.100125</v>
       </c>
       <c r="F13" t="n">
-        <v>15718592446</v>
+        <v>15635492125</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>3160716957</v>
+        <v>2382661626</v>
       </c>
       <c r="I13" t="n">
         <v>0.105575</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09251</v>
+        <v>0.097356</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00726657</v>
+        <v>0.00082386</v>
       </c>
       <c r="L13" t="n">
-        <v>7.77292</v>
+        <v>0.82324</v>
       </c>
       <c r="M13" t="n">
-        <v>156021246383.7052</v>
+        <v>156025536383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171733843126.5791</v>
+        <v>171737883126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>572.97</v>
+        <v>567.3</v>
       </c>
       <c r="F14" t="n">
-        <v>10785142460</v>
+        <v>10671971138</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>183437802</v>
+        <v>163415960</v>
       </c>
       <c r="I14" t="n">
         <v>601.01</v>
       </c>
       <c r="J14" t="n">
-        <v>552.66</v>
+        <v>561.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.374429859507018</v>
+        <v>-29.0335298218157</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4127</v>
+        <v>-4.86632</v>
       </c>
       <c r="M14" t="n">
-        <v>18808007.51155922</v>
+        <v>18808120.908502</v>
       </c>
       <c r="N14" t="n">
-        <v>18808040.5111969</v>
+        <v>18808149.70786505</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.66</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10299673248</v>
+        <v>10304856260</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>176791671</v>
+        <v>148065627</v>
       </c>
       <c r="I15" t="n">
-        <v>87.91</v>
+        <v>87.28</v>
       </c>
       <c r="J15" t="n">
         <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.492012</v>
+        <v>-0.4387106662780695</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57098</v>
+        <v>-0.49605</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.06</v>
+        <v>12.91</v>
       </c>
       <c r="F16" t="n">
-        <v>9773544357</v>
+        <v>9671530693</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>684922983</v>
+        <v>581165005</v>
       </c>
       <c r="I16" t="n">
         <v>13.26</v>
       </c>
       <c r="J16" t="n">
-        <v>12.76</v>
+        <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>0.009376229999999999</v>
+        <v>-0.2186754109027937</v>
       </c>
       <c r="L16" t="n">
-        <v>0.07183</v>
+        <v>-1.64853</v>
       </c>
       <c r="M16" t="n">
         <v>748099970.424884</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9998939999999999</v>
+        <v>0.999922</v>
       </c>
       <c r="F17" t="n">
-        <v>9583360912</v>
+        <v>9592786193</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>238853572</v>
+        <v>247011578</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1518,16 +1518,16 @@
         <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>7.478999999999999e-05</v>
+        <v>-5.5729221229095e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>0.00748</v>
+        <v>-0.00507</v>
       </c>
       <c r="M17" t="n">
-        <v>9583873777.059114</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="N17" t="n">
-        <v>9576750341.247417</v>
+        <v>9593648553.437454</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,144 +1539,144 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.01348809</v>
+        <v>0.251416</v>
       </c>
       <c r="F18" t="n">
-        <v>9559476072</v>
+        <v>9443905073</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>17859980</v>
+        <v>878661987</v>
       </c>
       <c r="I18" t="n">
-        <v>0.01420135</v>
+        <v>0.253817</v>
       </c>
       <c r="J18" t="n">
-        <v>0.01343954</v>
+        <v>0.240769</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.000638838496365042</v>
+        <v>0.00659619</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.52213</v>
+        <v>2.72814</v>
       </c>
       <c r="M18" t="n">
-        <v>709239700254.0453</v>
+        <v>37529061988.53558</v>
       </c>
       <c r="N18" t="n">
-        <v>1142408526965.963</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01946402</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.252441</v>
+        <v>0.01309167</v>
       </c>
       <c r="F19" t="n">
-        <v>9470964968</v>
+        <v>9284605249</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>838000406</v>
+        <v>24775479</v>
       </c>
       <c r="I19" t="n">
-        <v>0.251521</v>
+        <v>0.01400767</v>
       </c>
       <c r="J19" t="n">
-        <v>0.240416</v>
+        <v>0.0130726</v>
       </c>
       <c r="K19" t="n">
-        <v>0.007827020000000001</v>
+        <v>-0.000864517740068033</v>
       </c>
       <c r="L19" t="n">
-        <v>3.19974</v>
+        <v>-6.27118</v>
       </c>
       <c r="M19" t="n">
-        <v>37529061988.53558</v>
+        <v>709239749032.6418</v>
       </c>
       <c r="N19" t="n">
-        <v>45000000000</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O19" t="n">
-        <v>3.09</v>
+        <v>0.01946402</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8251314793</v>
+        <v>8260445947</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>157365</v>
+        <v>127098</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.779999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.01618964306871185</v>
+        <v>0.02568804</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.18016</v>
+        <v>0.28873</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T135928Z-22f6ba</t>
+          <t>20260922T215956Z-37a324</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.214975</v>
+        <v>0.215138</v>
       </c>
       <c r="F21" t="n">
-        <v>7505565898</v>
+        <v>7524022577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>450679611</v>
+        <v>382146995</v>
       </c>
       <c r="I21" t="n">
         <v>0.219762</v>
       </c>
       <c r="J21" t="n">
-        <v>0.206236</v>
+        <v>0.209091</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00500717</v>
+        <v>-0.001449679238016699</v>
       </c>
       <c r="L21" t="n">
-        <v>2.38473</v>
+        <v>-0.76252</v>
       </c>
       <c r="M21" t="n">
-        <v>34931879410.76893</v>
+        <v>34931895481.5965</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-22T13:56:10.000Z</t>
+          <t>2026-09-22T21:57:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86238</v>
+        <v>86091</v>
       </c>
       <c r="F2" t="n">
-        <v>1732793991467</v>
+        <v>1729404845826</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>43485131868</v>
+        <v>43292611645</v>
       </c>
       <c r="I2" t="n">
-        <v>86722</v>
+        <v>86669</v>
       </c>
       <c r="J2" t="n">
         <v>85107</v>
       </c>
       <c r="K2" t="n">
-        <v>-377.4880582667683</v>
+        <v>-493.3569849451887</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.42991</v>
+        <v>-0.5698</v>
       </c>
       <c r="M2" t="n">
         <v>20088034</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2748.95</v>
+        <v>2740.68</v>
       </c>
       <c r="F3" t="n">
-        <v>335700394407</v>
+        <v>334532231831</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16208315503</v>
+        <v>16217849740</v>
       </c>
       <c r="I3" t="n">
         <v>2786.01</v>
@@ -608,10 +608,10 @@
         <v>2716.11</v>
       </c>
       <c r="K3" t="n">
-        <v>-21.36690103358978</v>
+        <v>-33.60544003023369</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.75097</v>
+        <v>-1.21132</v>
       </c>
       <c r="M3" t="n">
         <v>122070499.1930826</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999898</v>
+        <v>0.999907</v>
       </c>
       <c r="F4" t="n">
-        <v>183363689877</v>
+        <v>183365485085</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>78958984976</v>
+        <v>78653569988</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
@@ -673,10 +673,10 @@
         <v>0.999627</v>
       </c>
       <c r="K4" t="n">
-        <v>6.751e-05</v>
+        <v>0.00010509</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00721</v>
+        <v>0.01051</v>
       </c>
       <c r="M4" t="n">
         <v>183384649781.6938</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,31 +720,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>784.49</v>
+        <v>783.59</v>
       </c>
       <c r="F5" t="n">
-        <v>104509508003</v>
+        <v>104365737195</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1338733134</v>
+        <v>1332694189</v>
       </c>
       <c r="I5" t="n">
-        <v>806.75</v>
+        <v>803.09</v>
       </c>
       <c r="J5" t="n">
         <v>781.83</v>
       </c>
       <c r="K5" t="n">
-        <v>-20.06454466473849</v>
+        <v>-21.77282668240503</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.48689</v>
+        <v>-2.70348</v>
       </c>
       <c r="M5" t="n">
-        <v>133160045.24</v>
+        <v>133160043.94</v>
       </c>
       <c r="N5" t="n">
         <v>133160043.94</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="F6" t="n">
-        <v>98935861541</v>
+        <v>97984064776</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6013941970</v>
+        <v>6102739669</v>
       </c>
       <c r="I6" t="n">
         <v>1.61</v>
@@ -803,10 +803,10 @@
         <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02050936</v>
+        <v>-0.003611992187942059</v>
       </c>
       <c r="L6" t="n">
-        <v>1.26594</v>
+        <v>-0.23129</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999892</v>
+        <v>0.999896</v>
       </c>
       <c r="F7" t="n">
-        <v>75082614224</v>
+        <v>75083335862</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20211770616</v>
+        <v>20036837511</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999695</v>
+        <v>0.999744</v>
       </c>
       <c r="K7" t="n">
-        <v>8.51e-06</v>
+        <v>3.21e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00201</v>
+        <v>0.00321</v>
       </c>
       <c r="M7" t="n">
         <v>75091582641.99438</v>
       </c>
       <c r="N7" t="n">
-        <v>75091431783.64163</v>
+        <v>75118327863.70384</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.13</v>
+        <v>117.81</v>
       </c>
       <c r="F8" t="n">
-        <v>69442081520</v>
+        <v>69220864144</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4713073391</v>
+        <v>4526147359</v>
       </c>
       <c r="I8" t="n">
         <v>119.82</v>
@@ -933,13 +933,13 @@
         <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.022544647266727</v>
+        <v>-1.566908205533849</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.84705</v>
+        <v>-1.31262</v>
       </c>
       <c r="M8" t="n">
-        <v>587507395.8954812</v>
+        <v>587507355.8515188</v>
       </c>
       <c r="N8" t="n">
         <v>634531021.326126</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.34165</v>
+        <v>0.341646</v>
       </c>
       <c r="F9" t="n">
-        <v>32442198365</v>
+        <v>32445098179</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>605341752</v>
+        <v>609223370</v>
       </c>
       <c r="I9" t="n">
         <v>0.349178</v>
@@ -998,10 +998,10 @@
         <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002637683000221824</v>
+        <v>-0.002577573979136272</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.75484</v>
+        <v>-0.74881</v>
       </c>
       <c r="M9" t="n">
         <v>94961729708.24278</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1518.81</v>
+        <v>1517.69</v>
       </c>
       <c r="F10" t="n">
-        <v>25756147448</v>
+        <v>25711477168</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1389815932</v>
+        <v>1293999353</v>
       </c>
       <c r="I10" t="n">
         <v>1562.57</v>
@@ -1063,10 +1063,10 @@
         <v>1445.89</v>
       </c>
       <c r="K10" t="n">
-        <v>56.04</v>
+        <v>51.21</v>
       </c>
       <c r="L10" t="n">
-        <v>3.7356</v>
+        <v>3.49205</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1113,13 +1113,13 @@
         <v>1.039</v>
       </c>
       <c r="F11" t="n">
-        <v>23858934286</v>
+        <v>23851750157</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>83847558</v>
+        <v>84486417</v>
       </c>
       <c r="I11" t="n">
         <v>1.043</v>
@@ -1128,10 +1128,10 @@
         <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0261228</v>
+        <v>0.02578041</v>
       </c>
       <c r="L11" t="n">
-        <v>2.57897</v>
+        <v>2.54554</v>
       </c>
       <c r="M11" t="n">
         <v>22966221270.418</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>97.31999999999999</v>
+        <v>96.73</v>
       </c>
       <c r="F12" t="n">
-        <v>21655414643</v>
+        <v>21532342792</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1249913907</v>
+        <v>1239088705</v>
       </c>
       <c r="I12" t="n">
-        <v>96.87</v>
+        <v>97.72</v>
       </c>
       <c r="J12" t="n">
         <v>92.19</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="L12" t="n">
-        <v>4.26103</v>
+        <v>3.81642</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,16 +1240,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.100125</v>
+        <v>0.09957199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15635492125</v>
+        <v>15542670956</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>2382661626</v>
+        <v>2351774773</v>
       </c>
       <c r="I13" t="n">
         <v>0.105575</v>
@@ -1258,16 +1258,16 @@
         <v>0.097356</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00082386</v>
+        <v>-0.000911816708137669</v>
       </c>
       <c r="L13" t="n">
-        <v>0.82324</v>
+        <v>-0.90742</v>
       </c>
       <c r="M13" t="n">
         <v>156025536383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171737883126.579</v>
+        <v>171738483126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,16 +1305,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>567.3</v>
+        <v>565.58</v>
       </c>
       <c r="F14" t="n">
-        <v>10671971138</v>
+        <v>10647327594</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>163415960</v>
+        <v>162542598</v>
       </c>
       <c r="I14" t="n">
         <v>601.01</v>
@@ -1323,13 +1323,13 @@
         <v>561.65</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.0335298218157</v>
+        <v>-29.14801141764497</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.86632</v>
+        <v>-4.90107</v>
       </c>
       <c r="M14" t="n">
-        <v>18808120.908502</v>
+        <v>18808149.70786505</v>
       </c>
       <c r="N14" t="n">
         <v>18808149.70786505</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,16 +1370,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.68000000000001</v>
+        <v>86.51000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10304856260</v>
+        <v>10282998071</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>148065627</v>
+        <v>147623670</v>
       </c>
       <c r="I15" t="n">
         <v>87.28</v>
@@ -1388,10 +1388,10 @@
         <v>85.56999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.4387106662780695</v>
+        <v>-0.6142900680501384</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.49605</v>
+        <v>-0.70508</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,16 +1435,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.91</v>
+        <v>12.87</v>
       </c>
       <c r="F16" t="n">
-        <v>9671530693</v>
+        <v>9628433562</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>581165005</v>
+        <v>579744023</v>
       </c>
       <c r="I16" t="n">
         <v>13.26</v>
@@ -1453,10 +1453,10 @@
         <v>12.78</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2186754109027937</v>
+        <v>-0.2855421127928377</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.64853</v>
+        <v>-2.17079</v>
       </c>
       <c r="M16" t="n">
         <v>748099970.424884</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,16 +1500,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999922</v>
+        <v>0.999928</v>
       </c>
       <c r="F17" t="n">
-        <v>9592786193</v>
+        <v>9591907549</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>247011578</v>
+        <v>246657449</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1518,16 +1518,16 @@
         <v>0.999729</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.5729221229095e-05</v>
+        <v>-0.000119341335104495</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00507</v>
+        <v>-0.01193</v>
       </c>
       <c r="M17" t="n">
         <v>9593648553.437454</v>
       </c>
       <c r="N17" t="n">
-        <v>9593648553.437454</v>
+        <v>9595406974.451723</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,16 +1565,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.251416</v>
+        <v>0.250084</v>
       </c>
       <c r="F18" t="n">
-        <v>9443905073</v>
+        <v>9387066598</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>878661987</v>
+        <v>878118215</v>
       </c>
       <c r="I18" t="n">
         <v>0.253817</v>
@@ -1583,10 +1583,10 @@
         <v>0.240769</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00659619</v>
+        <v>0.00426462</v>
       </c>
       <c r="L18" t="n">
-        <v>2.72814</v>
+        <v>1.73486</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01309167</v>
+        <v>0.01306924</v>
       </c>
       <c r="F19" t="n">
-        <v>9284605249</v>
+        <v>9265634480</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24775479</v>
+        <v>24665700</v>
       </c>
       <c r="I19" t="n">
         <v>0.01400767</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0130726</v>
+        <v>0.0130548</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000864517740068033</v>
+        <v>-0.000895503351973326</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.27118</v>
+        <v>-6.4126</v>
       </c>
       <c r="M19" t="n">
-        <v>709239749032.6418</v>
+        <v>709239749688.8101</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1698,13 +1698,13 @@
         <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8260445947</v>
+        <v>8256209354</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>127098</v>
+        <v>122371</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
@@ -1713,10 +1713,10 @@
         <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02568804</v>
+        <v>0.02214698</v>
       </c>
       <c r="L20" t="n">
-        <v>0.28873</v>
+        <v>0.24736</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T215956Z-37a324</t>
+          <t>20260922T221307Z-199638</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.215138</v>
+        <v>0.213671</v>
       </c>
       <c r="F21" t="n">
-        <v>7524022577</v>
+        <v>7466217685</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>382146995</v>
+        <v>374469403</v>
       </c>
       <c r="I21" t="n">
-        <v>0.219762</v>
+        <v>0.218266</v>
       </c>
       <c r="J21" t="n">
         <v>0.209091</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001449679238016699</v>
+        <v>-0.004282575427316249</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.76252</v>
+        <v>-1.9649</v>
       </c>
       <c r="M21" t="n">
-        <v>34931895481.5965</v>
+        <v>34932729791.51797</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-22T21:57:10.000Z</t>
+          <t>2026-09-22T22:10:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86091</v>
+        <v>85660</v>
       </c>
       <c r="F2" t="n">
-        <v>1729404845826</v>
+        <v>1720796656545</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>43292611645</v>
+        <v>40475457238</v>
       </c>
       <c r="I2" t="n">
-        <v>86669</v>
+        <v>87251</v>
       </c>
       <c r="J2" t="n">
-        <v>85107</v>
+        <v>85266</v>
       </c>
       <c r="K2" t="n">
-        <v>-493.3569849451887</v>
+        <v>-433.6906185361877</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.5698</v>
+        <v>-0.50375</v>
       </c>
       <c r="M2" t="n">
-        <v>20088034</v>
+        <v>20088325</v>
       </c>
       <c r="N2" t="n">
-        <v>20088056</v>
+        <v>20088325</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2740.68</v>
+        <v>2713.74</v>
       </c>
       <c r="F3" t="n">
-        <v>334532231831</v>
+        <v>331259670445</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16217849740</v>
+        <v>16541219556</v>
       </c>
       <c r="I3" t="n">
-        <v>2786.01</v>
+        <v>2786.6</v>
       </c>
       <c r="J3" t="n">
-        <v>2716.11</v>
+        <v>2714.35</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.60544003023369</v>
+        <v>-38.06506006067275</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.21132</v>
+        <v>-1.38328</v>
       </c>
       <c r="M3" t="n">
-        <v>122070499.1930826</v>
+        <v>122073393.4861459</v>
       </c>
       <c r="N3" t="n">
-        <v>122070499.1930825</v>
+        <v>122073393.4861459</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999907</v>
+        <v>0.9997239999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183365485085</v>
+        <v>183423662761</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>78653569988</v>
+        <v>77641044569</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999627</v>
+        <v>0.9996159999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00010509</v>
+        <v>-1.3375693649009e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01051</v>
+        <v>-0.00134</v>
       </c>
       <c r="M4" t="n">
-        <v>183384649781.6938</v>
+        <v>183470116796.0007</v>
       </c>
       <c r="N4" t="n">
-        <v>188851595759.0362</v>
+        <v>188937062885.4362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>783.59</v>
+        <v>780.89</v>
       </c>
       <c r="F5" t="n">
-        <v>104365737195</v>
+        <v>103989325404</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1332694189</v>
+        <v>1153867414</v>
       </c>
       <c r="I5" t="n">
-        <v>803.09</v>
+        <v>798.34</v>
       </c>
       <c r="J5" t="n">
-        <v>781.83</v>
+        <v>777.16</v>
       </c>
       <c r="K5" t="n">
-        <v>-21.77282668240503</v>
+        <v>-8.973599075082916</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.70348</v>
+        <v>-1.1361</v>
       </c>
       <c r="M5" t="n">
-        <v>133160043.94</v>
+        <v>133159986.57</v>
       </c>
       <c r="N5" t="n">
-        <v>133160043.94</v>
+        <v>133159986.57</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="F6" t="n">
-        <v>97984064776</v>
+        <v>98975003054</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6102739669</v>
+        <v>6721150870</v>
       </c>
       <c r="I6" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003611992187942059</v>
+        <v>0.00486281</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.23129</v>
+        <v>0.30987</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999896</v>
+        <v>0.9998</v>
       </c>
       <c r="F7" t="n">
-        <v>75083335862</v>
+        <v>75112332603</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20036837511</v>
+        <v>20985936797</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999744</v>
+        <v>0.999641</v>
       </c>
       <c r="K7" t="n">
-        <v>3.21e-05</v>
+        <v>-2.9422490854358e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00321</v>
+        <v>-0.00294</v>
       </c>
       <c r="M7" t="n">
-        <v>75091582641.99438</v>
+        <v>75125433963.32286</v>
       </c>
       <c r="N7" t="n">
-        <v>75118327863.70384</v>
+        <v>75154585345.82596</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>117.81</v>
+        <v>116.72</v>
       </c>
       <c r="F8" t="n">
-        <v>69220864144</v>
+        <v>68558658494</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4526147359</v>
+        <v>4497356714</v>
       </c>
       <c r="I8" t="n">
-        <v>119.82</v>
+        <v>119.66</v>
       </c>
       <c r="J8" t="n">
-        <v>115.58</v>
+        <v>116.08</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.566908205533849</v>
+        <v>-0.8052274963640826</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.31262</v>
+        <v>-0.68515</v>
       </c>
       <c r="M8" t="n">
-        <v>587507355.8515188</v>
+        <v>587506755.615492</v>
       </c>
       <c r="N8" t="n">
-        <v>634531021.326126</v>
+        <v>634530393.8774225</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.341646</v>
+        <v>0.34171</v>
       </c>
       <c r="F9" t="n">
-        <v>32445098179</v>
+        <v>32452956079</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>609223370</v>
+        <v>464108235</v>
       </c>
       <c r="I9" t="n">
-        <v>0.349178</v>
+        <v>0.345004</v>
       </c>
       <c r="J9" t="n">
         <v>0.34041</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002577573979136272</v>
+        <v>-0.001158784293061932</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.74881</v>
+        <v>-0.33797</v>
       </c>
       <c r="M9" t="n">
         <v>94961729708.24278</v>
       </c>
       <c r="N9" t="n">
-        <v>94962102587.18929</v>
+        <v>94963358525.63339</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1517.69</v>
+        <v>1634.87</v>
       </c>
       <c r="F10" t="n">
-        <v>25711477168</v>
+        <v>27693853314</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1293999353</v>
+        <v>2062081097</v>
       </c>
       <c r="I10" t="n">
-        <v>1562.57</v>
+        <v>1658.86</v>
       </c>
       <c r="J10" t="n">
-        <v>1445.89</v>
+        <v>1501.2</v>
       </c>
       <c r="K10" t="n">
-        <v>51.21</v>
+        <v>119.98</v>
       </c>
       <c r="L10" t="n">
-        <v>3.49205</v>
+        <v>7.92037</v>
       </c>
       <c r="M10" t="n">
         <v>16945106.4155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16946950.1655448</v>
+        <v>16948106.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.039</v>
+        <v>1.031</v>
       </c>
       <c r="F11" t="n">
-        <v>23851750157</v>
+        <v>23674581041</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>84486417</v>
+        <v>189366594</v>
       </c>
       <c r="I11" t="n">
         <v>1.043</v>
@@ -1128,10 +1128,10 @@
         <v>1.006</v>
       </c>
       <c r="K11" t="n">
-        <v>0.02578041</v>
+        <v>0.01784585</v>
       </c>
       <c r="L11" t="n">
-        <v>2.54554</v>
+        <v>1.76152</v>
       </c>
       <c r="M11" t="n">
         <v>22966221270.418</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>96.73</v>
+        <v>95.42</v>
       </c>
       <c r="F12" t="n">
-        <v>21532342792</v>
+        <v>21227739049</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1239088705</v>
+        <v>1156045775</v>
       </c>
       <c r="I12" t="n">
-        <v>97.72</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>92.19</v>
+        <v>93.83</v>
       </c>
       <c r="K12" t="n">
-        <v>3.56</v>
+        <v>0.102821</v>
       </c>
       <c r="L12" t="n">
-        <v>3.81642</v>
+        <v>0.10787</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1205,23 +1205,23 @@
         <v>955307079.4341414</v>
       </c>
       <c r="O12" t="n">
-        <v>97.72</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-22T21:54:40.000Z</t>
+          <t>2026-09-23T05:16:50.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09957199999999999</v>
+        <v>0.09939099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>15542670956</v>
+        <v>15510961595</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>2351774773</v>
+        <v>1716316067</v>
       </c>
       <c r="I13" t="n">
-        <v>0.105575</v>
+        <v>0.104229</v>
       </c>
       <c r="J13" t="n">
-        <v>0.097356</v>
+        <v>0.098667</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000911816708137669</v>
+        <v>-0.001316097675634703</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.90742</v>
+        <v>-1.30685</v>
       </c>
       <c r="M13" t="n">
-        <v>156025536383.7052</v>
+        <v>156034686383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171738483126.579</v>
+        <v>156034696383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>565.58</v>
+        <v>563.9299999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10647327594</v>
+        <v>10598490531</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>162542598</v>
+        <v>147373493</v>
       </c>
       <c r="I14" t="n">
-        <v>601.01</v>
+        <v>577.02</v>
       </c>
       <c r="J14" t="n">
-        <v>561.65</v>
+        <v>555.9400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-29.14801141764497</v>
+        <v>-10.32139536398063</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.90107</v>
+        <v>-1.79737</v>
       </c>
       <c r="M14" t="n">
-        <v>18808149.70786505</v>
+        <v>18808405.30238605</v>
       </c>
       <c r="N14" t="n">
-        <v>18808149.70786505</v>
+        <v>18808438.90178666</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>86.51000000000001</v>
+        <v>85.92</v>
       </c>
       <c r="F15" t="n">
-        <v>10282998071</v>
+        <v>10212986508</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>147623670</v>
+        <v>120844109</v>
       </c>
       <c r="I15" t="n">
-        <v>87.28</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>85.56999999999999</v>
+        <v>85.67</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6142900680501384</v>
+        <v>-0.6889404075766237</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.70508</v>
+        <v>-0.7954599999999999</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1409,144 +1409,144 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.87</v>
+        <v>0.999889</v>
       </c>
       <c r="F16" t="n">
-        <v>9628433562</v>
+        <v>9604357137</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>579744023</v>
+        <v>213968809</v>
       </c>
       <c r="I16" t="n">
-        <v>13.26</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>12.78</v>
+        <v>0.999631</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2855421127928377</v>
+        <v>-5.6344570002698e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.17079</v>
+        <v>-0.00563</v>
       </c>
       <c r="M16" t="n">
-        <v>748099970.424884</v>
+        <v>9604704100.806463</v>
       </c>
       <c r="N16" t="n">
-        <v>1000000000</v>
+        <v>9607472753.612017</v>
       </c>
       <c r="O16" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999928</v>
+        <v>12.67</v>
       </c>
       <c r="F17" t="n">
-        <v>9591907549</v>
+        <v>9479889414</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>246657449</v>
+        <v>562753051</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>13.21</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999729</v>
+        <v>12.68</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000119341335104495</v>
+        <v>-0.3822432461842418</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01193</v>
+        <v>-2.92782</v>
       </c>
       <c r="M17" t="n">
-        <v>9593648553.437454</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>9595406974.451723</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>1.057</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.250084</v>
+        <v>0.248372</v>
       </c>
       <c r="F18" t="n">
-        <v>9387066598</v>
+        <v>9320073154</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>878118215</v>
+        <v>864974645</v>
       </c>
       <c r="I18" t="n">
-        <v>0.253817</v>
+        <v>0.261886</v>
       </c>
       <c r="J18" t="n">
-        <v>0.240769</v>
+        <v>0.246132</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00426462</v>
+        <v>-0.004014587718880164</v>
       </c>
       <c r="L18" t="n">
-        <v>1.73486</v>
+        <v>-1.59065</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01306924</v>
+        <v>0.01268255</v>
       </c>
       <c r="F19" t="n">
-        <v>9265634480</v>
+        <v>8997710190</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24665700</v>
+        <v>25047308</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01400767</v>
+        <v>0.01348598</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0130548</v>
+        <v>0.01270828</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000895503351973326</v>
+        <v>-0.000786568705675847</v>
       </c>
       <c r="L19" t="n">
-        <v>-6.4126</v>
+        <v>-5.8398</v>
       </c>
       <c r="M19" t="n">
-        <v>709239749688.8101</v>
+        <v>709240042765.4675</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1698,25 +1698,25 @@
         <v>8.98</v>
       </c>
       <c r="F20" t="n">
-        <v>8256209354</v>
+        <v>8264196225</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>122371</v>
+        <v>174153</v>
       </c>
       <c r="I20" t="n">
         <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>0.02214698</v>
+        <v>0.01392138</v>
       </c>
       <c r="L20" t="n">
-        <v>0.24736</v>
+        <v>0.1552</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260922T221307Z-199638</t>
+          <t>20260923T135515Z-a501e2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.213671</v>
+        <v>0.212671</v>
       </c>
       <c r="F21" t="n">
-        <v>7466217685</v>
+        <v>7429479507</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>374469403</v>
+        <v>393742905</v>
       </c>
       <c r="I21" t="n">
-        <v>0.218266</v>
+        <v>0.224502</v>
       </c>
       <c r="J21" t="n">
-        <v>0.209091</v>
+        <v>0.210057</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.004282575427316249</v>
+        <v>-0.001867059350335182</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9649</v>
+        <v>-0.87027</v>
       </c>
       <c r="M21" t="n">
-        <v>34932729791.51797</v>
+        <v>34932724603.07527</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70148</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-22T22:10:10.000Z</t>
+          <t>2026-09-23T13:52:50.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85660</v>
+        <v>83978</v>
       </c>
       <c r="F2" t="n">
-        <v>1720796656545</v>
+        <v>1687012220721</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>40475457238</v>
+        <v>44006821718</v>
       </c>
       <c r="I2" t="n">
-        <v>87251</v>
+        <v>85876</v>
       </c>
       <c r="J2" t="n">
-        <v>85266</v>
+        <v>82941</v>
       </c>
       <c r="K2" t="n">
-        <v>-433.6906185361877</v>
+        <v>-1701.113919286392</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.50375</v>
+        <v>-1.97836</v>
       </c>
       <c r="M2" t="n">
-        <v>20088325</v>
+        <v>20088671</v>
       </c>
       <c r="N2" t="n">
-        <v>20088325</v>
+        <v>20088728</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2713.74</v>
+        <v>2664.09</v>
       </c>
       <c r="F3" t="n">
-        <v>331259670445</v>
+        <v>325222379231</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16541219556</v>
+        <v>16572408474</v>
       </c>
       <c r="I3" t="n">
-        <v>2786.6</v>
+        <v>2720.31</v>
       </c>
       <c r="J3" t="n">
-        <v>2714.35</v>
+        <v>2634.74</v>
       </c>
       <c r="K3" t="n">
-        <v>-38.06506006067275</v>
+        <v>-49.80841626912115</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.38328</v>
+        <v>-1.81017</v>
       </c>
       <c r="M3" t="n">
-        <v>122073393.4861459</v>
+        <v>122076229.2680794</v>
       </c>
       <c r="N3" t="n">
-        <v>122073393.4861459</v>
+        <v>122076229.2680793</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9997239999999999</v>
+        <v>0.999744</v>
       </c>
       <c r="F4" t="n">
-        <v>183423662761</v>
+        <v>183495697334</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>77641044569</v>
+        <v>77473994732</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.999937</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9996159999999999</v>
+        <v>0.999652</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.3375693649009e-05</v>
+        <v>-8.90247621177e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00134</v>
+        <v>-0.00043</v>
       </c>
       <c r="M4" t="n">
-        <v>183470116796.0007</v>
+        <v>183542716766.929</v>
       </c>
       <c r="N4" t="n">
-        <v>188937062885.4362</v>
+        <v>189009662872.4462</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>780.89</v>
+        <v>775.11</v>
       </c>
       <c r="F5" t="n">
-        <v>103989325404</v>
+        <v>103213855578</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1153867414</v>
+        <v>1197659217</v>
       </c>
       <c r="I5" t="n">
-        <v>798.34</v>
+        <v>781.95</v>
       </c>
       <c r="J5" t="n">
-        <v>777.16</v>
+        <v>758.22</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.973599075082916</v>
+        <v>-5.754073065851458</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.1361</v>
+        <v>-0.70514</v>
       </c>
       <c r="M5" t="n">
-        <v>133159986.57</v>
+        <v>133159906.26</v>
       </c>
       <c r="N5" t="n">
-        <v>133159986.57</v>
+        <v>133159906.26</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>98975003054</v>
+        <v>94214439065</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6721150870</v>
+        <v>4658671923</v>
       </c>
       <c r="I6" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00486281</v>
+        <v>-0.07669192306231665</v>
       </c>
       <c r="L6" t="n">
-        <v>0.30987</v>
+        <v>-4.8361</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9998</v>
+        <v>0.99982</v>
       </c>
       <c r="F7" t="n">
-        <v>75112332603</v>
+        <v>75208946184</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20985936797</v>
+        <v>21520943946</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999641</v>
+        <v>0.999305</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9422490854358e-05</v>
+        <v>5.7299e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00294</v>
+        <v>0.00027</v>
       </c>
       <c r="M7" t="n">
-        <v>75125433963.32286</v>
+        <v>75222489862.57661</v>
       </c>
       <c r="N7" t="n">
-        <v>75154585345.82596</v>
+        <v>75208587556.4671</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>116.72</v>
+        <v>114.78</v>
       </c>
       <c r="F8" t="n">
-        <v>68558658494</v>
+        <v>67442627183</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4497356714</v>
+        <v>4787195372</v>
       </c>
       <c r="I8" t="n">
-        <v>119.66</v>
+        <v>116.94</v>
       </c>
       <c r="J8" t="n">
-        <v>116.08</v>
+        <v>112.72</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.8052274963640826</v>
+        <v>-1.945020311639823</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.68515</v>
+        <v>-1.62052</v>
       </c>
       <c r="M8" t="n">
-        <v>587506755.615492</v>
+        <v>587577149.9029876</v>
       </c>
       <c r="N8" t="n">
-        <v>634530393.8774225</v>
+        <v>634608286.6592437</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.34171</v>
+        <v>0.339884</v>
       </c>
       <c r="F9" t="n">
-        <v>32452956079</v>
+        <v>32277074717</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>464108235</v>
+        <v>508747370</v>
       </c>
       <c r="I9" t="n">
-        <v>0.345004</v>
+        <v>0.343877</v>
       </c>
       <c r="J9" t="n">
-        <v>0.34041</v>
+        <v>0.338585</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001158784293061932</v>
+        <v>-0.001792421662365318</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.33797</v>
+        <v>-0.53525</v>
       </c>
       <c r="M9" t="n">
-        <v>94961729708.24278</v>
+        <v>94964948406.9399</v>
       </c>
       <c r="N9" t="n">
-        <v>94963358525.63339</v>
+        <v>94965004918.81999</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1634.87</v>
+        <v>1514.5</v>
       </c>
       <c r="F10" t="n">
-        <v>27693853314</v>
+        <v>25670307558</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2062081097</v>
+        <v>1530755188</v>
       </c>
       <c r="I10" t="n">
-        <v>1658.86</v>
+        <v>1638.23</v>
       </c>
       <c r="J10" t="n">
-        <v>1501.2</v>
+        <v>1461.52</v>
       </c>
       <c r="K10" t="n">
-        <v>119.98</v>
+        <v>-120.5149810899129</v>
       </c>
       <c r="L10" t="n">
-        <v>7.92037</v>
+        <v>-7.53144</v>
       </c>
       <c r="M10" t="n">
-        <v>16945106.4155448</v>
+        <v>16949703.2905448</v>
       </c>
       <c r="N10" t="n">
-        <v>16948106.4155448</v>
+        <v>16949931.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.031</v>
+        <v>1.037</v>
       </c>
       <c r="F11" t="n">
-        <v>23674581041</v>
+        <v>23885874146</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>189366594</v>
+        <v>30426403</v>
       </c>
       <c r="I11" t="n">
-        <v>1.043</v>
+        <v>1.037</v>
       </c>
       <c r="J11" t="n">
-        <v>1.006</v>
+        <v>1.022</v>
       </c>
       <c r="K11" t="n">
-        <v>0.01784585</v>
+        <v>0.00575091</v>
       </c>
       <c r="L11" t="n">
-        <v>1.76152</v>
+        <v>0.55813</v>
       </c>
       <c r="M11" t="n">
-        <v>22966221270.418</v>
+        <v>23042572971.368</v>
       </c>
       <c r="N11" t="n">
-        <v>22966221270.418</v>
+        <v>23042572971.368</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>95.42</v>
+        <v>92.52</v>
       </c>
       <c r="F12" t="n">
-        <v>21227739049</v>
+        <v>20581429395</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1156045775</v>
+        <v>1338426068</v>
       </c>
       <c r="I12" t="n">
-        <v>97.95999999999999</v>
+        <v>95.77</v>
       </c>
       <c r="J12" t="n">
-        <v>93.83</v>
+        <v>89.91</v>
       </c>
       <c r="K12" t="n">
-        <v>0.102821</v>
+        <v>-2.957293932139351</v>
       </c>
       <c r="L12" t="n">
-        <v>0.10787</v>
+        <v>-3.12298</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09939099999999999</v>
+        <v>0.093919</v>
       </c>
       <c r="F13" t="n">
-        <v>15510961595</v>
+        <v>14655932118</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1716316067</v>
+        <v>1578915177</v>
       </c>
       <c r="I13" t="n">
-        <v>0.104229</v>
+        <v>0.099772</v>
       </c>
       <c r="J13" t="n">
-        <v>0.098667</v>
+        <v>0.091664</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001316097675634703</v>
+        <v>-0.005505030732556204</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.30685</v>
+        <v>-5.47073</v>
       </c>
       <c r="M13" t="n">
-        <v>156034686383.7052</v>
+        <v>156048806383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>156034696383.7052</v>
+        <v>156048456383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>563.9299999999999</v>
+        <v>549.51</v>
       </c>
       <c r="F14" t="n">
-        <v>10598490531</v>
+        <v>10335646084</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>147373493</v>
+        <v>131877115</v>
       </c>
       <c r="I14" t="n">
-        <v>577.02</v>
+        <v>566.0700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>555.9400000000001</v>
+        <v>542.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-10.32139536398063</v>
+        <v>-13.80552932081468</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.79737</v>
+        <v>-2.47342</v>
       </c>
       <c r="M14" t="n">
-        <v>18808405.30238605</v>
+        <v>18808857.69615291</v>
       </c>
       <c r="N14" t="n">
-        <v>18808438.90178666</v>
+        <v>18808888.29599696</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,28 +1370,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>85.92</v>
+        <v>83.98999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10212986508</v>
+        <v>9982633074</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120844109</v>
+        <v>140612680</v>
       </c>
       <c r="I15" t="n">
-        <v>87.68000000000001</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>85.67</v>
+        <v>82.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.6889404075766237</v>
+        <v>-1.943211609221805</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.7954599999999999</v>
+        <v>-2.22567</v>
       </c>
       <c r="M15" t="n">
         <v>118852171</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999889</v>
+        <v>0.999883</v>
       </c>
       <c r="F16" t="n">
-        <v>9604357137</v>
+        <v>9686691626</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>213968809</v>
+        <v>141654011</v>
       </c>
       <c r="I16" t="n">
         <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999631</v>
+        <v>0.999647</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.6344570002698e-05</v>
+        <v>-2.8205541120485e-05</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.00563</v>
+        <v>-0.009090000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>9604704100.806463</v>
+        <v>9687827058.865</v>
       </c>
       <c r="N16" t="n">
-        <v>9607472753.612017</v>
+        <v>9697547815.27993</v>
       </c>
       <c r="O16" t="n">
         <v>1.057</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.67</v>
+        <v>12.46</v>
       </c>
       <c r="F17" t="n">
-        <v>9479889414</v>
+        <v>9317677595</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>562753051</v>
+        <v>522257174</v>
       </c>
       <c r="I17" t="n">
-        <v>13.21</v>
+        <v>12.75</v>
       </c>
       <c r="J17" t="n">
-        <v>12.68</v>
+        <v>12.1</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3822432461842418</v>
+        <v>-0.2108202456293533</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.92782</v>
+        <v>-1.59865</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.248372</v>
+        <v>0.240627</v>
       </c>
       <c r="F18" t="n">
-        <v>9320073154</v>
+        <v>9030496797</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>864974645</v>
+        <v>592604878</v>
       </c>
       <c r="I18" t="n">
-        <v>0.261886</v>
+        <v>0.249431</v>
       </c>
       <c r="J18" t="n">
-        <v>0.246132</v>
+        <v>0.233288</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.004014587718880164</v>
+        <v>-0.007681261816755242</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.59065</v>
+        <v>-3.03354</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01268255</v>
+        <v>0.01204162</v>
       </c>
       <c r="F19" t="n">
-        <v>8997710190</v>
+        <v>8540399072</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>25047308</v>
+        <v>19988680</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01348598</v>
+        <v>0.01271105</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01270828</v>
+        <v>0.01195719</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000786568705675847</v>
+        <v>-0.0006301626399832819</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.8398</v>
+        <v>-5.2628</v>
       </c>
       <c r="M19" t="n">
-        <v>709240042765.4675</v>
+        <v>709240298301.3969</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.98</v>
+        <v>8.9</v>
       </c>
       <c r="F20" t="n">
-        <v>8264196225</v>
+        <v>8187966753</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>174153</v>
+        <v>399230</v>
       </c>
       <c r="I20" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>8.949999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01392138</v>
+        <v>-0.08439936080502441</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1552</v>
+        <v>-0.93935</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260923T135515Z-a501e2</t>
+          <t>20260924T135205Z-d42d69</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.212671</v>
+        <v>0.20324</v>
       </c>
       <c r="F21" t="n">
-        <v>7429479507</v>
+        <v>7100935549</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>393742905</v>
+        <v>321290636</v>
       </c>
       <c r="I21" t="n">
-        <v>0.224502</v>
+        <v>0.213122</v>
       </c>
       <c r="J21" t="n">
-        <v>0.210057</v>
+        <v>0.197178</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001867059350335182</v>
+        <v>-0.009336099321796909</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.87027</v>
+        <v>-4.38715</v>
       </c>
       <c r="M21" t="n">
-        <v>34932724603.07527</v>
+        <v>34938629825.38779</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70148</v>
+        <v>50001786839.70147</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-23T13:52:50.000Z</t>
+          <t>2026-09-24T13:48:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83978</v>
+        <v>83598</v>
       </c>
       <c r="F2" t="n">
-        <v>1687012220721</v>
+        <v>1679162755062</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>44006821718</v>
+        <v>38514548082</v>
       </c>
       <c r="I2" t="n">
-        <v>85876</v>
+        <v>85208</v>
       </c>
       <c r="J2" t="n">
-        <v>82941</v>
+        <v>83513</v>
       </c>
       <c r="K2" t="n">
-        <v>-1701.113919286392</v>
+        <v>-604.7274447487289</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.97836</v>
+        <v>-0.77851</v>
       </c>
       <c r="M2" t="n">
-        <v>20088671</v>
+        <v>20089181</v>
       </c>
       <c r="N2" t="n">
-        <v>20088728</v>
+        <v>20089196</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2664.09</v>
+        <v>2688.92</v>
       </c>
       <c r="F3" t="n">
-        <v>325222379231</v>
+        <v>328251353932</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16572408474</v>
+        <v>15862968693</v>
       </c>
       <c r="I3" t="n">
-        <v>2720.31</v>
+        <v>2739.52</v>
       </c>
       <c r="J3" t="n">
-        <v>2634.74</v>
+        <v>2653.81</v>
       </c>
       <c r="K3" t="n">
-        <v>-49.80841626912115</v>
+        <v>21.97</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.81017</v>
+        <v>0.79044</v>
       </c>
       <c r="M3" t="n">
-        <v>122076229.2680794</v>
+        <v>122078905.3531288</v>
       </c>
       <c r="N3" t="n">
-        <v>122076229.2680793</v>
+        <v>122078905.3531288</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999744</v>
+        <v>0.99973</v>
       </c>
       <c r="F4" t="n">
-        <v>183495697334</v>
+        <v>183727460118</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>77473994732</v>
+        <v>72786037039</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999937</v>
+        <v>0.9998899999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999652</v>
+        <v>0.999287</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.90247621177e-07</v>
+        <v>6.05e-06</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00043</v>
+        <v>0.00347</v>
       </c>
       <c r="M4" t="n">
-        <v>183542716766.929</v>
+        <v>183779015975.4778</v>
       </c>
       <c r="N4" t="n">
-        <v>189009662872.4462</v>
+        <v>189245961986.9062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>775.11</v>
+        <v>772.7</v>
       </c>
       <c r="F5" t="n">
-        <v>103213855578</v>
+        <v>102856673958</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1197659217</v>
+        <v>1165366190</v>
       </c>
       <c r="I5" t="n">
-        <v>781.95</v>
+        <v>785.3099999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>758.22</v>
+        <v>770.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-5.754073065851458</v>
+        <v>-4.873413513556216</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.70514</v>
+        <v>-0.62303</v>
       </c>
       <c r="M5" t="n">
-        <v>133159906.26</v>
+        <v>133159842.41</v>
       </c>
       <c r="N5" t="n">
-        <v>133159906.26</v>
+        <v>133159833.97</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="F6" t="n">
-        <v>94214439065</v>
+        <v>99229873529</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4658671923</v>
+        <v>6282193834</v>
       </c>
       <c r="I6" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="J6" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07669192306231665</v>
+        <v>0.07800700000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.8361</v>
+        <v>5.11372</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99982</v>
+        <v>0.999853</v>
       </c>
       <c r="F7" t="n">
-        <v>75208946184</v>
+        <v>75342386451</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>21520943946</v>
+        <v>20818639756</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999305</v>
+        <v>0.99942</v>
       </c>
       <c r="K7" t="n">
-        <v>5.7299e-07</v>
+        <v>3.113e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00027</v>
+        <v>0.00606</v>
       </c>
       <c r="M7" t="n">
-        <v>75222489862.57661</v>
+        <v>75354142543.02426</v>
       </c>
       <c r="N7" t="n">
-        <v>75208587556.4671</v>
+        <v>75302398987.78542</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>114.78</v>
+        <v>119.58</v>
       </c>
       <c r="F8" t="n">
-        <v>67442627183</v>
+        <v>70220425043</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4787195372</v>
+        <v>5871439186</v>
       </c>
       <c r="I8" t="n">
-        <v>116.94</v>
+        <v>122.01</v>
       </c>
       <c r="J8" t="n">
-        <v>112.72</v>
+        <v>114.46</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.945020311639823</v>
+        <v>4.61</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.62052</v>
+        <v>4.02766</v>
       </c>
       <c r="M8" t="n">
-        <v>587577149.9029876</v>
+        <v>587647593.3659807</v>
       </c>
       <c r="N8" t="n">
-        <v>634608286.6592437</v>
+        <v>634686100.9544628</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.339884</v>
+        <v>0.337211</v>
       </c>
       <c r="F9" t="n">
-        <v>32277074717</v>
+        <v>32018650054</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>508747370</v>
+        <v>461988718</v>
       </c>
       <c r="I9" t="n">
-        <v>0.343877</v>
+        <v>0.341481</v>
       </c>
       <c r="J9" t="n">
-        <v>0.338585</v>
+        <v>0.336802</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001792421662365318</v>
+        <v>-0.002870799508586985</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.53525</v>
+        <v>-0.8316</v>
       </c>
       <c r="M9" t="n">
         <v>94964948406.9399</v>
       </c>
       <c r="N9" t="n">
-        <v>94965004918.81999</v>
+        <v>94966809744.41438</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1514.5</v>
+        <v>1593.72</v>
       </c>
       <c r="F10" t="n">
-        <v>25670307558</v>
+        <v>27023589668</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1530755188</v>
+        <v>1279929296</v>
       </c>
       <c r="I10" t="n">
-        <v>1638.23</v>
+        <v>1622.95</v>
       </c>
       <c r="J10" t="n">
-        <v>1461.52</v>
+        <v>1491.28</v>
       </c>
       <c r="K10" t="n">
-        <v>-120.5149810899129</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-7.53144</v>
+        <v>5.35021</v>
       </c>
       <c r="M10" t="n">
-        <v>16949703.2905448</v>
+        <v>16951193.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16949931.4155448</v>
+        <v>16951806.4155448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.037</v>
+        <v>1.027</v>
       </c>
       <c r="F11" t="n">
-        <v>23885874146</v>
+        <v>23712065535</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>30426403</v>
+        <v>585257867</v>
       </c>
       <c r="I11" t="n">
-        <v>1.037</v>
+        <v>1.047</v>
       </c>
       <c r="J11" t="n">
-        <v>1.022</v>
+        <v>1.012</v>
       </c>
       <c r="K11" t="n">
-        <v>0.00575091</v>
+        <v>-0.009244703155131262</v>
       </c>
       <c r="L11" t="n">
-        <v>0.55813</v>
+        <v>-0.89492</v>
       </c>
       <c r="M11" t="n">
-        <v>23042572971.368</v>
+        <v>23089131934.788</v>
       </c>
       <c r="N11" t="n">
-        <v>23042572971.368</v>
+        <v>23089131934.788</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.52</v>
+        <v>92.18000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>20581429395</v>
+        <v>20488667956</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1338426068</v>
+        <v>1155605568</v>
       </c>
       <c r="I12" t="n">
-        <v>95.77</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.91</v>
+        <v>91</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.957293932139351</v>
+        <v>-0.1386147680552199</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.12298</v>
+        <v>-0.12922</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.093919</v>
+        <v>0.097402</v>
       </c>
       <c r="F13" t="n">
-        <v>14655932118</v>
+        <v>15194781531</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1578915177</v>
+        <v>1266625089</v>
       </c>
       <c r="I13" t="n">
-        <v>0.099772</v>
+        <v>0.098981</v>
       </c>
       <c r="J13" t="n">
-        <v>0.091664</v>
+        <v>0.094092</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.005505030732556204</v>
+        <v>0.00300281</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.47073</v>
+        <v>3.13939</v>
       </c>
       <c r="M13" t="n">
-        <v>156048806383.7053</v>
+        <v>156060896383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156048456383.7052</v>
+        <v>171774773126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,274 +1279,274 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>549.51</v>
+        <v>13.87</v>
       </c>
       <c r="F14" t="n">
-        <v>10335646084</v>
+        <v>10373383774</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131877115</v>
+        <v>1063141253</v>
       </c>
       <c r="I14" t="n">
-        <v>566.0700000000001</v>
+        <v>14.19</v>
       </c>
       <c r="J14" t="n">
-        <v>542.46</v>
+        <v>12.46</v>
       </c>
       <c r="K14" t="n">
-        <v>-13.80552932081468</v>
+        <v>1.34</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.47342</v>
+        <v>10.71284</v>
       </c>
       <c r="M14" t="n">
-        <v>18808857.69615291</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N14" t="n">
-        <v>18808888.29599696</v>
+        <v>1000000000</v>
       </c>
       <c r="O14" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>83.98999999999999</v>
+        <v>549.15</v>
       </c>
       <c r="F15" t="n">
-        <v>9982633074</v>
+        <v>10313844161</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>140612680</v>
+        <v>144904867</v>
       </c>
       <c r="I15" t="n">
-        <v>86.09999999999999</v>
+        <v>577.46</v>
       </c>
       <c r="J15" t="n">
-        <v>82.98</v>
+        <v>545.25</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.943211609221805</v>
+        <v>-1.992583697525561</v>
       </c>
       <c r="L15" t="n">
-        <v>-2.22567</v>
+        <v>-0.38245</v>
       </c>
       <c r="M15" t="n">
-        <v>118852171</v>
+        <v>18809274.09052855</v>
       </c>
       <c r="N15" t="n">
-        <v>293421670</v>
+        <v>18809314.29046824</v>
       </c>
       <c r="O15" t="n">
-        <v>87.91</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.999883</v>
+        <v>83.58</v>
       </c>
       <c r="F16" t="n">
-        <v>9686691626</v>
+        <v>9932139589</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>141654011</v>
+        <v>128664165</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>85.16</v>
       </c>
       <c r="J16" t="n">
-        <v>0.999647</v>
+        <v>83.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.8205541120485e-05</v>
+        <v>-0.5541301889751509</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.009090000000000001</v>
+        <v>-0.86936</v>
       </c>
       <c r="M16" t="n">
-        <v>9687827058.865</v>
+        <v>118852171</v>
       </c>
       <c r="N16" t="n">
-        <v>9697547815.27993</v>
+        <v>293421670</v>
       </c>
       <c r="O16" t="n">
-        <v>1.057</v>
+        <v>87.91</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.46</v>
+        <v>0.99963</v>
       </c>
       <c r="F17" t="n">
-        <v>9317677595</v>
+        <v>9719421143</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>522257174</v>
+        <v>125292033</v>
       </c>
       <c r="I17" t="n">
-        <v>12.75</v>
+        <v>0.99998</v>
       </c>
       <c r="J17" t="n">
-        <v>12.1</v>
+        <v>0.9994</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2108202456293533</v>
+        <v>-0.000183372176973173</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.59865</v>
+        <v>-0.01564</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>9723114647.376017</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>9723685294.041584</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.240627</v>
+        <v>0.253462</v>
       </c>
       <c r="F18" t="n">
-        <v>9030496797</v>
+        <v>9508956148</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>592604878</v>
+        <v>716129718</v>
       </c>
       <c r="I18" t="n">
-        <v>0.249431</v>
+        <v>0.258045</v>
       </c>
       <c r="J18" t="n">
-        <v>0.233288</v>
+        <v>0.244758</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007681261816755242</v>
+        <v>0.0097284</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.03354</v>
+        <v>3.92179</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01204162</v>
+        <v>0.01183191</v>
       </c>
       <c r="F19" t="n">
-        <v>8540399072</v>
+        <v>8393353185</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>19988680</v>
+        <v>21898288</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01271105</v>
+        <v>0.01211884</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01195719</v>
+        <v>0.01183761</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0006301626399832819</v>
+        <v>-0.000213334567861646</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.2628</v>
+        <v>-1.88845</v>
       </c>
       <c r="M19" t="n">
-        <v>709240298301.3969</v>
+        <v>709240425836.8521</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.9</v>
+        <v>8.83</v>
       </c>
       <c r="F20" t="n">
-        <v>8187966753</v>
+        <v>8118726601</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>399230</v>
+        <v>418695</v>
       </c>
       <c r="I20" t="n">
-        <v>9.029999999999999</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>8.880000000000001</v>
+        <v>8.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.08439936080502441</v>
+        <v>-0.07010463306942505</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.93935</v>
+        <v>-0.78849</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260924T135205Z-d42d69</t>
+          <t>20260925T141457Z-834e04</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.20324</v>
+        <v>0.216625</v>
       </c>
       <c r="F21" t="n">
-        <v>7100935549</v>
+        <v>7572724921</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>321290636</v>
+        <v>576611230</v>
       </c>
       <c r="I21" t="n">
-        <v>0.213122</v>
+        <v>0.226335</v>
       </c>
       <c r="J21" t="n">
-        <v>0.197178</v>
+        <v>0.20527</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.009336099321796909</v>
+        <v>0.01193091</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.38715</v>
+        <v>5.72779</v>
       </c>
       <c r="M21" t="n">
-        <v>34938629825.38779</v>
+        <v>34944206739.02777</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70147</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-24T13:48:20.000Z</t>
+          <t>2026-09-25T14:12:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83598</v>
+        <v>83960</v>
       </c>
       <c r="F2" t="n">
-        <v>1679162755062</v>
+        <v>1686713805167</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>38514548082</v>
+        <v>25094148124</v>
       </c>
       <c r="I2" t="n">
-        <v>85208</v>
+        <v>84296</v>
       </c>
       <c r="J2" t="n">
-        <v>83513</v>
+        <v>83230</v>
       </c>
       <c r="K2" t="n">
-        <v>-604.7274447487289</v>
+        <v>-256.859398715038</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.77851</v>
+        <v>-0.32156</v>
       </c>
       <c r="M2" t="n">
-        <v>20089181</v>
+        <v>20089568</v>
       </c>
       <c r="N2" t="n">
-        <v>20089196</v>
+        <v>20089609</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2688.92</v>
+        <v>2685.41</v>
       </c>
       <c r="F3" t="n">
-        <v>328251353932</v>
+        <v>327852902474</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15862968693</v>
+        <v>9448881653</v>
       </c>
       <c r="I3" t="n">
-        <v>2739.52</v>
+        <v>2697.72</v>
       </c>
       <c r="J3" t="n">
-        <v>2653.81</v>
+        <v>2669.73</v>
       </c>
       <c r="K3" t="n">
-        <v>21.97</v>
+        <v>-20.30064927189733</v>
       </c>
       <c r="L3" t="n">
-        <v>0.79044</v>
+        <v>-0.78586</v>
       </c>
       <c r="M3" t="n">
-        <v>122078905.3531288</v>
+        <v>122081755.2385784</v>
       </c>
       <c r="N3" t="n">
-        <v>122078905.3531288</v>
+        <v>122081755.2385784</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99973</v>
+        <v>0.999844</v>
       </c>
       <c r="F4" t="n">
-        <v>183727460118</v>
+        <v>183789394509</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>72786037039</v>
+        <v>49145434159</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998899999999999</v>
+        <v>0.999887</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999287</v>
+        <v>0.999719</v>
       </c>
       <c r="K4" t="n">
-        <v>6.05e-06</v>
+        <v>8.093e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00347</v>
+        <v>0.00231</v>
       </c>
       <c r="M4" t="n">
-        <v>183779015975.4778</v>
+        <v>183818815971.0418</v>
       </c>
       <c r="N4" t="n">
-        <v>189245961986.9062</v>
+        <v>189285761986.9062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>772.7</v>
+        <v>772.3099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>102856673958</v>
+        <v>102840641561</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1165366190</v>
+        <v>743839388</v>
       </c>
       <c r="I5" t="n">
-        <v>785.3099999999999</v>
+        <v>777.74</v>
       </c>
       <c r="J5" t="n">
-        <v>770.72</v>
+        <v>769.51</v>
       </c>
       <c r="K5" t="n">
-        <v>-4.873413513556216</v>
+        <v>-3.343418307023285</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.62303</v>
+        <v>-0.44597</v>
       </c>
       <c r="M5" t="n">
-        <v>133159842.41</v>
+        <v>133159792.88</v>
       </c>
       <c r="N5" t="n">
-        <v>133159833.97</v>
+        <v>133159791.14</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="F6" t="n">
-        <v>99229873529</v>
+        <v>96751811786</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>6282193834</v>
+        <v>3887008543</v>
       </c>
       <c r="I6" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49</v>
+        <v>1.54</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07800700000000001</v>
+        <v>-0.05239949727053506</v>
       </c>
       <c r="L6" t="n">
-        <v>5.11372</v>
+        <v>-3.32178</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999853</v>
+        <v>0.9998899999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>75342386451</v>
+        <v>75325511675</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20818639756</v>
+        <v>13529945029</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99942</v>
+        <v>0.999804</v>
       </c>
       <c r="K7" t="n">
-        <v>3.113e-05</v>
+        <v>-3.190448686907e-06</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00606</v>
+        <v>-0.00778</v>
       </c>
       <c r="M7" t="n">
-        <v>75354142543.02426</v>
+        <v>75333929675.06418</v>
       </c>
       <c r="N7" t="n">
-        <v>75302398987.78542</v>
+        <v>75334626227.45894</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>119.58</v>
+        <v>120.65</v>
       </c>
       <c r="F8" t="n">
-        <v>70220425043</v>
+        <v>70914599486</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5871439186</v>
+        <v>4716262120</v>
       </c>
       <c r="I8" t="n">
-        <v>122.01</v>
+        <v>122.75</v>
       </c>
       <c r="J8" t="n">
-        <v>114.46</v>
+        <v>118.59</v>
       </c>
       <c r="K8" t="n">
-        <v>4.61</v>
+        <v>0.7919079999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>4.02766</v>
+        <v>0.60627</v>
       </c>
       <c r="M8" t="n">
-        <v>587647593.3659807</v>
+        <v>587712762.0220828</v>
       </c>
       <c r="N8" t="n">
-        <v>634686100.9544628</v>
+        <v>634763960.9711117</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.337211</v>
+        <v>0.336607</v>
       </c>
       <c r="F9" t="n">
-        <v>32018650054</v>
+        <v>31961192093</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>461988718</v>
+        <v>267042689</v>
       </c>
       <c r="I9" t="n">
-        <v>0.341481</v>
+        <v>0.338229</v>
       </c>
       <c r="J9" t="n">
-        <v>0.336802</v>
+        <v>0.33599</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002870799508586985</v>
+        <v>-0.000351358735391327</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.8316</v>
+        <v>-0.13818</v>
       </c>
       <c r="M9" t="n">
-        <v>94964948406.9399</v>
+        <v>94967057481.15408</v>
       </c>
       <c r="N9" t="n">
-        <v>94966809744.41438</v>
+        <v>94968826620.64949</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1593.72</v>
+        <v>1539.58</v>
       </c>
       <c r="F10" t="n">
-        <v>27023589668</v>
+        <v>26102989564</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1279929296</v>
+        <v>778167418</v>
       </c>
       <c r="I10" t="n">
-        <v>1622.95</v>
+        <v>1596.86</v>
       </c>
       <c r="J10" t="n">
-        <v>1491.28</v>
+        <v>1517.49</v>
       </c>
       <c r="K10" t="n">
-        <v>80.68000000000001</v>
+        <v>-76.6470678720184</v>
       </c>
       <c r="L10" t="n">
-        <v>5.35021</v>
+        <v>-4.78454</v>
       </c>
       <c r="M10" t="n">
-        <v>16951193.9155448</v>
+        <v>16952175.1655448</v>
       </c>
       <c r="N10" t="n">
-        <v>16951806.4155448</v>
+        <v>16953504.8530448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.027</v>
+        <v>1.026</v>
       </c>
       <c r="F11" t="n">
-        <v>23712065535</v>
+        <v>23747335901</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>585257867</v>
+        <v>22346272</v>
       </c>
       <c r="I11" t="n">
-        <v>1.047</v>
+        <v>1.032</v>
       </c>
       <c r="J11" t="n">
-        <v>1.012</v>
+        <v>1.023</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.009244703155131262</v>
+        <v>-0.001108940741380682</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.89492</v>
+        <v>-0.10223</v>
       </c>
       <c r="M11" t="n">
-        <v>23089131934.788</v>
+        <v>23149018497.978</v>
       </c>
       <c r="N11" t="n">
-        <v>23089131934.788</v>
+        <v>23149018497.978</v>
       </c>
       <c r="O11" t="n">
         <v>1.061</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.18000000000001</v>
+        <v>91.83</v>
       </c>
       <c r="F12" t="n">
-        <v>20488667956</v>
+        <v>20428508325</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1155605568</v>
+        <v>693710930</v>
       </c>
       <c r="I12" t="n">
-        <v>94.73999999999999</v>
+        <v>92.81999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>91</v>
+        <v>90.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1386147680552199</v>
+        <v>-1.224155095273204</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.12922</v>
+        <v>-1.3402</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097402</v>
+        <v>0.097069</v>
       </c>
       <c r="F13" t="n">
-        <v>15194781531</v>
+        <v>15151071047</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1266625089</v>
+        <v>996069177</v>
       </c>
       <c r="I13" t="n">
-        <v>0.098981</v>
+        <v>0.099703</v>
       </c>
       <c r="J13" t="n">
-        <v>0.094092</v>
+        <v>0.09641</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00300281</v>
+        <v>-0.000756068771230411</v>
       </c>
       <c r="L13" t="n">
-        <v>3.13939</v>
+        <v>-0.76364</v>
       </c>
       <c r="M13" t="n">
-        <v>156060896383.7052</v>
+        <v>156075366383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>171774773126.5791</v>
+        <v>171787443126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.87</v>
+        <v>14.22</v>
       </c>
       <c r="F14" t="n">
-        <v>10373383774</v>
+        <v>10640884885</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1063141253</v>
+        <v>707084096</v>
       </c>
       <c r="I14" t="n">
-        <v>14.19</v>
+        <v>14.35</v>
       </c>
       <c r="J14" t="n">
-        <v>12.46</v>
+        <v>13.69</v>
       </c>
       <c r="K14" t="n">
-        <v>1.34</v>
+        <v>0.198978</v>
       </c>
       <c r="L14" t="n">
-        <v>10.71284</v>
+        <v>1.36679</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>549.15</v>
+        <v>549.3</v>
       </c>
       <c r="F15" t="n">
-        <v>10313844161</v>
+        <v>10336344317</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>144904867</v>
+        <v>92067811</v>
       </c>
       <c r="I15" t="n">
-        <v>577.46</v>
+        <v>561.22</v>
       </c>
       <c r="J15" t="n">
-        <v>545.25</v>
+        <v>546.01</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.992583697525561</v>
+        <v>-7.378489186112347</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.38245</v>
+        <v>-1.39045</v>
       </c>
       <c r="M15" t="n">
-        <v>18809274.09052855</v>
+        <v>18809710.28932691</v>
       </c>
       <c r="N15" t="n">
-        <v>18809314.29046824</v>
+        <v>18809742.0893211</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.58</v>
+        <v>83.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9932139589</v>
+        <v>9959623112</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>128664165</v>
+        <v>77723889</v>
       </c>
       <c r="I16" t="n">
-        <v>85.16</v>
+        <v>84.13</v>
       </c>
       <c r="J16" t="n">
-        <v>83.58</v>
+        <v>83.17</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.5541301889751509</v>
+        <v>-0.346154198101928</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.86936</v>
+        <v>-0.44687</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.99963</v>
+        <v>0.999721</v>
       </c>
       <c r="F17" t="n">
-        <v>9719421143</v>
+        <v>9746623829</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>125292033</v>
+        <v>172309969</v>
       </c>
       <c r="I17" t="n">
-        <v>0.99998</v>
+        <v>0.999868</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9994</v>
+        <v>0.999566</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000183372176973173</v>
+        <v>5.916e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01564</v>
+        <v>4e-05</v>
       </c>
       <c r="M17" t="n">
-        <v>9723114647.376017</v>
+        <v>9748883836.049854</v>
       </c>
       <c r="N17" t="n">
-        <v>9723685294.041584</v>
+        <v>9749012892.848028</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.253462</v>
+        <v>0.254453</v>
       </c>
       <c r="F18" t="n">
-        <v>9508956148</v>
+        <v>9549016320</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>716129718</v>
+        <v>640158278</v>
       </c>
       <c r="I18" t="n">
-        <v>0.258045</v>
+        <v>0.26468</v>
       </c>
       <c r="J18" t="n">
-        <v>0.244758</v>
+        <v>0.251137</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0097284</v>
+        <v>-0.00139232354027119</v>
       </c>
       <c r="L18" t="n">
-        <v>3.92179</v>
+        <v>-0.55041</v>
       </c>
       <c r="M18" t="n">
         <v>37529061988.53558</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01183191</v>
+        <v>0.0123665</v>
       </c>
       <c r="F19" t="n">
-        <v>8393353185</v>
+        <v>8770640199</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>21898288</v>
+        <v>21274799</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01211884</v>
+        <v>0.01245443</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01183761</v>
+        <v>0.01041574</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000213334567861646</v>
+        <v>0.00048121</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.88845</v>
+        <v>4.06067</v>
       </c>
       <c r="M19" t="n">
-        <v>709240425836.8521</v>
+        <v>709240980011.2261</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.83</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>8118726601</v>
+        <v>8240992585</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>418695</v>
+        <v>256366</v>
       </c>
       <c r="I20" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="J20" t="n">
-        <v>8.77</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.07010463306942505</v>
+        <v>0.123426</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.78849</v>
+        <v>1.39349</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260925T141457Z-834e04</t>
+          <t>20260926T132619Z-dbc214</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.216625</v>
+        <v>0.217446</v>
       </c>
       <c r="F21" t="n">
-        <v>7572724921</v>
+        <v>7604775177</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>576611230</v>
+        <v>309237779</v>
       </c>
       <c r="I21" t="n">
-        <v>0.226335</v>
+        <v>0.222301</v>
       </c>
       <c r="J21" t="n">
-        <v>0.20527</v>
+        <v>0.214962</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01193091</v>
+        <v>-0.004574860917676671</v>
       </c>
       <c r="L21" t="n">
-        <v>5.72779</v>
+        <v>-2.08151</v>
       </c>
       <c r="M21" t="n">
-        <v>34944206739.02777</v>
+        <v>34970186880.78098</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70147</v>
+        <v>50001786839.70047</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-25T14:12:20.000Z</t>
+          <t>2026-09-26T13:23:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83960</v>
+        <v>84945</v>
       </c>
       <c r="F2" t="n">
-        <v>1686713805167</v>
+        <v>1706532619602</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>25094148124</v>
+        <v>21184097131</v>
       </c>
       <c r="I2" t="n">
-        <v>84296</v>
+        <v>85089</v>
       </c>
       <c r="J2" t="n">
-        <v>83230</v>
+        <v>83835</v>
       </c>
       <c r="K2" t="n">
-        <v>-256.859398715038</v>
+        <v>994.61</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.32156</v>
+        <v>1.14458</v>
       </c>
       <c r="M2" t="n">
-        <v>20089568</v>
+        <v>20089965</v>
       </c>
       <c r="N2" t="n">
-        <v>20089609</v>
+        <v>20090134</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2685.41</v>
+        <v>2704.75</v>
       </c>
       <c r="F3" t="n">
-        <v>327852902474</v>
+        <v>330207990871</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9448881653</v>
+        <v>7613539121</v>
       </c>
       <c r="I3" t="n">
-        <v>2697.72</v>
+        <v>2720.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2669.73</v>
+        <v>2666.72</v>
       </c>
       <c r="K3" t="n">
-        <v>-20.30064927189733</v>
+        <v>17.76</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.78586</v>
+        <v>0.58869</v>
       </c>
       <c r="M3" t="n">
-        <v>122081755.2385784</v>
+        <v>122084677.7313143</v>
       </c>
       <c r="N3" t="n">
-        <v>122081755.2385784</v>
+        <v>122084677.7313143</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999844</v>
+        <v>0.999839</v>
       </c>
       <c r="F4" t="n">
-        <v>183789394509</v>
+        <v>183789253110</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>49145434159</v>
+        <v>41514989094</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999887</v>
+        <v>0.999873</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999719</v>
+        <v>0.999715</v>
       </c>
       <c r="K4" t="n">
-        <v>8.093e-05</v>
+        <v>1.089e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00231</v>
+        <v>-0.001</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815971.0418</v>
+        <v>183818815967.1891</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>772.3099999999999</v>
+        <v>779.8099999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>102840641561</v>
+        <v>103839803578</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>743839388</v>
+        <v>709749417</v>
       </c>
       <c r="I5" t="n">
-        <v>777.74</v>
+        <v>782.71</v>
       </c>
       <c r="J5" t="n">
-        <v>769.51</v>
+        <v>766.86</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.343418307023285</v>
+        <v>7.32</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.44597</v>
+        <v>0.8614000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>133159792.88</v>
+        <v>133159695.65</v>
       </c>
       <c r="N5" t="n">
-        <v>133159791.14</v>
+        <v>133159692.37</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="F6" t="n">
-        <v>96751811786</v>
+        <v>96195766748</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3887008543</v>
+        <v>2780906745</v>
       </c>
       <c r="I6" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05239949727053506</v>
+        <v>-0.01407680591755334</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.32178</v>
+        <v>-1.07668</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9998899999999999</v>
+        <v>0.99999</v>
       </c>
       <c r="F7" t="n">
-        <v>75325511675</v>
+        <v>75195810814</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13529945029</v>
+        <v>9492352280</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999804</v>
+        <v>0.999451</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.190448686907e-06</v>
+        <v>0.00010164</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00778</v>
+        <v>0.0074</v>
       </c>
       <c r="M7" t="n">
-        <v>75333929675.06418</v>
+        <v>75196575861.07713</v>
       </c>
       <c r="N7" t="n">
-        <v>75334626227.45894</v>
+        <v>75209861269.7758</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>120.65</v>
+        <v>122.88</v>
       </c>
       <c r="F8" t="n">
-        <v>70914599486</v>
+        <v>72226558654</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4716262120</v>
+        <v>3632253379</v>
       </c>
       <c r="I8" t="n">
-        <v>122.75</v>
+        <v>124.77</v>
       </c>
       <c r="J8" t="n">
-        <v>118.59</v>
+        <v>120.11</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7919079999999999</v>
+        <v>1.94</v>
       </c>
       <c r="L8" t="n">
-        <v>0.60627</v>
+        <v>1.39633</v>
       </c>
       <c r="M8" t="n">
-        <v>587712762.0220828</v>
+        <v>587783255.1105938</v>
       </c>
       <c r="N8" t="n">
-        <v>634763960.9711117</v>
+        <v>634841718.6764878</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336607</v>
+        <v>0.333493</v>
       </c>
       <c r="F9" t="n">
-        <v>31961192093</v>
+        <v>31670810269</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>267042689</v>
+        <v>346156219</v>
       </c>
       <c r="I9" t="n">
-        <v>0.338229</v>
+        <v>0.336714</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33599</v>
+        <v>0.33245</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000351358735391327</v>
+        <v>-0.002821045035316549</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.13818</v>
+        <v>-0.84712</v>
       </c>
       <c r="M9" t="n">
         <v>94967057481.15408</v>
       </c>
       <c r="N9" t="n">
-        <v>94968826620.64949</v>
+        <v>94971253492.20189</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1539.58</v>
+        <v>1643.08</v>
       </c>
       <c r="F10" t="n">
-        <v>26102989564</v>
+        <v>27858352423</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>778167418</v>
+        <v>1413804468</v>
       </c>
       <c r="I10" t="n">
-        <v>1596.86</v>
+        <v>1687.78</v>
       </c>
       <c r="J10" t="n">
-        <v>1517.49</v>
+        <v>1546.39</v>
       </c>
       <c r="K10" t="n">
-        <v>-76.6470678720184</v>
+        <v>101.84</v>
       </c>
       <c r="L10" t="n">
-        <v>-4.78454</v>
+        <v>6.20596</v>
       </c>
       <c r="M10" t="n">
-        <v>16952175.1655448</v>
+        <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16953504.8530448</v>
+        <v>16955384.5405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,53 +1110,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.026</v>
+        <v>1.058</v>
       </c>
       <c r="F11" t="n">
-        <v>23747335901</v>
+        <v>24516003984</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>22346272</v>
+        <v>401487</v>
       </c>
       <c r="I11" t="n">
-        <v>1.032</v>
+        <v>1.062</v>
       </c>
       <c r="J11" t="n">
-        <v>1.023</v>
+        <v>1.016</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.001108940741380682</v>
+        <v>0.0316886</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.10223</v>
+        <v>3.09073</v>
       </c>
       <c r="M11" t="n">
-        <v>23149018497.978</v>
+        <v>23181959779.848</v>
       </c>
       <c r="N11" t="n">
-        <v>23149018497.978</v>
+        <v>23193525454.108</v>
       </c>
       <c r="O11" t="n">
-        <v>1.061</v>
+        <v>1.062</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-08-03T14:19:20.000Z</t>
+          <t>2026-09-27T13:07:30.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T13:11:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>91.83</v>
+        <v>92.06999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>20428508325</v>
+        <v>20480194044</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>693710930</v>
+        <v>607402270</v>
       </c>
       <c r="I12" t="n">
-        <v>92.81999999999999</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>90.41</v>
+        <v>91.06</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.224155095273204</v>
+        <v>-0.1449201937953575</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.3402</v>
+        <v>-0.28565</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.097069</v>
+        <v>0.09762</v>
       </c>
       <c r="F13" t="n">
-        <v>15151071047</v>
+        <v>15237393273</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>996069177</v>
+        <v>773469735</v>
       </c>
       <c r="I13" t="n">
-        <v>0.099703</v>
+        <v>0.098832</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09641</v>
+        <v>0.095327</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000756068771230411</v>
+        <v>0.00030094</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.76364</v>
+        <v>0.11394</v>
       </c>
       <c r="M13" t="n">
-        <v>156075366383.7053</v>
+        <v>156089086383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171787443126.579</v>
+        <v>171801603126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.22</v>
+        <v>14.11</v>
       </c>
       <c r="F14" t="n">
-        <v>10640884885</v>
+        <v>10552392004</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>707084096</v>
+        <v>450403576</v>
       </c>
       <c r="I14" t="n">
-        <v>14.35</v>
+        <v>14.47</v>
       </c>
       <c r="J14" t="n">
-        <v>13.69</v>
+        <v>13.91</v>
       </c>
       <c r="K14" t="n">
-        <v>0.198978</v>
+        <v>-0.2941581756086027</v>
       </c>
       <c r="L14" t="n">
-        <v>1.36679</v>
+        <v>-2.07594</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>549.3</v>
+        <v>547.5599999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10336344317</v>
+        <v>10299613386</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>92067811</v>
+        <v>98485371</v>
       </c>
       <c r="I15" t="n">
-        <v>561.22</v>
+        <v>562.88</v>
       </c>
       <c r="J15" t="n">
-        <v>546.01</v>
+        <v>546.5</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.378489186112347</v>
+        <v>-2.077478602360884</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.39045</v>
+        <v>-0.5147</v>
       </c>
       <c r="M15" t="n">
-        <v>18809710.28932691</v>
+        <v>18810142.88639648</v>
       </c>
       <c r="N15" t="n">
-        <v>18809742.0893211</v>
+        <v>18810186.68579455</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.8</v>
+        <v>84.7</v>
       </c>
       <c r="F16" t="n">
-        <v>9959623112</v>
+        <v>10066394234</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>77723889</v>
+        <v>38669946</v>
       </c>
       <c r="I16" t="n">
-        <v>84.13</v>
+        <v>84.88</v>
       </c>
       <c r="J16" t="n">
-        <v>83.17</v>
+        <v>83.59</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.346154198101928</v>
+        <v>0.922706</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.44687</v>
+        <v>1.03738</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999721</v>
+        <v>0.999722</v>
       </c>
       <c r="F17" t="n">
-        <v>9746623829</v>
+        <v>9770898995</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>172309969</v>
+        <v>50701799</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999868</v>
+        <v>0.999846</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999566</v>
+        <v>0.999595</v>
       </c>
       <c r="K17" t="n">
-        <v>5.916e-05</v>
+        <v>1.442e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>4e-05</v>
+        <v>-0.00079</v>
       </c>
       <c r="M17" t="n">
-        <v>9748883836.049854</v>
+        <v>9773614544.067293</v>
       </c>
       <c r="N17" t="n">
-        <v>9749012892.848028</v>
+        <v>9773387427.242182</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,31 +1565,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.254453</v>
+        <v>0.255618</v>
       </c>
       <c r="F18" t="n">
-        <v>9549016320</v>
+        <v>9594683963</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>640158278</v>
+        <v>441302587</v>
       </c>
       <c r="I18" t="n">
-        <v>0.26468</v>
+        <v>0.260642</v>
       </c>
       <c r="J18" t="n">
-        <v>0.251137</v>
+        <v>0.248192</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.00139232354027119</v>
+        <v>-2.0971475922005e-05</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.55041</v>
+        <v>-0.18042</v>
       </c>
       <c r="M18" t="n">
-        <v>37529061988.53558</v>
+        <v>37535193928.91081</v>
       </c>
       <c r="N18" t="n">
         <v>45000000000</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.0123665</v>
+        <v>0.01263123</v>
       </c>
       <c r="F19" t="n">
-        <v>8770640199</v>
+        <v>8958633558</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>21274799</v>
+        <v>16784296</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01245443</v>
+        <v>0.01335759</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01041574</v>
+        <v>0.0125299</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00048121</v>
+        <v>-6.0112472093053e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>4.06067</v>
+        <v>-0.66867</v>
       </c>
       <c r="M19" t="n">
-        <v>709240980011.2261</v>
+        <v>709244646514.1578</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.960000000000001</v>
+        <v>9.02</v>
       </c>
       <c r="F20" t="n">
-        <v>8240992585</v>
+        <v>8297568479</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>256366</v>
+        <v>457739</v>
       </c>
       <c r="I20" t="n">
-        <v>8.99</v>
+        <v>9.09</v>
       </c>
       <c r="J20" t="n">
-        <v>8.789999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>0.123426</v>
+        <v>0.060879</v>
       </c>
       <c r="L20" t="n">
-        <v>1.39349</v>
+        <v>0.67213</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260926T132619Z-dbc214</t>
+          <t>20260927T142239Z-bc386a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.217446</v>
+        <v>0.216352</v>
       </c>
       <c r="F21" t="n">
-        <v>7604775177</v>
+        <v>7565866358</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>309237779</v>
+        <v>183063798</v>
       </c>
       <c r="I21" t="n">
-        <v>0.222301</v>
+        <v>0.22079</v>
       </c>
       <c r="J21" t="n">
-        <v>0.214962</v>
+        <v>0.213075</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.004574860917676671</v>
+        <v>-0.001367816087023216</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.08151</v>
+        <v>-0.78912</v>
       </c>
       <c r="M21" t="n">
-        <v>34970186880.78098</v>
+        <v>34970178928.73618</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.70047</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-26T13:23:30.000Z</t>
+          <t>2026-09-27T14:19:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84945</v>
+        <v>83628</v>
       </c>
       <c r="F2" t="n">
-        <v>1706532619602</v>
+        <v>1680129050993</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>21184097131</v>
+        <v>40095045364</v>
       </c>
       <c r="I2" t="n">
-        <v>85089</v>
+        <v>84945</v>
       </c>
       <c r="J2" t="n">
-        <v>83835</v>
+        <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>994.61</v>
+        <v>-800.5256324028014</v>
       </c>
       <c r="L2" t="n">
-        <v>1.14458</v>
+        <v>-0.9496</v>
       </c>
       <c r="M2" t="n">
-        <v>20089965</v>
+        <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090134</v>
+        <v>20090481</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2704.75</v>
+        <v>2684.27</v>
       </c>
       <c r="F3" t="n">
-        <v>330207990871</v>
+        <v>327704876617</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>7613539121</v>
+        <v>15847058740</v>
       </c>
       <c r="I3" t="n">
-        <v>2720.75</v>
+        <v>2698.21</v>
       </c>
       <c r="J3" t="n">
-        <v>2666.72</v>
+        <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>17.76</v>
+        <v>-4.079040065399113</v>
       </c>
       <c r="L3" t="n">
-        <v>0.58869</v>
+        <v>-0.1606</v>
       </c>
       <c r="M3" t="n">
-        <v>122084677.7313143</v>
+        <v>122087473.8258867</v>
       </c>
       <c r="N3" t="n">
-        <v>122084677.7313143</v>
+        <v>122087473.8258867</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999839</v>
+        <v>0.999806</v>
       </c>
       <c r="F4" t="n">
-        <v>183789253110</v>
+        <v>183775189298</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>41514989094</v>
+        <v>71523929844</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999873</v>
+        <v>0.999854</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999715</v>
+        <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>1.089e-05</v>
+        <v>6.45e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.001</v>
+        <v>0.00226</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815967.1891</v>
+        <v>183818815964.5838</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>779.8099999999999</v>
+        <v>766.03</v>
       </c>
       <c r="F5" t="n">
-        <v>103839803578</v>
+        <v>102003832094</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>709749417</v>
+        <v>1032103584</v>
       </c>
       <c r="I5" t="n">
-        <v>782.71</v>
+        <v>783.74</v>
       </c>
       <c r="J5" t="n">
-        <v>766.86</v>
+        <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>7.32</v>
+        <v>-9.840246612364126</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8614000000000001</v>
+        <v>-1.27744</v>
       </c>
       <c r="M5" t="n">
-        <v>133159695.65</v>
+        <v>133159627.49</v>
       </c>
       <c r="N5" t="n">
-        <v>133159692.37</v>
+        <v>133159623.53</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>96195766748</v>
+        <v>93930368802</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2780906745</v>
+        <v>4038950114</v>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01407680591755334</v>
+        <v>-0.02702585931666324</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.07668</v>
+        <v>-1.80241</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99999</v>
+        <v>0.999896</v>
       </c>
       <c r="F7" t="n">
-        <v>75195810814</v>
+        <v>74840870406</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>9492352280</v>
+        <v>24447087511</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9999400000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999451</v>
+        <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00010164</v>
+        <v>2.851e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0074</v>
+        <v>-0.00016</v>
       </c>
       <c r="M7" t="n">
-        <v>75196575861.07713</v>
+        <v>74852146130.23332</v>
       </c>
       <c r="N7" t="n">
-        <v>75209861269.7758</v>
+        <v>74843470364.92506</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>122.88</v>
+        <v>118.84</v>
       </c>
       <c r="F8" t="n">
-        <v>72226558654</v>
+        <v>69846507958</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3632253379</v>
+        <v>4138249881</v>
       </c>
       <c r="I8" t="n">
-        <v>124.77</v>
+        <v>123.36</v>
       </c>
       <c r="J8" t="n">
-        <v>120.11</v>
+        <v>117.57</v>
       </c>
       <c r="K8" t="n">
-        <v>1.94</v>
+        <v>-3.085955386790999</v>
       </c>
       <c r="L8" t="n">
-        <v>1.39633</v>
+        <v>-2.55265</v>
       </c>
       <c r="M8" t="n">
-        <v>587783255.1105938</v>
+        <v>587781862.721426</v>
       </c>
       <c r="N8" t="n">
-        <v>634841718.6764878</v>
+        <v>634840553.4996796</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.333493</v>
+        <v>0.33473</v>
       </c>
       <c r="F9" t="n">
-        <v>31670810269</v>
+        <v>31789740830</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>346156219</v>
+        <v>374027967</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336714</v>
+        <v>0.335666</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33245</v>
+        <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002821045035316549</v>
+        <v>0.00079635</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.84712</v>
+        <v>0.22394</v>
       </c>
       <c r="M9" t="n">
-        <v>94967057481.15408</v>
+        <v>94972937401.45468</v>
       </c>
       <c r="N9" t="n">
-        <v>94971253492.20189</v>
+        <v>94972951495.66699</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1643.08</v>
+        <v>1520.86</v>
       </c>
       <c r="F10" t="n">
-        <v>27858352423</v>
+        <v>25781910827</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1413804468</v>
+        <v>1007938825</v>
       </c>
       <c r="I10" t="n">
-        <v>1687.78</v>
+        <v>1612.88</v>
       </c>
       <c r="J10" t="n">
-        <v>1546.39</v>
+        <v>1510.24</v>
       </c>
       <c r="K10" t="n">
-        <v>101.84</v>
+        <v>-60.80843903747132</v>
       </c>
       <c r="L10" t="n">
-        <v>6.20596</v>
+        <v>-3.87843</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16955384.5405448</v>
+        <v>16957395.4780448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,30 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.058</v>
+        <v>1.059</v>
       </c>
       <c r="F11" t="n">
-        <v>24516003984</v>
+        <v>24577771416</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>401487</v>
+        <v>24871973</v>
       </c>
       <c r="I11" t="n">
-        <v>1.062</v>
+        <v>1.061</v>
       </c>
       <c r="J11" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="K11" t="n">
-        <v>0.0316886</v>
-      </c>
-      <c r="L11" t="n">
-        <v>3.09073</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
       <c r="M11" t="n">
-        <v>23181959779.848</v>
+        <v>23202972251.118</v>
       </c>
       <c r="N11" t="n">
-        <v>23193525454.108</v>
+        <v>23202972251.118</v>
       </c>
       <c r="O11" t="n">
         <v>1.062</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-27T13:11:40.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.06999999999999</v>
+        <v>88.73</v>
       </c>
       <c r="F12" t="n">
-        <v>20480194044</v>
+        <v>19730034003</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>607402270</v>
+        <v>946302648</v>
       </c>
       <c r="I12" t="n">
-        <v>93.84999999999999</v>
+        <v>92.09999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>91.06</v>
+        <v>86.95</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.1449201937953575</v>
+        <v>-2.541052861800551</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.28565</v>
+        <v>-2.84228</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09762</v>
+        <v>0.094098</v>
       </c>
       <c r="F13" t="n">
-        <v>15237393273</v>
+        <v>14688879088</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>773469735</v>
+        <v>1186766570</v>
       </c>
       <c r="I13" t="n">
-        <v>0.098832</v>
+        <v>0.09775</v>
       </c>
       <c r="J13" t="n">
-        <v>0.095327</v>
+        <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00030094</v>
+        <v>-0.002719752810769568</v>
       </c>
       <c r="L13" t="n">
-        <v>0.11394</v>
+        <v>-2.81425</v>
       </c>
       <c r="M13" t="n">
-        <v>156089086383.7052</v>
+        <v>156104906383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171801603126.579</v>
+        <v>156104946383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1301,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.11</v>
+        <v>15.24</v>
       </c>
       <c r="F14" t="n">
-        <v>10552392004</v>
+        <v>11408877171</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>450403576</v>
+        <v>1101883443</v>
       </c>
       <c r="I14" t="n">
-        <v>14.47</v>
+        <v>15.26</v>
       </c>
       <c r="J14" t="n">
-        <v>13.91</v>
+        <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.2941581756086027</v>
+        <v>1.13</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.07594</v>
+        <v>8.05315</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>547.5599999999999</v>
+        <v>538.36</v>
       </c>
       <c r="F15" t="n">
-        <v>10299613386</v>
+        <v>10125842981</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>98485371</v>
+        <v>120623998</v>
       </c>
       <c r="I15" t="n">
-        <v>562.88</v>
+        <v>552.95</v>
       </c>
       <c r="J15" t="n">
-        <v>546.5</v>
+        <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.077478602360884</v>
+        <v>-6.988445927827684</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.5147</v>
+        <v>-1.28901</v>
       </c>
       <c r="M15" t="n">
-        <v>18810142.88639648</v>
+        <v>18810613.88120856</v>
       </c>
       <c r="N15" t="n">
-        <v>18810186.68579455</v>
+        <v>18810665.48043185</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1431,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84.7</v>
+        <v>83.58</v>
       </c>
       <c r="F16" t="n">
-        <v>10066394234</v>
+        <v>9934621135</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>38669946</v>
+        <v>129548567</v>
       </c>
       <c r="I16" t="n">
-        <v>84.88</v>
+        <v>84.67</v>
       </c>
       <c r="J16" t="n">
-        <v>83.59</v>
+        <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>0.922706</v>
+        <v>-0.6630199170941751</v>
       </c>
       <c r="L16" t="n">
-        <v>1.03738</v>
+        <v>-0.7719</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999722</v>
+        <v>0.999699</v>
       </c>
       <c r="F17" t="n">
-        <v>9770898995</v>
+        <v>9780317209</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>50701799</v>
+        <v>123079087</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999846</v>
+        <v>0.999839</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999595</v>
+        <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>1.442e-05</v>
+        <v>-2.0502185588134e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00079</v>
+        <v>-0.00617</v>
       </c>
       <c r="M17" t="n">
-        <v>9773614544.067293</v>
+        <v>9783695712.381886</v>
       </c>
       <c r="N17" t="n">
-        <v>9773387427.242182</v>
+        <v>9782223070.353539</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.255618</v>
+        <v>0.245232</v>
       </c>
       <c r="F18" t="n">
-        <v>9594683963</v>
+        <v>9204678078</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>441302587</v>
+        <v>647377627</v>
       </c>
       <c r="I18" t="n">
-        <v>0.260642</v>
+        <v>0.257648</v>
       </c>
       <c r="J18" t="n">
-        <v>0.248192</v>
+        <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.0971475922005e-05</v>
+        <v>-0.009054533622238931</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.18042</v>
+        <v>-3.58698</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1626,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01263123</v>
+        <v>0.01254237</v>
       </c>
       <c r="F19" t="n">
-        <v>8958633558</v>
+        <v>8901184461</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>16784296</v>
+        <v>23847322</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01335759</v>
+        <v>0.01276074</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0125299</v>
+        <v>0.01249052</v>
       </c>
       <c r="K19" t="n">
-        <v>-6.0112472093053e-05</v>
+        <v>-3.131499559115e-05</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.66867</v>
+        <v>-0.22871</v>
       </c>
       <c r="M19" t="n">
-        <v>709244646514.1578</v>
+        <v>709245362584.6495</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1691,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.02</v>
+        <v>9.06</v>
       </c>
       <c r="F20" t="n">
-        <v>8297568479</v>
+        <v>8334089166</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>457739</v>
+        <v>442380</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
       </c>
       <c r="J20" t="n">
-        <v>8.960000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>0.060879</v>
+        <v>0.04916048</v>
       </c>
       <c r="L20" t="n">
-        <v>0.67213</v>
+        <v>0.54394</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260927T142239Z-bc386a</t>
+          <t>20260928T170645Z-be524b</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1756,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.216352</v>
+        <v>0.224252</v>
       </c>
       <c r="F21" t="n">
-        <v>7565866358</v>
+        <v>7854903242</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>183063798</v>
+        <v>619426342</v>
       </c>
       <c r="I21" t="n">
-        <v>0.22079</v>
+        <v>0.230315</v>
       </c>
       <c r="J21" t="n">
-        <v>0.213075</v>
+        <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001367816087023216</v>
+        <v>0.00840275</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.78912</v>
+        <v>4.06931</v>
       </c>
       <c r="M21" t="n">
-        <v>34970178928.73618</v>
+        <v>34970168660.84914</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.70047</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O21" t="n">
         <v>0.875563</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-27T14:19:30.000Z</t>
+          <t>2026-09-28T17:04:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83628</v>
+        <v>83568</v>
       </c>
       <c r="F2" t="n">
-        <v>1680129050993</v>
+        <v>1679008903650</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>40095045364</v>
+        <v>41791363643</v>
       </c>
       <c r="I2" t="n">
         <v>84945</v>
@@ -543,16 +543,16 @@
         <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>-800.5256324028014</v>
+        <v>-786.8917941942054</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.9496</v>
+        <v>-0.93283</v>
       </c>
       <c r="M2" t="n">
         <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090481</v>
+        <v>20090690</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,28 +590,28 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2684.27</v>
+        <v>2690.99</v>
       </c>
       <c r="F3" t="n">
-        <v>327704876617</v>
+        <v>328578897942</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15847058740</v>
+        <v>17136731362</v>
       </c>
       <c r="I3" t="n">
-        <v>2698.21</v>
+        <v>2717.37</v>
       </c>
       <c r="J3" t="n">
         <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.079040065399113</v>
+        <v>7.15</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.1606</v>
+        <v>0.26649</v>
       </c>
       <c r="M3" t="n">
         <v>122087473.8258867</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999806</v>
+        <v>0.999718</v>
       </c>
       <c r="F4" t="n">
-        <v>183775189298</v>
+        <v>183821621020</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>71523929844</v>
+        <v>76015680441</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999854</v>
+        <v>0.9998359999999999</v>
       </c>
       <c r="J4" t="n">
         <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>6.45e-05</v>
+        <v>-3.3051755416236e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00226</v>
+        <v>-0.00331</v>
       </c>
       <c r="M4" t="n">
-        <v>183818815964.5838</v>
+        <v>183874242892.1083</v>
       </c>
       <c r="N4" t="n">
         <v>189285761986.9062</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>766.03</v>
+        <v>763.86</v>
       </c>
       <c r="F5" t="n">
-        <v>102003832094</v>
+        <v>101716240299</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1032103584</v>
+        <v>1060279716</v>
       </c>
       <c r="I5" t="n">
         <v>783.74</v>
@@ -738,16 +738,16 @@
         <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.840246612364126</v>
+        <v>-13.44815267303102</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.27744</v>
+        <v>-1.73009</v>
       </c>
       <c r="M5" t="n">
-        <v>133159627.49</v>
+        <v>133159615.43</v>
       </c>
       <c r="N5" t="n">
-        <v>133159623.53</v>
+        <v>133159615.43</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>93930368802</v>
+        <v>94079399488</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4038950114</v>
+        <v>4363467206</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
         <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02702585931666324</v>
+        <v>-0.0167705133797087</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.80241</v>
+        <v>-1.10837</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999896</v>
+        <v>0.999924</v>
       </c>
       <c r="F7" t="n">
-        <v>74840870406</v>
+        <v>74721963135</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24447087511</v>
+        <v>20683397359</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9999400000000001</v>
+        <v>0.99999</v>
       </c>
       <c r="J7" t="n">
         <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>2.851e-05</v>
+        <v>9.628000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00016</v>
+        <v>0.00963</v>
       </c>
       <c r="M7" t="n">
-        <v>74852146130.23332</v>
+        <v>74728156839.12137</v>
       </c>
       <c r="N7" t="n">
-        <v>74843470364.92506</v>
+        <v>74784667843.85722</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.84</v>
+        <v>118.76</v>
       </c>
       <c r="F8" t="n">
-        <v>69846507958</v>
+        <v>69818192382</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4138249881</v>
+        <v>4131466796</v>
       </c>
       <c r="I8" t="n">
-        <v>123.36</v>
+        <v>122.78</v>
       </c>
       <c r="J8" t="n">
-        <v>117.57</v>
+        <v>117.29</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.085955386790999</v>
+        <v>-3.09094262113662</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.55265</v>
+        <v>-2.53671</v>
       </c>
       <c r="M8" t="n">
-        <v>587781862.721426</v>
+        <v>587852966.003577</v>
       </c>
       <c r="N8" t="n">
-        <v>634840553.4996796</v>
+        <v>634919033.5810466</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33473</v>
+        <v>0.335415</v>
       </c>
       <c r="F9" t="n">
-        <v>31789740830</v>
+        <v>31859208139</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>374027967</v>
+        <v>370370261</v>
       </c>
       <c r="I9" t="n">
-        <v>0.335666</v>
+        <v>0.336428</v>
       </c>
       <c r="J9" t="n">
         <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00079635</v>
+        <v>0.00208902</v>
       </c>
       <c r="L9" t="n">
-        <v>0.22394</v>
+        <v>0.6267200000000001</v>
       </c>
       <c r="M9" t="n">
         <v>94972937401.45468</v>
       </c>
       <c r="N9" t="n">
-        <v>94972951495.66699</v>
+        <v>94973450849.00569</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1520.86</v>
+        <v>1483.83</v>
       </c>
       <c r="F10" t="n">
-        <v>25781910827</v>
+        <v>25160679961</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1007938825</v>
+        <v>1246400077</v>
       </c>
       <c r="I10" t="n">
-        <v>1612.88</v>
+        <v>1597.81</v>
       </c>
       <c r="J10" t="n">
-        <v>1510.24</v>
+        <v>1449.25</v>
       </c>
       <c r="K10" t="n">
-        <v>-60.80843903747132</v>
+        <v>-106.6162647415517</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.87843</v>
+        <v>-6.70353</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
       </c>
       <c r="N10" t="n">
-        <v>16957395.4780448</v>
+        <v>16957822.0405448</v>
       </c>
       <c r="O10" t="n">
         <v>3191.93</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.059</v>
+        <v>1.004</v>
       </c>
       <c r="F11" t="n">
-        <v>24577771416</v>
+        <v>23304050621</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>24871973</v>
+        <v>346868158</v>
       </c>
       <c r="I11" t="n">
         <v>1.061</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88.73</v>
+        <v>87.48</v>
       </c>
       <c r="F12" t="n">
-        <v>19730034003</v>
+        <v>19463829972</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>946302648</v>
+        <v>947092964</v>
       </c>
       <c r="I12" t="n">
-        <v>92.09999999999999</v>
+        <v>92.02</v>
       </c>
       <c r="J12" t="n">
-        <v>86.95</v>
+        <v>86.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.541052861800551</v>
+        <v>-4.128673681278386</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.84228</v>
+        <v>-4.50706</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.094098</v>
+        <v>0.093836</v>
       </c>
       <c r="F13" t="n">
-        <v>14688879088</v>
+        <v>14648714526</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1186766570</v>
+        <v>1130717325</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09775</v>
+        <v>0.097729</v>
       </c>
       <c r="J13" t="n">
         <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002719752810769568</v>
+        <v>-0.002506339708048783</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.81425</v>
+        <v>-2.6015</v>
       </c>
       <c r="M13" t="n">
-        <v>156104906383.7052</v>
+        <v>156108476383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156104946383.7052</v>
+        <v>156108686383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.24</v>
+        <v>15.43</v>
       </c>
       <c r="F14" t="n">
-        <v>11408877171</v>
+        <v>11540186445</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1101883443</v>
+        <v>1376547983</v>
       </c>
       <c r="I14" t="n">
-        <v>15.26</v>
+        <v>15.44</v>
       </c>
       <c r="J14" t="n">
         <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="L14" t="n">
-        <v>8.05315</v>
+        <v>10.23398</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>538.36</v>
+        <v>541.1799999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10125842981</v>
+        <v>10184194565</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>120623998</v>
+        <v>134844428</v>
       </c>
       <c r="I15" t="n">
         <v>552.95</v>
@@ -1384,16 +1384,16 @@
         <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.988445927827684</v>
+        <v>-6.981361077774636</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.28901</v>
+        <v>-1.27359</v>
       </c>
       <c r="M15" t="n">
-        <v>18810613.88120856</v>
+        <v>18810763.27902782</v>
       </c>
       <c r="N15" t="n">
-        <v>18810665.48043185</v>
+        <v>18810782.47899366</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.58</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9934621135</v>
+        <v>9937666187</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>129548567</v>
+        <v>143486762</v>
       </c>
       <c r="I16" t="n">
         <v>84.67</v>
@@ -1449,10 +1449,10 @@
         <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6630199170941751</v>
+        <v>-0.6211830702093124</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.7719</v>
+        <v>-0.73752</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,34 +1496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999699</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>9780317209</v>
+        <v>9787052779</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>123079087</v>
+        <v>182329149</v>
       </c>
       <c r="I17" t="n">
-        <v>0.999839</v>
+        <v>1</v>
       </c>
       <c r="J17" t="n">
         <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>-2.0502185588134e-05</v>
+        <v>0.00050491</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00617</v>
+        <v>0.05051</v>
       </c>
       <c r="M17" t="n">
-        <v>9783695712.381886</v>
+        <v>9785581101.437241</v>
       </c>
       <c r="N17" t="n">
-        <v>9782223070.353539</v>
+        <v>9785581101.437241</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.245232</v>
+        <v>0.246807</v>
       </c>
       <c r="F18" t="n">
-        <v>9204678078</v>
+        <v>9262416295</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>647377627</v>
+        <v>688332747</v>
       </c>
       <c r="I18" t="n">
         <v>0.257648</v>
@@ -1579,10 +1579,10 @@
         <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.009054533622238931</v>
+        <v>-0.007398015687884063</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.58698</v>
+        <v>-2.91026</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,31 +1626,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01254237</v>
+        <v>0.01249497</v>
       </c>
       <c r="F19" t="n">
-        <v>8901184461</v>
+        <v>8856846797</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>23847322</v>
+        <v>22092708</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01276074</v>
+        <v>0.01272728</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01249052</v>
+        <v>0.01243449</v>
       </c>
       <c r="K19" t="n">
-        <v>-3.131499559115e-05</v>
+        <v>-0.000240401238128117</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.22871</v>
+        <v>-1.88767</v>
       </c>
       <c r="M19" t="n">
-        <v>709245362584.6495</v>
+        <v>709245550890.849</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,16 +1691,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.06</v>
+        <v>9.01</v>
       </c>
       <c r="F20" t="n">
-        <v>8334089166</v>
+        <v>8289654987</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>442380</v>
+        <v>513731</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
@@ -1709,10 +1709,10 @@
         <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>0.04916048</v>
+        <v>-0.03364701529956093</v>
       </c>
       <c r="L20" t="n">
-        <v>0.54394</v>
+        <v>-0.37197</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T170645Z-be524b</t>
+          <t>20260928T234727Z-2816d9</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.224252</v>
+        <v>0.231162</v>
       </c>
       <c r="F21" t="n">
-        <v>7854903242</v>
+        <v>8084763830</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>619426342</v>
+        <v>804882888</v>
       </c>
       <c r="I21" t="n">
-        <v>0.230315</v>
+        <v>0.234286</v>
       </c>
       <c r="J21" t="n">
         <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00840275</v>
+        <v>0.0158957</v>
       </c>
       <c r="L21" t="n">
-        <v>4.06931</v>
+        <v>7.3842</v>
       </c>
       <c r="M21" t="n">
-        <v>34970168660.84914</v>
+        <v>35011603519.11985</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-28T17:04:20.000Z</t>
+          <t>2026-09-28T23:45:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -546,7 +546,7 @@
         <v>-786.8917941942054</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.93283</v>
+        <v>-0.96811</v>
       </c>
       <c r="M2" t="n">
         <v>20090481</v>
@@ -571,7 +571,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -611,7 +611,7 @@
         <v>7.15</v>
       </c>
       <c r="L3" t="n">
-        <v>0.26649</v>
+        <v>0.22628</v>
       </c>
       <c r="M3" t="n">
         <v>122087473.8258867</v>
@@ -636,7 +636,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -676,7 +676,7 @@
         <v>-3.3051755416236e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00331</v>
+        <v>-0.00743</v>
       </c>
       <c r="M4" t="n">
         <v>183874242892.1083</v>
@@ -701,7 +701,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -741,7 +741,7 @@
         <v>-13.44815267303102</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.73009</v>
+        <v>-1.78878</v>
       </c>
       <c r="M5" t="n">
         <v>133159615.43</v>
@@ -766,7 +766,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -806,7 +806,7 @@
         <v>-0.0167705133797087</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.10837</v>
+        <v>-1.17184</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -831,7 +831,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -871,7 +871,7 @@
         <v>9.628000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00963</v>
+        <v>0.00563</v>
       </c>
       <c r="M7" t="n">
         <v>74728156839.12137</v>
@@ -896,7 +896,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -936,7 +936,7 @@
         <v>-3.09094262113662</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.53671</v>
+        <v>-2.5772</v>
       </c>
       <c r="M8" t="n">
         <v>587852966.003577</v>
@@ -961,7 +961,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1001,7 +1001,7 @@
         <v>0.00208902</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6267200000000001</v>
+        <v>0.63358</v>
       </c>
       <c r="M9" t="n">
         <v>94972937401.45468</v>
@@ -1026,7 +1026,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1066,7 +1066,7 @@
         <v>-106.6162647415517</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.70353</v>
+        <v>-6.81608</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
@@ -1091,7 +1091,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1152,7 +1152,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1192,7 +1192,7 @@
         <v>-4.128673681278386</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.50706</v>
+        <v>-4.56371</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1217,7 +1217,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1257,7 +1257,7 @@
         <v>-0.002506339708048783</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6015</v>
+        <v>-2.67188</v>
       </c>
       <c r="M13" t="n">
         <v>156108476383.7052</v>
@@ -1282,7 +1282,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1322,7 +1322,7 @@
         <v>1.43</v>
       </c>
       <c r="L14" t="n">
-        <v>10.23398</v>
+        <v>10.01587</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1387,7 +1387,7 @@
         <v>-6.981361077774636</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.27359</v>
+        <v>-1.25552</v>
       </c>
       <c r="M15" t="n">
         <v>18810763.27902782</v>
@@ -1412,7 +1412,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1452,7 +1452,7 @@
         <v>-0.6211830702093124</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.73752</v>
+        <v>-0.78371</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1477,7 +1477,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1517,7 +1517,7 @@
         <v>0.00050491</v>
       </c>
       <c r="L17" t="n">
-        <v>0.05051</v>
+        <v>0.03653</v>
       </c>
       <c r="M17" t="n">
         <v>9785581101.437241</v>
@@ -1542,7 +1542,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1582,7 +1582,7 @@
         <v>-0.007398015687884063</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.91026</v>
+        <v>-2.96002</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1607,7 +1607,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1647,7 +1647,7 @@
         <v>-0.000240401238128117</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.88767</v>
+        <v>-1.98898</v>
       </c>
       <c r="M19" t="n">
         <v>709245550890.849</v>
@@ -1672,7 +1672,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1712,7 +1712,7 @@
         <v>-0.03364701529956093</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.37197</v>
+        <v>-0.36073</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1737,7 +1737,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T234727Z-2816d9</t>
+          <t>20260928T234827Z-635cce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1777,7 +1777,7 @@
         <v>0.0158957</v>
       </c>
       <c r="L21" t="n">
-        <v>7.3842</v>
+        <v>7.38063</v>
       </c>
       <c r="M21" t="n">
         <v>35011603519.11985</v>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,16 +525,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83568</v>
+        <v>83507</v>
       </c>
       <c r="F2" t="n">
-        <v>1679008903650</v>
+        <v>1677708109294</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>41791363643</v>
+        <v>41723595724</v>
       </c>
       <c r="I2" t="n">
         <v>84945</v>
@@ -543,16 +543,16 @@
         <v>82581</v>
       </c>
       <c r="K2" t="n">
-        <v>-786.8917941942054</v>
+        <v>-943.0202493105753</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.96811</v>
+        <v>-1.09898</v>
       </c>
       <c r="M2" t="n">
         <v>20090481</v>
       </c>
       <c r="N2" t="n">
-        <v>20090690</v>
+        <v>20090790</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,16 +590,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2690.99</v>
+        <v>2688.58</v>
       </c>
       <c r="F3" t="n">
-        <v>328578897942</v>
+        <v>328230175563</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17136731362</v>
+        <v>17124992169</v>
       </c>
       <c r="I3" t="n">
         <v>2717.37</v>
@@ -608,10 +608,10 @@
         <v>2636.99</v>
       </c>
       <c r="K3" t="n">
-        <v>7.15</v>
+        <v>1.57</v>
       </c>
       <c r="L3" t="n">
-        <v>0.22628</v>
+        <v>0.06862</v>
       </c>
       <c r="M3" t="n">
         <v>122087473.8258867</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,16 +655,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999718</v>
+        <v>0.99966</v>
       </c>
       <c r="F4" t="n">
-        <v>183821621020</v>
+        <v>183812509434</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>76015680441</v>
+        <v>75915231025</v>
       </c>
       <c r="I4" t="n">
         <v>0.9998359999999999</v>
@@ -673,10 +673,10 @@
         <v>0.999602</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.3051755416236e-05</v>
+        <v>-0.000117278820729316</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00743</v>
+        <v>-0.00747</v>
       </c>
       <c r="M4" t="n">
         <v>183874242892.1083</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,16 +720,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>763.86</v>
+        <v>763.48</v>
       </c>
       <c r="F5" t="n">
-        <v>101716240299</v>
+        <v>101664628051</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1060279716</v>
+        <v>1057079982</v>
       </c>
       <c r="I5" t="n">
         <v>783.74</v>
@@ -738,10 +738,10 @@
         <v>757.15</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.44815267303102</v>
+        <v>-15.24681102564591</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.78878</v>
+        <v>-1.92599</v>
       </c>
       <c r="M5" t="n">
         <v>133159615.43</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,13 +788,13 @@
         <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>94079399488</v>
+        <v>94017254994</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4363467206</v>
+        <v>4351788248</v>
       </c>
       <c r="I6" t="n">
         <v>1.53</v>
@@ -803,10 +803,10 @@
         <v>1.47</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0167705133797087</v>
+        <v>-0.02329244526184704</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.17184</v>
+        <v>-1.49005</v>
       </c>
       <c r="M6" t="n">
         <v>62879209849</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,16 +850,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999924</v>
+        <v>0.999868</v>
       </c>
       <c r="F7" t="n">
-        <v>74721963135</v>
+        <v>74718233752</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20683397359</v>
+        <v>20699802142</v>
       </c>
       <c r="I7" t="n">
         <v>0.99999</v>
@@ -868,10 +868,10 @@
         <v>0.99954</v>
       </c>
       <c r="K7" t="n">
-        <v>9.628000000000001e-05</v>
+        <v>1.402e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00563</v>
+        <v>0.00566</v>
       </c>
       <c r="M7" t="n">
         <v>74728156839.12137</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.76</v>
+        <v>118.72</v>
       </c>
       <c r="F8" t="n">
-        <v>69818192382</v>
+        <v>69795574274</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4131466796</v>
+        <v>4127386361</v>
       </c>
       <c r="I8" t="n">
         <v>122.78</v>
@@ -933,10 +933,10 @@
         <v>117.29</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.09094262113662</v>
+        <v>-3.397568826272234</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.5772</v>
+        <v>-2.76459</v>
       </c>
       <c r="M8" t="n">
         <v>587852966.003577</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,16 +980,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335415</v>
+        <v>0.335426</v>
       </c>
       <c r="F9" t="n">
-        <v>31859208139</v>
+        <v>31855177757</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>370370261</v>
+        <v>369670324</v>
       </c>
       <c r="I9" t="n">
         <v>0.336428</v>
@@ -998,10 +998,10 @@
         <v>0.332966</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00208902</v>
+        <v>0.0020336</v>
       </c>
       <c r="L9" t="n">
-        <v>0.63358</v>
+        <v>0.63876</v>
       </c>
       <c r="M9" t="n">
         <v>94972937401.45468</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,16 +1045,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1483.83</v>
+        <v>1482.49</v>
       </c>
       <c r="F10" t="n">
-        <v>25160679961</v>
+        <v>25135097323</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1246400077</v>
+        <v>1174267473</v>
       </c>
       <c r="I10" t="n">
         <v>1597.81</v>
@@ -1063,10 +1063,10 @@
         <v>1449.25</v>
       </c>
       <c r="K10" t="n">
-        <v>-106.6162647415517</v>
+        <v>-109.1756073353763</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.81608</v>
+        <v>-6.84076</v>
       </c>
       <c r="M10" t="n">
         <v>16954918.9155448</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1113,13 +1113,13 @@
         <v>1.004</v>
       </c>
       <c r="F11" t="n">
-        <v>23304050621</v>
+        <v>23305129622</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>346868158</v>
+        <v>346887269</v>
       </c>
       <c r="I11" t="n">
         <v>1.061</v>
@@ -1145,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,16 +1171,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.48</v>
+        <v>87.42</v>
       </c>
       <c r="F12" t="n">
-        <v>19463829972</v>
+        <v>19448324061</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>947092964</v>
+        <v>945834851</v>
       </c>
       <c r="I12" t="n">
         <v>92.02</v>
@@ -1189,10 +1189,10 @@
         <v>86.41</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.128673681278386</v>
+        <v>-4.268039658764607</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.56371</v>
+        <v>-4.60868</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,16 +1236,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.093836</v>
+        <v>0.09386799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>14648714526</v>
+        <v>14653287577</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1130717325</v>
+        <v>1169157074</v>
       </c>
       <c r="I13" t="n">
         <v>0.097729</v>
@@ -1254,10 +1254,10 @@
         <v>0.09178600000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002506339708048783</v>
+        <v>-0.003065646797607444</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.67188</v>
+        <v>-3.10572</v>
       </c>
       <c r="M13" t="n">
         <v>156108476383.7052</v>
@@ -1275,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,16 +1301,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.43</v>
+        <v>15.45</v>
       </c>
       <c r="F14" t="n">
-        <v>11540186445</v>
+        <v>11559102076</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1376547983</v>
+        <v>1380617023</v>
       </c>
       <c r="I14" t="n">
         <v>15.44</v>
@@ -1319,10 +1319,10 @@
         <v>13.54</v>
       </c>
       <c r="K14" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="L14" t="n">
-        <v>10.01587</v>
+        <v>10.05567</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1340,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,16 +1366,16 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>541.1799999999999</v>
+        <v>540.59</v>
       </c>
       <c r="F15" t="n">
-        <v>10184194565</v>
+        <v>10167764151</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>134844428</v>
+        <v>134744544</v>
       </c>
       <c r="I15" t="n">
         <v>552.95</v>
@@ -1384,10 +1384,10 @@
         <v>526.49</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.981361077774636</v>
+        <v>-7.731023366242312</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.25552</v>
+        <v>-1.42426</v>
       </c>
       <c r="M15" t="n">
         <v>18810763.27902782</v>
@@ -1405,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,16 +1431,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.59999999999999</v>
+        <v>83.55</v>
       </c>
       <c r="F16" t="n">
-        <v>9937666187</v>
+        <v>9929723944</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>143486762</v>
+        <v>140390630</v>
       </c>
       <c r="I16" t="n">
         <v>84.67</v>
@@ -1449,10 +1449,10 @@
         <v>82.44</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6211830702093124</v>
+        <v>-0.7241445535054822</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.78371</v>
+        <v>-0.8309800000000001</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1470,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,16 +1496,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0.9993880000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9787052779</v>
+        <v>9780099329</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>182329149</v>
+        <v>184157283</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
@@ -1514,10 +1514,10 @@
         <v>0.999263</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00050491</v>
+        <v>-0.000242087193309426</v>
       </c>
       <c r="L17" t="n">
-        <v>0.03653</v>
+        <v>0.04688</v>
       </c>
       <c r="M17" t="n">
         <v>9785581101.437241</v>
@@ -1535,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,16 +1561,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.246807</v>
+        <v>0.246928</v>
       </c>
       <c r="F18" t="n">
-        <v>9262416295</v>
+        <v>9267950685</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>688332747</v>
+        <v>688844092</v>
       </c>
       <c r="I18" t="n">
         <v>0.257648</v>
@@ -1579,10 +1579,10 @@
         <v>0.239932</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007398015687884063</v>
+        <v>-0.008754438216891397</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.96002</v>
+        <v>-3.43806</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1600,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,16 +1626,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01249497</v>
+        <v>0.01246908</v>
       </c>
       <c r="F19" t="n">
-        <v>8856846797</v>
+        <v>8843668256</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>22092708</v>
+        <v>24550183</v>
       </c>
       <c r="I19" t="n">
         <v>0.01272728</v>
@@ -1644,10 +1644,10 @@
         <v>0.01243449</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000240401238128117</v>
+        <v>-0.000276699067652026</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.98898</v>
+        <v>-2.10203</v>
       </c>
       <c r="M19" t="n">
         <v>709245550890.849</v>
@@ -1665,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1694,13 +1694,13 @@
         <v>9.01</v>
       </c>
       <c r="F20" t="n">
-        <v>8289654987</v>
+        <v>8291891423</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>513731</v>
+        <v>514783</v>
       </c>
       <c r="I20" t="n">
         <v>9.09</v>
@@ -1709,10 +1709,10 @@
         <v>8.99</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.03364701529956093</v>
+        <v>-0.02435654173043034</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.36073</v>
+        <v>-0.26776</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1730,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T234827Z-635cce</t>
+          <t>20260928T235236Z-ebdef0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.231162</v>
+        <v>0.231172</v>
       </c>
       <c r="F21" t="n">
-        <v>8084763830</v>
+        <v>8093216704</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>804882888</v>
+        <v>807501121</v>
       </c>
       <c r="I21" t="n">
         <v>0.234286</v>
@@ -1774,10 +1774,10 @@
         <v>0.207092</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0158957</v>
+        <v>0.01511079</v>
       </c>
       <c r="L21" t="n">
-        <v>7.38063</v>
+        <v>7.12082</v>
       </c>
       <c r="M21" t="n">
         <v>35011603519.11985</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-28T23:45:20.000Z</t>
+          <t>2026-09-28T23:50:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83507</v>
+        <v>83733</v>
       </c>
       <c r="F2" t="n">
-        <v>1677708109294</v>
+        <v>1682985218380</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>41723595724</v>
+        <v>34959956786</v>
       </c>
       <c r="I2" t="n">
-        <v>84945</v>
+        <v>85518</v>
       </c>
       <c r="J2" t="n">
-        <v>82581</v>
+        <v>82911</v>
       </c>
       <c r="K2" t="n">
-        <v>-943.0202493105753</v>
+        <v>729.05</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.09898</v>
+        <v>0.94076</v>
       </c>
       <c r="M2" t="n">
-        <v>20090481</v>
+        <v>20090909</v>
       </c>
       <c r="N2" t="n">
-        <v>20090790</v>
+        <v>20090909</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2688.58</v>
+        <v>2672.67</v>
       </c>
       <c r="F3" t="n">
-        <v>328230175563</v>
+        <v>326449172566</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17124992169</v>
+        <v>14871641419</v>
       </c>
       <c r="I3" t="n">
-        <v>2717.37</v>
+        <v>2736.98</v>
       </c>
       <c r="J3" t="n">
-        <v>2636.99</v>
+        <v>2657.67</v>
       </c>
       <c r="K3" t="n">
-        <v>1.57</v>
+        <v>-3.372896421189125</v>
       </c>
       <c r="L3" t="n">
-        <v>0.06862</v>
+        <v>-0.08332000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>122087473.8258867</v>
+        <v>122092940.7490518</v>
       </c>
       <c r="N3" t="n">
-        <v>122087473.8258867</v>
+        <v>122092940.7490518</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99966</v>
+        <v>0.999508</v>
       </c>
       <c r="F4" t="n">
-        <v>183812509434</v>
+        <v>183780430899</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>75915231025</v>
+        <v>63995119342</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9998359999999999</v>
+        <v>0.999907</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999602</v>
+        <v>0.999551</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000117278820729316</v>
+        <v>-0.000268402896748121</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00747</v>
+        <v>-0.02385</v>
       </c>
       <c r="M4" t="n">
-        <v>183874242892.1083</v>
+        <v>183870584013.1206</v>
       </c>
       <c r="N4" t="n">
-        <v>189285761986.9062</v>
+        <v>189337530060.8262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>763.48</v>
+        <v>766.1799999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>101664628051</v>
+        <v>102063628562</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1057079982</v>
+        <v>957021712</v>
       </c>
       <c r="I5" t="n">
-        <v>783.74</v>
+        <v>778.49</v>
       </c>
       <c r="J5" t="n">
-        <v>757.15</v>
+        <v>750.63</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.24681102564591</v>
+        <v>10.7</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.92599</v>
+        <v>1.43509</v>
       </c>
       <c r="M5" t="n">
-        <v>133159615.43</v>
+        <v>133159463.23</v>
       </c>
       <c r="N5" t="n">
-        <v>133159615.43</v>
+        <v>133159452.19</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,34 +785,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>94017254994</v>
+        <v>94386823528</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4351788248</v>
+        <v>3577972373</v>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02329244526184704</v>
+        <v>-0.01884122113988318</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.49005</v>
+        <v>-1.26995</v>
       </c>
       <c r="M6" t="n">
-        <v>62879209849</v>
+        <v>63092975951</v>
       </c>
       <c r="N6" t="n">
-        <v>99985622230</v>
+        <v>99985612577</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999868</v>
+        <v>0.999744</v>
       </c>
       <c r="F7" t="n">
-        <v>74718233752</v>
+        <v>74252256183</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20699802142</v>
+        <v>17858609980</v>
       </c>
       <c r="I7" t="n">
-        <v>0.99999</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99954</v>
+        <v>0.999736</v>
       </c>
       <c r="K7" t="n">
-        <v>1.402e-05</v>
+        <v>-0.000157659049448533</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00566</v>
+        <v>-0.01205</v>
       </c>
       <c r="M7" t="n">
-        <v>74728156839.12137</v>
+        <v>74271158723.4574</v>
       </c>
       <c r="N7" t="n">
-        <v>74784667843.85722</v>
+        <v>74219208687.05562</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.72</v>
+        <v>118.35</v>
       </c>
       <c r="F8" t="n">
-        <v>69795574274</v>
+        <v>69629312154</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4127386361</v>
+        <v>4170824395</v>
       </c>
       <c r="I8" t="n">
-        <v>122.78</v>
+        <v>122.6</v>
       </c>
       <c r="J8" t="n">
-        <v>117.29</v>
+        <v>117.46</v>
       </c>
       <c r="K8" t="n">
-        <v>-3.397568826272234</v>
+        <v>0.04096635</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.76459</v>
+        <v>0.14214</v>
       </c>
       <c r="M8" t="n">
-        <v>587852966.003577</v>
+        <v>588005786.7804404</v>
       </c>
       <c r="N8" t="n">
-        <v>634919033.5810466</v>
+        <v>634996134.9104906</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335426</v>
+        <v>0.338719</v>
       </c>
       <c r="F9" t="n">
-        <v>31855177757</v>
+        <v>32179982004</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>369670324</v>
+        <v>397692650</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336428</v>
+        <v>0.340711</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332966</v>
+        <v>0.333923</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0020336</v>
+        <v>0.00456806</v>
       </c>
       <c r="L9" t="n">
-        <v>0.63876</v>
+        <v>1.36379</v>
       </c>
       <c r="M9" t="n">
-        <v>94972937401.45468</v>
+        <v>94975594210.46889</v>
       </c>
       <c r="N9" t="n">
-        <v>94973450849.00569</v>
+        <v>94975566451.06459</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,140 +1019,144 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>figure-heloc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>figr_heloc</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Figure Heloc</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1482.49</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>25135097323</v>
+        <v>24032326816</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>1174267473</v>
+        <v>542904134</v>
       </c>
       <c r="I10" t="n">
-        <v>1597.81</v>
+        <v>1.03</v>
       </c>
       <c r="J10" t="n">
-        <v>1449.25</v>
+        <v>1.001</v>
       </c>
       <c r="K10" t="n">
-        <v>-109.1756073353763</v>
+        <v>0.02890712</v>
       </c>
       <c r="L10" t="n">
-        <v>-6.84076</v>
+        <v>2.88499</v>
       </c>
       <c r="M10" t="n">
-        <v>16954918.9155448</v>
+        <v>23338281494.918</v>
       </c>
       <c r="N10" t="n">
-        <v>16957822.0405448</v>
+        <v>23338281494.918</v>
       </c>
       <c r="O10" t="n">
-        <v>3191.93</v>
+        <v>1.062</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2016-10-28T16:00:00.000Z</t>
+          <t>2026-09-27T13:07:30.000Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>figure-heloc</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>figr_heloc</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Figure Heloc</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1.004</v>
+        <v>1412.92</v>
       </c>
       <c r="F11" t="n">
-        <v>23305129622</v>
+        <v>23993997090</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>346887269</v>
+        <v>1070334527</v>
       </c>
       <c r="I11" t="n">
-        <v>1.061</v>
+        <v>1490.56</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
+        <v>1382.17</v>
+      </c>
+      <c r="K11" t="n">
+        <v>21.51</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.89807</v>
+      </c>
       <c r="M11" t="n">
-        <v>23202972251.118</v>
+        <v>16960081.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>23202972251.118</v>
+        <v>16960843.9155448</v>
       </c>
       <c r="O11" t="n">
-        <v>1.062</v>
+        <v>3191.93</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-27T13:07:30.000Z</t>
+          <t>2016-10-28T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.42</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19448324061</v>
+        <v>19102276091</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>945834851</v>
+        <v>856259432</v>
       </c>
       <c r="I12" t="n">
-        <v>92.02</v>
+        <v>87.78</v>
       </c>
       <c r="J12" t="n">
-        <v>86.41</v>
+        <v>84.94</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.268039658764607</v>
+        <v>-0.774846804013734</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.60868</v>
+        <v>-0.77765</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09386799999999999</v>
+        <v>0.094495</v>
       </c>
       <c r="F13" t="n">
-        <v>14653287577</v>
+        <v>14768716178</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1169157074</v>
+        <v>1029914116</v>
       </c>
       <c r="I13" t="n">
-        <v>0.097729</v>
+        <v>0.097941</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09178600000000001</v>
+        <v>0.09289799999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003065646797607444</v>
+        <v>0.00081257</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.10572</v>
+        <v>0.96385</v>
       </c>
       <c r="M13" t="n">
-        <v>156108476383.7052</v>
+        <v>156131006383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156108686383.7052</v>
+        <v>171843213126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>15.45</v>
+        <v>14.14</v>
       </c>
       <c r="F14" t="n">
-        <v>11559102076</v>
+        <v>10586902220</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>1380617023</v>
+        <v>604859057</v>
       </c>
       <c r="I14" t="n">
-        <v>15.44</v>
+        <v>14.88</v>
       </c>
       <c r="J14" t="n">
-        <v>13.54</v>
+        <v>14.07</v>
       </c>
       <c r="K14" t="n">
-        <v>1.4</v>
+        <v>-0.6552530784628097</v>
       </c>
       <c r="L14" t="n">
-        <v>10.05567</v>
+        <v>-4.35529</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>540.59</v>
+        <v>537.66</v>
       </c>
       <c r="F15" t="n">
-        <v>10167764151</v>
+        <v>10116067900</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>134744544</v>
+        <v>106446294</v>
       </c>
       <c r="I15" t="n">
-        <v>552.95</v>
+        <v>550.1900000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>526.49</v>
+        <v>536.75</v>
       </c>
       <c r="K15" t="n">
-        <v>-7.731023366242312</v>
+        <v>-1.387822398318121</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.42426</v>
+        <v>-0.26448</v>
       </c>
       <c r="M15" t="n">
-        <v>18810763.27902782</v>
+        <v>18811450.26886855</v>
       </c>
       <c r="N15" t="n">
-        <v>18810782.47899366</v>
+        <v>18811489.86840629</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1405,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.55</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9929723944</v>
+        <v>9931440658</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>140390630</v>
+        <v>125736613</v>
       </c>
       <c r="I16" t="n">
-        <v>84.67</v>
+        <v>85.44</v>
       </c>
       <c r="J16" t="n">
-        <v>82.44</v>
+        <v>82.89</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.7241445535054822</v>
+        <v>0.461985</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.8309800000000001</v>
+        <v>0.65469</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
@@ -1470,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9993880000000001</v>
+        <v>0.99949</v>
       </c>
       <c r="F17" t="n">
-        <v>9780099329</v>
+        <v>9802734613</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>184157283</v>
+        <v>169565227</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999263</v>
+        <v>0.999121</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000242087193309426</v>
+        <v>0.00020221</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04688</v>
+        <v>0.02412</v>
       </c>
       <c r="M17" t="n">
-        <v>9785581101.437241</v>
+        <v>9807716175.04208</v>
       </c>
       <c r="N17" t="n">
-        <v>9785581101.437241</v>
+        <v>9801796986.491272</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1535,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.246928</v>
+        <v>0.243803</v>
       </c>
       <c r="F18" t="n">
-        <v>9267950685</v>
+        <v>9160732353</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>688844092</v>
+        <v>517060573</v>
       </c>
       <c r="I18" t="n">
-        <v>0.257648</v>
+        <v>0.256263</v>
       </c>
       <c r="J18" t="n">
-        <v>0.239932</v>
+        <v>0.240145</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008754438216891397</v>
+        <v>-0.001614369320090098</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.43806</v>
+        <v>-0.5736</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01246908</v>
+        <v>0.01231888</v>
       </c>
       <c r="F19" t="n">
-        <v>8843668256</v>
+        <v>8736612893</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>24550183</v>
+        <v>23995582</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01272728</v>
+        <v>0.01289522</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01243449</v>
+        <v>0.01218467</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000276699067652026</v>
+        <v>0.00011486</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.10203</v>
+        <v>0.8652</v>
       </c>
       <c r="M19" t="n">
-        <v>709245550890.849</v>
+        <v>709247494967.3281</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.01</v>
+        <v>9.02</v>
       </c>
       <c r="F20" t="n">
-        <v>8291891423</v>
+        <v>8301155927</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>514783</v>
+        <v>680856</v>
       </c>
       <c r="I20" t="n">
-        <v>9.09</v>
+        <v>9.1</v>
       </c>
       <c r="J20" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02435654173043034</v>
+        <v>0.01950777</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.26776</v>
+        <v>0.21646</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260928T235236Z-ebdef0</t>
+          <t>20260930T152623Z-6f5bf7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.231172</v>
+        <v>0.221314</v>
       </c>
       <c r="F21" t="n">
-        <v>8093216704</v>
+        <v>7757401322</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>807501121</v>
+        <v>404294489</v>
       </c>
       <c r="I21" t="n">
-        <v>0.234286</v>
+        <v>0.231452</v>
       </c>
       <c r="J21" t="n">
-        <v>0.207092</v>
+        <v>0.219711</v>
       </c>
       <c r="K21" t="n">
-        <v>0.01511079</v>
+        <v>-0.005143103937809923</v>
       </c>
       <c r="L21" t="n">
-        <v>7.12082</v>
+        <v>-2.26628</v>
       </c>
       <c r="M21" t="n">
-        <v>35011603519.11985</v>
+        <v>35021215736.39494</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-28T23:50:30.000Z</t>
+          <t>2026-09-30T15:24:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83733</v>
+        <v>83851</v>
       </c>
       <c r="F2" t="n">
-        <v>1682985218380</v>
+        <v>1684091366610</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>34959956786</v>
+        <v>30990564895</v>
       </c>
       <c r="I2" t="n">
-        <v>85518</v>
+        <v>84422</v>
       </c>
       <c r="J2" t="n">
-        <v>82911</v>
+        <v>83182</v>
       </c>
       <c r="K2" t="n">
-        <v>729.05</v>
+        <v>-245.2135340266686</v>
       </c>
       <c r="L2" t="n">
-        <v>0.94076</v>
+        <v>-0.29159</v>
       </c>
       <c r="M2" t="n">
         <v>20090909</v>
       </c>
       <c r="N2" t="n">
-        <v>20090909</v>
+        <v>20091365</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2672.67</v>
+        <v>2676.18</v>
       </c>
       <c r="F3" t="n">
-        <v>326449172566</v>
+        <v>326535788715</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>14871641419</v>
+        <v>13127468864</v>
       </c>
       <c r="I3" t="n">
-        <v>2736.98</v>
+        <v>2720.25</v>
       </c>
       <c r="J3" t="n">
-        <v>2657.67</v>
+        <v>2667.89</v>
       </c>
       <c r="K3" t="n">
-        <v>-3.372896421189125</v>
+        <v>-6.144350369201675</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.08332000000000001</v>
+        <v>-0.22907</v>
       </c>
       <c r="M3" t="n">
-        <v>122092940.7490518</v>
+        <v>122095846.2324841</v>
       </c>
       <c r="N3" t="n">
-        <v>122092940.7490518</v>
+        <v>122095846.2324841</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999508</v>
+        <v>0.999683</v>
       </c>
       <c r="F4" t="n">
-        <v>183780430899</v>
+        <v>183807116612</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>63995119342</v>
+        <v>60857792199</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999907</v>
+        <v>0.999792</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999551</v>
+        <v>0.9993610000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000268402896748121</v>
+        <v>0.00020616</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02385</v>
+        <v>0.02063</v>
       </c>
       <c r="M4" t="n">
-        <v>183870584013.1206</v>
+        <v>183870683998.9219</v>
       </c>
       <c r="N4" t="n">
-        <v>189337530060.8262</v>
+        <v>189337630047.8362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>766.1799999999999</v>
+        <v>764.71</v>
       </c>
       <c r="F5" t="n">
-        <v>102063628562</v>
+        <v>101800481697</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>957021712</v>
+        <v>642547832</v>
       </c>
       <c r="I5" t="n">
-        <v>778.49</v>
+        <v>772.0599999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>750.63</v>
+        <v>763.42</v>
       </c>
       <c r="K5" t="n">
-        <v>10.7</v>
+        <v>-3.280642744291981</v>
       </c>
       <c r="L5" t="n">
-        <v>1.43509</v>
+        <v>-0.42717</v>
       </c>
       <c r="M5" t="n">
-        <v>133159463.23</v>
+        <v>133159374.13</v>
       </c>
       <c r="N5" t="n">
-        <v>133159452.19</v>
+        <v>133159364.89</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="F6" t="n">
-        <v>94386823528</v>
+        <v>93375944438</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3577972373</v>
+        <v>2223101456</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="J6" t="n">
         <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.01884122113988318</v>
+        <v>-0.0216405295083455</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.26995</v>
+        <v>-1.44083</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999744</v>
+        <v>0.999928</v>
       </c>
       <c r="F7" t="n">
-        <v>74252256183</v>
+        <v>74164693715</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17858609980</v>
+        <v>19683088972</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999736</v>
+        <v>0.9993109999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000157659049448533</v>
+        <v>0.00018685</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01205</v>
+        <v>0.01869</v>
       </c>
       <c r="M7" t="n">
-        <v>74271158723.4574</v>
+        <v>74172496327.15332</v>
       </c>
       <c r="N7" t="n">
-        <v>74219208687.05562</v>
+        <v>74183779202.68307</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>118.35</v>
+        <v>117.03</v>
       </c>
       <c r="F8" t="n">
-        <v>69629312154</v>
+        <v>68799947859</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4170824395</v>
+        <v>3378855083</v>
       </c>
       <c r="I8" t="n">
-        <v>122.6</v>
+        <v>120.44</v>
       </c>
       <c r="J8" t="n">
-        <v>117.46</v>
+        <v>116.75</v>
       </c>
       <c r="K8" t="n">
-        <v>0.04096635</v>
+        <v>-2.03975679522398</v>
       </c>
       <c r="L8" t="n">
-        <v>0.14214</v>
+        <v>-1.71301</v>
       </c>
       <c r="M8" t="n">
-        <v>588005786.7804404</v>
+        <v>588076201.7255846</v>
       </c>
       <c r="N8" t="n">
-        <v>634996134.9104906</v>
+        <v>635073850.4986274</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.338719</v>
+        <v>0.333672</v>
       </c>
       <c r="F9" t="n">
-        <v>32179982004</v>
+        <v>31688194712</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>397692650</v>
+        <v>416861878</v>
       </c>
       <c r="I9" t="n">
-        <v>0.340711</v>
+        <v>0.33856</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333923</v>
+        <v>0.332343</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00456806</v>
+        <v>-0.004905037574011228</v>
       </c>
       <c r="L9" t="n">
-        <v>1.36379</v>
+        <v>-1.44872</v>
       </c>
       <c r="M9" t="n">
-        <v>94975594210.46889</v>
+        <v>94976619405.13579</v>
       </c>
       <c r="N9" t="n">
-        <v>94975566451.06459</v>
+        <v>94976612142.31288</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.03</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>24032326816</v>
+        <v>24038818214</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>542904134</v>
+        <v>271462226</v>
       </c>
       <c r="I10" t="n">
-        <v>1.03</v>
+        <v>1.031</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001</v>
+        <v>1.026</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02890712</v>
+        <v>-0.002372046996639066</v>
       </c>
       <c r="L10" t="n">
-        <v>2.88499</v>
+        <v>-0.23037</v>
       </c>
       <c r="M10" t="n">
-        <v>23338281494.918</v>
+        <v>23399762227.818</v>
       </c>
       <c r="N10" t="n">
-        <v>23338281494.918</v>
+        <v>23399762227.818</v>
       </c>
       <c r="O10" t="n">
         <v>1.062</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1412.92</v>
+        <v>1372.05</v>
       </c>
       <c r="F11" t="n">
-        <v>23993997090</v>
+        <v>23253223934</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1070334527</v>
+        <v>860638673</v>
       </c>
       <c r="I11" t="n">
-        <v>1490.56</v>
+        <v>1478.71</v>
       </c>
       <c r="J11" t="n">
-        <v>1382.17</v>
+        <v>1368.07</v>
       </c>
       <c r="K11" t="n">
-        <v>21.51</v>
+        <v>-62.7551059101495</v>
       </c>
       <c r="L11" t="n">
-        <v>1.89807</v>
+        <v>-4.37378</v>
       </c>
       <c r="M11" t="n">
         <v>16960081.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>16960843.9155448</v>
+        <v>16962586.1030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.79000000000001</v>
+        <v>87.98</v>
       </c>
       <c r="F12" t="n">
-        <v>19102276091</v>
+        <v>19553534576</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>856259432</v>
+        <v>1083754243</v>
       </c>
       <c r="I12" t="n">
-        <v>87.78</v>
+        <v>91.75</v>
       </c>
       <c r="J12" t="n">
-        <v>84.94</v>
+        <v>87.66</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.774846804013734</v>
+        <v>1.64</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.77765</v>
+        <v>1.89668</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.094495</v>
+        <v>0.093935</v>
       </c>
       <c r="F13" t="n">
-        <v>14768716178</v>
+        <v>14659795305</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1029914116</v>
+        <v>662592065</v>
       </c>
       <c r="I13" t="n">
-        <v>0.097941</v>
+        <v>0.095997</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09289799999999999</v>
+        <v>0.093518</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00081257</v>
+        <v>-0.001176711942266123</v>
       </c>
       <c r="L13" t="n">
-        <v>0.96385</v>
+        <v>-1.23719</v>
       </c>
       <c r="M13" t="n">
-        <v>156131006383.7052</v>
+        <v>156144326383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171843213126.579</v>
+        <v>156144846383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.14</v>
+        <v>14.23</v>
       </c>
       <c r="F14" t="n">
-        <v>10586902220</v>
+        <v>10637886270</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>604859057</v>
+        <v>427706963</v>
       </c>
       <c r="I14" t="n">
-        <v>14.88</v>
+        <v>14.54</v>
       </c>
       <c r="J14" t="n">
-        <v>14.07</v>
+        <v>14.15</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.6552530784628097</v>
+        <v>-0.002592197671384966</v>
       </c>
       <c r="L14" t="n">
-        <v>-4.35529</v>
+        <v>-0.01821</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>537.66</v>
+        <v>538.3200000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>10116067900</v>
+        <v>10123627651</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>106446294</v>
+        <v>104973745</v>
       </c>
       <c r="I15" t="n">
-        <v>550.1900000000001</v>
+        <v>552.8200000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>536.75</v>
+        <v>537.22</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.387822398318121</v>
+        <v>-1.216495108928143</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.26448</v>
+        <v>-0.22547</v>
       </c>
       <c r="M15" t="n">
-        <v>18811450.26886855</v>
+        <v>18811903.25693148</v>
       </c>
       <c r="N15" t="n">
-        <v>18811489.86840629</v>
+        <v>18811936.25637681</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.54000000000001</v>
+        <v>83.61</v>
       </c>
       <c r="F16" t="n">
-        <v>9931440658</v>
+        <v>9934720747</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>125736613</v>
+        <v>98984275</v>
       </c>
       <c r="I16" t="n">
-        <v>85.44</v>
+        <v>84.34</v>
       </c>
       <c r="J16" t="n">
-        <v>82.89</v>
+        <v>83.12</v>
       </c>
       <c r="K16" t="n">
-        <v>0.461985</v>
+        <v>-0.2401699842165073</v>
       </c>
       <c r="L16" t="n">
-        <v>0.65469</v>
+        <v>-0.28643</v>
       </c>
       <c r="M16" t="n">
         <v>118852171</v>
       </c>
       <c r="N16" t="n">
-        <v>293421670</v>
+        <v>293389244</v>
       </c>
       <c r="O16" t="n">
         <v>87.91</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.99949</v>
+        <v>0.999881</v>
       </c>
       <c r="F17" t="n">
-        <v>9802734613</v>
+        <v>9915835445</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>169565227</v>
+        <v>179238630</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999121</v>
+        <v>0.999294</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00020221</v>
+        <v>0.00040836</v>
       </c>
       <c r="L17" t="n">
-        <v>0.02412</v>
+        <v>0.04086</v>
       </c>
       <c r="M17" t="n">
-        <v>9807716175.04208</v>
+        <v>9917344885.967585</v>
       </c>
       <c r="N17" t="n">
-        <v>9801796986.491272</v>
+        <v>9923468959.345402</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.243803</v>
+        <v>0.244586</v>
       </c>
       <c r="F18" t="n">
-        <v>9160732353</v>
+        <v>9175548003</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>517060573</v>
+        <v>473072687</v>
       </c>
       <c r="I18" t="n">
-        <v>0.256263</v>
+        <v>0.254096</v>
       </c>
       <c r="J18" t="n">
-        <v>0.240145</v>
+        <v>0.241802</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.001614369320090098</v>
+        <v>-0.001178743552030403</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5736</v>
+        <v>-0.47962</v>
       </c>
       <c r="M18" t="n">
         <v>37535193928.91081</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01231888</v>
+        <v>0.01180163</v>
       </c>
       <c r="F19" t="n">
-        <v>8736612893</v>
+        <v>8377720104</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>23995582</v>
+        <v>11420057</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01289522</v>
+        <v>0.01239808</v>
       </c>
       <c r="J19" t="n">
-        <v>0.01218467</v>
+        <v>0.0120899</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00011486</v>
+        <v>-0.000513673620672875</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8652</v>
+        <v>-4.17102</v>
       </c>
       <c r="M19" t="n">
-        <v>709247494967.3281</v>
+        <v>709247692082.7036</v>
       </c>
       <c r="N19" t="n">
         <v>1142408526965.963</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>9.02</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>8301155927</v>
+        <v>8146979388</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>680856</v>
+        <v>550518</v>
       </c>
       <c r="I20" t="n">
-        <v>9.1</v>
+        <v>9.07</v>
       </c>
       <c r="J20" t="n">
-        <v>9</v>
+        <v>8.81</v>
       </c>
       <c r="K20" t="n">
-        <v>0.01950777</v>
+        <v>-0.1675847110773105</v>
       </c>
       <c r="L20" t="n">
-        <v>0.21646</v>
+        <v>-1.85704</v>
       </c>
       <c r="M20" t="n">
         <v>919857851.9</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20260930T152623Z-6f5bf7</t>
+          <t>20261001T154712Z-f23fce</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.221314</v>
+        <v>0.218152</v>
       </c>
       <c r="F21" t="n">
-        <v>7757401322</v>
+        <v>7637950972</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>404294489</v>
+        <v>266302070</v>
       </c>
       <c r="I21" t="n">
-        <v>0.231452</v>
+        <v>0.230817</v>
       </c>
       <c r="J21" t="n">
-        <v>0.219711</v>
+        <v>0.217818</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005143103937809923</v>
+        <v>-0.003998353064852578</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.26628</v>
+        <v>-1.79984</v>
       </c>
       <c r="M21" t="n">
-        <v>35021215736.39494</v>
+        <v>35022047284.21333</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-09-30T15:24:20.000Z</t>
+          <t>2026-10-01T15:44:20.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83851</v>
+        <v>85500</v>
       </c>
       <c r="F2" t="n">
-        <v>1684091366610</v>
+        <v>1718568233595</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>30990564895</v>
+        <v>42498423772</v>
       </c>
       <c r="I2" t="n">
-        <v>84422</v>
+        <v>87086</v>
       </c>
       <c r="J2" t="n">
-        <v>83182</v>
+        <v>84068</v>
       </c>
       <c r="K2" t="n">
-        <v>-245.2135340266686</v>
+        <v>1433.39</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.29159</v>
+        <v>1.70506</v>
       </c>
       <c r="M2" t="n">
-        <v>20090909</v>
+        <v>20092434</v>
       </c>
       <c r="N2" t="n">
-        <v>20091365</v>
+        <v>20092503</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2676.18</v>
+        <v>2704.01</v>
       </c>
       <c r="F3" t="n">
-        <v>326535788715</v>
+        <v>330288217977</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13127468864</v>
+        <v>17285850908</v>
       </c>
       <c r="I3" t="n">
-        <v>2720.25</v>
+        <v>2768.44</v>
       </c>
       <c r="J3" t="n">
-        <v>2667.89</v>
+        <v>2677.23</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.144350369201675</v>
+        <v>16.98</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.22907</v>
+        <v>0.63198</v>
       </c>
       <c r="M3" t="n">
-        <v>122095846.2324841</v>
+        <v>122098689.5021315</v>
       </c>
       <c r="N3" t="n">
-        <v>122095846.2324841</v>
+        <v>122098689.5021315</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999683</v>
+        <v>0.999821</v>
       </c>
       <c r="F4" t="n">
-        <v>183807116612</v>
+        <v>184032029420</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>60857792199</v>
+        <v>76697955011</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999792</v>
+        <v>0.9999209999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9993610000000001</v>
+        <v>0.999586</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00020616</v>
+        <v>8.614999999999999e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02063</v>
+        <v>0.008619999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>183870683998.9219</v>
+        <v>184057713983.9332</v>
       </c>
       <c r="N4" t="n">
-        <v>189337630047.8362</v>
+        <v>189524660047.5562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>764.71</v>
+        <v>774.39</v>
       </c>
       <c r="F5" t="n">
-        <v>101800481697</v>
+        <v>103140693116</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>642547832</v>
+        <v>909316444</v>
       </c>
       <c r="I5" t="n">
-        <v>772.0599999999999</v>
+        <v>783.58</v>
       </c>
       <c r="J5" t="n">
-        <v>763.42</v>
+        <v>765.99</v>
       </c>
       <c r="K5" t="n">
-        <v>-3.280642744291981</v>
+        <v>8</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.42717</v>
+        <v>1.04367</v>
       </c>
       <c r="M5" t="n">
-        <v>133159374.13</v>
+        <v>133159291.91</v>
       </c>
       <c r="N5" t="n">
-        <v>133159364.89</v>
+        <v>133159275.87</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="F6" t="n">
-        <v>93375944438</v>
+        <v>95186878143</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2223101456</v>
+        <v>3273192539</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
         <v>1.48</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0216405295083455</v>
+        <v>0.02510336</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.44083</v>
+        <v>1.69292</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999928</v>
+        <v>0.9999</v>
       </c>
       <c r="F7" t="n">
-        <v>74164693715</v>
+        <v>73926183386</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19683088972</v>
+        <v>23498092619</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9993109999999999</v>
+        <v>0.999514</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00018685</v>
+        <v>-1.7638395622854e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01869</v>
+        <v>-0.00176</v>
       </c>
       <c r="M7" t="n">
-        <v>74172496327.15332</v>
+        <v>73930687451.97484</v>
       </c>
       <c r="N7" t="n">
-        <v>74183779202.68307</v>
+        <v>74032177689.71619</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>117.03</v>
+        <v>120.16</v>
       </c>
       <c r="F8" t="n">
-        <v>68799947859</v>
+        <v>70736536608</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3378855083</v>
+        <v>4542940138</v>
       </c>
       <c r="I8" t="n">
-        <v>120.44</v>
+        <v>123.55</v>
       </c>
       <c r="J8" t="n">
-        <v>116.75</v>
+        <v>116.97</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.03975679522398</v>
+        <v>2.98</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.71301</v>
+        <v>2.54295</v>
       </c>
       <c r="M8" t="n">
-        <v>588076201.7255846</v>
+        <v>588075145.1455896</v>
       </c>
       <c r="N8" t="n">
-        <v>635073850.4986274</v>
+        <v>635072790.6347431</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.333672</v>
+        <v>0.335006</v>
       </c>
       <c r="F9" t="n">
-        <v>31688194712</v>
+        <v>31819594052</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>416861878</v>
+        <v>319102987</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33856</v>
+        <v>0.336268</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332343</v>
+        <v>0.333825</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.004905037574011228</v>
+        <v>0.00173538</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.44872</v>
+        <v>0.52071</v>
       </c>
       <c r="M9" t="n">
-        <v>94976619405.13579</v>
+        <v>94977784305.8391</v>
       </c>
       <c r="N9" t="n">
-        <v>94976612142.31288</v>
+        <v>94977771159.73709</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.027</v>
+        <v>1.012</v>
       </c>
       <c r="F10" t="n">
-        <v>24038818214</v>
+        <v>23672068222</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>271462226</v>
+        <v>13685769</v>
       </c>
       <c r="I10" t="n">
         <v>1.031</v>
       </c>
       <c r="J10" t="n">
-        <v>1.026</v>
+        <v>1.012</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.002372046996639066</v>
+        <v>-0.01531564108646744</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.23037</v>
+        <v>-1.49131</v>
       </c>
       <c r="M10" t="n">
         <v>23399762227.818</v>
       </c>
       <c r="N10" t="n">
-        <v>23399762227.818</v>
+        <v>23434048822.568</v>
       </c>
       <c r="O10" t="n">
         <v>1.062</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1372.05</v>
+        <v>1367.6</v>
       </c>
       <c r="F11" t="n">
-        <v>23253223934</v>
+        <v>23176621404</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>860638673</v>
+        <v>1229193289</v>
       </c>
       <c r="I11" t="n">
-        <v>1478.71</v>
+        <v>1408</v>
       </c>
       <c r="J11" t="n">
-        <v>1368.07</v>
+        <v>1305.82</v>
       </c>
       <c r="K11" t="n">
-        <v>-62.7551059101495</v>
+        <v>-8.32583717670127</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.37378</v>
+        <v>-0.60511</v>
       </c>
       <c r="M11" t="n">
         <v>16960081.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>16962586.1030448</v>
+        <v>16964425.1655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="F12" t="n">
-        <v>19553534576</v>
+        <v>19902424701</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1083754243</v>
+        <v>915352448</v>
       </c>
       <c r="I12" t="n">
-        <v>91.75</v>
+        <v>91.44</v>
       </c>
       <c r="J12" t="n">
-        <v>87.66</v>
+        <v>86.5</v>
       </c>
       <c r="K12" t="n">
-        <v>1.64</v>
+        <v>0.938259</v>
       </c>
       <c r="L12" t="n">
-        <v>1.89668</v>
+        <v>1.06047</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.093935</v>
+        <v>0.095203</v>
       </c>
       <c r="F13" t="n">
-        <v>14659795305</v>
+        <v>14874263523</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>662592065</v>
+        <v>941725006</v>
       </c>
       <c r="I13" t="n">
-        <v>0.095997</v>
+        <v>0.09784900000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.093518</v>
+        <v>0.09320000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001176711942266123</v>
+        <v>0.00116103</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.23719</v>
+        <v>1.23459</v>
       </c>
       <c r="M13" t="n">
-        <v>156144326383.7052</v>
+        <v>156158436383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156144846383.7052</v>
+        <v>171870613126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.23</v>
+        <v>14.2</v>
       </c>
       <c r="F14" t="n">
-        <v>10637886270</v>
+        <v>10629088978</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>427706963</v>
+        <v>543682903</v>
       </c>
       <c r="I14" t="n">
-        <v>14.54</v>
+        <v>14.64</v>
       </c>
       <c r="J14" t="n">
-        <v>14.15</v>
+        <v>14.17</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.002592197671384966</v>
+        <v>-0.09491227374897981</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01821</v>
+        <v>-0.66396</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>538.3200000000001</v>
+        <v>541.59</v>
       </c>
       <c r="F15" t="n">
-        <v>10123627651</v>
+        <v>10195246972</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>104973745</v>
+        <v>124020280</v>
       </c>
       <c r="I15" t="n">
-        <v>552.8200000000001</v>
+        <v>550.88</v>
       </c>
       <c r="J15" t="n">
-        <v>537.22</v>
+        <v>540.0700000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.216495108928143</v>
+        <v>3.11</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.22547</v>
+        <v>0.57797</v>
       </c>
       <c r="M15" t="n">
-        <v>18811903.25693148</v>
+        <v>18812327.44954666</v>
       </c>
       <c r="N15" t="n">
-        <v>18811936.25637681</v>
+        <v>18812370.64941302</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,31 +1435,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>83.61</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9934720747</v>
+        <v>10107594626</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>98984275</v>
+        <v>131162196</v>
       </c>
       <c r="I16" t="n">
-        <v>84.34</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>83.12</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2401699842165073</v>
+        <v>1.21</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.28643</v>
+        <v>1.44729</v>
       </c>
       <c r="M16" t="n">
-        <v>118852171</v>
+        <v>118819745</v>
       </c>
       <c r="N16" t="n">
         <v>293389244</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999881</v>
+        <v>0.999754</v>
       </c>
       <c r="F17" t="n">
-        <v>9915835445</v>
+        <v>9954572707</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>179238630</v>
+        <v>308529175</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999294</v>
+        <v>0.999521</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00040836</v>
+        <v>-0.000172617139321152</v>
       </c>
       <c r="L17" t="n">
-        <v>0.04086</v>
+        <v>-0.01726</v>
       </c>
       <c r="M17" t="n">
-        <v>9917344885.967585</v>
+        <v>9956158465.499102</v>
       </c>
       <c r="N17" t="n">
-        <v>9923468959.345402</v>
+        <v>9957439061.486336</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,31 +1565,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.244586</v>
+        <v>0.251719</v>
       </c>
       <c r="F18" t="n">
-        <v>9175548003</v>
+        <v>9452790749</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>473072687</v>
+        <v>596723058</v>
       </c>
       <c r="I18" t="n">
-        <v>0.254096</v>
+        <v>0.258534</v>
       </c>
       <c r="J18" t="n">
-        <v>0.241802</v>
+        <v>0.244271</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.001178743552030403</v>
+        <v>0.00693412</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.47962</v>
+        <v>2.83275</v>
       </c>
       <c r="M18" t="n">
-        <v>37535193928.91081</v>
+        <v>37541298084.96014</v>
       </c>
       <c r="N18" t="n">
         <v>45000000000</v>
@@ -1604,144 +1604,144 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01180163</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8377720104</v>
+        <v>8247023571</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>11420057</v>
+        <v>297535</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01239808</v>
+        <v>9</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0120899</v>
+        <v>8.85</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.000513673620672875</v>
+        <v>0.113304</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.17102</v>
+        <v>1.27997</v>
       </c>
       <c r="M19" t="n">
-        <v>709247692082.7036</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1142408526965.963</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01946402</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.859999999999999</v>
+        <v>0.01146963</v>
       </c>
       <c r="F20" t="n">
-        <v>8146979388</v>
+        <v>8139308876</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>550518</v>
+        <v>23841123</v>
       </c>
       <c r="I20" t="n">
-        <v>9.07</v>
+        <v>0.01256654</v>
       </c>
       <c r="J20" t="n">
-        <v>8.81</v>
+        <v>0.01146909</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1675847110773105</v>
+        <v>-0.000624261362235147</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.85704</v>
+        <v>-5.16179</v>
       </c>
       <c r="M20" t="n">
-        <v>919857851.9</v>
+        <v>709250269390.2727</v>
       </c>
       <c r="N20" t="n">
-        <v>985239504</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O20" t="n">
-        <v>10.61</v>
+        <v>0.01946402</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261001T154712Z-f23fce</t>
+          <t>20261002T150823Z-e01d4e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.218152</v>
+        <v>0.221146</v>
       </c>
       <c r="F21" t="n">
-        <v>7637950972</v>
+        <v>7753605592</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>266302070</v>
+        <v>240477078</v>
       </c>
       <c r="I21" t="n">
-        <v>0.230817</v>
+        <v>0.226843</v>
       </c>
       <c r="J21" t="n">
-        <v>0.217818</v>
+        <v>0.216878</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.003998353064852578</v>
+        <v>0.00295541</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.79984</v>
+        <v>1.35451</v>
       </c>
       <c r="M21" t="n">
-        <v>35022047284.21333</v>
+        <v>35040039313.24195</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-01T15:44:20.000Z</t>
+          <t>2026-10-02T15:05:10.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85500</v>
+        <v>84859</v>
       </c>
       <c r="F2" t="n">
-        <v>1718568233595</v>
+        <v>1705128592815</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>42498423772</v>
+        <v>28063519544</v>
       </c>
       <c r="I2" t="n">
-        <v>87086</v>
+        <v>86796</v>
       </c>
       <c r="J2" t="n">
-        <v>84068</v>
+        <v>83898</v>
       </c>
       <c r="K2" t="n">
-        <v>1433.39</v>
+        <v>-1691.822726662882</v>
       </c>
       <c r="L2" t="n">
-        <v>1.70506</v>
+        <v>-1.99546</v>
       </c>
       <c r="M2" t="n">
-        <v>20092434</v>
+        <v>20092821</v>
       </c>
       <c r="N2" t="n">
-        <v>20092503</v>
+        <v>20092881</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2704.01</v>
+        <v>2681.58</v>
       </c>
       <c r="F3" t="n">
-        <v>330288217977</v>
+        <v>327436580212</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>17285850908</v>
+        <v>12119834011</v>
       </c>
       <c r="I3" t="n">
-        <v>2768.44</v>
+        <v>2749.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2677.23</v>
+        <v>2652.62</v>
       </c>
       <c r="K3" t="n">
-        <v>16.98</v>
+        <v>-62.61681457381519</v>
       </c>
       <c r="L3" t="n">
-        <v>0.63198</v>
+        <v>-2.33059</v>
       </c>
       <c r="M3" t="n">
-        <v>122098689.5021315</v>
+        <v>122101617.2835702</v>
       </c>
       <c r="N3" t="n">
-        <v>122098689.5021315</v>
+        <v>122101617.2835702</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999821</v>
+        <v>0.999884</v>
       </c>
       <c r="F4" t="n">
-        <v>184032029420</v>
+        <v>184065994775</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>76697955011</v>
+        <v>52849144705</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9999209999999999</v>
+        <v>0.999987</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999586</v>
+        <v>0.999784</v>
       </c>
       <c r="K4" t="n">
-        <v>8.614999999999999e-05</v>
+        <v>7.71348e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.008619999999999999</v>
+        <v>0.00468</v>
       </c>
       <c r="M4" t="n">
-        <v>184057713983.9332</v>
+        <v>184086263963.6941</v>
       </c>
       <c r="N4" t="n">
-        <v>189524660047.5562</v>
+        <v>189553210047.5562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>774.39</v>
+        <v>774.15</v>
       </c>
       <c r="F5" t="n">
-        <v>103140693116</v>
+        <v>103085701105</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>909316444</v>
+        <v>628494791</v>
       </c>
       <c r="I5" t="n">
-        <v>783.58</v>
+        <v>781.99</v>
       </c>
       <c r="J5" t="n">
-        <v>765.99</v>
+        <v>760.6799999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>-6.483904366601905</v>
       </c>
       <c r="L5" t="n">
-        <v>1.04367</v>
+        <v>-0.88873</v>
       </c>
       <c r="M5" t="n">
-        <v>133159291.91</v>
+        <v>133159202.69</v>
       </c>
       <c r="N5" t="n">
-        <v>133159275.87</v>
+        <v>133159189.02</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="F6" t="n">
-        <v>95186878143</v>
+        <v>93754169096</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>3273192539</v>
+        <v>2443425017</v>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="J6" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02510336</v>
+        <v>-0.04608558487804149</v>
       </c>
       <c r="L6" t="n">
-        <v>1.69292</v>
+        <v>-3.0341</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9999</v>
+        <v>0.99996</v>
       </c>
       <c r="F7" t="n">
-        <v>73926183386</v>
+        <v>74123182828</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>23498092619</v>
+        <v>14411072626</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999514</v>
+        <v>0.99977</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.7638395622854e-05</v>
+        <v>2.878e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00176</v>
+        <v>0.01011</v>
       </c>
       <c r="M7" t="n">
-        <v>73930687451.97484</v>
+        <v>74125782505.24651</v>
       </c>
       <c r="N7" t="n">
-        <v>74032177689.71619</v>
+        <v>74126783179.75063</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>120.16</v>
+        <v>119.4</v>
       </c>
       <c r="F8" t="n">
-        <v>70736536608</v>
+        <v>70236201286</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4542940138</v>
+        <v>2695236716</v>
       </c>
       <c r="I8" t="n">
-        <v>123.55</v>
+        <v>122.37</v>
       </c>
       <c r="J8" t="n">
-        <v>116.97</v>
+        <v>117.38</v>
       </c>
       <c r="K8" t="n">
-        <v>2.98</v>
+        <v>-2.664514317461979</v>
       </c>
       <c r="L8" t="n">
-        <v>2.54295</v>
+        <v>-2.20467</v>
       </c>
       <c r="M8" t="n">
-        <v>588075145.1455896</v>
+        <v>588145964.4167494</v>
       </c>
       <c r="N8" t="n">
-        <v>635072790.6347431</v>
+        <v>635150522.6732608</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335006</v>
+        <v>0.335844</v>
       </c>
       <c r="F9" t="n">
-        <v>31819594052</v>
+        <v>31902896355</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>319102987</v>
+        <v>293510682</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336268</v>
+        <v>0.337274</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333825</v>
+        <v>0.334153</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00173538</v>
+        <v>0.00106617</v>
       </c>
       <c r="L9" t="n">
-        <v>0.52071</v>
+        <v>0.3356</v>
       </c>
       <c r="M9" t="n">
-        <v>94977784305.8391</v>
+        <v>94979300905.16328</v>
       </c>
       <c r="N9" t="n">
-        <v>94977771159.73709</v>
+        <v>94979483456.93779</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,31 +1045,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.012</v>
+        <v>1.046</v>
       </c>
       <c r="F10" t="n">
-        <v>23672068222</v>
+        <v>24509175718</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>13685769</v>
+        <v>32693167</v>
       </c>
       <c r="I10" t="n">
-        <v>1.031</v>
+        <v>1.049</v>
       </c>
       <c r="J10" t="n">
         <v>1.012</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01531564108646744</v>
+        <v>0.02666383</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.49131</v>
+        <v>2.61206</v>
       </c>
       <c r="M10" t="n">
-        <v>23399762227.818</v>
+        <v>23434048822.568</v>
       </c>
       <c r="N10" t="n">
         <v>23434048822.568</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1367.6</v>
+        <v>1302.68</v>
       </c>
       <c r="F11" t="n">
-        <v>23176621404</v>
+        <v>22105049250</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1229193289</v>
+        <v>653057193</v>
       </c>
       <c r="I11" t="n">
-        <v>1408</v>
+        <v>1397.85</v>
       </c>
       <c r="J11" t="n">
-        <v>1305.82</v>
+        <v>1276.55</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.32583717670127</v>
+        <v>-76.93298930898936</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.60511</v>
+        <v>-5.67072</v>
       </c>
       <c r="M11" t="n">
-        <v>16960081.4155448</v>
+        <v>16965175.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16964425.1655448</v>
+        <v>16966118.9155448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>89.41</v>
+        <v>88.52</v>
       </c>
       <c r="F12" t="n">
-        <v>19902424701</v>
+        <v>19689262564</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>915352448</v>
+        <v>807503060</v>
       </c>
       <c r="I12" t="n">
-        <v>91.44</v>
+        <v>90.94</v>
       </c>
       <c r="J12" t="n">
-        <v>86.5</v>
+        <v>86.16</v>
       </c>
       <c r="K12" t="n">
-        <v>0.938259</v>
+        <v>-2.087573502247878</v>
       </c>
       <c r="L12" t="n">
-        <v>1.06047</v>
+        <v>-2.47525</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.095203</v>
+        <v>0.092853</v>
       </c>
       <c r="F13" t="n">
-        <v>14874263523</v>
+        <v>14501142984</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>941725006</v>
+        <v>772793109</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09784900000000001</v>
+        <v>0.096995</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09320000000000001</v>
+        <v>0.09050900000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00116103</v>
+        <v>-0.003768147383103979</v>
       </c>
       <c r="L13" t="n">
-        <v>1.23459</v>
+        <v>-3.95802</v>
       </c>
       <c r="M13" t="n">
-        <v>156158436383.7052</v>
+        <v>156169766383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171870613126.579</v>
+        <v>156171486383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.2</v>
+        <v>13.88</v>
       </c>
       <c r="F14" t="n">
-        <v>10629088978</v>
+        <v>10380842281</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>543682903</v>
+        <v>438080231</v>
       </c>
       <c r="I14" t="n">
-        <v>14.64</v>
+        <v>14.4</v>
       </c>
       <c r="J14" t="n">
-        <v>14.17</v>
+        <v>13.47</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.09491227374897981</v>
+        <v>-0.4705330631047548</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.66396</v>
+        <v>-3.35842</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>541.59</v>
+        <v>547.3</v>
       </c>
       <c r="F15" t="n">
-        <v>10195246972</v>
+        <v>10293908427</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>124020280</v>
+        <v>88284298</v>
       </c>
       <c r="I15" t="n">
-        <v>550.88</v>
+        <v>549.74</v>
       </c>
       <c r="J15" t="n">
-        <v>540.0700000000001</v>
+        <v>532.34</v>
       </c>
       <c r="K15" t="n">
-        <v>3.11</v>
+        <v>3.01</v>
       </c>
       <c r="L15" t="n">
-        <v>0.57797</v>
+        <v>0.53135</v>
       </c>
       <c r="M15" t="n">
-        <v>18812327.44954666</v>
+        <v>18812716.2439284</v>
       </c>
       <c r="N15" t="n">
-        <v>18812370.64941302</v>
+        <v>18812770.24384427</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85.01000000000001</v>
+        <v>84.36</v>
       </c>
       <c r="F16" t="n">
-        <v>10107594626</v>
+        <v>10032601102</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>131162196</v>
+        <v>76813933</v>
       </c>
       <c r="I16" t="n">
-        <v>86.70999999999999</v>
+        <v>86.34999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>83.79000000000001</v>
+        <v>83.53</v>
       </c>
       <c r="K16" t="n">
-        <v>1.21</v>
+        <v>-1.762384655180284</v>
       </c>
       <c r="L16" t="n">
-        <v>1.44729</v>
+        <v>-2.00836</v>
       </c>
       <c r="M16" t="n">
         <v>118819745</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999754</v>
+        <v>0.9999130000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9954572707</v>
+        <v>9952515870</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>308529175</v>
+        <v>128319857</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999521</v>
+        <v>0.99959</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.000172617139321152</v>
+        <v>0.00014247</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01726</v>
+        <v>0.01819</v>
       </c>
       <c r="M17" t="n">
-        <v>9956158465.499102</v>
+        <v>9953329052.999266</v>
       </c>
       <c r="N17" t="n">
-        <v>9957439061.486336</v>
+        <v>9954689537.639244</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.251719</v>
+        <v>0.24514</v>
       </c>
       <c r="F18" t="n">
-        <v>9452790749</v>
+        <v>9201880924</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>596723058</v>
+        <v>490169628</v>
       </c>
       <c r="I18" t="n">
-        <v>0.258534</v>
+        <v>0.256436</v>
       </c>
       <c r="J18" t="n">
-        <v>0.244271</v>
+        <v>0.237332</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00693412</v>
+        <v>-0.01032635804537746</v>
       </c>
       <c r="L18" t="n">
-        <v>2.83275</v>
+        <v>-4.1433</v>
       </c>
       <c r="M18" t="n">
         <v>37541298084.96014</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.970000000000001</v>
+        <v>9</v>
       </c>
       <c r="F19" t="n">
-        <v>8247023571</v>
+        <v>8275943835</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>297535</v>
+        <v>183818</v>
       </c>
       <c r="I19" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>8.85</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.113304</v>
+        <v>0.02834261</v>
       </c>
       <c r="L19" t="n">
-        <v>1.27997</v>
+        <v>0.3177</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01146963</v>
+        <v>0.215469</v>
       </c>
       <c r="F20" t="n">
-        <v>8139308876</v>
+        <v>7553113510</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>23841123</v>
+        <v>155567600</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01256654</v>
+        <v>0.22509</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01146909</v>
+        <v>0.210675</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000624261362235147</v>
+        <v>-0.008894459544244893</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.16179</v>
+        <v>-4.05522</v>
       </c>
       <c r="M20" t="n">
-        <v>709250269390.2727</v>
+        <v>35057725191.80408</v>
       </c>
       <c r="N20" t="n">
-        <v>1142408526965.963</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261002T150823Z-e01d4e</t>
+          <t>20261003T140116Z-95d287</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.221146</v>
+        <v>0.01028682</v>
       </c>
       <c r="F21" t="n">
-        <v>7753605592</v>
+        <v>7295837577</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>240477078</v>
+        <v>10087726</v>
       </c>
       <c r="I21" t="n">
-        <v>0.226843</v>
+        <v>0.0116072</v>
       </c>
       <c r="J21" t="n">
-        <v>0.216878</v>
+        <v>0.00988614</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00295541</v>
+        <v>-0.001317581132989899</v>
       </c>
       <c r="L21" t="n">
-        <v>1.35451</v>
+        <v>-11.25238</v>
       </c>
       <c r="M21" t="n">
-        <v>35040039313.24195</v>
+        <v>709251594419.8831</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.69947</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>0.01946402</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-02T15:05:10.000Z</t>
+          <t>2026-10-03T13:58:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>84859</v>
+        <v>85154</v>
       </c>
       <c r="F2" t="n">
-        <v>1705128592815</v>
+        <v>1710930249368</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>28063519544</v>
+        <v>14818831586</v>
       </c>
       <c r="I2" t="n">
-        <v>86796</v>
+        <v>85401</v>
       </c>
       <c r="J2" t="n">
-        <v>83898</v>
+        <v>84572</v>
       </c>
       <c r="K2" t="n">
-        <v>-1691.822726662882</v>
+        <v>339.21</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.99546</v>
+        <v>0.39994</v>
       </c>
       <c r="M2" t="n">
-        <v>20092821</v>
+        <v>20093221</v>
       </c>
       <c r="N2" t="n">
-        <v>20092881</v>
+        <v>20093268</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2681.58</v>
+        <v>2695</v>
       </c>
       <c r="F3" t="n">
-        <v>327436580212</v>
+        <v>329063916849</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12119834011</v>
+        <v>4738533761</v>
       </c>
       <c r="I3" t="n">
-        <v>2749.75</v>
+        <v>2706.35</v>
       </c>
       <c r="J3" t="n">
-        <v>2652.62</v>
+        <v>2678.42</v>
       </c>
       <c r="K3" t="n">
-        <v>-62.61681457381519</v>
+        <v>14.03</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.33059</v>
+        <v>0.52328</v>
       </c>
       <c r="M3" t="n">
-        <v>122101617.2835702</v>
+        <v>122104582.2639211</v>
       </c>
       <c r="N3" t="n">
-        <v>122101617.2835702</v>
+        <v>122104582.2639211</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999884</v>
+        <v>0.9999</v>
       </c>
       <c r="F4" t="n">
-        <v>184065994775</v>
+        <v>184066108861</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52849144705</v>
+        <v>28563118182</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999987</v>
+        <v>0.999933</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999784</v>
+        <v>0.99984</v>
       </c>
       <c r="K4" t="n">
-        <v>7.71348e-07</v>
+        <v>1.763e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00468</v>
+        <v>0.00176</v>
       </c>
       <c r="M4" t="n">
-        <v>184086263963.6941</v>
+        <v>184086263957.7444</v>
       </c>
       <c r="N4" t="n">
         <v>189553210047.5562</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>774.15</v>
+        <v>786.52</v>
       </c>
       <c r="F5" t="n">
-        <v>103085701105</v>
+        <v>104725111617</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>628494791</v>
+        <v>753104584</v>
       </c>
       <c r="I5" t="n">
-        <v>781.99</v>
+        <v>794.7</v>
       </c>
       <c r="J5" t="n">
-        <v>760.6799999999999</v>
+        <v>776.27</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.483904366601905</v>
+        <v>10.87</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.88873</v>
+        <v>1.40204</v>
       </c>
       <c r="M5" t="n">
-        <v>133159202.69</v>
+        <v>133159110.66</v>
       </c>
       <c r="N5" t="n">
-        <v>133159189.02</v>
+        <v>133159105.87</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>93754169096</v>
+        <v>94590401230</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2443425017</v>
+        <v>1002523734</v>
       </c>
       <c r="I6" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="J6" t="n">
-        <v>1.45</v>
+        <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04608558487804149</v>
+        <v>0.01450756</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.0341</v>
+        <v>0.97698</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99996</v>
+        <v>0.999973</v>
       </c>
       <c r="F7" t="n">
-        <v>74123182828</v>
+        <v>74111013200</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14411072626</v>
+        <v>6964290918</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99977</v>
+        <v>0.999157</v>
       </c>
       <c r="K7" t="n">
-        <v>2.878e-05</v>
+        <v>1.456e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01011</v>
+        <v>0.00146</v>
       </c>
       <c r="M7" t="n">
-        <v>74125782505.24651</v>
+        <v>74113658151.79991</v>
       </c>
       <c r="N7" t="n">
-        <v>74126783179.75063</v>
+        <v>74129284739.4176</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>119.4</v>
+        <v>121.32</v>
       </c>
       <c r="F8" t="n">
-        <v>70236201286</v>
+        <v>71372729334</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2695236716</v>
+        <v>1816714665</v>
       </c>
       <c r="I8" t="n">
-        <v>122.37</v>
+        <v>121.88</v>
       </c>
       <c r="J8" t="n">
-        <v>117.38</v>
+        <v>119.46</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.664514317461979</v>
+        <v>1.95</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.20467</v>
+        <v>1.63456</v>
       </c>
       <c r="M8" t="n">
-        <v>588145964.4167494</v>
+        <v>588314702.9910932</v>
       </c>
       <c r="N8" t="n">
-        <v>635150522.6732608</v>
+        <v>635228159.1617928</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335844</v>
+        <v>0.335694</v>
       </c>
       <c r="F9" t="n">
-        <v>31902896355</v>
+        <v>31878475075</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>293510682</v>
+        <v>205286272</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337274</v>
+        <v>0.337393</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334153</v>
+        <v>0.334911</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00106617</v>
+        <v>-0.000251595144521999</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3356</v>
+        <v>-0.07489</v>
       </c>
       <c r="M9" t="n">
-        <v>94979300905.16328</v>
+        <v>94979892506.28088</v>
       </c>
       <c r="N9" t="n">
-        <v>94979483456.93779</v>
+        <v>94981692941.34779</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,53 +1045,53 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.046</v>
+        <v>1.07</v>
       </c>
       <c r="F10" t="n">
-        <v>24509175718</v>
+        <v>25112322544</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>32693167</v>
+        <v>478121</v>
       </c>
       <c r="I10" t="n">
-        <v>1.049</v>
+        <v>1.07</v>
       </c>
       <c r="J10" t="n">
-        <v>1.012</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>0.02666383</v>
+        <v>0.02272884</v>
       </c>
       <c r="L10" t="n">
-        <v>2.61206</v>
+        <v>2.17084</v>
       </c>
       <c r="M10" t="n">
-        <v>23434048822.568</v>
+        <v>23475311103.758</v>
       </c>
       <c r="N10" t="n">
-        <v>23434048822.568</v>
+        <v>23483399173.928</v>
       </c>
       <c r="O10" t="n">
-        <v>1.062</v>
+        <v>1.07</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-09-27T13:07:30.000Z</t>
+          <t>2026-10-04T13:12:30.000Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T13:13:10.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1302.68</v>
+        <v>1322.08</v>
       </c>
       <c r="F11" t="n">
-        <v>22105049250</v>
+        <v>22433871443</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>653057193</v>
+        <v>554030571</v>
       </c>
       <c r="I11" t="n">
-        <v>1397.85</v>
+        <v>1342.98</v>
       </c>
       <c r="J11" t="n">
-        <v>1276.55</v>
+        <v>1284.26</v>
       </c>
       <c r="K11" t="n">
-        <v>-76.93298930898936</v>
+        <v>30.05</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.67072</v>
+        <v>2.32616</v>
       </c>
       <c r="M11" t="n">
-        <v>16965175.1655448</v>
+        <v>16966725.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16966118.9155448</v>
+        <v>16967926.7280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88.52</v>
+        <v>89.86</v>
       </c>
       <c r="F12" t="n">
-        <v>19689262564</v>
+        <v>19987662185</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>807503060</v>
+        <v>423615316</v>
       </c>
       <c r="I12" t="n">
-        <v>90.94</v>
+        <v>90.88</v>
       </c>
       <c r="J12" t="n">
-        <v>86.16</v>
+        <v>88.61</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.087573502247878</v>
+        <v>1.39</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.47525</v>
+        <v>1.57619</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.092853</v>
+        <v>0.09352199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>14501142984</v>
+        <v>14604561334</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>772793109</v>
+        <v>378754925</v>
       </c>
       <c r="I13" t="n">
-        <v>0.096995</v>
+        <v>0.093766</v>
       </c>
       <c r="J13" t="n">
-        <v>0.09050900000000001</v>
+        <v>0.092557</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003768147383103979</v>
+        <v>0.00060281</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.95802</v>
+        <v>0.64874</v>
       </c>
       <c r="M13" t="n">
-        <v>156169766383.7052</v>
+        <v>156184096383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156171486383.7052</v>
+        <v>156185126383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,28 +1305,28 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13.88</v>
+        <v>14.12</v>
       </c>
       <c r="F14" t="n">
-        <v>10380842281</v>
+        <v>10559341609</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>438080231</v>
+        <v>230457617</v>
       </c>
       <c r="I14" t="n">
-        <v>14.4</v>
+        <v>14.22</v>
       </c>
       <c r="J14" t="n">
-        <v>13.47</v>
+        <v>13.79</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.4705330631047548</v>
+        <v>0.258149</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.35842</v>
+        <v>1.86244</v>
       </c>
       <c r="M14" t="n">
         <v>748099970.424884</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>547.3</v>
+        <v>549.63</v>
       </c>
       <c r="F15" t="n">
-        <v>10293908427</v>
+        <v>10331443646</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>88284298</v>
+        <v>81348971</v>
       </c>
       <c r="I15" t="n">
-        <v>549.74</v>
+        <v>562.23</v>
       </c>
       <c r="J15" t="n">
-        <v>532.34</v>
+        <v>543.5</v>
       </c>
       <c r="K15" t="n">
-        <v>3.01</v>
+        <v>-1.038719444862636</v>
       </c>
       <c r="L15" t="n">
-        <v>0.53135</v>
+        <v>-0.18863</v>
       </c>
       <c r="M15" t="n">
-        <v>18812716.2439284</v>
+        <v>18813201.64050072</v>
       </c>
       <c r="N15" t="n">
-        <v>18812770.24384427</v>
+        <v>18813224.44033616</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84.36</v>
+        <v>84.72</v>
       </c>
       <c r="F16" t="n">
-        <v>10032601102</v>
+        <v>10066036248</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>76813933</v>
+        <v>24945372</v>
       </c>
       <c r="I16" t="n">
-        <v>86.34999999999999</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>83.53</v>
+        <v>84.19</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.762384655180284</v>
+        <v>0.316304</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.00836</v>
+        <v>0.37474</v>
       </c>
       <c r="M16" t="n">
         <v>118819745</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1500,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.9999130000000001</v>
+        <v>0.999849</v>
       </c>
       <c r="F17" t="n">
-        <v>9952515870</v>
+        <v>9969566355</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>128319857</v>
+        <v>45361863</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.99959</v>
+        <v>0.999722</v>
       </c>
       <c r="K17" t="n">
-        <v>0.00014247</v>
+        <v>-0.00015990031456059</v>
       </c>
       <c r="L17" t="n">
-        <v>0.01819</v>
+        <v>-0.01599</v>
       </c>
       <c r="M17" t="n">
-        <v>9953329052.999266</v>
+        <v>9971164452.646639</v>
       </c>
       <c r="N17" t="n">
-        <v>9954689537.639244</v>
+        <v>9971046667.233015</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.24514</v>
+        <v>0.244853</v>
       </c>
       <c r="F18" t="n">
-        <v>9201880924</v>
+        <v>9189534538</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>490169628</v>
+        <v>231831103</v>
       </c>
       <c r="I18" t="n">
-        <v>0.256436</v>
+        <v>0.246722</v>
       </c>
       <c r="J18" t="n">
-        <v>0.237332</v>
+        <v>0.242486</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01032635804537746</v>
+        <v>-0.000477765272112546</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.1433</v>
+        <v>-0.19474</v>
       </c>
       <c r="M18" t="n">
         <v>37541298084.96014</v>
@@ -1604,202 +1604,202 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9</v>
+        <v>0.01210861</v>
       </c>
       <c r="F19" t="n">
-        <v>8275943835</v>
+        <v>8589125510</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>183818</v>
+        <v>20624955</v>
       </c>
       <c r="I19" t="n">
-        <v>9.029999999999999</v>
+        <v>0.01355918</v>
       </c>
       <c r="J19" t="n">
-        <v>8.949999999999999</v>
+        <v>0.00996705</v>
       </c>
       <c r="K19" t="n">
-        <v>0.02834261</v>
+        <v>0.00214742</v>
       </c>
       <c r="L19" t="n">
-        <v>0.3177</v>
+        <v>21.55786</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>709252171474.8611</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>0.01946402</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.215469</v>
+        <v>8.99</v>
       </c>
       <c r="F20" t="n">
-        <v>7553113510</v>
+        <v>8270775708</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>155567600</v>
+        <v>175907</v>
       </c>
       <c r="I20" t="n">
-        <v>0.22509</v>
+        <v>9.01</v>
       </c>
       <c r="J20" t="n">
-        <v>0.210675</v>
+        <v>8.92</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.008894459544244893</v>
+        <v>-0.005599520367441713</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.05522</v>
+        <v>-0.06224</v>
       </c>
       <c r="M20" t="n">
-        <v>35057725191.80408</v>
+        <v>919857851.9</v>
       </c>
       <c r="N20" t="n">
-        <v>50001786839.69947</v>
+        <v>985239504</v>
       </c>
       <c r="O20" t="n">
-        <v>0.875563</v>
+        <v>10.61</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261003T140116Z-95d287</t>
+          <t>20261004T142841Z-426f68</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.01028682</v>
+        <v>0.216259</v>
       </c>
       <c r="F21" t="n">
-        <v>7295837577</v>
+        <v>7576950229</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>10087726</v>
+        <v>94423147</v>
       </c>
       <c r="I21" t="n">
-        <v>0.0116072</v>
+        <v>0.217792</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00988614</v>
+        <v>0.213163</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.001317581132989899</v>
+        <v>0.00093349</v>
       </c>
       <c r="L21" t="n">
-        <v>-11.25238</v>
+        <v>0.43352</v>
       </c>
       <c r="M21" t="n">
-        <v>709251594419.8831</v>
+        <v>35057717989.92455</v>
       </c>
       <c r="N21" t="n">
-        <v>1142408526965.963</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-03T13:58:30.000Z</t>
+          <t>2026-10-04T14:25:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85154</v>
+        <v>85360</v>
       </c>
       <c r="F2" t="n">
-        <v>1710930249368</v>
+        <v>1715207966027</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>14818831586</v>
+        <v>32890397309</v>
       </c>
       <c r="I2" t="n">
-        <v>85401</v>
+        <v>86949</v>
       </c>
       <c r="J2" t="n">
-        <v>84572</v>
+        <v>85010</v>
       </c>
       <c r="K2" t="n">
-        <v>339.21</v>
+        <v>-9.899217347148806</v>
       </c>
       <c r="L2" t="n">
-        <v>0.39994</v>
+        <v>-0.01497</v>
       </c>
       <c r="M2" t="n">
-        <v>20093221</v>
+        <v>20093759</v>
       </c>
       <c r="N2" t="n">
-        <v>20093268</v>
+        <v>20093875</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2695</v>
+        <v>2700.39</v>
       </c>
       <c r="F3" t="n">
-        <v>329063916849</v>
+        <v>329738550431</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>4738533761</v>
+        <v>13143006521</v>
       </c>
       <c r="I3" t="n">
-        <v>2706.35</v>
+        <v>2736.97</v>
       </c>
       <c r="J3" t="n">
-        <v>2678.42</v>
+        <v>2680.92</v>
       </c>
       <c r="K3" t="n">
-        <v>14.03</v>
+        <v>-2.443212934988878</v>
       </c>
       <c r="L3" t="n">
-        <v>0.52328</v>
+        <v>-0.09475</v>
       </c>
       <c r="M3" t="n">
-        <v>122104582.2639211</v>
+        <v>122107545.6913652</v>
       </c>
       <c r="N3" t="n">
-        <v>122104582.2639211</v>
+        <v>122107545.6913651</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9999</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
-        <v>184066108861</v>
+        <v>184088992130</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>28563118182</v>
+        <v>59377507003</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999933</v>
+        <v>0.999987</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99984</v>
+        <v>0.999709</v>
       </c>
       <c r="K4" t="n">
-        <v>1.763e-05</v>
+        <v>0.00012671</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00176</v>
+        <v>0.00946</v>
       </c>
       <c r="M4" t="n">
-        <v>184086263957.7444</v>
+        <v>184088295340.2641</v>
       </c>
       <c r="N4" t="n">
-        <v>189553210047.5562</v>
+        <v>189555241729.7862</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>786.52</v>
+        <v>786.65</v>
       </c>
       <c r="F5" t="n">
-        <v>104725111617</v>
+        <v>104749585140</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>753104584</v>
+        <v>960373637</v>
       </c>
       <c r="I5" t="n">
-        <v>794.7</v>
+        <v>809.02</v>
       </c>
       <c r="J5" t="n">
-        <v>776.27</v>
+        <v>785.16</v>
       </c>
       <c r="K5" t="n">
-        <v>10.87</v>
+        <v>-2.361053870255091</v>
       </c>
       <c r="L5" t="n">
-        <v>1.40204</v>
+        <v>-0.28939</v>
       </c>
       <c r="M5" t="n">
-        <v>133159110.66</v>
+        <v>133159026.3</v>
       </c>
       <c r="N5" t="n">
-        <v>133159105.87</v>
+        <v>133159021.42</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.5</v>
       </c>
       <c r="F6" t="n">
-        <v>94590401230</v>
+        <v>94334984776</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1002523734</v>
+        <v>2074137070</v>
       </c>
       <c r="I6" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="J6" t="n">
         <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01450756</v>
+        <v>-0.005108972037996429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.97698</v>
+        <v>-0.34532</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999973</v>
+        <v>0.999986</v>
       </c>
       <c r="F7" t="n">
-        <v>74111013200</v>
+        <v>74016386129</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6964290918</v>
+        <v>17123786775</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999157</v>
+        <v>0.999733</v>
       </c>
       <c r="K7" t="n">
-        <v>1.456e-05</v>
+        <v>5.528e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00146</v>
+        <v>0.00156</v>
       </c>
       <c r="M7" t="n">
-        <v>74113658151.79991</v>
+        <v>74017394917.68677</v>
       </c>
       <c r="N7" t="n">
-        <v>74129284739.4176</v>
+        <v>74295867493.97673</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>121.32</v>
+        <v>119.83</v>
       </c>
       <c r="F8" t="n">
-        <v>71372729334</v>
+        <v>70506625674</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1816714665</v>
+        <v>2678182321</v>
       </c>
       <c r="I8" t="n">
-        <v>121.88</v>
+        <v>122.21</v>
       </c>
       <c r="J8" t="n">
-        <v>119.46</v>
+        <v>118.97</v>
       </c>
       <c r="K8" t="n">
-        <v>1.95</v>
+        <v>-1.908747727400907</v>
       </c>
       <c r="L8" t="n">
-        <v>1.63456</v>
+        <v>-1.58098</v>
       </c>
       <c r="M8" t="n">
-        <v>588314702.9910932</v>
+        <v>588384888.7764523</v>
       </c>
       <c r="N8" t="n">
-        <v>635228159.1617928</v>
+        <v>635305658.9358269</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335694</v>
+        <v>0.336646</v>
       </c>
       <c r="F9" t="n">
-        <v>31878475075</v>
+        <v>31975708162</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>205286272</v>
+        <v>301871306</v>
       </c>
       <c r="I9" t="n">
-        <v>0.337393</v>
+        <v>0.336932</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334911</v>
+        <v>0.334871</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000251595144521999</v>
+        <v>0.00129082</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.07489</v>
+        <v>0.3832</v>
       </c>
       <c r="M9" t="n">
-        <v>94979892506.28088</v>
+        <v>94983279066.75409</v>
       </c>
       <c r="N9" t="n">
-        <v>94981692941.34779</v>
+        <v>94983288546.42538</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,53 +1045,49 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.07</v>
+        <v>1.063</v>
       </c>
       <c r="F10" t="n">
-        <v>25112322544</v>
+        <v>24974067459</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>478121</v>
+        <v>11406008</v>
       </c>
       <c r="I10" t="n">
-        <v>1.07</v>
+        <v>1.075</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.02272884</v>
-      </c>
-      <c r="L10" t="n">
-        <v>2.17084</v>
-      </c>
+        <v>1.063</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>23475311103.758</v>
+        <v>23490927107.778</v>
       </c>
       <c r="N10" t="n">
-        <v>23483399173.928</v>
+        <v>23490927107.778</v>
       </c>
       <c r="O10" t="n">
-        <v>1.07</v>
+        <v>1.075</v>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>2026-10-04T13:12:30.000Z</t>
+          <t>2026-10-05T13:59:20.000Z</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-04T13:13:10.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1322.08</v>
+        <v>1307.36</v>
       </c>
       <c r="F11" t="n">
-        <v>22433871443</v>
+        <v>22181624069</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>554030571</v>
+        <v>711521991</v>
       </c>
       <c r="I11" t="n">
-        <v>1342.98</v>
+        <v>1366.35</v>
       </c>
       <c r="J11" t="n">
-        <v>1284.26</v>
+        <v>1281.4</v>
       </c>
       <c r="K11" t="n">
-        <v>30.05</v>
+        <v>-28.83469236704468</v>
       </c>
       <c r="L11" t="n">
-        <v>2.32616</v>
+        <v>-2.03807</v>
       </c>
       <c r="M11" t="n">
         <v>16966725.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16967926.7280448</v>
+        <v>16969907.9780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>89.86</v>
+        <v>93.31</v>
       </c>
       <c r="F12" t="n">
-        <v>19987662185</v>
+        <v>20755879419</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>423615316</v>
+        <v>1022066982</v>
       </c>
       <c r="I12" t="n">
-        <v>90.88</v>
+        <v>93.8</v>
       </c>
       <c r="J12" t="n">
-        <v>88.61</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.39</v>
+        <v>3.34</v>
       </c>
       <c r="L12" t="n">
-        <v>1.57619</v>
+        <v>3.79948</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.09352199999999999</v>
+        <v>0.094555</v>
       </c>
       <c r="F13" t="n">
-        <v>14604561334</v>
+        <v>14769253345</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>378754925</v>
+        <v>872165796</v>
       </c>
       <c r="I13" t="n">
-        <v>0.093766</v>
+        <v>0.09743599999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.092557</v>
+        <v>0.093941</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00060281</v>
+        <v>-0.000677599123369635</v>
       </c>
       <c r="L13" t="n">
-        <v>0.64874</v>
+        <v>-0.7067600000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>156184096383.7052</v>
+        <v>156198076383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>156185126383.7052</v>
+        <v>156200356383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,144 +1275,144 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>14.12</v>
+        <v>554.26</v>
       </c>
       <c r="F14" t="n">
-        <v>10559341609</v>
+        <v>10427713259</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>230457617</v>
+        <v>137957024</v>
       </c>
       <c r="I14" t="n">
-        <v>14.22</v>
+        <v>557.99</v>
       </c>
       <c r="J14" t="n">
-        <v>13.79</v>
+        <v>535.22</v>
       </c>
       <c r="K14" t="n">
-        <v>0.258149</v>
+        <v>7.35</v>
       </c>
       <c r="L14" t="n">
-        <v>1.86244</v>
+        <v>1.33069</v>
       </c>
       <c r="M14" t="n">
-        <v>748099970.424884</v>
+        <v>18813681.03120079</v>
       </c>
       <c r="N14" t="n">
-        <v>1000000000</v>
+        <v>18813705.03080577</v>
       </c>
       <c r="O14" t="n">
-        <v>52.7</v>
+        <v>797.73</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>549.63</v>
+        <v>13.88</v>
       </c>
       <c r="F15" t="n">
-        <v>10331443646</v>
+        <v>10386502883</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>81348971</v>
+        <v>302188315</v>
       </c>
       <c r="I15" t="n">
-        <v>562.23</v>
+        <v>14.32</v>
       </c>
       <c r="J15" t="n">
-        <v>543.5</v>
+        <v>13.71</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.038719444862636</v>
+        <v>-0.2254109638653237</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.18863</v>
+        <v>-1.58682</v>
       </c>
       <c r="M15" t="n">
-        <v>18813201.64050072</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N15" t="n">
-        <v>18813224.44033616</v>
+        <v>1000000000</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1431,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>84.72</v>
+        <v>85.26000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>10066036248</v>
+        <v>10127540820</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>24945372</v>
+        <v>108558874</v>
       </c>
       <c r="I16" t="n">
-        <v>85.01000000000001</v>
+        <v>86.48</v>
       </c>
       <c r="J16" t="n">
-        <v>84.19</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.316304</v>
+        <v>0.344704</v>
       </c>
       <c r="L16" t="n">
-        <v>0.37474</v>
+        <v>0.4304</v>
       </c>
       <c r="M16" t="n">
-        <v>118819745</v>
+        <v>118786640</v>
       </c>
       <c r="N16" t="n">
-        <v>293389244</v>
+        <v>293356139</v>
       </c>
       <c r="O16" t="n">
         <v>87.91</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,34 +1496,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999849</v>
+        <v>0.999853</v>
       </c>
       <c r="F17" t="n">
-        <v>9969566355</v>
+        <v>10016013334</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>45361863</v>
+        <v>99689486</v>
       </c>
       <c r="I17" t="n">
         <v>1</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999722</v>
+        <v>0.999618</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.00015990031456059</v>
+        <v>3.206e-05</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.01599</v>
+        <v>-0.00019</v>
       </c>
       <c r="M17" t="n">
-        <v>9971164452.646639</v>
+        <v>10017482703.60781</v>
       </c>
       <c r="N17" t="n">
-        <v>9971046667.233015</v>
+        <v>10068312098.89016</v>
       </c>
       <c r="O17" t="n">
         <v>1.057</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.244853</v>
+        <v>0.265124</v>
       </c>
       <c r="F18" t="n">
-        <v>9189534538</v>
+        <v>9953113044</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>231831103</v>
+        <v>1204275641</v>
       </c>
       <c r="I18" t="n">
-        <v>0.246722</v>
+        <v>0.276329</v>
       </c>
       <c r="J18" t="n">
-        <v>0.242486</v>
+        <v>0.247495</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.000477765272112546</v>
+        <v>0.01784314</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.19474</v>
+        <v>7.20921</v>
       </c>
       <c r="M18" t="n">
         <v>37541298084.96014</v>
@@ -1604,144 +1600,144 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.01210861</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8589125510</v>
+        <v>8228678470</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>20624955</v>
+        <v>229430</v>
       </c>
       <c r="I19" t="n">
-        <v>0.01355918</v>
+        <v>9.01</v>
       </c>
       <c r="J19" t="n">
-        <v>0.00996705</v>
+        <v>8.9</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00214742</v>
+        <v>-0.04515496733862356</v>
       </c>
       <c r="L19" t="n">
-        <v>21.55786</v>
+        <v>-0.50068</v>
       </c>
       <c r="M19" t="n">
-        <v>709252171474.8611</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1142408526965.963</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01946402</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>8.99</v>
+        <v>0.01157077</v>
       </c>
       <c r="F20" t="n">
-        <v>8270775708</v>
+        <v>8206599356</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>175907</v>
+        <v>11960814</v>
       </c>
       <c r="I20" t="n">
-        <v>9.01</v>
+        <v>0.01291487</v>
       </c>
       <c r="J20" t="n">
-        <v>8.92</v>
+        <v>0.01123283</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.005599520367441713</v>
+        <v>-0.000130940427666246</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.06224</v>
+        <v>-1.13682</v>
       </c>
       <c r="M20" t="n">
-        <v>919857851.9</v>
+        <v>709252458265.8584</v>
       </c>
       <c r="N20" t="n">
-        <v>985239504</v>
+        <v>1142408526965.963</v>
       </c>
       <c r="O20" t="n">
-        <v>10.61</v>
+        <v>0.01946402</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261004T142841Z-426f68</t>
+          <t>20261005T173104Z-7b343a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1756,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.216259</v>
+        <v>0.212306</v>
       </c>
       <c r="F21" t="n">
-        <v>7576950229</v>
+        <v>7442972700</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>94423147</v>
+        <v>221143673</v>
       </c>
       <c r="I21" t="n">
-        <v>0.217792</v>
+        <v>0.226886</v>
       </c>
       <c r="J21" t="n">
-        <v>0.213163</v>
+        <v>0.211031</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00093349</v>
+        <v>-0.005088020555284345</v>
       </c>
       <c r="L21" t="n">
-        <v>0.43352</v>
+        <v>-2.37444</v>
       </c>
       <c r="M21" t="n">
-        <v>35057717989.92455</v>
+        <v>35057710390.73232</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-04T14:25:30.000Z</t>
+          <t>2026-10-05T17:28:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>85360</v>
+        <v>86260</v>
       </c>
       <c r="F2" t="n">
-        <v>1715207966027</v>
+        <v>1733333010828</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32890397309</v>
+        <v>26760310215</v>
       </c>
       <c r="I2" t="n">
-        <v>86949</v>
+        <v>86625</v>
       </c>
       <c r="J2" t="n">
         <v>85010</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.899217347148806</v>
+        <v>752.4299999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.01497</v>
+        <v>0.87413</v>
       </c>
       <c r="M2" t="n">
-        <v>20093759</v>
+        <v>20094278</v>
       </c>
       <c r="N2" t="n">
-        <v>20093875</v>
+        <v>20094303</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2700.39</v>
+        <v>2715.01</v>
       </c>
       <c r="F3" t="n">
-        <v>329738550431</v>
+        <v>331530995789</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13143006521</v>
+        <v>10858150367</v>
       </c>
       <c r="I3" t="n">
-        <v>2736.97</v>
+        <v>2722</v>
       </c>
       <c r="J3" t="n">
         <v>2680.92</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.443212934988878</v>
+        <v>11.81</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.09475</v>
+        <v>0.43231</v>
       </c>
       <c r="M3" t="n">
-        <v>122107545.6913652</v>
+        <v>122110434.6948541</v>
       </c>
       <c r="N3" t="n">
-        <v>122107545.6913651</v>
+        <v>122110434.694854</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0.999954</v>
       </c>
       <c r="F4" t="n">
-        <v>184088992130</v>
+        <v>184079892402</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>59377507003</v>
+        <v>51759458346</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999987</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999709</v>
+        <v>0.999743</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00012671</v>
+        <v>0.00010835</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00946</v>
+        <v>0.00709</v>
       </c>
       <c r="M4" t="n">
         <v>184088295340.2641</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>786.65</v>
+        <v>785.71</v>
       </c>
       <c r="F5" t="n">
-        <v>104749585140</v>
+        <v>104623702827</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>960373637</v>
+        <v>632179317</v>
       </c>
       <c r="I5" t="n">
-        <v>809.02</v>
+        <v>789.14</v>
       </c>
       <c r="J5" t="n">
-        <v>785.16</v>
+        <v>778.04</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.361053870255091</v>
+        <v>-2.723026585974935</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.28939</v>
+        <v>-0.35227</v>
       </c>
       <c r="M5" t="n">
-        <v>133159026.3</v>
+        <v>133158975.72</v>
       </c>
       <c r="N5" t="n">
-        <v>133159021.42</v>
+        <v>133158964.13</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="F6" t="n">
-        <v>94334984776</v>
+        <v>95665500207</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2074137070</v>
+        <v>1552405454</v>
       </c>
       <c r="I6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J6" t="n">
         <v>1.49</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.005108972037996429</v>
+        <v>0.01793924</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.34532</v>
+        <v>1.1939</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999986</v>
+        <v>0.999978</v>
       </c>
       <c r="F7" t="n">
-        <v>74016386129</v>
+        <v>74132610724</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17123786775</v>
+        <v>16638315955</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999733</v>
+        <v>0.9997200000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>5.528e-05</v>
+        <v>4.947e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00156</v>
+        <v>0.00155</v>
       </c>
       <c r="M7" t="n">
-        <v>74017394917.68677</v>
+        <v>74134279281.5563</v>
       </c>
       <c r="N7" t="n">
-        <v>74295867493.97673</v>
+        <v>74196956085.77791</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>119.83</v>
+        <v>121.43</v>
       </c>
       <c r="F8" t="n">
-        <v>70506625674</v>
+        <v>71446106129</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2678182321</v>
+        <v>2482208998</v>
       </c>
       <c r="I8" t="n">
-        <v>122.21</v>
+        <v>121.79</v>
       </c>
       <c r="J8" t="n">
         <v>118.97</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.908747727400907</v>
+        <v>1.81</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.58098</v>
+        <v>1.49918</v>
       </c>
       <c r="M8" t="n">
-        <v>588384888.7764523</v>
+        <v>588385203.3705763</v>
       </c>
       <c r="N8" t="n">
-        <v>635305658.9358269</v>
+        <v>635304739.9793986</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336646</v>
+        <v>0.335698</v>
       </c>
       <c r="F9" t="n">
-        <v>31975708162</v>
+        <v>31886114554</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>301871306</v>
+        <v>287161043</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336932</v>
+        <v>0.336972</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334871</v>
+        <v>0.335132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00129082</v>
+        <v>-0.000526238718021543</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3832</v>
+        <v>-0.13396</v>
       </c>
       <c r="M9" t="n">
-        <v>94983279066.75409</v>
+        <v>94984533534.1917</v>
       </c>
       <c r="N9" t="n">
-        <v>94983288546.42538</v>
+        <v>94984539147.30809</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,30 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.063</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>24974067459</v>
+        <v>24129166974</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>11406008</v>
+        <v>18620598</v>
       </c>
       <c r="I10" t="n">
-        <v>1.075</v>
+        <v>1.063</v>
       </c>
       <c r="J10" t="n">
-        <v>1.063</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.033</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.03679744089561177</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-3.45459</v>
+      </c>
       <c r="M10" t="n">
         <v>23490927107.778</v>
       </c>
       <c r="N10" t="n">
-        <v>23490927107.778</v>
+        <v>23544660846.378</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1307.36</v>
+        <v>1368.41</v>
       </c>
       <c r="F11" t="n">
-        <v>22181624069</v>
+        <v>23217478913</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>711521991</v>
+        <v>837540075</v>
       </c>
       <c r="I11" t="n">
-        <v>1366.35</v>
+        <v>1381.47</v>
       </c>
       <c r="J11" t="n">
         <v>1281.4</v>
       </c>
       <c r="K11" t="n">
-        <v>-28.83469236704468</v>
+        <v>60.28</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.03807</v>
+        <v>4.56359</v>
       </c>
       <c r="M11" t="n">
         <v>16966725.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16969907.9780448</v>
+        <v>16971548.6030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93.31</v>
+        <v>92.77</v>
       </c>
       <c r="F12" t="n">
-        <v>20755879419</v>
+        <v>20636185695</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1022066982</v>
+        <v>1058509494</v>
       </c>
       <c r="I12" t="n">
-        <v>93.8</v>
+        <v>95.20999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>89.98999999999999</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>3.34</v>
+        <v>-0.517034199202655</v>
       </c>
       <c r="L12" t="n">
-        <v>3.79948</v>
+        <v>-0.6027</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.094555</v>
+        <v>0.095898</v>
       </c>
       <c r="F13" t="n">
-        <v>14769253345</v>
+        <v>14980439298</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>872165796</v>
+        <v>479082613</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09743599999999999</v>
+        <v>0.096305</v>
       </c>
       <c r="J13" t="n">
         <v>0.093941</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000677599123369635</v>
+        <v>0.00108088</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7067600000000001</v>
+        <v>1.12377</v>
       </c>
       <c r="M13" t="n">
-        <v>156198076383.7053</v>
+        <v>156212746383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>156200356383.7052</v>
+        <v>156212726383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>554.26</v>
+        <v>562.16</v>
       </c>
       <c r="F14" t="n">
-        <v>10427713259</v>
+        <v>10576523752</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>137957024</v>
+        <v>120797790</v>
       </c>
       <c r="I14" t="n">
-        <v>557.99</v>
+        <v>564.26</v>
       </c>
       <c r="J14" t="n">
-        <v>535.22</v>
+        <v>550.3200000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>7.35</v>
+        <v>4.57</v>
       </c>
       <c r="L14" t="n">
-        <v>1.33069</v>
+        <v>0.80452</v>
       </c>
       <c r="M14" t="n">
-        <v>18813681.03120079</v>
+        <v>18814063.22921376</v>
       </c>
       <c r="N14" t="n">
-        <v>18813705.03080577</v>
+        <v>18814092.62811599</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,28 +1370,28 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.88</v>
+        <v>14.06</v>
       </c>
       <c r="F15" t="n">
-        <v>10386502883</v>
+        <v>10519572395</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>302188315</v>
+        <v>271342961</v>
       </c>
       <c r="I15" t="n">
-        <v>14.32</v>
+        <v>14.09</v>
       </c>
       <c r="J15" t="n">
-        <v>13.71</v>
+        <v>13.72</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.2254109638653237</v>
+        <v>0.235562</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.58682</v>
+        <v>1.6589</v>
       </c>
       <c r="M15" t="n">
         <v>748099970.424884</v>
@@ -1405,209 +1409,209 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>85.26000000000001</v>
+        <v>0.273612</v>
       </c>
       <c r="F16" t="n">
-        <v>10127540820</v>
+        <v>10271756837</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>108558874</v>
+        <v>751551962</v>
       </c>
       <c r="I16" t="n">
-        <v>86.48</v>
+        <v>0.281737</v>
       </c>
       <c r="J16" t="n">
-        <v>84.84999999999999</v>
+        <v>0.261873</v>
       </c>
       <c r="K16" t="n">
-        <v>0.344704</v>
+        <v>0.00605626</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4304</v>
+        <v>2.24407</v>
       </c>
       <c r="M16" t="n">
-        <v>118786640</v>
+        <v>37541298084.96014</v>
       </c>
       <c r="N16" t="n">
-        <v>293356139</v>
+        <v>45000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>87.91</v>
+        <v>3.09</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.999853</v>
+        <v>86.13</v>
       </c>
       <c r="F17" t="n">
-        <v>10016013334</v>
+        <v>10230615798</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>99689486</v>
+        <v>74737220</v>
       </c>
       <c r="I17" t="n">
-        <v>1</v>
+        <v>86.45</v>
       </c>
       <c r="J17" t="n">
-        <v>0.999618</v>
+        <v>84.94</v>
       </c>
       <c r="K17" t="n">
-        <v>3.206e-05</v>
+        <v>0.785992</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.00019</v>
+        <v>0.92019</v>
       </c>
       <c r="M17" t="n">
-        <v>10017482703.60781</v>
+        <v>118786640</v>
       </c>
       <c r="N17" t="n">
-        <v>10068312098.89016</v>
+        <v>293356139</v>
       </c>
       <c r="O17" t="n">
-        <v>1.057</v>
+        <v>87.91</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.265124</v>
+        <v>0.999914</v>
       </c>
       <c r="F18" t="n">
-        <v>9953113044</v>
+        <v>10120723593</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>1204275641</v>
+        <v>199760600</v>
       </c>
       <c r="I18" t="n">
-        <v>0.276329</v>
+        <v>1</v>
       </c>
       <c r="J18" t="n">
-        <v>0.247495</v>
+        <v>0.999466</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01784314</v>
+        <v>0.00012534</v>
       </c>
       <c r="L18" t="n">
-        <v>7.20921</v>
+        <v>0.0184</v>
       </c>
       <c r="M18" t="n">
-        <v>37541298084.96014</v>
+        <v>10121590281.14417</v>
       </c>
       <c r="N18" t="n">
-        <v>45000000000</v>
+        <v>10121310757.69294</v>
       </c>
       <c r="O18" t="n">
-        <v>3.09</v>
+        <v>1.057</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8228678470</v>
+        <v>8174555175</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>229430</v>
+        <v>193876</v>
       </c>
       <c r="I19" t="n">
-        <v>9.01</v>
+        <v>8.98</v>
       </c>
       <c r="J19" t="n">
-        <v>8.9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.04515496733862356</v>
+        <v>-0.06298877182380203</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.50068</v>
+        <v>-0.70163</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01157077</v>
+        <v>0.01131258</v>
       </c>
       <c r="F20" t="n">
-        <v>8206599356</v>
+        <v>8023478377</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>11960814</v>
+        <v>11036411</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01291487</v>
+        <v>0.01168627</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01123283</v>
+        <v>0.01128135</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000130940427666246</v>
+        <v>-0.000343751861191281</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.13682</v>
+        <v>-2.91016</v>
       </c>
       <c r="M20" t="n">
-        <v>709252458265.8584</v>
+        <v>709252653794.365</v>
       </c>
       <c r="N20" t="n">
         <v>1142408526965.963</v>
@@ -1730,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261005T173104Z-7b343a</t>
+          <t>20261006T153102Z-ef41e6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1756,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.212306</v>
+        <v>0.215301</v>
       </c>
       <c r="F21" t="n">
-        <v>7442972700</v>
+        <v>7547522912</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>221143673</v>
+        <v>192403218</v>
       </c>
       <c r="I21" t="n">
-        <v>0.226886</v>
+        <v>0.217005</v>
       </c>
       <c r="J21" t="n">
-        <v>0.211031</v>
+        <v>0.210971</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005088020555284345</v>
+        <v>0.00173573</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.37444</v>
+        <v>0.8093</v>
       </c>
       <c r="M21" t="n">
-        <v>35057710390.73232</v>
+        <v>35055619198.2393</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1795,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-05T17:28:30.000Z</t>
+          <t>2026-10-06T15:27:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>86260</v>
+        <v>83294</v>
       </c>
       <c r="F2" t="n">
-        <v>1733333010828</v>
+        <v>1673874022988</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>26760310215</v>
+        <v>38491171726</v>
       </c>
       <c r="I2" t="n">
-        <v>86625</v>
+        <v>85824</v>
       </c>
       <c r="J2" t="n">
-        <v>85010</v>
+        <v>82830</v>
       </c>
       <c r="K2" t="n">
-        <v>752.4299999999999</v>
+        <v>-2727.985607153212</v>
       </c>
       <c r="L2" t="n">
-        <v>0.87413</v>
+        <v>-3.17128</v>
       </c>
       <c r="M2" t="n">
-        <v>20094278</v>
+        <v>20094800</v>
       </c>
       <c r="N2" t="n">
-        <v>20094303</v>
+        <v>20094840</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2715.01</v>
+        <v>2563.98</v>
       </c>
       <c r="F3" t="n">
-        <v>331530995789</v>
+        <v>313102738146</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>10858150367</v>
+        <v>18953547562</v>
       </c>
       <c r="I3" t="n">
-        <v>2722</v>
+        <v>2706.4</v>
       </c>
       <c r="J3" t="n">
-        <v>2680.92</v>
+        <v>2554.67</v>
       </c>
       <c r="K3" t="n">
-        <v>11.81</v>
+        <v>-146.6474657697954</v>
       </c>
       <c r="L3" t="n">
-        <v>0.43231</v>
+        <v>-5.41009</v>
       </c>
       <c r="M3" t="n">
-        <v>122110434.6948541</v>
+        <v>122113300.6445289</v>
       </c>
       <c r="N3" t="n">
-        <v>122110434.694854</v>
+        <v>122113300.6445289</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999954</v>
+        <v>0.999657</v>
       </c>
       <c r="F4" t="n">
-        <v>184079892402</v>
+        <v>184024739868</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51759458346</v>
+        <v>70890232603</v>
       </c>
       <c r="I4" t="n">
         <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999743</v>
+        <v>0.9996969999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00010835</v>
+        <v>-0.000283683330175366</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00709</v>
+        <v>-0.02837</v>
       </c>
       <c r="M4" t="n">
         <v>184088295340.2641</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>785.71</v>
+        <v>768.89</v>
       </c>
       <c r="F5" t="n">
-        <v>104623702827</v>
+        <v>102386705728</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>632179317</v>
+        <v>956765677</v>
       </c>
       <c r="I5" t="n">
-        <v>789.14</v>
+        <v>783.75</v>
       </c>
       <c r="J5" t="n">
-        <v>778.04</v>
+        <v>759.7</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.723026585974935</v>
+        <v>-15.89842921753348</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.35227</v>
+        <v>-2.02583</v>
       </c>
       <c r="M5" t="n">
-        <v>133158975.72</v>
+        <v>133158900.53</v>
       </c>
       <c r="N5" t="n">
-        <v>133158964.13</v>
+        <v>133158895.86</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.52</v>
+        <v>1.43</v>
       </c>
       <c r="F6" t="n">
-        <v>95665500207</v>
+        <v>90258712518</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1552405454</v>
+        <v>2356734848</v>
       </c>
       <c r="I6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="J6" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01793924</v>
+        <v>-0.07998528859241238</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1939</v>
+        <v>-5.2954</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999978</v>
+        <v>0.999772</v>
       </c>
       <c r="F7" t="n">
-        <v>74132610724</v>
+        <v>73807045678</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16638315955</v>
+        <v>19412496327</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9997200000000001</v>
+        <v>0.9996930000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>4.947e-05</v>
+        <v>-0.000185814575094589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00155</v>
+        <v>-0.01858</v>
       </c>
       <c r="M7" t="n">
-        <v>74134279281.5563</v>
+        <v>73824304674.12912</v>
       </c>
       <c r="N7" t="n">
-        <v>74196956085.77791</v>
+        <v>73892500989.58794</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>121.43</v>
+        <v>116.54</v>
       </c>
       <c r="F8" t="n">
-        <v>71446106129</v>
+        <v>68648764460</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2482208998</v>
+        <v>2976532357</v>
       </c>
       <c r="I8" t="n">
-        <v>121.79</v>
+        <v>121.42</v>
       </c>
       <c r="J8" t="n">
-        <v>118.97</v>
+        <v>115.58</v>
       </c>
       <c r="K8" t="n">
-        <v>1.81</v>
+        <v>-4.434457163822955</v>
       </c>
       <c r="L8" t="n">
-        <v>1.49918</v>
+        <v>-3.66573</v>
       </c>
       <c r="M8" t="n">
-        <v>588385203.3705763</v>
+        <v>589094366.4621038</v>
       </c>
       <c r="N8" t="n">
-        <v>635304739.9793986</v>
+        <v>635382237.2552732</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335698</v>
+        <v>0.33497</v>
       </c>
       <c r="F9" t="n">
-        <v>31886114554</v>
+        <v>31815831391</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>287161043</v>
+        <v>383766010</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336972</v>
+        <v>0.336337</v>
       </c>
       <c r="J9" t="n">
-        <v>0.335132</v>
+        <v>0.332038</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000526238718021543</v>
+        <v>-0.000646152911107811</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.13396</v>
+        <v>-0.19253</v>
       </c>
       <c r="M9" t="n">
-        <v>94984533534.1917</v>
+        <v>94985842073.90219</v>
       </c>
       <c r="N9" t="n">
-        <v>94984539147.30809</v>
+        <v>94985842034.73439</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.027</v>
+        <v>1.036</v>
       </c>
       <c r="F10" t="n">
-        <v>24129166974</v>
+        <v>24400779197</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>18620598</v>
+        <v>42318399</v>
       </c>
       <c r="I10" t="n">
-        <v>1.063</v>
+        <v>1.045</v>
       </c>
       <c r="J10" t="n">
-        <v>1.033</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03679744089561177</v>
+        <v>0.00917217</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.45459</v>
+        <v>0.89294</v>
       </c>
       <c r="M10" t="n">
-        <v>23490927107.778</v>
+        <v>23544660846.378</v>
       </c>
       <c r="N10" t="n">
-        <v>23544660846.378</v>
+        <v>23624390711.938</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1368.41</v>
+        <v>1328.4</v>
       </c>
       <c r="F11" t="n">
-        <v>23217478913</v>
+        <v>22538337192</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>837540075</v>
+        <v>662476158</v>
       </c>
       <c r="I11" t="n">
-        <v>1381.47</v>
+        <v>1372.71</v>
       </c>
       <c r="J11" t="n">
-        <v>1281.4</v>
+        <v>1290.32</v>
       </c>
       <c r="K11" t="n">
-        <v>60.28</v>
+        <v>-38.57750273453371</v>
       </c>
       <c r="L11" t="n">
-        <v>4.56359</v>
+        <v>-2.82209</v>
       </c>
       <c r="M11" t="n">
         <v>16966725.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16971548.6030448</v>
+        <v>16973411.1030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>92.77</v>
+        <v>88.48</v>
       </c>
       <c r="F12" t="n">
-        <v>20636185695</v>
+        <v>19681215781</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1058509494</v>
+        <v>921768723</v>
       </c>
       <c r="I12" t="n">
-        <v>95.20999999999999</v>
+        <v>92.69</v>
       </c>
       <c r="J12" t="n">
-        <v>92.29000000000001</v>
+        <v>88.12</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.517034199202655</v>
+        <v>-4.357509282893488</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.6027</v>
+        <v>-4.69352</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.095898</v>
+        <v>0.08853</v>
       </c>
       <c r="F13" t="n">
-        <v>14980439298</v>
+        <v>13829916812</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>479082613</v>
+        <v>1289976831</v>
       </c>
       <c r="I13" t="n">
-        <v>0.096305</v>
+        <v>0.095608</v>
       </c>
       <c r="J13" t="n">
-        <v>0.093941</v>
+        <v>0.08802</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00108088</v>
+        <v>-0.007330841534385416</v>
       </c>
       <c r="L13" t="n">
-        <v>1.12377</v>
+        <v>-7.64738</v>
       </c>
       <c r="M13" t="n">
-        <v>156212746383.7053</v>
+        <v>156221976383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156212726383.7052</v>
+        <v>156227106383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>562.16</v>
+        <v>551.5700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>10576523752</v>
+        <v>10379062182</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>120797790</v>
+        <v>131925000</v>
       </c>
       <c r="I14" t="n">
-        <v>564.26</v>
+        <v>571.13</v>
       </c>
       <c r="J14" t="n">
-        <v>550.3200000000001</v>
+        <v>546.26</v>
       </c>
       <c r="K14" t="n">
-        <v>4.57</v>
+        <v>-11.06474666563224</v>
       </c>
       <c r="L14" t="n">
-        <v>0.80452</v>
+        <v>-1.96658</v>
       </c>
       <c r="M14" t="n">
-        <v>18814063.22921376</v>
+        <v>18814509.01509035</v>
       </c>
       <c r="N14" t="n">
-        <v>18814092.62811599</v>
+        <v>18814534.21500215</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,144 +1344,144 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>14.06</v>
+        <v>0.999261</v>
       </c>
       <c r="F15" t="n">
-        <v>10519572395</v>
+        <v>10213026946</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>271342961</v>
+        <v>234422650</v>
       </c>
       <c r="I15" t="n">
-        <v>14.09</v>
+        <v>1.001</v>
       </c>
       <c r="J15" t="n">
-        <v>13.72</v>
+        <v>0.9972839999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>0.235562</v>
+        <v>-0.000638180382625086</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6589</v>
+        <v>-0.06382</v>
       </c>
       <c r="M15" t="n">
-        <v>748099970.424884</v>
+        <v>10219583954.93842</v>
       </c>
       <c r="N15" t="n">
-        <v>1000000000</v>
+        <v>10225135591.02598</v>
       </c>
       <c r="O15" t="n">
-        <v>52.7</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.273612</v>
+        <v>13.38</v>
       </c>
       <c r="F16" t="n">
-        <v>10271756837</v>
+        <v>10007919360</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>751551962</v>
+        <v>359633874</v>
       </c>
       <c r="I16" t="n">
-        <v>0.281737</v>
+        <v>14.03</v>
       </c>
       <c r="J16" t="n">
-        <v>0.261873</v>
+        <v>13.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00605626</v>
+        <v>-0.6434031945828256</v>
       </c>
       <c r="L16" t="n">
-        <v>2.24407</v>
+        <v>-4.58915</v>
       </c>
       <c r="M16" t="n">
-        <v>37541298084.96014</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>45000000000</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>3.09</v>
+        <v>52.7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>86.13</v>
+        <v>82.84</v>
       </c>
       <c r="F17" t="n">
-        <v>10230615798</v>
+        <v>9840284078</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>74737220</v>
+        <v>96063383</v>
       </c>
       <c r="I17" t="n">
-        <v>86.45</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>84.94</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.785992</v>
+        <v>-3.079920322956198</v>
       </c>
       <c r="L17" t="n">
-        <v>0.92019</v>
+        <v>-3.58467</v>
       </c>
       <c r="M17" t="n">
         <v>118786640</v>
@@ -1539,79 +1539,79 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.999914</v>
+        <v>0.254716</v>
       </c>
       <c r="F18" t="n">
-        <v>10120723593</v>
+        <v>9563470546</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>199760600</v>
+        <v>669732544</v>
       </c>
       <c r="I18" t="n">
-        <v>1</v>
+        <v>0.273346</v>
       </c>
       <c r="J18" t="n">
-        <v>0.999466</v>
+        <v>0.251674</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00012534</v>
+        <v>-0.01806671782487718</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0184</v>
+        <v>-6.62311</v>
       </c>
       <c r="M18" t="n">
-        <v>10121590281.14417</v>
+        <v>37547445640.06296</v>
       </c>
       <c r="N18" t="n">
-        <v>10121310757.69294</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>1.057</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F19" t="n">
-        <v>8174555175</v>
+        <v>8185480786</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>193876</v>
+        <v>168767</v>
       </c>
       <c r="I19" t="n">
-        <v>8.98</v>
+        <v>8.94</v>
       </c>
       <c r="J19" t="n">
-        <v>8.890000000000001</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.06298877182380203</v>
+        <v>0.01187828</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.70163</v>
+        <v>0.13366</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01131258</v>
+        <v>0.01093967</v>
       </c>
       <c r="F20" t="n">
-        <v>8023478377</v>
+        <v>7761341518</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>11036411</v>
+        <v>19340374</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01168627</v>
+        <v>0.01158268</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01128135</v>
+        <v>0.01086226</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000343751861191281</v>
+        <v>-0.000349764978778226</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.91016</v>
+        <v>-3.09816</v>
       </c>
       <c r="M20" t="n">
-        <v>709252653794.365</v>
+        <v>709253096298.4821</v>
       </c>
       <c r="N20" t="n">
         <v>1142408526965.963</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261006T153102Z-ef41e6</t>
+          <t>20261007T155208Z-6097ef</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.215301</v>
+        <v>0.199864</v>
       </c>
       <c r="F21" t="n">
-        <v>7547522912</v>
+        <v>7004341485</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>192403218</v>
+        <v>182609425</v>
       </c>
       <c r="I21" t="n">
-        <v>0.217005</v>
+        <v>0.214726</v>
       </c>
       <c r="J21" t="n">
-        <v>0.210971</v>
+        <v>0.200037</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00173573</v>
+        <v>-0.01507322184339882</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8093</v>
+        <v>-7.01285</v>
       </c>
       <c r="M21" t="n">
-        <v>35055619198.2393</v>
+        <v>35039548656.1776</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-06T15:27:30.000Z</t>
+          <t>2026-10-07T15:49:30.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83294</v>
+        <v>81396</v>
       </c>
       <c r="F2" t="n">
-        <v>1673874022988</v>
+        <v>1635464580346</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>38491171726</v>
+        <v>36173945818</v>
       </c>
       <c r="I2" t="n">
-        <v>85824</v>
+        <v>83616</v>
       </c>
       <c r="J2" t="n">
-        <v>82830</v>
+        <v>81792</v>
       </c>
       <c r="K2" t="n">
-        <v>-2727.985607153212</v>
+        <v>-1981.28377951149</v>
       </c>
       <c r="L2" t="n">
-        <v>-3.17128</v>
+        <v>-2.37628</v>
       </c>
       <c r="M2" t="n">
-        <v>20094800</v>
+        <v>20095253</v>
       </c>
       <c r="N2" t="n">
-        <v>20094840</v>
+        <v>20095287</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2563.98</v>
+        <v>2453.75</v>
       </c>
       <c r="F3" t="n">
-        <v>313102738146</v>
+        <v>299616447986</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>18953547562</v>
+        <v>16109455999</v>
       </c>
       <c r="I3" t="n">
-        <v>2706.4</v>
+        <v>2584.49</v>
       </c>
       <c r="J3" t="n">
-        <v>2554.67</v>
+        <v>2505.93</v>
       </c>
       <c r="K3" t="n">
-        <v>-146.6474657697954</v>
+        <v>-112.9431574399232</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.41009</v>
+        <v>-4.40033</v>
       </c>
       <c r="M3" t="n">
-        <v>122113300.6445289</v>
+        <v>122116138.3627867</v>
       </c>
       <c r="N3" t="n">
-        <v>122113300.6445289</v>
+        <v>122116138.3627866</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999657</v>
+        <v>0.999266</v>
       </c>
       <c r="F4" t="n">
-        <v>184024739868</v>
+        <v>183947973674</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>70890232603</v>
+        <v>72685776344</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0.999737</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9996969999999999</v>
+        <v>0.999286</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000283683330175366</v>
+        <v>-0.000356363244156999</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02837</v>
+        <v>-0.03565</v>
       </c>
       <c r="M4" t="n">
         <v>184088295340.2641</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>768.89</v>
+        <v>737.47</v>
       </c>
       <c r="F5" t="n">
-        <v>102386705728</v>
+        <v>98245388192</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>956765677</v>
+        <v>913601189</v>
       </c>
       <c r="I5" t="n">
-        <v>783.75</v>
+        <v>775.55</v>
       </c>
       <c r="J5" t="n">
-        <v>759.7</v>
+        <v>753.78</v>
       </c>
       <c r="K5" t="n">
-        <v>-15.89842921753348</v>
+        <v>-31.87099163766561</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.02583</v>
+        <v>-4.14266</v>
       </c>
       <c r="M5" t="n">
-        <v>133158900.53</v>
+        <v>133158851.29</v>
       </c>
       <c r="N5" t="n">
-        <v>133158895.86</v>
+        <v>133158844.31</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>90258712518</v>
+        <v>85525825977</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2356734848</v>
+        <v>2752650752</v>
       </c>
       <c r="I6" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="J6" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07998528859241238</v>
+        <v>-0.07707604883707941</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.2954</v>
+        <v>-5.37967</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999772</v>
+        <v>0.9996080000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>73807045678</v>
+        <v>73471207690</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19412496327</v>
+        <v>25037493604</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999999</v>
+        <v>0.999947</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9996930000000001</v>
+        <v>0.999571</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000185814575094589</v>
+        <v>-0.000135193043981352</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01858</v>
+        <v>-0.01352</v>
       </c>
       <c r="M7" t="n">
-        <v>73824304674.12912</v>
+        <v>73501552634.68355</v>
       </c>
       <c r="N7" t="n">
-        <v>73892500989.58794</v>
+        <v>73533457037.85652</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>116.54</v>
+        <v>109.46</v>
       </c>
       <c r="F8" t="n">
-        <v>68648764460</v>
+        <v>64476917607</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2976532357</v>
+        <v>3749023976</v>
       </c>
       <c r="I8" t="n">
-        <v>121.42</v>
+        <v>117.12</v>
       </c>
       <c r="J8" t="n">
-        <v>115.58</v>
+        <v>111.31</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.434457163822955</v>
+        <v>-7.185932086156669</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.66573</v>
+        <v>-6.16057</v>
       </c>
       <c r="M8" t="n">
-        <v>589094366.4621038</v>
+        <v>589164869.8296187</v>
       </c>
       <c r="N8" t="n">
-        <v>635382237.2552732</v>
+        <v>635459783.215508</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33497</v>
+        <v>0.332967</v>
       </c>
       <c r="F9" t="n">
-        <v>31815831391</v>
+        <v>31619383250</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>383766010</v>
+        <v>381635897</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336337</v>
+        <v>0.336339</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332038</v>
+        <v>0.334195</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000646152911107811</v>
+        <v>-0.001995348797104557</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.19253</v>
+        <v>-0.5956900000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>94985842073.90219</v>
+        <v>94987253784.43079</v>
       </c>
       <c r="N9" t="n">
-        <v>94985842034.73439</v>
+        <v>94987248406.44139</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.036</v>
+        <v>1.018</v>
       </c>
       <c r="F10" t="n">
-        <v>24400779197</v>
+        <v>24057016883</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>42318399</v>
+        <v>50723304</v>
       </c>
       <c r="I10" t="n">
-        <v>1.045</v>
+        <v>1.05</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
+        <v>1.015</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00917217</v>
+        <v>-0.01811179848908506</v>
       </c>
       <c r="L10" t="n">
-        <v>0.89294</v>
+        <v>-1.74758</v>
       </c>
       <c r="M10" t="n">
-        <v>23544660846.378</v>
+        <v>23624390711.938</v>
       </c>
       <c r="N10" t="n">
-        <v>23624390711.938</v>
+        <v>23680455088.278</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1328.4</v>
+        <v>1138.18</v>
       </c>
       <c r="F11" t="n">
-        <v>22538337192</v>
+        <v>19318937576</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>662476158</v>
+        <v>1168009645</v>
       </c>
       <c r="I11" t="n">
-        <v>1372.71</v>
+        <v>1342.46</v>
       </c>
       <c r="J11" t="n">
-        <v>1290.32</v>
+        <v>1197.31</v>
       </c>
       <c r="K11" t="n">
-        <v>-38.57750273453371</v>
+        <v>-191.2417607644527</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.82209</v>
+        <v>-14.38531</v>
       </c>
       <c r="M11" t="n">
-        <v>16966725.1655448</v>
+        <v>16975014.2280448</v>
       </c>
       <c r="N11" t="n">
-        <v>16973411.1030448</v>
+        <v>16975168.9155448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>88.48</v>
+        <v>83.77</v>
       </c>
       <c r="F12" t="n">
-        <v>19681215781</v>
+        <v>18622053784</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>921768723</v>
+        <v>722499696</v>
       </c>
       <c r="I12" t="n">
-        <v>92.69</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>88.12</v>
+        <v>84.81999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.357509282893488</v>
+        <v>-4.729306967090295</v>
       </c>
       <c r="L12" t="n">
-        <v>-4.69352</v>
+        <v>-5.34369</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08853</v>
+        <v>0.08343</v>
       </c>
       <c r="F13" t="n">
-        <v>13829916812</v>
+        <v>13035376113</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1289976831</v>
+        <v>1035494540</v>
       </c>
       <c r="I13" t="n">
-        <v>0.095608</v>
+        <v>0.089611</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08802</v>
+        <v>0.086212</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.007330841534385416</v>
+        <v>-0.005327263690678111</v>
       </c>
       <c r="L13" t="n">
-        <v>-7.64738</v>
+        <v>-6.00208</v>
       </c>
       <c r="M13" t="n">
-        <v>156221976383.7052</v>
+        <v>156240286383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156227106383.7052</v>
+        <v>156240336383.7052</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,274 +1279,274 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>551.5700000000001</v>
+        <v>0.998779</v>
       </c>
       <c r="F14" t="n">
-        <v>10379062182</v>
+        <v>10160841510</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131925000</v>
+        <v>261209419</v>
       </c>
       <c r="I14" t="n">
-        <v>571.13</v>
+        <v>0.9993840000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>546.26</v>
+        <v>0.998564</v>
       </c>
       <c r="K14" t="n">
-        <v>-11.06474666563224</v>
+        <v>-0.000404272260524419</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.96658</v>
+        <v>-0.04046</v>
       </c>
       <c r="M14" t="n">
-        <v>18814509.01509035</v>
+        <v>10173593673.88628</v>
       </c>
       <c r="N14" t="n">
-        <v>18814534.21500215</v>
+        <v>10176138131.64019</v>
       </c>
       <c r="O14" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999261</v>
+        <v>529.37</v>
       </c>
       <c r="F15" t="n">
-        <v>10213026946</v>
+        <v>10001073256</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>234422650</v>
+        <v>105287832</v>
       </c>
       <c r="I15" t="n">
-        <v>1.001</v>
+        <v>562.48</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9972839999999999</v>
+        <v>543.02</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000638180382625086</v>
+        <v>-24.6022872021058</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.06382</v>
+        <v>-4.44109</v>
       </c>
       <c r="M15" t="n">
-        <v>10219583954.93842</v>
+        <v>18814914.61013515</v>
       </c>
       <c r="N15" t="n">
-        <v>10225135591.02598</v>
+        <v>18814951.21008307</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.38</v>
+        <v>80.52</v>
       </c>
       <c r="F16" t="n">
-        <v>10007919360</v>
+        <v>9563923473</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>359633874</v>
+        <v>116583702</v>
       </c>
       <c r="I16" t="n">
-        <v>14.03</v>
+        <v>83.15000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>13.3</v>
+        <v>81.25</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6434031945828256</v>
+        <v>-2.414882848260817</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.58915</v>
+        <v>-2.91192</v>
       </c>
       <c r="M16" t="n">
-        <v>748099970.424884</v>
+        <v>118786640</v>
       </c>
       <c r="N16" t="n">
-        <v>1000000000</v>
+        <v>293356139</v>
       </c>
       <c r="O16" t="n">
-        <v>52.7</v>
+        <v>87.91</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>82.84</v>
+        <v>12.5</v>
       </c>
       <c r="F17" t="n">
-        <v>9840284078</v>
+        <v>9346647077</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>96063383</v>
+        <v>363849364</v>
       </c>
       <c r="I17" t="n">
-        <v>85.76000000000001</v>
+        <v>13.51</v>
       </c>
       <c r="J17" t="n">
-        <v>82.43000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="K17" t="n">
-        <v>-3.079920322956198</v>
+        <v>-0.9183556652922942</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.58467</v>
+        <v>-6.84296</v>
       </c>
       <c r="M17" t="n">
-        <v>118786640</v>
+        <v>748099970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>293356139</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>87.91</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.254716</v>
+        <v>0.234448</v>
       </c>
       <c r="F18" t="n">
-        <v>9563470546</v>
+        <v>8800411697</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>669732544</v>
+        <v>566946360</v>
       </c>
       <c r="I18" t="n">
-        <v>0.273346</v>
+        <v>0.257921</v>
       </c>
       <c r="J18" t="n">
-        <v>0.251674</v>
+        <v>0.245488</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01806671782487718</v>
+        <v>-0.02118463027107437</v>
       </c>
       <c r="L18" t="n">
-        <v>-6.62311</v>
+        <v>-8.287140000000001</v>
       </c>
       <c r="M18" t="n">
         <v>37547445640.06296</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.9</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8185480786</v>
+        <v>8228365665</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>168767</v>
+        <v>183100</v>
       </c>
       <c r="I19" t="n">
-        <v>8.94</v>
+        <v>8.98</v>
       </c>
       <c r="J19" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01187828</v>
+        <v>0.04636461</v>
       </c>
       <c r="L19" t="n">
-        <v>0.13366</v>
+        <v>0.52103</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01093967</v>
+        <v>0.0102398</v>
       </c>
       <c r="F20" t="n">
-        <v>7761341518</v>
+        <v>7263022872</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>19340374</v>
+        <v>11342867</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01158268</v>
+        <v>0.01104738</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01086226</v>
+        <v>0.01051044</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000349764978778226</v>
+        <v>-0.000719488865830247</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.09816</v>
+        <v>-6.5651</v>
       </c>
       <c r="M20" t="n">
-        <v>709253096298.4821</v>
+        <v>709255220640.1809</v>
       </c>
       <c r="N20" t="n">
-        <v>1142408526965.963</v>
+        <v>1142408457495.08</v>
       </c>
       <c r="O20" t="n">
         <v>0.01946402</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261007T155208Z-6097ef</t>
+          <t>20261008T155523Z-5280ca</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.199864</v>
+        <v>0.190704</v>
       </c>
       <c r="F21" t="n">
-        <v>7004341485</v>
+        <v>6679365869</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>182609425</v>
+        <v>212934869</v>
       </c>
       <c r="I21" t="n">
-        <v>0.214726</v>
+        <v>0.201748</v>
       </c>
       <c r="J21" t="n">
-        <v>0.200037</v>
+        <v>0.196579</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.01507322184339882</v>
+        <v>-0.009446584420751858</v>
       </c>
       <c r="L21" t="n">
-        <v>-7.01285</v>
+        <v>-4.71975</v>
       </c>
       <c r="M21" t="n">
-        <v>35039548656.1776</v>
+        <v>35040796089.828</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-07T15:49:30.000Z</t>
+          <t>2026-10-08T15:53:48.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81396</v>
+        <v>82896</v>
       </c>
       <c r="F2" t="n">
-        <v>1635464580346</v>
+        <v>1666087027653</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>36173945818</v>
+        <v>35334605442</v>
       </c>
       <c r="I2" t="n">
-        <v>83616</v>
+        <v>83398</v>
       </c>
       <c r="J2" t="n">
-        <v>81792</v>
+        <v>80427</v>
       </c>
       <c r="K2" t="n">
-        <v>-1981.28377951149</v>
+        <v>1716.21</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.37628</v>
+        <v>2.11407</v>
       </c>
       <c r="M2" t="n">
-        <v>20095253</v>
+        <v>20095612</v>
       </c>
       <c r="N2" t="n">
-        <v>20095287</v>
+        <v>20095756</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2453.75</v>
+        <v>2488.08</v>
       </c>
       <c r="F3" t="n">
-        <v>299616447986</v>
+        <v>303910519652</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>16109455999</v>
+        <v>14357957337</v>
       </c>
       <c r="I3" t="n">
-        <v>2584.49</v>
+        <v>2512.13</v>
       </c>
       <c r="J3" t="n">
-        <v>2505.93</v>
+        <v>2409.36</v>
       </c>
       <c r="K3" t="n">
-        <v>-112.9431574399232</v>
+        <v>39.73</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.40033</v>
+        <v>1.62291</v>
       </c>
       <c r="M3" t="n">
-        <v>122116138.3627867</v>
+        <v>122118912.3561888</v>
       </c>
       <c r="N3" t="n">
-        <v>122116138.3627866</v>
+        <v>122118912.3561887</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999266</v>
+        <v>0.99924</v>
       </c>
       <c r="F4" t="n">
-        <v>183947973674</v>
+        <v>184100942277</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>72685776344</v>
+        <v>66783503413</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999737</v>
+        <v>0.9995039999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999286</v>
+        <v>0.9991370000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000356363244156999</v>
+        <v>-6.9524370260421e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.03565</v>
+        <v>-0.00696</v>
       </c>
       <c r="M4" t="n">
-        <v>184088295340.2641</v>
+        <v>184243755711.5305</v>
       </c>
       <c r="N4" t="n">
-        <v>189555241729.7862</v>
+        <v>189710704214.9262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>737.47</v>
+        <v>739.1900000000001</v>
       </c>
       <c r="F5" t="n">
-        <v>98245388192</v>
+        <v>98453907261</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>913601189</v>
+        <v>1066213692</v>
       </c>
       <c r="I5" t="n">
-        <v>775.55</v>
+        <v>744.62</v>
       </c>
       <c r="J5" t="n">
-        <v>753.78</v>
+        <v>717.92</v>
       </c>
       <c r="K5" t="n">
-        <v>-31.87099163766561</v>
+        <v>5.28</v>
       </c>
       <c r="L5" t="n">
-        <v>-4.14266</v>
+        <v>0.71936</v>
       </c>
       <c r="M5" t="n">
-        <v>133158851.29</v>
+        <v>133158806.3</v>
       </c>
       <c r="N5" t="n">
-        <v>133158844.31</v>
+        <v>133158797.11</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="F6" t="n">
-        <v>85525825977</v>
+        <v>87186569386</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2752650752</v>
+        <v>2629892556</v>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.07707604883707941</v>
+        <v>0.03037017</v>
       </c>
       <c r="L6" t="n">
-        <v>-5.37967</v>
+        <v>2.24843</v>
       </c>
       <c r="M6" t="n">
         <v>63092975951</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9996080000000001</v>
+        <v>0.999657</v>
       </c>
       <c r="F7" t="n">
-        <v>73471207690</v>
+        <v>73015073825</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>25037493604</v>
+        <v>20659935548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999947</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999571</v>
+        <v>0.999533</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000135193043981352</v>
+        <v>1.587e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01352</v>
+        <v>0.00159</v>
       </c>
       <c r="M7" t="n">
-        <v>73501552634.68355</v>
+        <v>73041605055.77086</v>
       </c>
       <c r="N7" t="n">
-        <v>73533457037.85652</v>
+        <v>72953730836.52467</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>109.46</v>
+        <v>109.53</v>
       </c>
       <c r="F8" t="n">
-        <v>64476917607</v>
+        <v>64513588491</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3749023976</v>
+        <v>4088516662</v>
       </c>
       <c r="I8" t="n">
-        <v>117.12</v>
+        <v>111.76</v>
       </c>
       <c r="J8" t="n">
-        <v>111.31</v>
+        <v>105.85</v>
       </c>
       <c r="K8" t="n">
-        <v>-7.185932086156669</v>
+        <v>0.891673</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.16057</v>
+        <v>0.82074</v>
       </c>
       <c r="M8" t="n">
-        <v>589164869.8296187</v>
+        <v>588768792.7130715</v>
       </c>
       <c r="N8" t="n">
-        <v>635459783.215508</v>
+        <v>635458796.9438441</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332967</v>
+        <v>0.332224</v>
       </c>
       <c r="F9" t="n">
-        <v>31619383250</v>
+        <v>31554983849</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>381635897</v>
+        <v>343172826</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336339</v>
+        <v>0.33388</v>
       </c>
       <c r="J9" t="n">
-        <v>0.334195</v>
+        <v>0.331625</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001995348797104557</v>
+        <v>-0.0007353347170117039</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.5956900000000001</v>
+        <v>-0.22085</v>
       </c>
       <c r="M9" t="n">
-        <v>94987253784.43079</v>
+        <v>94988557102.43939</v>
       </c>
       <c r="N9" t="n">
-        <v>94987248406.44139</v>
+        <v>94988550336.58499</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.018</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>24057016883</v>
+        <v>24390911217</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>50723304</v>
+        <v>27898545</v>
       </c>
       <c r="I10" t="n">
-        <v>1.05</v>
+        <v>1.033</v>
       </c>
       <c r="J10" t="n">
-        <v>1.015</v>
+        <v>1.004</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01811179848908506</v>
+        <v>0.01174397</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.74758</v>
+        <v>1.15336</v>
       </c>
       <c r="M10" t="n">
-        <v>23624390711.938</v>
+        <v>23680455088.278</v>
       </c>
       <c r="N10" t="n">
-        <v>23680455088.278</v>
+        <v>23720592133.328</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1138.18</v>
+        <v>1218.38</v>
       </c>
       <c r="F11" t="n">
-        <v>19318937576</v>
+        <v>20688657319</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1168009645</v>
+        <v>1263543238</v>
       </c>
       <c r="I11" t="n">
-        <v>1342.46</v>
+        <v>1245.56</v>
       </c>
       <c r="J11" t="n">
-        <v>1197.31</v>
+        <v>1118.04</v>
       </c>
       <c r="K11" t="n">
-        <v>-191.2417607644527</v>
+        <v>76</v>
       </c>
       <c r="L11" t="n">
-        <v>-14.38531</v>
+        <v>6.65255</v>
       </c>
       <c r="M11" t="n">
-        <v>16975014.2280448</v>
+        <v>16975986.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>16975168.9155448</v>
+        <v>16976967.3530448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>83.77</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>18622053784</v>
+        <v>18979857472</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>722499696</v>
+        <v>989779284</v>
       </c>
       <c r="I12" t="n">
-        <v>88.98999999999999</v>
+        <v>86.48999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>84.81999999999999</v>
+        <v>82.69</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.729306967090295</v>
+        <v>1.54</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.34369</v>
+        <v>1.84152</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08343</v>
+        <v>0.08448700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13035376113</v>
+        <v>13204586196</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1035494540</v>
+        <v>827079275</v>
       </c>
       <c r="I13" t="n">
-        <v>0.089611</v>
+        <v>0.08548</v>
       </c>
       <c r="J13" t="n">
-        <v>0.086212</v>
+        <v>0.08118599999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.005327263690678111</v>
+        <v>0.00155924</v>
       </c>
       <c r="L13" t="n">
-        <v>-6.00208</v>
+        <v>1.88023</v>
       </c>
       <c r="M13" t="n">
-        <v>156240286383.7052</v>
+        <v>156253346383.7053</v>
       </c>
       <c r="N13" t="n">
-        <v>156240336383.7052</v>
+        <v>171966153126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.998779</v>
+        <v>0.99909</v>
       </c>
       <c r="F14" t="n">
-        <v>10160841510</v>
+        <v>10132011002</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>261209419</v>
+        <v>180771476</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9993840000000001</v>
+        <v>0.999689</v>
       </c>
       <c r="J14" t="n">
-        <v>0.998564</v>
+        <v>0.998767</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000404272260524419</v>
+        <v>0.00026629</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.04046</v>
+        <v>0.02666</v>
       </c>
       <c r="M14" t="n">
-        <v>10173593673.88628</v>
+        <v>10140893505.77248</v>
       </c>
       <c r="N14" t="n">
-        <v>10176138131.64019</v>
+        <v>10146161517.0051</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.37</v>
+        <v>535.72</v>
       </c>
       <c r="F15" t="n">
-        <v>10001073256</v>
+        <v>10089670168</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>105287832</v>
+        <v>136277979</v>
       </c>
       <c r="I15" t="n">
-        <v>562.48</v>
+        <v>547.99</v>
       </c>
       <c r="J15" t="n">
-        <v>543.02</v>
+        <v>518.46</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.6022872021058</v>
+        <v>2.89</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.44109</v>
+        <v>0.5421</v>
       </c>
       <c r="M15" t="n">
-        <v>18814914.61013515</v>
+        <v>18815332.80427901</v>
       </c>
       <c r="N15" t="n">
-        <v>18814951.21008307</v>
+        <v>18815379.00072787</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80.52</v>
+        <v>81.42</v>
       </c>
       <c r="F16" t="n">
-        <v>9563923473</v>
+        <v>9673565600</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>116583702</v>
+        <v>131123874</v>
       </c>
       <c r="I16" t="n">
-        <v>83.15000000000001</v>
+        <v>81.92</v>
       </c>
       <c r="J16" t="n">
-        <v>81.25</v>
+        <v>79.09</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.414882848260817</v>
+        <v>1.041</v>
       </c>
       <c r="L16" t="n">
-        <v>-2.91192</v>
+        <v>1.29541</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.5</v>
+        <v>12.8</v>
       </c>
       <c r="F17" t="n">
-        <v>9346647077</v>
+        <v>9579548881</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>363849364</v>
+        <v>391108683</v>
       </c>
       <c r="I17" t="n">
-        <v>13.51</v>
+        <v>12.96</v>
       </c>
       <c r="J17" t="n">
-        <v>12.83</v>
+        <v>12.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.9183556652922942</v>
+        <v>0.39424</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.84296</v>
+        <v>3.17697</v>
       </c>
       <c r="M17" t="n">
         <v>748099970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.234448</v>
+        <v>0.236879</v>
       </c>
       <c r="F18" t="n">
-        <v>8800411697</v>
+        <v>8899618341</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>566946360</v>
+        <v>657309375</v>
       </c>
       <c r="I18" t="n">
-        <v>0.257921</v>
+        <v>0.240873</v>
       </c>
       <c r="J18" t="n">
-        <v>0.245488</v>
+        <v>0.224223</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.02118463027107437</v>
+        <v>0.00400053</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.287140000000001</v>
+        <v>1.71786</v>
       </c>
       <c r="M18" t="n">
         <v>37547445640.06296</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="F19" t="n">
-        <v>8228365665</v>
+        <v>8210362841</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>183100</v>
+        <v>237852</v>
       </c>
       <c r="I19" t="n">
-        <v>8.98</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>8.880000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.04636461</v>
+        <v>-0.02133319201318429</v>
       </c>
       <c r="L19" t="n">
-        <v>0.52103</v>
+        <v>-0.23844</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.0102398</v>
+        <v>0.01027616</v>
       </c>
       <c r="F20" t="n">
-        <v>7263022872</v>
+        <v>7289138703</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>11342867</v>
+        <v>14164329</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01104738</v>
+        <v>0.01038489</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01051044</v>
+        <v>0.01009653</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000719488865830247</v>
+        <v>-1.8986119798692e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>-6.5651</v>
+        <v>-0.18442</v>
       </c>
       <c r="M20" t="n">
-        <v>709255220640.1809</v>
+        <v>709255213582.6736</v>
       </c>
       <c r="N20" t="n">
-        <v>1142408457495.08</v>
+        <v>1142408456721.49</v>
       </c>
       <c r="O20" t="n">
         <v>0.01946402</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261008T155523Z-5280ca</t>
+          <t>20261009T153754Z-425c8a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.190704</v>
+        <v>0.192395</v>
       </c>
       <c r="F21" t="n">
-        <v>6679365869</v>
+        <v>6743401016</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>212934869</v>
+        <v>162076610</v>
       </c>
       <c r="I21" t="n">
-        <v>0.201748</v>
+        <v>0.19548</v>
       </c>
       <c r="J21" t="n">
-        <v>0.196579</v>
+        <v>0.185599</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.009446584420751858</v>
+        <v>0.00290656</v>
       </c>
       <c r="L21" t="n">
-        <v>-4.71975</v>
+        <v>1.5339</v>
       </c>
       <c r="M21" t="n">
-        <v>35040796089.828</v>
+        <v>35047668674.76303</v>
       </c>
       <c r="N21" t="n">
         <v>50001786839.69947</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-08T15:53:48.000Z</t>
+          <t>2026-10-09T15:36:53.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82896</v>
+        <v>82943</v>
       </c>
       <c r="F2" t="n">
-        <v>1666087027653</v>
+        <v>1666880202390</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>35334605442</v>
+        <v>18184434014</v>
       </c>
       <c r="I2" t="n">
-        <v>83398</v>
+        <v>83003</v>
       </c>
       <c r="J2" t="n">
-        <v>80427</v>
+        <v>82229</v>
       </c>
       <c r="K2" t="n">
-        <v>1716.21</v>
+        <v>63.33</v>
       </c>
       <c r="L2" t="n">
-        <v>2.11407</v>
+        <v>0.00809</v>
       </c>
       <c r="M2" t="n">
-        <v>20095612</v>
+        <v>20096093</v>
       </c>
       <c r="N2" t="n">
-        <v>20095756</v>
+        <v>20096150</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2488.08</v>
+        <v>2507.29</v>
       </c>
       <c r="F3" t="n">
-        <v>303910519652</v>
+        <v>306208138076</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>14357957337</v>
+        <v>5815677560</v>
       </c>
       <c r="I3" t="n">
-        <v>2512.13</v>
+        <v>2497.44</v>
       </c>
       <c r="J3" t="n">
-        <v>2409.36</v>
+        <v>2473.24</v>
       </c>
       <c r="K3" t="n">
-        <v>39.73</v>
+        <v>20.43</v>
       </c>
       <c r="L3" t="n">
-        <v>1.62291</v>
+        <v>0.76512</v>
       </c>
       <c r="M3" t="n">
-        <v>122118912.3561888</v>
+        <v>122121843.6487577</v>
       </c>
       <c r="N3" t="n">
-        <v>122118912.3561887</v>
+        <v>122121843.6487576</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99924</v>
+        <v>0.99915</v>
       </c>
       <c r="F4" t="n">
-        <v>184100942277</v>
+        <v>184096328968</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>66783503413</v>
+        <v>33993309550</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9995039999999999</v>
+        <v>0.999347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9991370000000001</v>
+        <v>0.999153</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.9524370260421e-05</v>
+        <v>-4.9786123598516e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00696</v>
+        <v>-0.00423</v>
       </c>
       <c r="M4" t="n">
-        <v>184243755711.5305</v>
+        <v>184252955809.8857</v>
       </c>
       <c r="N4" t="n">
-        <v>189710704214.9262</v>
+        <v>189719904214.9262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>739.1900000000001</v>
+        <v>752.8</v>
       </c>
       <c r="F5" t="n">
-        <v>98453907261</v>
+        <v>100247043054</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1066213692</v>
+        <v>545683879</v>
       </c>
       <c r="I5" t="n">
-        <v>744.62</v>
+        <v>750.52</v>
       </c>
       <c r="J5" t="n">
-        <v>717.92</v>
+        <v>736.83</v>
       </c>
       <c r="K5" t="n">
-        <v>5.28</v>
+        <v>12.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71936</v>
+        <v>1.66487</v>
       </c>
       <c r="M5" t="n">
-        <v>133158806.3</v>
+        <v>133158766.16</v>
       </c>
       <c r="N5" t="n">
-        <v>133158797.11</v>
+        <v>133158760.66</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,34 +785,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="F6" t="n">
-        <v>87186569386</v>
+        <v>88922561743</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2629892556</v>
+        <v>1131832042</v>
       </c>
       <c r="I6" t="n">
         <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03037017</v>
+        <v>0.02694059</v>
       </c>
       <c r="L6" t="n">
-        <v>2.24843</v>
+        <v>1.85108</v>
       </c>
       <c r="M6" t="n">
-        <v>63092975951</v>
+        <v>63129671205</v>
       </c>
       <c r="N6" t="n">
-        <v>99985612577</v>
+        <v>99985607990</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999657</v>
+        <v>0.999706</v>
       </c>
       <c r="F7" t="n">
-        <v>73015073825</v>
+        <v>72926018956</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>20659935548</v>
+        <v>9296881091</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999533</v>
+        <v>0.999595</v>
       </c>
       <c r="K7" t="n">
-        <v>1.587e-05</v>
+        <v>8.435e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00159</v>
+        <v>0.00515</v>
       </c>
       <c r="M7" t="n">
-        <v>73041605055.77086</v>
+        <v>72949857527.59346</v>
       </c>
       <c r="N7" t="n">
-        <v>72953730836.52467</v>
+        <v>72950949062.63478</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>109.53</v>
+        <v>110.49</v>
       </c>
       <c r="F8" t="n">
-        <v>64513588491</v>
+        <v>65052571359</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4088516662</v>
+        <v>1865014891</v>
       </c>
       <c r="I8" t="n">
-        <v>111.76</v>
+        <v>110.25</v>
       </c>
       <c r="J8" t="n">
-        <v>105.85</v>
+        <v>108.42</v>
       </c>
       <c r="K8" t="n">
-        <v>0.891673</v>
+        <v>0.557211</v>
       </c>
       <c r="L8" t="n">
-        <v>0.82074</v>
+        <v>0.43693</v>
       </c>
       <c r="M8" t="n">
-        <v>588768792.7130715</v>
+        <v>588791600.2704512</v>
       </c>
       <c r="N8" t="n">
-        <v>635458796.9438441</v>
+        <v>635536242.7030827</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332224</v>
+        <v>0.331292</v>
       </c>
       <c r="F9" t="n">
-        <v>31554983849</v>
+        <v>31469152769</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>343172826</v>
+        <v>297248561</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33388</v>
+        <v>0.33278</v>
       </c>
       <c r="J9" t="n">
-        <v>0.331625</v>
+        <v>0.330537</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0007353347170117039</v>
+        <v>-0.001038510521755243</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.22085</v>
+        <v>-0.34836</v>
       </c>
       <c r="M9" t="n">
-        <v>94988557102.43939</v>
+        <v>94989440644.44269</v>
       </c>
       <c r="N9" t="n">
-        <v>94988550336.58499</v>
+        <v>94990293974.8167</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.03</v>
+        <v>1.001</v>
       </c>
       <c r="F10" t="n">
-        <v>24390911217</v>
+        <v>23747297960</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>27898545</v>
+        <v>696058509</v>
       </c>
       <c r="I10" t="n">
-        <v>1.033</v>
+        <v>1.035</v>
       </c>
       <c r="J10" t="n">
-        <v>1.004</v>
+        <v>1.001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.01174397</v>
+        <v>-0.02865054697437874</v>
       </c>
       <c r="L10" t="n">
-        <v>1.15336</v>
+        <v>-2.78279</v>
       </c>
       <c r="M10" t="n">
-        <v>23680455088.278</v>
+        <v>23720592133.328</v>
       </c>
       <c r="N10" t="n">
-        <v>23720592133.328</v>
+        <v>23760321232.028</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1218.38</v>
+        <v>1234.92</v>
       </c>
       <c r="F11" t="n">
-        <v>20688657319</v>
+        <v>20959845647</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1263543238</v>
+        <v>476957388</v>
       </c>
       <c r="I11" t="n">
-        <v>1245.56</v>
+        <v>1233.47</v>
       </c>
       <c r="J11" t="n">
-        <v>1118.04</v>
+        <v>1199.31</v>
       </c>
       <c r="K11" t="n">
-        <v>76</v>
+        <v>17.99</v>
       </c>
       <c r="L11" t="n">
-        <v>6.65255</v>
+        <v>1.25865</v>
       </c>
       <c r="M11" t="n">
-        <v>16975986.1030448</v>
+        <v>16978514.2280448</v>
       </c>
       <c r="N11" t="n">
-        <v>16976967.3530448</v>
+        <v>16978714.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.29000000000001</v>
+        <v>85.93000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>18979857472</v>
+        <v>19100968853</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>989779284</v>
+        <v>561969940</v>
       </c>
       <c r="I12" t="n">
-        <v>86.48999999999999</v>
+        <v>85.62</v>
       </c>
       <c r="J12" t="n">
-        <v>82.69</v>
+        <v>83.34999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.54</v>
+        <v>0.455243</v>
       </c>
       <c r="L12" t="n">
-        <v>1.84152</v>
+        <v>0.53284</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08448700000000001</v>
+        <v>0.086352</v>
       </c>
       <c r="F13" t="n">
-        <v>13204586196</v>
+        <v>13491985354</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>827079275</v>
+        <v>411218989</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08548</v>
+        <v>0.086574</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08118599999999999</v>
+        <v>0.084193</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00155924</v>
+        <v>0.00185734</v>
       </c>
       <c r="L13" t="n">
-        <v>1.88023</v>
+        <v>2.13147</v>
       </c>
       <c r="M13" t="n">
-        <v>156253346383.7053</v>
+        <v>156266976383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171966153126.579</v>
+        <v>171978973126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.99909</v>
+        <v>0.999719</v>
       </c>
       <c r="F14" t="n">
-        <v>10132011002</v>
+        <v>10137062606</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>180771476</v>
+        <v>106054519</v>
       </c>
       <c r="I14" t="n">
-        <v>0.999689</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.998767</v>
+        <v>0.998852</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00026629</v>
+        <v>0.00066631</v>
       </c>
       <c r="L14" t="n">
-        <v>0.02666</v>
+        <v>0.0722</v>
       </c>
       <c r="M14" t="n">
-        <v>10140893505.77248</v>
+        <v>10139915011.99066</v>
       </c>
       <c r="N14" t="n">
-        <v>10146161517.0051</v>
+        <v>10135652198.44782</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,209 +1344,209 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>535.72</v>
+        <v>13.19</v>
       </c>
       <c r="F15" t="n">
-        <v>10089670168</v>
+        <v>10117713780</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>136277979</v>
+        <v>215923036</v>
       </c>
       <c r="I15" t="n">
-        <v>547.99</v>
+        <v>13.1</v>
       </c>
       <c r="J15" t="n">
-        <v>518.46</v>
+        <v>12.71</v>
       </c>
       <c r="K15" t="n">
-        <v>2.89</v>
+        <v>0.399951</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5421</v>
+        <v>3.00469</v>
       </c>
       <c r="M15" t="n">
-        <v>18815332.80427901</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N15" t="n">
-        <v>18815379.00072787</v>
+        <v>1000000000</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81.42</v>
+        <v>528.5700000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9673565600</v>
+        <v>9946781965</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>131123874</v>
+        <v>120336678</v>
       </c>
       <c r="I16" t="n">
-        <v>81.92</v>
+        <v>538.76</v>
       </c>
       <c r="J16" t="n">
-        <v>79.09</v>
+        <v>514.87</v>
       </c>
       <c r="K16" t="n">
-        <v>1.041</v>
+        <v>-5.724317877995986</v>
       </c>
       <c r="L16" t="n">
-        <v>1.29541</v>
+        <v>-1.16601</v>
       </c>
       <c r="M16" t="n">
-        <v>118786640</v>
+        <v>18815769.59700966</v>
       </c>
       <c r="N16" t="n">
-        <v>293356139</v>
+        <v>18815793.59685232</v>
       </c>
       <c r="O16" t="n">
-        <v>87.91</v>
+        <v>797.73</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.8</v>
+        <v>81.59</v>
       </c>
       <c r="F17" t="n">
-        <v>9579548881</v>
+        <v>9691998896</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>391108683</v>
+        <v>39442675</v>
       </c>
       <c r="I17" t="n">
-        <v>12.96</v>
+        <v>81.52</v>
       </c>
       <c r="J17" t="n">
-        <v>12.11</v>
+        <v>80.84</v>
       </c>
       <c r="K17" t="n">
-        <v>0.39424</v>
+        <v>0.19654</v>
       </c>
       <c r="L17" t="n">
-        <v>3.17697</v>
+        <v>0.15835</v>
       </c>
       <c r="M17" t="n">
-        <v>748099970.424884</v>
+        <v>118786640</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>293356139</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>87.91</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.236879</v>
+        <v>0.257615</v>
       </c>
       <c r="F18" t="n">
-        <v>8899618341</v>
+        <v>9675714571</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>657309375</v>
+        <v>549979641</v>
       </c>
       <c r="I18" t="n">
-        <v>0.240873</v>
+        <v>0.25707</v>
       </c>
       <c r="J18" t="n">
-        <v>0.224223</v>
+        <v>0.235245</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00400053</v>
+        <v>0.02050313</v>
       </c>
       <c r="L18" t="n">
-        <v>1.71786</v>
+        <v>8.57197</v>
       </c>
       <c r="M18" t="n">
         <v>37547445640.06296</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.93</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8210362841</v>
+        <v>8109941201</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>237852</v>
+        <v>426317</v>
       </c>
       <c r="I19" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="J19" t="n">
-        <v>8.869999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.02133319201318429</v>
+        <v>-0.09994458944429141</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.23844</v>
+        <v>-1.12373</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01027616</v>
+        <v>0.01027819</v>
       </c>
       <c r="F20" t="n">
-        <v>7289138703</v>
+        <v>7292297237</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>14164329</v>
+        <v>14662024</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01038489</v>
+        <v>0.01036208</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01009653</v>
+        <v>0.01016087</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.8986119798692e-05</v>
+        <v>2.975e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.18442</v>
+        <v>0.05059</v>
       </c>
       <c r="M20" t="n">
-        <v>709255213582.6736</v>
+        <v>709255212863.9448</v>
       </c>
       <c r="N20" t="n">
         <v>1142408456721.49</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261009T153754Z-425c8a</t>
+          <t>20261010T145227Z-64b977</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.192395</v>
+        <v>5.39</v>
       </c>
       <c r="F21" t="n">
-        <v>6743401016</v>
+        <v>7063281836</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>162076610</v>
+        <v>903088531</v>
       </c>
       <c r="I21" t="n">
-        <v>0.19548</v>
+        <v>5.37</v>
       </c>
       <c r="J21" t="n">
-        <v>0.185599</v>
+        <v>4.64</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00290656</v>
+        <v>0.629455</v>
       </c>
       <c r="L21" t="n">
-        <v>1.5339</v>
+        <v>12.90829</v>
       </c>
       <c r="M21" t="n">
-        <v>35047668674.76303</v>
+        <v>1308604470</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.69947</v>
+        <v>1308604442</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-09T15:36:53.000Z</t>
+          <t>2026-10-10T14:49:44.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82943</v>
+        <v>83059</v>
       </c>
       <c r="F2" t="n">
-        <v>1666880202390</v>
+        <v>1669227546176</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>18184434014</v>
+        <v>12186587000</v>
       </c>
       <c r="I2" t="n">
-        <v>83003</v>
+        <v>83167</v>
       </c>
       <c r="J2" t="n">
-        <v>82229</v>
+        <v>82735</v>
       </c>
       <c r="K2" t="n">
-        <v>63.33</v>
+        <v>143.12</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00809</v>
+        <v>0.1726</v>
       </c>
       <c r="M2" t="n">
-        <v>20096093</v>
+        <v>20096581</v>
       </c>
       <c r="N2" t="n">
-        <v>20096150</v>
+        <v>20096675</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2507.29</v>
+        <v>2504.79</v>
       </c>
       <c r="F3" t="n">
-        <v>306208138076</v>
+        <v>305909194915</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>5815677560</v>
+        <v>6731141853</v>
       </c>
       <c r="I3" t="n">
-        <v>2497.44</v>
+        <v>2516.64</v>
       </c>
       <c r="J3" t="n">
-        <v>2473.24</v>
+        <v>2495.93</v>
       </c>
       <c r="K3" t="n">
-        <v>20.43</v>
+        <v>-1.428077983568073</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76512</v>
+        <v>-0.05698</v>
       </c>
       <c r="M3" t="n">
-        <v>122121843.6487577</v>
+        <v>122124805.030901</v>
       </c>
       <c r="N3" t="n">
-        <v>122121843.6487576</v>
+        <v>122124805.030901</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99915</v>
+        <v>0.999084</v>
       </c>
       <c r="F4" t="n">
-        <v>184096328968</v>
+        <v>184081178651</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>33993309550</v>
+        <v>27521247829</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999347</v>
+        <v>0.999295</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999153</v>
+        <v>0.999019</v>
       </c>
       <c r="K4" t="n">
-        <v>-4.9786123598516e-05</v>
+        <v>-6.1568393554867e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00423</v>
+        <v>-0.00616</v>
       </c>
       <c r="M4" t="n">
-        <v>184252955809.8857</v>
+        <v>184250955801.4404</v>
       </c>
       <c r="N4" t="n">
-        <v>189719904214.9262</v>
+        <v>189717904214.9262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>752.8</v>
+        <v>749.51</v>
       </c>
       <c r="F5" t="n">
-        <v>100247043054</v>
+        <v>99810670681</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>545683879</v>
+        <v>358305896</v>
       </c>
       <c r="I5" t="n">
-        <v>750.52</v>
+        <v>751.0700000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>736.83</v>
+        <v>744.37</v>
       </c>
       <c r="K5" t="n">
-        <v>12.75</v>
+        <v>-1.901632290828047</v>
       </c>
       <c r="L5" t="n">
-        <v>1.66487</v>
+        <v>-0.25307</v>
       </c>
       <c r="M5" t="n">
-        <v>133158766.16</v>
+        <v>133158726.55</v>
       </c>
       <c r="N5" t="n">
-        <v>133158760.66</v>
+        <v>133158719.93</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="F6" t="n">
-        <v>88922561743</v>
+        <v>88357526663</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1131832042</v>
+        <v>670734569</v>
       </c>
       <c r="I6" t="n">
         <v>1.41</v>
       </c>
       <c r="J6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02694059</v>
+        <v>-0.006635651416276866</v>
       </c>
       <c r="L6" t="n">
-        <v>1.85108</v>
+        <v>-0.47192</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999706</v>
+        <v>0.999649</v>
       </c>
       <c r="F7" t="n">
-        <v>72926018956</v>
+        <v>72957415683</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>9296881091</v>
+        <v>6836688585</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999595</v>
+        <v>0.999541</v>
       </c>
       <c r="K7" t="n">
-        <v>8.435e-05</v>
+        <v>-3.7944440052451e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00515</v>
+        <v>-0.0038</v>
       </c>
       <c r="M7" t="n">
-        <v>72949857527.59346</v>
+        <v>72982742216.50526</v>
       </c>
       <c r="N7" t="n">
-        <v>72950949062.63478</v>
+        <v>72990569880.65465</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>110.49</v>
+        <v>109.66</v>
       </c>
       <c r="F8" t="n">
-        <v>65052571359</v>
+        <v>64600960688</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1865014891</v>
+        <v>1484280077</v>
       </c>
       <c r="I8" t="n">
-        <v>110.25</v>
+        <v>110.51</v>
       </c>
       <c r="J8" t="n">
-        <v>108.42</v>
+        <v>108.94</v>
       </c>
       <c r="K8" t="n">
-        <v>0.557211</v>
+        <v>-0.7783395538901061</v>
       </c>
       <c r="L8" t="n">
-        <v>0.43693</v>
+        <v>-0.70478</v>
       </c>
       <c r="M8" t="n">
-        <v>588791600.2704512</v>
+        <v>589050940.0924026</v>
       </c>
       <c r="N8" t="n">
-        <v>635536242.7030827</v>
+        <v>635597924.89221</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.331292</v>
+        <v>0.330214</v>
       </c>
       <c r="F9" t="n">
-        <v>31469152769</v>
+        <v>31354148691</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>297248561</v>
+        <v>234764466</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33278</v>
+        <v>0.331141</v>
       </c>
       <c r="J9" t="n">
-        <v>0.330537</v>
+        <v>0.329959</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001038510521755243</v>
+        <v>-0.000904145028157777</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.34836</v>
+        <v>-0.27306</v>
       </c>
       <c r="M9" t="n">
-        <v>94989440644.44269</v>
+        <v>94991264224.08649</v>
       </c>
       <c r="N9" t="n">
-        <v>94990293974.8167</v>
+        <v>94992384211.12158</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.001</v>
+        <v>1.056</v>
       </c>
       <c r="F10" t="n">
-        <v>23747297960</v>
+        <v>25089705065</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>696058509</v>
+        <v>106017</v>
       </c>
       <c r="I10" t="n">
-        <v>1.035</v>
+        <v>1.065</v>
       </c>
       <c r="J10" t="n">
         <v>1.001</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.02865054697437874</v>
+        <v>0.054826</v>
       </c>
       <c r="L10" t="n">
-        <v>-2.78279</v>
+        <v>5.47649</v>
       </c>
       <c r="M10" t="n">
-        <v>23720592133.328</v>
+        <v>23760321232.028</v>
       </c>
       <c r="N10" t="n">
-        <v>23760321232.028</v>
+        <v>23768766961.538</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T13:11:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1234.92</v>
+        <v>1229.26</v>
       </c>
       <c r="F11" t="n">
-        <v>20959845647</v>
+        <v>20872690637</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>476957388</v>
+        <v>384641429</v>
       </c>
       <c r="I11" t="n">
-        <v>1233.47</v>
+        <v>1242.11</v>
       </c>
       <c r="J11" t="n">
-        <v>1199.31</v>
+        <v>1217.38</v>
       </c>
       <c r="K11" t="n">
-        <v>17.99</v>
+        <v>-8.702892782682511</v>
       </c>
       <c r="L11" t="n">
-        <v>1.25865</v>
+        <v>-0.703</v>
       </c>
       <c r="M11" t="n">
-        <v>16978514.2280448</v>
+        <v>16980234.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16978714.2280448</v>
+        <v>16980537.6655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.93000000000001</v>
+        <v>85.7</v>
       </c>
       <c r="F12" t="n">
-        <v>19100968853</v>
+        <v>19067227028</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>561969940</v>
+        <v>407592971</v>
       </c>
       <c r="I12" t="n">
-        <v>85.62</v>
+        <v>86.06999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>83.34999999999999</v>
+        <v>84.61</v>
       </c>
       <c r="K12" t="n">
-        <v>0.455243</v>
+        <v>-0.7873690517116074</v>
       </c>
       <c r="L12" t="n">
-        <v>0.53284</v>
+        <v>-0.91035</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.086352</v>
+        <v>0.08579000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>13491985354</v>
+        <v>13408006409</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>411218989</v>
+        <v>325766008</v>
       </c>
       <c r="I13" t="n">
-        <v>0.086574</v>
+        <v>0.086212</v>
       </c>
       <c r="J13" t="n">
-        <v>0.084193</v>
+        <v>0.084881</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00185734</v>
+        <v>-0.000378416736457513</v>
       </c>
       <c r="L13" t="n">
-        <v>2.13147</v>
+        <v>-0.43916</v>
       </c>
       <c r="M13" t="n">
-        <v>156266976383.7052</v>
+        <v>156280186383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171978973126.579</v>
+        <v>171992943126.579</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999719</v>
+        <v>0.9998629999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>10137062606</v>
+        <v>10230597218</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>106054519</v>
+        <v>95132429</v>
       </c>
       <c r="I14" t="n">
         <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.998852</v>
+        <v>0.999613</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00066631</v>
+        <v>0.00010294</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0722</v>
+        <v>0.0103</v>
       </c>
       <c r="M14" t="n">
-        <v>10139915011.99066</v>
+        <v>10232058647.55109</v>
       </c>
       <c r="N14" t="n">
-        <v>10135652198.44782</v>
+        <v>10243719480.66228</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,144 +1344,144 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13.19</v>
+        <v>534.26</v>
       </c>
       <c r="F15" t="n">
-        <v>10117713780</v>
+        <v>10052137818</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>215923036</v>
+        <v>79685467</v>
       </c>
       <c r="I15" t="n">
-        <v>13.1</v>
+        <v>534.21</v>
       </c>
       <c r="J15" t="n">
-        <v>12.71</v>
+        <v>516.71</v>
       </c>
       <c r="K15" t="n">
-        <v>0.399951</v>
+        <v>6.97</v>
       </c>
       <c r="L15" t="n">
-        <v>3.00469</v>
+        <v>1.32135</v>
       </c>
       <c r="M15" t="n">
-        <v>766849970.424884</v>
+        <v>18816203.99329853</v>
       </c>
       <c r="N15" t="n">
-        <v>1000000000</v>
+        <v>18816244.19323827</v>
       </c>
       <c r="O15" t="n">
-        <v>52.7</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>528.5700000000001</v>
+        <v>13.1</v>
       </c>
       <c r="F16" t="n">
-        <v>9946781965</v>
+        <v>10051898235</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>120336678</v>
+        <v>181011706</v>
       </c>
       <c r="I16" t="n">
-        <v>538.76</v>
+        <v>13.13</v>
       </c>
       <c r="J16" t="n">
-        <v>514.87</v>
+        <v>12.83</v>
       </c>
       <c r="K16" t="n">
-        <v>-5.724317877995986</v>
+        <v>-0.01843439623908516</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.16601</v>
+        <v>-0.14049</v>
       </c>
       <c r="M16" t="n">
-        <v>18815769.59700966</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>18815793.59685232</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>797.73</v>
+        <v>52.7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>81.59</v>
+        <v>81.68000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9691998896</v>
+        <v>9702723318</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>39442675</v>
+        <v>21085098</v>
       </c>
       <c r="I17" t="n">
-        <v>81.52</v>
+        <v>81.77</v>
       </c>
       <c r="J17" t="n">
-        <v>80.84</v>
+        <v>81.36</v>
       </c>
       <c r="K17" t="n">
-        <v>0.19654</v>
+        <v>0.096194</v>
       </c>
       <c r="L17" t="n">
-        <v>0.15835</v>
+        <v>0.1179</v>
       </c>
       <c r="M17" t="n">
         <v>118786640</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.257615</v>
+        <v>0.24878</v>
       </c>
       <c r="F18" t="n">
-        <v>9675714571</v>
+        <v>9342857433</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>549979641</v>
+        <v>352422148</v>
       </c>
       <c r="I18" t="n">
-        <v>0.25707</v>
+        <v>0.255736</v>
       </c>
       <c r="J18" t="n">
-        <v>0.235245</v>
+        <v>0.245082</v>
       </c>
       <c r="K18" t="n">
-        <v>0.02050313</v>
+        <v>-0.00655251918655958</v>
       </c>
       <c r="L18" t="n">
-        <v>8.57197</v>
+        <v>-2.56627</v>
       </c>
       <c r="M18" t="n">
         <v>37547445640.06296</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.800000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="F19" t="n">
-        <v>8109941201</v>
+        <v>8198349023</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>426317</v>
+        <v>272068</v>
       </c>
       <c r="I19" t="n">
-        <v>8.94</v>
+        <v>8.91</v>
       </c>
       <c r="J19" t="n">
-        <v>8.65</v>
+        <v>8.81</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.09994458944429141</v>
+        <v>0.124024</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.12373</v>
+        <v>1.4112</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01027819</v>
+        <v>0.01024847</v>
       </c>
       <c r="F20" t="n">
-        <v>7292297237</v>
+        <v>7252585180</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>14662024</v>
+        <v>17188189</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01036208</v>
+        <v>0.01236574</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01016087</v>
+        <v>0.01011368</v>
       </c>
       <c r="K20" t="n">
-        <v>2.975e-05</v>
+        <v>1.923e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>0.05059</v>
+        <v>0.188</v>
       </c>
       <c r="M20" t="n">
-        <v>709255212863.9448</v>
+        <v>709255212503.9934</v>
       </c>
       <c r="N20" t="n">
-        <v>1142408456721.49</v>
+        <v>1142408331879.385</v>
       </c>
       <c r="O20" t="n">
         <v>0.01946402</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261010T145227Z-64b977</t>
+          <t>20261011T151020Z-45e7e2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.39</v>
+        <v>5.35</v>
       </c>
       <c r="F21" t="n">
-        <v>7063281836</v>
+        <v>7009818312</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>903088531</v>
+        <v>546659886</v>
       </c>
       <c r="I21" t="n">
-        <v>5.37</v>
+        <v>5.41</v>
       </c>
       <c r="J21" t="n">
-        <v>4.64</v>
+        <v>5.17</v>
       </c>
       <c r="K21" t="n">
-        <v>0.629455</v>
+        <v>-0.05075220492640042</v>
       </c>
       <c r="L21" t="n">
-        <v>12.90829</v>
+        <v>-0.93928</v>
       </c>
       <c r="M21" t="n">
-        <v>1308604470</v>
+        <v>1308678855</v>
       </c>
       <c r="N21" t="n">
-        <v>1308604442</v>
+        <v>1308678807</v>
       </c>
       <c r="O21" t="n">
         <v>20.44</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-10T14:49:44.000Z</t>
+          <t>2026-10-11T15:08:58.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83059</v>
+        <v>82419</v>
       </c>
       <c r="F2" t="n">
-        <v>1669227546176</v>
+        <v>1656427025732</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>12186587000</v>
+        <v>24650580952</v>
       </c>
       <c r="I2" t="n">
-        <v>83167</v>
+        <v>84231</v>
       </c>
       <c r="J2" t="n">
-        <v>82735</v>
+        <v>82345</v>
       </c>
       <c r="K2" t="n">
-        <v>143.12</v>
+        <v>-1348.280440237897</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1726</v>
+        <v>-1.59152</v>
       </c>
       <c r="M2" t="n">
-        <v>20096581</v>
+        <v>20097181</v>
       </c>
       <c r="N2" t="n">
-        <v>20096675</v>
+        <v>20097212</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2504.79</v>
+        <v>2510.53</v>
       </c>
       <c r="F3" t="n">
-        <v>305909194915</v>
+        <v>306634360427</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>6731141853</v>
+        <v>11982945045</v>
       </c>
       <c r="I3" t="n">
-        <v>2516.64</v>
+        <v>2575.42</v>
       </c>
       <c r="J3" t="n">
-        <v>2495.93</v>
+        <v>2502.7</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.428077983568073</v>
+        <v>-26.66465560980987</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.05698</v>
+        <v>-1.02365</v>
       </c>
       <c r="M3" t="n">
-        <v>122124805.030901</v>
+        <v>122127761.0974645</v>
       </c>
       <c r="N3" t="n">
-        <v>122124805.030901</v>
+        <v>122127761.0974645</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,31 +655,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999084</v>
+        <v>0.99912</v>
       </c>
       <c r="F4" t="n">
-        <v>184081178651</v>
+        <v>184089333502</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>27521247829</v>
+        <v>49274965340</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999295</v>
+        <v>0.999393</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999019</v>
+        <v>0.9990059999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>-6.1568393554867e-05</v>
+        <v>3.276e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00616</v>
+        <v>0.00314</v>
       </c>
       <c r="M4" t="n">
-        <v>184250955801.4404</v>
+        <v>184250955791.0506</v>
       </c>
       <c r="N4" t="n">
         <v>189717904214.9262</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>749.51</v>
+        <v>743.86</v>
       </c>
       <c r="F5" t="n">
-        <v>99810670681</v>
+        <v>99053409542</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>358305896</v>
+        <v>710031230</v>
       </c>
       <c r="I5" t="n">
-        <v>751.0700000000001</v>
+        <v>756.78</v>
       </c>
       <c r="J5" t="n">
-        <v>744.37</v>
+        <v>742.26</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.901632290828047</v>
+        <v>-9.201241026713774</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.25307</v>
+        <v>-1.21427</v>
       </c>
       <c r="M5" t="n">
-        <v>133158726.55</v>
+        <v>133158664.67</v>
       </c>
       <c r="N5" t="n">
-        <v>133158719.93</v>
+        <v>133158663.66</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>88357526663</v>
+        <v>85826320626</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>670734569</v>
+        <v>1548998925</v>
       </c>
       <c r="I6" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="J6" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.006635651416276866</v>
+        <v>-0.05437503489582962</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.47192</v>
+        <v>-3.8199</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999649</v>
+        <v>0.999719</v>
       </c>
       <c r="F7" t="n">
-        <v>72957415683</v>
+        <v>72801143161</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6836688585</v>
+        <v>14593943207</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999541</v>
+        <v>0.999603</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.7944440052451e-05</v>
+        <v>7.964e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0038</v>
+        <v>0.0064</v>
       </c>
       <c r="M7" t="n">
-        <v>72982742216.50526</v>
+        <v>72822710151.64021</v>
       </c>
       <c r="N7" t="n">
-        <v>72990569880.65465</v>
+        <v>72859308695.52313</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>109.66</v>
+        <v>107.65</v>
       </c>
       <c r="F8" t="n">
-        <v>64600960688</v>
+        <v>63423079493</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1484280077</v>
+        <v>2831206929</v>
       </c>
       <c r="I8" t="n">
-        <v>110.51</v>
+        <v>113.22</v>
       </c>
       <c r="J8" t="n">
-        <v>108.94</v>
+        <v>107.1</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7783395538901061</v>
+        <v>-4.188856501155911</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.70478</v>
+        <v>-3.73426</v>
       </c>
       <c r="M8" t="n">
-        <v>589050940.0924026</v>
+        <v>589106679.9280622</v>
       </c>
       <c r="N8" t="n">
-        <v>635597924.89221</v>
+        <v>635659513.0599921</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330214</v>
+        <v>0.330143</v>
       </c>
       <c r="F9" t="n">
-        <v>31354148691</v>
+        <v>31363906332</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>234764466</v>
+        <v>314031874</v>
       </c>
       <c r="I9" t="n">
-        <v>0.331141</v>
+        <v>0.332573</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329959</v>
+        <v>0.329791</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000904145028157777</v>
+        <v>-0.000488172078400628</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.27306</v>
+        <v>-0.17123</v>
       </c>
       <c r="M9" t="n">
-        <v>94991264224.08649</v>
+        <v>94993898714.32539</v>
       </c>
       <c r="N9" t="n">
-        <v>94992384211.12158</v>
+        <v>94993904104.35719</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.056</v>
+        <v>1.064</v>
       </c>
       <c r="F10" t="n">
-        <v>25089705065</v>
+        <v>25286757943</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>106017</v>
+        <v>20449604</v>
       </c>
       <c r="I10" t="n">
-        <v>1.065</v>
+        <v>1.064</v>
       </c>
       <c r="J10" t="n">
         <v>1.001</v>
       </c>
-      <c r="K10" t="n">
-        <v>0.054826</v>
-      </c>
-      <c r="L10" t="n">
-        <v>5.47649</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>23760321232.028</v>
+        <v>23765481428.638</v>
       </c>
       <c r="N10" t="n">
-        <v>23768766961.538</v>
+        <v>23765481428.638</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-11T13:11:49.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1229.26</v>
+        <v>1237.26</v>
       </c>
       <c r="F11" t="n">
-        <v>20872690637</v>
+        <v>21013202823</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>384641429</v>
+        <v>887452492</v>
       </c>
       <c r="I11" t="n">
-        <v>1242.11</v>
+        <v>1347</v>
       </c>
       <c r="J11" t="n">
-        <v>1217.38</v>
+        <v>1231.57</v>
       </c>
       <c r="K11" t="n">
-        <v>-8.702892782682511</v>
+        <v>-39.82823958688641</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.703</v>
+        <v>-3.10919</v>
       </c>
       <c r="M11" t="n">
-        <v>16980234.5405448</v>
+        <v>16981864.2280448</v>
       </c>
       <c r="N11" t="n">
-        <v>16980537.6655448</v>
+        <v>16982415.7905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>85.7</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>19067227028</v>
+        <v>18557420994</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>407592971</v>
+        <v>663151781</v>
       </c>
       <c r="I12" t="n">
-        <v>86.06999999999999</v>
+        <v>88</v>
       </c>
       <c r="J12" t="n">
-        <v>84.61</v>
+        <v>83.43000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.7873690517116074</v>
+        <v>-3.054013731208784</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.91035</v>
+        <v>-3.44129</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08579000000000001</v>
+        <v>0.084716</v>
       </c>
       <c r="F13" t="n">
-        <v>13408006409</v>
+        <v>13241384727</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>325766008</v>
+        <v>574892005</v>
       </c>
       <c r="I13" t="n">
-        <v>0.086212</v>
+        <v>0.087994</v>
       </c>
       <c r="J13" t="n">
-        <v>0.084881</v>
+        <v>0.08432000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000378416736457513</v>
+        <v>-0.002150878668448375</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.43916</v>
+        <v>-2.47312</v>
       </c>
       <c r="M13" t="n">
-        <v>156280186383.7052</v>
+        <v>156295516383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>171992943126.579</v>
+        <v>156295586383.7053</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.9998629999999999</v>
+        <v>0.999731</v>
       </c>
       <c r="F14" t="n">
-        <v>10230597218</v>
+        <v>10338798428</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>95132429</v>
+        <v>162818293</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999613</v>
+        <v>0.999603</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00010294</v>
+        <v>-0.000248847066838809</v>
       </c>
       <c r="L14" t="n">
-        <v>0.0103</v>
+        <v>-0.02451</v>
       </c>
       <c r="M14" t="n">
-        <v>10232058647.55109</v>
+        <v>10341534107.8296</v>
       </c>
       <c r="N14" t="n">
-        <v>10243719480.66228</v>
+        <v>10318236813.72889</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>534.26</v>
+        <v>532.08</v>
       </c>
       <c r="F15" t="n">
-        <v>10052137818</v>
+        <v>10012712675</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>79685467</v>
+        <v>117731720</v>
       </c>
       <c r="I15" t="n">
-        <v>534.21</v>
+        <v>544.37</v>
       </c>
       <c r="J15" t="n">
-        <v>516.71</v>
+        <v>528.4</v>
       </c>
       <c r="K15" t="n">
-        <v>6.97</v>
+        <v>-4.271410246690721</v>
       </c>
       <c r="L15" t="n">
-        <v>1.32135</v>
+        <v>-0.8133899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>18816203.99329853</v>
+        <v>18816701.84597846</v>
       </c>
       <c r="N15" t="n">
-        <v>18816244.19323827</v>
+        <v>18816711.44597846</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1409,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1431,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>13.1</v>
+        <v>12.87</v>
       </c>
       <c r="F16" t="n">
-        <v>10051898235</v>
+        <v>9873475456</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>181011706</v>
+        <v>279155090</v>
       </c>
       <c r="I16" t="n">
-        <v>13.13</v>
+        <v>13.49</v>
       </c>
       <c r="J16" t="n">
-        <v>12.83</v>
+        <v>12.87</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.01843439623908516</v>
+        <v>-0.4710940885604717</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.14049</v>
+        <v>-3.53559</v>
       </c>
       <c r="M16" t="n">
         <v>766849970.424884</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>81.68000000000001</v>
+        <v>81.18000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9702723318</v>
+        <v>9641124283</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>21085098</v>
+        <v>75293335</v>
       </c>
       <c r="I17" t="n">
-        <v>81.77</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>81.36</v>
+        <v>81.05</v>
       </c>
       <c r="K17" t="n">
-        <v>0.096194</v>
+        <v>-1.275905863662047</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1179</v>
+        <v>-1.54001</v>
       </c>
       <c r="M17" t="n">
         <v>118786640</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,31 +1561,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.24878</v>
+        <v>0.241946</v>
       </c>
       <c r="F18" t="n">
-        <v>9342857433</v>
+        <v>9084341751</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>352422148</v>
+        <v>366016938</v>
       </c>
       <c r="I18" t="n">
-        <v>0.255736</v>
+        <v>0.255631</v>
       </c>
       <c r="J18" t="n">
-        <v>0.245082</v>
+        <v>0.240709</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.00655251918655958</v>
+        <v>-0.01063859813238999</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.56627</v>
+        <v>-4.24941</v>
       </c>
       <c r="M18" t="n">
-        <v>37547445640.06296</v>
+        <v>37553537941.9088</v>
       </c>
       <c r="N18" t="n">
         <v>45000000000</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.91</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8198349023</v>
+        <v>8171515359</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>272068</v>
+        <v>246457</v>
       </c>
       <c r="I19" t="n">
-        <v>8.91</v>
+        <v>8.93</v>
       </c>
       <c r="J19" t="n">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="K19" t="n">
-        <v>0.124024</v>
+        <v>-0.0301293965274354</v>
       </c>
       <c r="L19" t="n">
-        <v>1.4112</v>
+        <v>-0.33797</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1665,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1691,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01024847</v>
+        <v>0.01031817</v>
       </c>
       <c r="F20" t="n">
-        <v>7252585180</v>
+        <v>7312979215</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>17188189</v>
+        <v>17288281</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01236574</v>
+        <v>0.01044666</v>
       </c>
       <c r="J20" t="n">
-        <v>0.01011368</v>
+        <v>0.00930218</v>
       </c>
       <c r="K20" t="n">
-        <v>1.923e-05</v>
+        <v>-0.000121837721900196</v>
       </c>
       <c r="L20" t="n">
-        <v>0.188</v>
+        <v>-1.17802</v>
       </c>
       <c r="M20" t="n">
-        <v>709255212503.9934</v>
+        <v>709254167224.5737</v>
       </c>
       <c r="N20" t="n">
-        <v>1142408331879.385</v>
+        <v>1142407411082.119</v>
       </c>
       <c r="O20" t="n">
         <v>0.01946402</v>
@@ -1734,14 +1730,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261011T151020Z-45e7e2</t>
+          <t>20261012T181808Z-dd3add</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1756,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="F21" t="n">
-        <v>7009818312</v>
+        <v>7094008686</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>546659886</v>
+        <v>1058196053</v>
       </c>
       <c r="I21" t="n">
-        <v>5.41</v>
+        <v>5.97</v>
       </c>
       <c r="J21" t="n">
-        <v>5.17</v>
+        <v>5.38</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.05075220492640042</v>
+        <v>-0.2246557427977889</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.93928</v>
+        <v>-3.92788</v>
       </c>
       <c r="M21" t="n">
-        <v>1308678855</v>
+        <v>1308783290</v>
       </c>
       <c r="N21" t="n">
-        <v>1308678807</v>
+        <v>1308783331</v>
       </c>
       <c r="O21" t="n">
         <v>20.44</v>
@@ -1799,7 +1795,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-11T15:08:58.000Z</t>
+          <t>2026-10-12T18:16:58.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82419</v>
+        <v>83484</v>
       </c>
       <c r="F2" t="n">
-        <v>1656427025732</v>
+        <v>1677802941405</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>24650580952</v>
+        <v>32366344427</v>
       </c>
       <c r="I2" t="n">
-        <v>84231</v>
+        <v>84074</v>
       </c>
       <c r="J2" t="n">
-        <v>82345</v>
+        <v>81018</v>
       </c>
       <c r="K2" t="n">
-        <v>-1348.280440237897</v>
+        <v>674.51</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.59152</v>
+        <v>0.78382</v>
       </c>
       <c r="M2" t="n">
-        <v>20097181</v>
+        <v>20097368</v>
       </c>
       <c r="N2" t="n">
-        <v>20097212</v>
+        <v>20097665</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2510.53</v>
+        <v>2517.54</v>
       </c>
       <c r="F3" t="n">
-        <v>306634360427</v>
+        <v>307469153755</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11982945045</v>
+        <v>15094857039</v>
       </c>
       <c r="I3" t="n">
-        <v>2575.42</v>
+        <v>2535.36</v>
       </c>
       <c r="J3" t="n">
-        <v>2502.7</v>
+        <v>2411.24</v>
       </c>
       <c r="K3" t="n">
-        <v>-26.66465560980987</v>
+        <v>-11.22416947773218</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.02365</v>
+        <v>-0.48582</v>
       </c>
       <c r="M3" t="n">
-        <v>122127761.0974645</v>
+        <v>122130709.7379206</v>
       </c>
       <c r="N3" t="n">
-        <v>122127761.0974645</v>
+        <v>122130709.7379206</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99912</v>
+        <v>0.99939</v>
       </c>
       <c r="F4" t="n">
-        <v>184089333502</v>
+        <v>184087351209</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>49274965340</v>
+        <v>62852666179</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999393</v>
+        <v>0.999347</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9990059999999999</v>
+        <v>0.998987</v>
       </c>
       <c r="K4" t="n">
-        <v>3.276e-05</v>
+        <v>0.0001512</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00314</v>
+        <v>0.01148</v>
       </c>
       <c r="M4" t="n">
-        <v>184250955791.0506</v>
+        <v>184199691342.6323</v>
       </c>
       <c r="N4" t="n">
-        <v>189717904214.9262</v>
+        <v>189666639768.5562</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>743.86</v>
+        <v>745.0599999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>99053409542</v>
+        <v>99211410839</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>710031230</v>
+        <v>808365228</v>
       </c>
       <c r="I5" t="n">
-        <v>756.78</v>
+        <v>747.49</v>
       </c>
       <c r="J5" t="n">
-        <v>742.26</v>
+        <v>722.58</v>
       </c>
       <c r="K5" t="n">
-        <v>-9.201241026713774</v>
+        <v>-1.153053036656161</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.21427</v>
+        <v>-0.19066</v>
       </c>
       <c r="M5" t="n">
-        <v>133158664.67</v>
+        <v>133158622.31</v>
       </c>
       <c r="N5" t="n">
-        <v>133158663.66</v>
+        <v>133158614.4</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="F6" t="n">
-        <v>85826320626</v>
+        <v>86786019857</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1548998925</v>
+        <v>2234922341</v>
       </c>
       <c r="I6" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="J6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05437503489582962</v>
+        <v>-0.002333580879375186</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.8199</v>
+        <v>-0.2394</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999719</v>
+        <v>0.999854</v>
       </c>
       <c r="F7" t="n">
-        <v>72801143161</v>
+        <v>72643651578</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14593943207</v>
+        <v>19571506418</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999885</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999603</v>
+        <v>0.999664</v>
       </c>
       <c r="K7" t="n">
-        <v>7.964e-05</v>
+        <v>9.873e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0064</v>
+        <v>0.005</v>
       </c>
       <c r="M7" t="n">
-        <v>72822710151.64021</v>
+        <v>72654256775.06488</v>
       </c>
       <c r="N7" t="n">
-        <v>72859308695.52313</v>
+        <v>72615791006.75041</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>107.65</v>
+        <v>107.71</v>
       </c>
       <c r="F8" t="n">
-        <v>63423079493</v>
+        <v>63459711653</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2831206929</v>
+        <v>4137608387</v>
       </c>
       <c r="I8" t="n">
-        <v>113.22</v>
+        <v>108.89</v>
       </c>
       <c r="J8" t="n">
-        <v>107.1</v>
+        <v>102.19</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.188856501155911</v>
+        <v>-1.187708151020871</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.73426</v>
+        <v>-1.13652</v>
       </c>
       <c r="M8" t="n">
-        <v>589106679.9280622</v>
+        <v>589162540.5223119</v>
       </c>
       <c r="N8" t="n">
-        <v>635659513.0599921</v>
+        <v>635721176.4235597</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330143</v>
+        <v>0.327306</v>
       </c>
       <c r="F9" t="n">
-        <v>31363906332</v>
+        <v>31092473638</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>314031874</v>
+        <v>377841130</v>
       </c>
       <c r="I9" t="n">
-        <v>0.332573</v>
+        <v>0.330781</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329791</v>
+        <v>0.326852</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000488172078400628</v>
+        <v>-0.003635475615367922</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.17123</v>
+        <v>-1.06884</v>
       </c>
       <c r="M9" t="n">
-        <v>94993898714.32539</v>
+        <v>94995183371.01869</v>
       </c>
       <c r="N9" t="n">
-        <v>94993904104.35719</v>
+        <v>94995187293.75169</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,30 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.064</v>
+        <v>1.052</v>
       </c>
       <c r="F10" t="n">
-        <v>25286757943</v>
+        <v>24999203356</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>20449604</v>
+        <v>13751499</v>
       </c>
       <c r="I10" t="n">
-        <v>1.064</v>
+        <v>1.065</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.052</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.01197705163604001</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-1.12236</v>
+      </c>
       <c r="M10" t="n">
-        <v>23765481428.638</v>
+        <v>23771507038.718</v>
       </c>
       <c r="N10" t="n">
-        <v>23765481428.638</v>
+        <v>23771507038.718</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1237.26</v>
+        <v>1205.14</v>
       </c>
       <c r="F11" t="n">
-        <v>21013202823</v>
+        <v>20465566734</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>887452492</v>
+        <v>1049757217</v>
       </c>
       <c r="I11" t="n">
-        <v>1347</v>
+        <v>1246.72</v>
       </c>
       <c r="J11" t="n">
-        <v>1231.57</v>
+        <v>1125.65</v>
       </c>
       <c r="K11" t="n">
-        <v>-39.82823958688641</v>
+        <v>-55.07522991170049</v>
       </c>
       <c r="L11" t="n">
-        <v>-3.10919</v>
+        <v>-4.4828</v>
       </c>
       <c r="M11" t="n">
         <v>16981864.2280448</v>
       </c>
       <c r="N11" t="n">
-        <v>16982415.7905448</v>
+        <v>16984120.4780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>83.40000000000001</v>
+        <v>81.42</v>
       </c>
       <c r="F12" t="n">
-        <v>18557420994</v>
+        <v>18112496466</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>663151781</v>
+        <v>977002599</v>
       </c>
       <c r="I12" t="n">
-        <v>88</v>
+        <v>83.83</v>
       </c>
       <c r="J12" t="n">
-        <v>83.43000000000001</v>
+        <v>79.52</v>
       </c>
       <c r="K12" t="n">
-        <v>-3.054013731208784</v>
+        <v>-2.878024591999647</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.44129</v>
+        <v>-3.51302</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.084716</v>
+        <v>0.084467</v>
       </c>
       <c r="F13" t="n">
-        <v>13241384727</v>
+        <v>13202849848</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>574892005</v>
+        <v>770231015</v>
       </c>
       <c r="I13" t="n">
-        <v>0.087994</v>
+        <v>0.085368</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08432000000000001</v>
+        <v>0.08021499999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002150878668448375</v>
+        <v>-0.000609963815638118</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.47312</v>
+        <v>-0.7618200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>156295516383.7052</v>
+        <v>156308336383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156295586383.7053</v>
+        <v>172020613126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.999731</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
-        <v>10338798428</v>
+        <v>10345349924</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>162818293</v>
+        <v>98601636</v>
       </c>
       <c r="I14" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999603</v>
+        <v>0.999474</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000248847066838809</v>
+        <v>0.00021531</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.02451</v>
+        <v>0.01759</v>
       </c>
       <c r="M14" t="n">
-        <v>10341534107.8296</v>
+        <v>10342606746.26388</v>
       </c>
       <c r="N14" t="n">
-        <v>10318236813.72889</v>
+        <v>10339720906.07536</v>
       </c>
       <c r="O14" t="n">
         <v>1.057</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>532.08</v>
+        <v>529.4299999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10012712675</v>
+        <v>9962280629</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>117731720</v>
+        <v>91190599</v>
       </c>
       <c r="I15" t="n">
-        <v>544.37</v>
+        <v>544.02</v>
       </c>
       <c r="J15" t="n">
-        <v>528.4</v>
+        <v>520.71</v>
       </c>
       <c r="K15" t="n">
-        <v>-4.271410246690721</v>
+        <v>-5.439951510246374</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.8133899999999999</v>
+        <v>-0.9897899999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>18816701.84597846</v>
+        <v>18817072.64103359</v>
       </c>
       <c r="N15" t="n">
-        <v>18816711.44597846</v>
+        <v>18817108.63889607</v>
       </c>
       <c r="O15" t="n">
         <v>797.73</v>
@@ -1405,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.87</v>
+        <v>12.92</v>
       </c>
       <c r="F16" t="n">
-        <v>9873475456</v>
+        <v>9906640961</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>279155090</v>
+        <v>403759662</v>
       </c>
       <c r="I16" t="n">
-        <v>13.49</v>
+        <v>13.17</v>
       </c>
       <c r="J16" t="n">
-        <v>12.87</v>
+        <v>12.29</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4710940885604717</v>
+        <v>-0.1180999401439902</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.53559</v>
+        <v>-0.98659</v>
       </c>
       <c r="M16" t="n">
         <v>766849970.424884</v>
@@ -1470,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>81.18000000000001</v>
+        <v>82.04000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>9641124283</v>
+        <v>9744807842</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>75293335</v>
+        <v>133066970</v>
       </c>
       <c r="I17" t="n">
-        <v>82.98999999999999</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>81.05</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.275905863662047</v>
+        <v>0.439872</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.54001</v>
+        <v>0.51727</v>
       </c>
       <c r="M17" t="n">
         <v>118786640</v>
@@ -1535,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.241946</v>
+        <v>0.235639</v>
       </c>
       <c r="F18" t="n">
-        <v>9084341751</v>
+        <v>8849088292</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>366016938</v>
+        <v>500392272</v>
       </c>
       <c r="I18" t="n">
-        <v>0.255631</v>
+        <v>0.243667</v>
       </c>
       <c r="J18" t="n">
-        <v>0.240709</v>
+        <v>0.224713</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01063859813238999</v>
+        <v>-0.008187459966972538</v>
       </c>
       <c r="L18" t="n">
-        <v>-4.24941</v>
+        <v>-3.45018</v>
       </c>
       <c r="M18" t="n">
         <v>37553537941.9088</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.880000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="F19" t="n">
-        <v>8171515359</v>
+        <v>8182963832</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>246457</v>
+        <v>101405</v>
       </c>
       <c r="I19" t="n">
-        <v>8.93</v>
+        <v>8.92</v>
       </c>
       <c r="J19" t="n">
-        <v>8.77</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.0301293965274354</v>
+        <v>0.01134385</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.33797</v>
+        <v>0.12888</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1665,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1691,28 +1695,28 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01031817</v>
+        <v>0.01000173</v>
       </c>
       <c r="F20" t="n">
-        <v>7312979215</v>
+        <v>7093772088</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>17288281</v>
+        <v>19120331</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01044666</v>
+        <v>0.01080215</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00930218</v>
+        <v>0.009684709999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000121837721900196</v>
+        <v>-0.000371978617189444</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.17802</v>
+        <v>-3.50437</v>
       </c>
       <c r="M20" t="n">
         <v>709254167224.5737</v>
@@ -1730,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261012T181808Z-dd3add</t>
+          <t>20261013T163233Z-262e96</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5.42</v>
+        <v>0.191667</v>
       </c>
       <c r="F21" t="n">
-        <v>7094008686</v>
+        <v>6721545402</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>1058196053</v>
+        <v>172857446</v>
       </c>
       <c r="I21" t="n">
-        <v>5.97</v>
+        <v>0.197761</v>
       </c>
       <c r="J21" t="n">
-        <v>5.38</v>
+        <v>0.185963</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.2246557427977889</v>
+        <v>-0.005204149748995412</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.92788</v>
+        <v>-2.69876</v>
       </c>
       <c r="M21" t="n">
-        <v>1308783290</v>
+        <v>35068874082.14661</v>
       </c>
       <c r="N21" t="n">
-        <v>1308783331</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-12T18:16:58.000Z</t>
+          <t>2026-10-13T16:30:40.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83484</v>
+        <v>82306</v>
       </c>
       <c r="F2" t="n">
-        <v>1677802941405</v>
+        <v>1654139833137</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>32366344427</v>
+        <v>29774016812</v>
       </c>
       <c r="I2" t="n">
-        <v>84074</v>
+        <v>84025</v>
       </c>
       <c r="J2" t="n">
-        <v>81018</v>
+        <v>82294</v>
       </c>
       <c r="K2" t="n">
-        <v>674.51</v>
+        <v>-1059.60936893156</v>
       </c>
       <c r="L2" t="n">
-        <v>0.78382</v>
+        <v>-1.38046</v>
       </c>
       <c r="M2" t="n">
-        <v>20097368</v>
+        <v>20098084</v>
       </c>
       <c r="N2" t="n">
-        <v>20097665</v>
+        <v>20098109</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2517.54</v>
+        <v>2448.67</v>
       </c>
       <c r="F3" t="n">
-        <v>307469153755</v>
+        <v>299066836487</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>15094857039</v>
+        <v>10531020152</v>
       </c>
       <c r="I3" t="n">
-        <v>2535.36</v>
+        <v>2524.82</v>
       </c>
       <c r="J3" t="n">
-        <v>2411.24</v>
+        <v>2451.72</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.22416947773218</v>
+        <v>-60.37448102451754</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.48582</v>
+        <v>-2.54499</v>
       </c>
       <c r="M3" t="n">
-        <v>122130709.7379206</v>
+        <v>122133648.4596395</v>
       </c>
       <c r="N3" t="n">
-        <v>122130709.7379206</v>
+        <v>122133648.4596395</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99939</v>
+        <v>0.999299</v>
       </c>
       <c r="F4" t="n">
-        <v>184087351209</v>
+        <v>184028545895</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>62852666179</v>
+        <v>52091854825</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999347</v>
+        <v>0.99946</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998987</v>
+        <v>0.999126</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0001512</v>
+        <v>5.807e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01148</v>
+        <v>0.00856</v>
       </c>
       <c r="M4" t="n">
-        <v>184199691342.6323</v>
+        <v>184157562926.2007</v>
       </c>
       <c r="N4" t="n">
-        <v>189666639768.5562</v>
+        <v>189624511354.4362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>745.0599999999999</v>
+        <v>735.15</v>
       </c>
       <c r="F5" t="n">
-        <v>99211410839</v>
+        <v>97891555244</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>808365228</v>
+        <v>571835156</v>
       </c>
       <c r="I5" t="n">
-        <v>747.49</v>
+        <v>746.08</v>
       </c>
       <c r="J5" t="n">
-        <v>722.58</v>
+        <v>734.72</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.153053036656161</v>
+        <v>-6.649235851569642</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.19066</v>
+        <v>-0.98571</v>
       </c>
       <c r="M5" t="n">
-        <v>133158622.31</v>
+        <v>133158570.17</v>
       </c>
       <c r="N5" t="n">
-        <v>133158614.4</v>
+        <v>133158565.91</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="F6" t="n">
-        <v>86786019857</v>
+        <v>85021750019</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2234922341</v>
+        <v>1821354240</v>
       </c>
       <c r="I6" t="n">
         <v>1.38</v>
       </c>
       <c r="J6" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002333580879375186</v>
+        <v>-0.02042930438381951</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2394</v>
+        <v>-1.62587</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999854</v>
+        <v>0.999721</v>
       </c>
       <c r="F7" t="n">
-        <v>72643651578</v>
+        <v>72873847315</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>19571506418</v>
+        <v>17323291537</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999885</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999664</v>
+        <v>0.9996699999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>9.873e-05</v>
+        <v>-0.000110289901801508</v>
       </c>
       <c r="L7" t="n">
-        <v>0.005</v>
+        <v>-0.009520000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>72654256775.06488</v>
+        <v>72893974496.97348</v>
       </c>
       <c r="N7" t="n">
-        <v>72615791006.75041</v>
+        <v>72881598790.2923</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>107.71</v>
+        <v>104.93</v>
       </c>
       <c r="F8" t="n">
-        <v>63459711653</v>
+        <v>61823125671</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>4137608387</v>
+        <v>2940845509</v>
       </c>
       <c r="I8" t="n">
-        <v>108.89</v>
+        <v>108.45</v>
       </c>
       <c r="J8" t="n">
-        <v>102.19</v>
+        <v>104.58</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.187708151020871</v>
+        <v>-2.162155521293073</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.13652</v>
+        <v>-2.21144</v>
       </c>
       <c r="M8" t="n">
-        <v>589162540.5223119</v>
+        <v>589218898.6780165</v>
       </c>
       <c r="N8" t="n">
-        <v>635721176.4235597</v>
+        <v>635782894.6438751</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.327306</v>
+        <v>0.333534</v>
       </c>
       <c r="F9" t="n">
-        <v>31092473638</v>
+        <v>31683046873</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>377841130</v>
+        <v>524149454</v>
       </c>
       <c r="I9" t="n">
-        <v>0.330781</v>
+        <v>0.333945</v>
       </c>
       <c r="J9" t="n">
         <v>0.326852</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003635475615367922</v>
+        <v>0.00552974</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.06884</v>
+        <v>1.61013</v>
       </c>
       <c r="M9" t="n">
-        <v>94995183371.01869</v>
+        <v>94996465825.80299</v>
       </c>
       <c r="N9" t="n">
-        <v>94995187293.75169</v>
+        <v>94996511585.30508</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,28 +1045,28 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.052</v>
+        <v>1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>24999203356</v>
+        <v>24466422912</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>13751499</v>
+        <v>67824287</v>
       </c>
       <c r="I10" t="n">
         <v>1.065</v>
       </c>
       <c r="J10" t="n">
-        <v>1.052</v>
+        <v>1.026</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.01197705163604001</v>
+        <v>-0.03529815479486564</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.12236</v>
+        <v>-3.31786</v>
       </c>
       <c r="M10" t="n">
         <v>23771507038.718</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1205.14</v>
+        <v>1203.54</v>
       </c>
       <c r="F11" t="n">
-        <v>20465566734</v>
+        <v>20444041785</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1049757217</v>
+        <v>928902883</v>
       </c>
       <c r="I11" t="n">
-        <v>1246.72</v>
+        <v>1282.89</v>
       </c>
       <c r="J11" t="n">
-        <v>1125.65</v>
+        <v>1180</v>
       </c>
       <c r="K11" t="n">
-        <v>-55.07522991170049</v>
+        <v>7.69</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.4828</v>
+        <v>0.31565</v>
       </c>
       <c r="M11" t="n">
-        <v>16981864.2280448</v>
+        <v>16984484.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16984120.4780448</v>
+        <v>16985748.6030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.42</v>
+        <v>80.39</v>
       </c>
       <c r="F12" t="n">
-        <v>18112496466</v>
+        <v>17876945286</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>977002599</v>
+        <v>662045444</v>
       </c>
       <c r="I12" t="n">
-        <v>83.83</v>
+        <v>82.69</v>
       </c>
       <c r="J12" t="n">
-        <v>79.52</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.878024591999647</v>
+        <v>-1.081363668733943</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.51302</v>
+        <v>-1.50303</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.084467</v>
+        <v>0.082381</v>
       </c>
       <c r="F13" t="n">
-        <v>13202849848</v>
+        <v>12878212493</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>770231015</v>
+        <v>550628552</v>
       </c>
       <c r="I13" t="n">
-        <v>0.085368</v>
+        <v>0.08551400000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.08021499999999999</v>
+        <v>0.082498</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000609963815638118</v>
+        <v>-0.001803182353205701</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.7618200000000001</v>
+        <v>-2.3633</v>
       </c>
       <c r="M13" t="n">
-        <v>156308336383.7052</v>
+        <v>156319646383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>172020613126.5791</v>
+        <v>156320876383.7053</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,144 +1279,144 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>550.08</v>
       </c>
       <c r="F14" t="n">
-        <v>10345349924</v>
+        <v>10352378780</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>98601636</v>
+        <v>117010853</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>558.88</v>
       </c>
       <c r="J14" t="n">
-        <v>0.999474</v>
+        <v>527.27</v>
       </c>
       <c r="K14" t="n">
-        <v>0.00021531</v>
+        <v>18.87</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01759</v>
+        <v>3.45075</v>
       </c>
       <c r="M14" t="n">
-        <v>10342606746.26388</v>
+        <v>18817469.83365588</v>
       </c>
       <c r="N14" t="n">
-        <v>10339720906.07536</v>
+        <v>18817492.63333731</v>
       </c>
       <c r="O14" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>529.4299999999999</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>9962280629</v>
+        <v>10337881532</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>91190599</v>
+        <v>209439277</v>
       </c>
       <c r="I15" t="n">
-        <v>544.02</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>520.71</v>
+        <v>0.999814</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.439951510246374</v>
+        <v>0.00023478</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.9897899999999999</v>
+        <v>0.00502</v>
       </c>
       <c r="M15" t="n">
-        <v>18817072.64103359</v>
+        <v>10335395888.64588</v>
       </c>
       <c r="N15" t="n">
-        <v>18817108.63889607</v>
+        <v>10337085956.85417</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.92</v>
+        <v>12.52</v>
       </c>
       <c r="F16" t="n">
-        <v>9906640961</v>
+        <v>9599141993</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>403759662</v>
+        <v>268315817</v>
       </c>
       <c r="I16" t="n">
-        <v>13.17</v>
+        <v>13.08</v>
       </c>
       <c r="J16" t="n">
-        <v>12.29</v>
+        <v>12.55</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.1180999401439902</v>
+        <v>-0.4566976607014439</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.98659</v>
+        <v>-3.69841</v>
       </c>
       <c r="M16" t="n">
         <v>766849970.424884</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>82.04000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>9744807842</v>
+        <v>9587632993</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>133066970</v>
+        <v>99519468</v>
       </c>
       <c r="I17" t="n">
-        <v>82.56999999999999</v>
+        <v>82.5</v>
       </c>
       <c r="J17" t="n">
-        <v>79.40000000000001</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.439872</v>
+        <v>-1.188578390885382</v>
       </c>
       <c r="L17" t="n">
-        <v>0.51727</v>
+        <v>-1.69864</v>
       </c>
       <c r="M17" t="n">
         <v>118786640</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.235639</v>
+        <v>0.228718</v>
       </c>
       <c r="F18" t="n">
-        <v>8849088292</v>
+        <v>8590461602</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>500392272</v>
+        <v>344859482</v>
       </c>
       <c r="I18" t="n">
-        <v>0.243667</v>
+        <v>0.238831</v>
       </c>
       <c r="J18" t="n">
-        <v>0.224713</v>
+        <v>0.228086</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008187459966972538</v>
+        <v>-0.006988300013757942</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.45018</v>
+        <v>-3.15822</v>
       </c>
       <c r="M18" t="n">
         <v>37553537941.9088</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>8.9</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8182963832</v>
+        <v>8316004823</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>101405</v>
+        <v>323750</v>
       </c>
       <c r="I19" t="n">
-        <v>8.92</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J19" t="n">
         <v>8.869999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>0.01134385</v>
+        <v>0.139883</v>
       </c>
       <c r="L19" t="n">
-        <v>0.12888</v>
+        <v>1.57045</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.01000173</v>
+        <v>0.009483790000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>7093772088</v>
+        <v>6729689795</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>19120331</v>
+        <v>12114729</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01080215</v>
+        <v>0.01007919</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009684709999999999</v>
+        <v>0.009493069999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000371978617189444</v>
+        <v>-0.000532676767422035</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.50437</v>
+        <v>-5.31298</v>
       </c>
       <c r="M20" t="n">
-        <v>709254167224.5737</v>
+        <v>709252822919.6252</v>
       </c>
       <c r="N20" t="n">
-        <v>1142407411082.119</v>
+        <v>1142406066711.787</v>
       </c>
       <c r="O20" t="n">
         <v>0.01946402</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261013T163233Z-262e96</t>
+          <t>20261014T140702Z-2bd77c</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.191667</v>
+        <v>4.97</v>
       </c>
       <c r="F21" t="n">
-        <v>6721545402</v>
+        <v>6502590114</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>172857446</v>
+        <v>1002640137</v>
       </c>
       <c r="I21" t="n">
-        <v>0.197761</v>
+        <v>5.18</v>
       </c>
       <c r="J21" t="n">
-        <v>0.185963</v>
+        <v>4.9</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005204149748995412</v>
+        <v>-0.0818366411408542</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.69876</v>
+        <v>-2.07283</v>
       </c>
       <c r="M21" t="n">
-        <v>35068874082.14661</v>
+        <v>1308921703</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.69947</v>
+        <v>1308921781</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-13T16:30:40.000Z</t>
+          <t>2026-10-14T14:04:58.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>82306</v>
+        <v>80544</v>
       </c>
       <c r="F2" t="n">
-        <v>1654139833137</v>
+        <v>1618830291049</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29774016812</v>
+        <v>38670490738</v>
       </c>
       <c r="I2" t="n">
-        <v>84025</v>
+        <v>82416</v>
       </c>
       <c r="J2" t="n">
-        <v>82294</v>
+        <v>80444</v>
       </c>
       <c r="K2" t="n">
-        <v>-1059.60936893156</v>
+        <v>-2355.680979070108</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.38046</v>
+        <v>-2.84159</v>
       </c>
       <c r="M2" t="n">
-        <v>20098084</v>
+        <v>20098593</v>
       </c>
       <c r="N2" t="n">
-        <v>20098109</v>
+        <v>20098618</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2448.67</v>
+        <v>2349.54</v>
       </c>
       <c r="F3" t="n">
-        <v>299066836487</v>
+        <v>286964495478</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>10531020152</v>
+        <v>18812497359</v>
       </c>
       <c r="I3" t="n">
-        <v>2524.82</v>
+        <v>2454.61</v>
       </c>
       <c r="J3" t="n">
-        <v>2451.72</v>
+        <v>2332.43</v>
       </c>
       <c r="K3" t="n">
-        <v>-60.37448102451754</v>
+        <v>-130.587116978787</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.54499</v>
+        <v>-5.26534</v>
       </c>
       <c r="M3" t="n">
-        <v>122133648.4596395</v>
+        <v>122136580.3876922</v>
       </c>
       <c r="N3" t="n">
-        <v>122133648.4596395</v>
+        <v>122136580.3876922</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999299</v>
+        <v>0.9990520000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>184028545895</v>
+        <v>183871592394</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52091854825</v>
+        <v>70305718142</v>
       </c>
       <c r="I4" t="n">
-        <v>0.99946</v>
+        <v>0.999377</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999126</v>
+        <v>0.998949</v>
       </c>
       <c r="K4" t="n">
-        <v>5.807e-05</v>
+        <v>-0.0002369860106336</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00856</v>
+        <v>-0.02372</v>
       </c>
       <c r="M4" t="n">
-        <v>184157562926.2007</v>
+        <v>184045984068.8031</v>
       </c>
       <c r="N4" t="n">
-        <v>189624511354.4362</v>
+        <v>189512932501.9362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>735.15</v>
+        <v>717.87</v>
       </c>
       <c r="F5" t="n">
-        <v>97891555244</v>
+        <v>95590806473</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>571835156</v>
+        <v>980668229</v>
       </c>
       <c r="I5" t="n">
-        <v>746.08</v>
+        <v>736.39</v>
       </c>
       <c r="J5" t="n">
-        <v>734.72</v>
+        <v>712.11</v>
       </c>
       <c r="K5" t="n">
-        <v>-6.649235851569642</v>
+        <v>-22.40445705973787</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.98571</v>
+        <v>-3.0265</v>
       </c>
       <c r="M5" t="n">
-        <v>133158570.17</v>
+        <v>133158504.59</v>
       </c>
       <c r="N5" t="n">
-        <v>133158565.91</v>
+        <v>133158502.14</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>85021750019</v>
+        <v>82088587199</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1821354240</v>
+        <v>2326601884</v>
       </c>
       <c r="I6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="J6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.02042930438381951</v>
+        <v>-0.06316083653671822</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.62587</v>
+        <v>-4.63233</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999721</v>
+        <v>0.999578</v>
       </c>
       <c r="F7" t="n">
-        <v>72873847315</v>
+        <v>72633402185</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17323291537</v>
+        <v>21436878956</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999977</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9996699999999999</v>
+        <v>0.9990289999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000110289901801508</v>
+        <v>-0.000196223713799126</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.009520000000000001</v>
+        <v>-0.01963</v>
       </c>
       <c r="M7" t="n">
-        <v>72893974496.97348</v>
+        <v>72664063018.69038</v>
       </c>
       <c r="N7" t="n">
-        <v>72881598790.2923</v>
+        <v>72674112322.84962</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.93</v>
+        <v>101.9</v>
       </c>
       <c r="F8" t="n">
-        <v>61823125671</v>
+        <v>60044833365</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2940845509</v>
+        <v>3922595400</v>
       </c>
       <c r="I8" t="n">
-        <v>108.45</v>
+        <v>105.22</v>
       </c>
       <c r="J8" t="n">
-        <v>104.58</v>
+        <v>101.04</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.162155521293073</v>
+        <v>-4.166272074072509</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.21144</v>
+        <v>-3.92809</v>
       </c>
       <c r="M8" t="n">
-        <v>589218898.6780165</v>
+        <v>589268582.3539231</v>
       </c>
       <c r="N8" t="n">
-        <v>635782894.6438751</v>
+        <v>635844456.7292906</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.333534</v>
+        <v>0.329655</v>
       </c>
       <c r="F9" t="n">
-        <v>31683046873</v>
+        <v>31316440144</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>524149454</v>
+        <v>445972505</v>
       </c>
       <c r="I9" t="n">
-        <v>0.333945</v>
+        <v>0.334445</v>
       </c>
       <c r="J9" t="n">
-        <v>0.326852</v>
+        <v>0.329472</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00552974</v>
+        <v>-0.003896412099507252</v>
       </c>
       <c r="L9" t="n">
-        <v>1.61013</v>
+        <v>-1.16816</v>
       </c>
       <c r="M9" t="n">
-        <v>94996465825.80299</v>
+        <v>94997504981.59979</v>
       </c>
       <c r="N9" t="n">
-        <v>94996511585.30508</v>
+        <v>94997539923.79399</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.029</v>
+        <v>1.036</v>
       </c>
       <c r="F10" t="n">
-        <v>24466422912</v>
+        <v>24706588721</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>67824287</v>
+        <v>38032421</v>
       </c>
       <c r="I10" t="n">
-        <v>1.065</v>
+        <v>1.048</v>
       </c>
       <c r="J10" t="n">
-        <v>1.026</v>
+        <v>1.027</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.03529815479486564</v>
+        <v>0.00760568</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.31786</v>
+        <v>0.73939</v>
       </c>
       <c r="M10" t="n">
-        <v>23771507038.718</v>
+        <v>23842412585.148</v>
       </c>
       <c r="N10" t="n">
-        <v>23771507038.718</v>
+        <v>23908770801.868</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1203.54</v>
+        <v>1102.11</v>
       </c>
       <c r="F11" t="n">
-        <v>20444041785</v>
+        <v>18721526819</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>928902883</v>
+        <v>1130415936</v>
       </c>
       <c r="I11" t="n">
-        <v>1282.89</v>
+        <v>1208.48</v>
       </c>
       <c r="J11" t="n">
-        <v>1180</v>
+        <v>1077.27</v>
       </c>
       <c r="K11" t="n">
-        <v>7.69</v>
+        <v>-123.5403503501461</v>
       </c>
       <c r="L11" t="n">
-        <v>0.31565</v>
+        <v>-10.07956</v>
       </c>
       <c r="M11" t="n">
-        <v>16984484.5405448</v>
+        <v>16986953.2905448</v>
       </c>
       <c r="N11" t="n">
-        <v>16985748.6030448</v>
+        <v>16987540.7905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.39</v>
+        <v>78.55</v>
       </c>
       <c r="F12" t="n">
-        <v>17876945286</v>
+        <v>17472872603</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>662045444</v>
+        <v>869781986</v>
       </c>
       <c r="I12" t="n">
-        <v>82.69</v>
+        <v>81.95999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>80.06999999999999</v>
+        <v>78.15000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.081363668733943</v>
+        <v>-2.717313023391455</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.50303</v>
+        <v>-3.34372</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.082381</v>
+        <v>0.079287</v>
       </c>
       <c r="F13" t="n">
-        <v>12878212493</v>
+        <v>12395330553</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>550628552</v>
+        <v>1115377012</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08551400000000001</v>
+        <v>0.083111</v>
       </c>
       <c r="J13" t="n">
-        <v>0.082498</v>
+        <v>0.078426</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.001803182353205701</v>
+        <v>-0.004236572487430715</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.3633</v>
+        <v>-5.0723</v>
       </c>
       <c r="M13" t="n">
-        <v>156319646383.7052</v>
+        <v>156334786383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>156320876383.7053</v>
+        <v>172046483126.5791</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,469 +1279,469 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>550.08</v>
+        <v>0.99986</v>
       </c>
       <c r="F14" t="n">
-        <v>10352378780</v>
+        <v>10228235720</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>117010853</v>
+        <v>158733525</v>
       </c>
       <c r="I14" t="n">
-        <v>558.88</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
-        <v>527.27</v>
+        <v>0.9995270000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>18.87</v>
+        <v>-0.000369778481628003</v>
       </c>
       <c r="L14" t="n">
-        <v>3.45075</v>
+        <v>-0.03697</v>
       </c>
       <c r="M14" t="n">
-        <v>18817469.83365588</v>
+        <v>10229668775.45049</v>
       </c>
       <c r="N14" t="n">
-        <v>18817492.63333731</v>
+        <v>10221451773.2458</v>
       </c>
       <c r="O14" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>534.14</v>
       </c>
       <c r="F15" t="n">
-        <v>10337881532</v>
+        <v>10051410061</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>209439277</v>
+        <v>106408316</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>554.46</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999814</v>
+        <v>532.5700000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00023478</v>
+        <v>-24.38393745436792</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00502</v>
+        <v>-4.36578</v>
       </c>
       <c r="M15" t="n">
-        <v>10335395888.64588</v>
+        <v>18817906.0270791</v>
       </c>
       <c r="N15" t="n">
-        <v>10337085956.85417</v>
+        <v>18817922.82703639</v>
       </c>
       <c r="O15" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.52</v>
+        <v>78.8</v>
       </c>
       <c r="F16" t="n">
-        <v>9599141993</v>
+        <v>9360782906</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>268315817</v>
+        <v>173284780</v>
       </c>
       <c r="I16" t="n">
-        <v>13.08</v>
+        <v>80.81</v>
       </c>
       <c r="J16" t="n">
-        <v>12.55</v>
+        <v>78.54000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4566976607014439</v>
+        <v>-2.546606772425861</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.69841</v>
+        <v>-3.13043</v>
       </c>
       <c r="M16" t="n">
-        <v>766849970.424884</v>
+        <v>118786640</v>
       </c>
       <c r="N16" t="n">
-        <v>1000000000</v>
+        <v>293356139</v>
       </c>
       <c r="O16" t="n">
-        <v>52.7</v>
+        <v>87.91</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.70999999999999</v>
+        <v>11.98</v>
       </c>
       <c r="F17" t="n">
-        <v>9587632993</v>
+        <v>9183579262</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>99519468</v>
+        <v>387810109</v>
       </c>
       <c r="I17" t="n">
-        <v>82.5</v>
+        <v>12.61</v>
       </c>
       <c r="J17" t="n">
-        <v>80.70999999999999</v>
+        <v>11.92</v>
       </c>
       <c r="K17" t="n">
-        <v>-1.188578390885382</v>
+        <v>-0.7906116360447299</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.69864</v>
+        <v>-6.19294</v>
       </c>
       <c r="M17" t="n">
-        <v>118786640</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>293356139</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>87.91</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.228718</v>
+        <v>9.01</v>
       </c>
       <c r="F18" t="n">
-        <v>8590461602</v>
+        <v>8288160524</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>344859482</v>
+        <v>56979</v>
       </c>
       <c r="I18" t="n">
-        <v>0.238831</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.228086</v>
+        <v>9.01</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.006988300013757942</v>
+        <v>-0.03039784537098811</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.15822</v>
+        <v>-0.33623</v>
       </c>
       <c r="M18" t="n">
-        <v>37553537941.9088</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.039999999999999</v>
+        <v>0.220621</v>
       </c>
       <c r="F19" t="n">
-        <v>8316004823</v>
+        <v>8285097593</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>323750</v>
+        <v>458993751</v>
       </c>
       <c r="I19" t="n">
-        <v>9.039999999999999</v>
+        <v>0.231059</v>
       </c>
       <c r="J19" t="n">
-        <v>8.869999999999999</v>
+        <v>0.217472</v>
       </c>
       <c r="K19" t="n">
-        <v>0.139883</v>
+        <v>-0.01105172974186014</v>
       </c>
       <c r="L19" t="n">
-        <v>1.57045</v>
+        <v>-4.77041</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>37553537941.9088</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.009483790000000001</v>
+        <v>0.179069</v>
       </c>
       <c r="F20" t="n">
-        <v>6729689795</v>
+        <v>6295866990</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>12114729</v>
+        <v>175556459</v>
       </c>
       <c r="I20" t="n">
-        <v>0.01007919</v>
+        <v>0.278245</v>
       </c>
       <c r="J20" t="n">
-        <v>0.009493069999999999</v>
+        <v>0.177112</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.000532676767422035</v>
+        <v>-0.007988343704260492</v>
       </c>
       <c r="L20" t="n">
-        <v>-5.31298</v>
+        <v>-4.27053</v>
       </c>
       <c r="M20" t="n">
-        <v>709252822919.6252</v>
+        <v>35158914029.46671</v>
       </c>
       <c r="N20" t="n">
-        <v>1142406066711.787</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261014T140702Z-2bd77c</t>
+          <t>20261015T134536Z-07397d</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.97</v>
+        <v>4.61</v>
       </c>
       <c r="F21" t="n">
-        <v>6502590114</v>
+        <v>6040583904</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>1002640137</v>
+        <v>1014777715</v>
       </c>
       <c r="I21" t="n">
-        <v>5.18</v>
+        <v>4.99</v>
       </c>
       <c r="J21" t="n">
-        <v>4.9</v>
+        <v>4.54</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0818366411408542</v>
+        <v>-0.4073483179603006</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.07283</v>
+        <v>-8.11145</v>
       </c>
       <c r="M21" t="n">
-        <v>1308921703</v>
+        <v>1309031523</v>
       </c>
       <c r="N21" t="n">
-        <v>1308921781</v>
+        <v>1309031558</v>
       </c>
       <c r="O21" t="n">
         <v>20.44</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-14T14:04:58.000Z</t>
+          <t>2026-10-15T13:43:45.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80544</v>
+        <v>81829</v>
       </c>
       <c r="F2" t="n">
-        <v>1618830291049</v>
+        <v>1644518350708</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>38670490738</v>
+        <v>30753628678</v>
       </c>
       <c r="I2" t="n">
-        <v>82416</v>
+        <v>82816</v>
       </c>
       <c r="J2" t="n">
-        <v>80444</v>
+        <v>80074</v>
       </c>
       <c r="K2" t="n">
-        <v>-2355.680979070108</v>
+        <v>1534.29</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.84159</v>
+        <v>1.91081</v>
       </c>
       <c r="M2" t="n">
-        <v>20098593</v>
+        <v>20098843</v>
       </c>
       <c r="N2" t="n">
-        <v>20098618</v>
+        <v>20098843</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2349.54</v>
+        <v>2457.63</v>
       </c>
       <c r="F3" t="n">
-        <v>286964495478</v>
+        <v>300079533940</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>18812497359</v>
+        <v>14203142817</v>
       </c>
       <c r="I3" t="n">
-        <v>2454.61</v>
+        <v>2488.84</v>
       </c>
       <c r="J3" t="n">
-        <v>2332.43</v>
+        <v>2337.17</v>
       </c>
       <c r="K3" t="n">
-        <v>-130.587116978787</v>
+        <v>113.59</v>
       </c>
       <c r="L3" t="n">
-        <v>-5.26534</v>
+        <v>4.84583</v>
       </c>
       <c r="M3" t="n">
-        <v>122136580.3876922</v>
+        <v>122139509.3481655</v>
       </c>
       <c r="N3" t="n">
-        <v>122136580.3876922</v>
+        <v>122139509.3481655</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9990520000000001</v>
+        <v>0.999254</v>
       </c>
       <c r="F4" t="n">
-        <v>183871592394</v>
+        <v>183526384293</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>70305718142</v>
+        <v>57098113621</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999377</v>
+        <v>0.999297</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998949</v>
+        <v>0.998893</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.0002369860106336</v>
+        <v>0.00016956</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02372</v>
+        <v>0.01697</v>
       </c>
       <c r="M4" t="n">
-        <v>184045984068.8031</v>
+        <v>183663961196.8238</v>
       </c>
       <c r="N4" t="n">
-        <v>189512932501.9362</v>
+        <v>189130909645.4862</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>717.87</v>
+        <v>726.55</v>
       </c>
       <c r="F5" t="n">
-        <v>95590806473</v>
+        <v>96731153274</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>980668229</v>
+        <v>808100553</v>
       </c>
       <c r="I5" t="n">
-        <v>736.39</v>
+        <v>735.1</v>
       </c>
       <c r="J5" t="n">
-        <v>712.11</v>
+        <v>713.49</v>
       </c>
       <c r="K5" t="n">
-        <v>-22.40445705973787</v>
+        <v>9.720000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>-3.0265</v>
+        <v>1.35627</v>
       </c>
       <c r="M5" t="n">
-        <v>133158504.59</v>
+        <v>133158429.64</v>
       </c>
       <c r="N5" t="n">
-        <v>133158502.14</v>
+        <v>133158427.69</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,16 +785,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="F6" t="n">
-        <v>82088587199</v>
+        <v>84098131792</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>2326601884</v>
+        <v>1516404491</v>
       </c>
       <c r="I6" t="n">
         <v>1.35</v>
@@ -803,10 +803,10 @@
         <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.06316083653671822</v>
+        <v>0.03768771</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.63233</v>
+        <v>2.91068</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999578</v>
+        <v>0.999838</v>
       </c>
       <c r="F7" t="n">
-        <v>72633402185</v>
+        <v>72531055678</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>21436878956</v>
+        <v>17257821297</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999977</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9990289999999999</v>
+        <v>0.998157</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000196223713799126</v>
+        <v>0.00022946</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01963</v>
+        <v>0.02296</v>
       </c>
       <c r="M7" t="n">
-        <v>72664063018.69038</v>
+        <v>72542913150.43356</v>
       </c>
       <c r="N7" t="n">
-        <v>72674112322.84962</v>
+        <v>72556212479.25603</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.9</v>
+        <v>105.3</v>
       </c>
       <c r="F8" t="n">
-        <v>60044833365</v>
+        <v>62042020101</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3922595400</v>
+        <v>3115518446</v>
       </c>
       <c r="I8" t="n">
-        <v>105.22</v>
+        <v>107.18</v>
       </c>
       <c r="J8" t="n">
-        <v>101.04</v>
+        <v>101.31</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.166272074072509</v>
+        <v>3.75</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.92809</v>
+        <v>3.69712</v>
       </c>
       <c r="M8" t="n">
-        <v>589268582.3539231</v>
+        <v>589324236.4947505</v>
       </c>
       <c r="N8" t="n">
-        <v>635844456.7292906</v>
+        <v>635906005.5298247</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.329655</v>
+        <v>0.335147</v>
       </c>
       <c r="F9" t="n">
-        <v>31316440144</v>
+        <v>31837373435</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>445972505</v>
+        <v>379099734</v>
       </c>
       <c r="I9" t="n">
-        <v>0.334445</v>
+        <v>0.335918</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329472</v>
+        <v>0.329423</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003896412099507252</v>
+        <v>0.00536942</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.16816</v>
+        <v>1.62819</v>
       </c>
       <c r="M9" t="n">
-        <v>94997504981.59979</v>
+        <v>94998502604.69609</v>
       </c>
       <c r="N9" t="n">
-        <v>94997539923.79399</v>
+        <v>94998536194.20079</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,31 +1045,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.036</v>
+        <v>1.032</v>
       </c>
       <c r="F10" t="n">
-        <v>24706588721</v>
+        <v>24668780814</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>38032421</v>
+        <v>296352257</v>
       </c>
       <c r="I10" t="n">
-        <v>1.048</v>
+        <v>1.047</v>
       </c>
       <c r="J10" t="n">
-        <v>1.027</v>
+        <v>1.018</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00760568</v>
+        <v>-0.004493841927478259</v>
       </c>
       <c r="L10" t="n">
-        <v>0.73939</v>
+        <v>-0.43365</v>
       </c>
       <c r="M10" t="n">
-        <v>23842412585.148</v>
+        <v>23908770801.868</v>
       </c>
       <c r="N10" t="n">
         <v>23908770801.868</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1102.11</v>
+        <v>1219.82</v>
       </c>
       <c r="F11" t="n">
-        <v>18721526819</v>
+        <v>20706838541</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1130415936</v>
+        <v>1478344830</v>
       </c>
       <c r="I11" t="n">
-        <v>1208.48</v>
+        <v>1251.93</v>
       </c>
       <c r="J11" t="n">
-        <v>1077.27</v>
+        <v>1088.24</v>
       </c>
       <c r="K11" t="n">
-        <v>-123.5403503501461</v>
+        <v>124.57</v>
       </c>
       <c r="L11" t="n">
-        <v>-10.07956</v>
+        <v>11.37416</v>
       </c>
       <c r="M11" t="n">
-        <v>16986953.2905448</v>
+        <v>16988150.1655448</v>
       </c>
       <c r="N11" t="n">
-        <v>16987540.7905448</v>
+        <v>16989311.1030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.55</v>
+        <v>81.16</v>
       </c>
       <c r="F12" t="n">
-        <v>17472872603</v>
+        <v>18051336236</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>869781986</v>
+        <v>767236220</v>
       </c>
       <c r="I12" t="n">
-        <v>81.95999999999999</v>
+        <v>82.51000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>78.15000000000001</v>
+        <v>77.68000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.717313023391455</v>
+        <v>3.1</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.34372</v>
+        <v>3.97762</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.079287</v>
+        <v>0.081432</v>
       </c>
       <c r="F13" t="n">
-        <v>12395330553</v>
+        <v>12727417384</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1115377012</v>
+        <v>1040485472</v>
       </c>
       <c r="I13" t="n">
-        <v>0.083111</v>
+        <v>0.082757</v>
       </c>
       <c r="J13" t="n">
-        <v>0.078426</v>
+        <v>0.077935</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.004236572487430715</v>
+        <v>0.0022734</v>
       </c>
       <c r="L13" t="n">
-        <v>-5.0723</v>
+        <v>2.87196</v>
       </c>
       <c r="M13" t="n">
-        <v>156334786383.7052</v>
+        <v>156343966383.7052</v>
       </c>
       <c r="N13" t="n">
-        <v>172046483126.5791</v>
+        <v>156347892864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,527 +1279,527 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>monero</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>usds</t>
+          <t>xmr</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>USDS</t>
+          <t>Monero</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.99986</v>
+        <v>555.01</v>
       </c>
       <c r="F14" t="n">
-        <v>10228235720</v>
+        <v>10442877924</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>158733525</v>
+        <v>103362764</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>569.8200000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9995270000000001</v>
+        <v>527.91</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.000369778481628003</v>
+        <v>21.44</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.03697</v>
+        <v>4.01878</v>
       </c>
       <c r="M14" t="n">
-        <v>10229668775.45049</v>
+        <v>18818330.21818927</v>
       </c>
       <c r="N14" t="n">
-        <v>10221451773.2458</v>
+        <v>18818342.81815135</v>
       </c>
       <c r="O14" t="n">
-        <v>1.057</v>
+        <v>797.73</v>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>2024-10-28T21:40:51.000Z</t>
+          <t>2026-01-14T11:34:07.000Z</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>monero</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>xmr</t>
+          <t>usds</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Monero</t>
+          <t>USDS</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>534.14</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10051410061</v>
+        <v>10234140103</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>106408316</v>
+        <v>150420161</v>
       </c>
       <c r="I15" t="n">
-        <v>554.46</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>532.5700000000001</v>
+        <v>0.99962</v>
       </c>
       <c r="K15" t="n">
-        <v>-24.38393745436792</v>
+        <v>6.546e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-4.36578</v>
+        <v>0.00655</v>
       </c>
       <c r="M15" t="n">
-        <v>18817906.0270791</v>
+        <v>10235146527.19681</v>
       </c>
       <c r="N15" t="n">
-        <v>18817922.82703639</v>
+        <v>10235846819.45149</v>
       </c>
       <c r="O15" t="n">
-        <v>797.73</v>
+        <v>1.057</v>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>2026-01-14T11:34:07.000Z</t>
+          <t>2024-10-28T21:40:51.000Z</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>78.8</v>
+        <v>12.58</v>
       </c>
       <c r="F16" t="n">
-        <v>9360782906</v>
+        <v>9642886168</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>173284780</v>
+        <v>321698833</v>
       </c>
       <c r="I16" t="n">
-        <v>80.81</v>
+        <v>12.76</v>
       </c>
       <c r="J16" t="n">
-        <v>78.54000000000001</v>
+        <v>11.88</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.546606772425861</v>
+        <v>0.6705989999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.13043</v>
+        <v>5.63208</v>
       </c>
       <c r="M16" t="n">
-        <v>118786640</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>293356139</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>87.91</v>
+        <v>52.7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.98</v>
+        <v>80.52</v>
       </c>
       <c r="F17" t="n">
-        <v>9183579262</v>
+        <v>9562869831</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>387810109</v>
+        <v>123574619</v>
       </c>
       <c r="I17" t="n">
-        <v>12.61</v>
+        <v>81.48</v>
       </c>
       <c r="J17" t="n">
-        <v>11.92</v>
+        <v>78.34</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7906116360447299</v>
+        <v>1.96</v>
       </c>
       <c r="L17" t="n">
-        <v>-6.19294</v>
+        <v>2.50047</v>
       </c>
       <c r="M17" t="n">
-        <v>766849970.424884</v>
+        <v>118786640</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>293356139</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>87.91</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.01</v>
+        <v>0.228749</v>
       </c>
       <c r="F18" t="n">
-        <v>8288160524</v>
+        <v>8590157371</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>56979</v>
+        <v>327031124</v>
       </c>
       <c r="I18" t="n">
-        <v>9.039999999999999</v>
+        <v>0.233126</v>
       </c>
       <c r="J18" t="n">
-        <v>9.01</v>
+        <v>0.218627</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.03039784537098811</v>
+        <v>0.00908843</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.33623</v>
+        <v>4.13748</v>
       </c>
       <c r="M18" t="n">
-        <v>919857851.9</v>
+        <v>37553537941.9088</v>
       </c>
       <c r="N18" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.220621</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>8285097593</v>
+        <v>8318634333</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>458993751</v>
+        <v>148971</v>
       </c>
       <c r="I19" t="n">
-        <v>0.231059</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.217472</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01105172974186014</v>
+        <v>0.03347744</v>
       </c>
       <c r="L19" t="n">
-        <v>-4.77041</v>
+        <v>0.37156</v>
       </c>
       <c r="M19" t="n">
-        <v>37553537941.9088</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.179069</v>
+        <v>5.25</v>
       </c>
       <c r="F20" t="n">
-        <v>6295866990</v>
+        <v>6868939868</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>175556459</v>
+        <v>1346539922</v>
       </c>
       <c r="I20" t="n">
-        <v>0.278245</v>
+        <v>5.43</v>
       </c>
       <c r="J20" t="n">
-        <v>0.177112</v>
+        <v>4.57</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.007988343704260492</v>
+        <v>0.625414</v>
       </c>
       <c r="L20" t="n">
-        <v>-4.27053</v>
+        <v>13.52871</v>
       </c>
       <c r="M20" t="n">
-        <v>35158914029.46671</v>
+        <v>1309110317</v>
       </c>
       <c r="N20" t="n">
-        <v>50001786839.69947</v>
+        <v>1309110350</v>
       </c>
       <c r="O20" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261015T134536Z-07397d</t>
+          <t>20261016T133536Z-dad102</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.61</v>
+        <v>0.009155470000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>6040583904</v>
+        <v>6496562156</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>1014777715</v>
+        <v>14600288</v>
       </c>
       <c r="I21" t="n">
-        <v>4.99</v>
+        <v>0.009755740000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>4.54</v>
+        <v>0.007951949999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4073483179603006</v>
+        <v>0.0011497</v>
       </c>
       <c r="L21" t="n">
-        <v>-8.11145</v>
+        <v>14.3609</v>
       </c>
       <c r="M21" t="n">
-        <v>1309031523</v>
+        <v>709252819526.8486</v>
       </c>
       <c r="N21" t="n">
-        <v>1309031558</v>
+        <v>1142406063382.48</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>0.01946402</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-15T13:43:45.000Z</t>
+          <t>2026-10-16T13:33:49.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81829</v>
+        <v>81449</v>
       </c>
       <c r="F2" t="n">
-        <v>1644518350708</v>
+        <v>1637036303957</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>30753628678</v>
+        <v>22285614325</v>
       </c>
       <c r="I2" t="n">
-        <v>82816</v>
+        <v>82385</v>
       </c>
       <c r="J2" t="n">
-        <v>80074</v>
+        <v>80761</v>
       </c>
       <c r="K2" t="n">
-        <v>1534.29</v>
+        <v>-793.1984415269108</v>
       </c>
       <c r="L2" t="n">
-        <v>1.91081</v>
+        <v>-0.96446</v>
       </c>
       <c r="M2" t="n">
         <v>20098843</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2457.63</v>
+        <v>2427.76</v>
       </c>
       <c r="F3" t="n">
-        <v>300079533940</v>
+        <v>296532252463</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>14203142817</v>
+        <v>8860960660</v>
       </c>
       <c r="I3" t="n">
-        <v>2488.84</v>
+        <v>2477.01</v>
       </c>
       <c r="J3" t="n">
-        <v>2337.17</v>
+        <v>2392.9</v>
       </c>
       <c r="K3" t="n">
-        <v>113.59</v>
+        <v>-43.75325902150735</v>
       </c>
       <c r="L3" t="n">
-        <v>4.84583</v>
+        <v>-1.7703</v>
       </c>
       <c r="M3" t="n">
-        <v>122139509.3481655</v>
+        <v>122142460.7593166</v>
       </c>
       <c r="N3" t="n">
-        <v>122139509.3481655</v>
+        <v>122142460.7593166</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999254</v>
+        <v>0.9988669999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>183526384293</v>
+        <v>183456895114</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>57098113621</v>
+        <v>41563710771</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999297</v>
+        <v>0.999401</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998893</v>
+        <v>0.9988320000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00016956</v>
+        <v>-0.000339479352379102</v>
       </c>
       <c r="L4" t="n">
-        <v>0.01697</v>
+        <v>-0.03397</v>
       </c>
       <c r="M4" t="n">
-        <v>183663961196.8238</v>
+        <v>183665036252.9821</v>
       </c>
       <c r="N4" t="n">
-        <v>189130909645.4862</v>
+        <v>189131984703.7462</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>726.55</v>
+        <v>719.37</v>
       </c>
       <c r="F5" t="n">
-        <v>96731153274</v>
+        <v>95790328662</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>808100553</v>
+        <v>550447004</v>
       </c>
       <c r="I5" t="n">
-        <v>735.1</v>
+        <v>730.23</v>
       </c>
       <c r="J5" t="n">
-        <v>713.49</v>
+        <v>718.12</v>
       </c>
       <c r="K5" t="n">
-        <v>9.720000000000001</v>
+        <v>-10.32157869100968</v>
       </c>
       <c r="L5" t="n">
-        <v>1.35627</v>
+        <v>-1.41451</v>
       </c>
       <c r="M5" t="n">
-        <v>133158429.64</v>
+        <v>133158380.58</v>
       </c>
       <c r="N5" t="n">
-        <v>133158427.69</v>
+        <v>133158373.97</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>84098131792</v>
+        <v>82042442751</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1516404491</v>
+        <v>1101326585</v>
       </c>
       <c r="I6" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="J6" t="n">
         <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03768771</v>
+        <v>-0.04065648424111967</v>
       </c>
       <c r="L6" t="n">
-        <v>2.91068</v>
+        <v>-3.03352</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999838</v>
+        <v>0.99957</v>
       </c>
       <c r="F7" t="n">
-        <v>72531055678</v>
+        <v>72550189435</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17257821297</v>
+        <v>13466994831</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.998157</v>
+        <v>0.9995230000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00022946</v>
+        <v>-0.000273425420727391</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02296</v>
+        <v>-0.02735</v>
       </c>
       <c r="M7" t="n">
-        <v>72542913150.43356</v>
+        <v>72581370791.43715</v>
       </c>
       <c r="N7" t="n">
-        <v>72556212479.25603</v>
+        <v>72581370791.43715</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>105.3</v>
+        <v>104.25</v>
       </c>
       <c r="F8" t="n">
-        <v>62042020101</v>
+        <v>61445173307</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3115518446</v>
+        <v>2304642554</v>
       </c>
       <c r="I8" t="n">
-        <v>107.18</v>
+        <v>106.46</v>
       </c>
       <c r="J8" t="n">
-        <v>101.31</v>
+        <v>102.51</v>
       </c>
       <c r="K8" t="n">
-        <v>3.75</v>
+        <v>-2.093693293325174</v>
       </c>
       <c r="L8" t="n">
-        <v>3.69712</v>
+        <v>-1.96874</v>
       </c>
       <c r="M8" t="n">
-        <v>589324236.4947505</v>
+        <v>589385048.0487075</v>
       </c>
       <c r="N8" t="n">
-        <v>635906005.5298247</v>
+        <v>635967584.9728914</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.335147</v>
+        <v>0.336684</v>
       </c>
       <c r="F9" t="n">
-        <v>31837373435</v>
+        <v>31984906743</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>379099734</v>
+        <v>302031533</v>
       </c>
       <c r="I9" t="n">
-        <v>0.335918</v>
+        <v>0.336655</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329423</v>
+        <v>0.333992</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00536942</v>
+        <v>0.0015323</v>
       </c>
       <c r="L9" t="n">
-        <v>1.62819</v>
+        <v>0.4572</v>
       </c>
       <c r="M9" t="n">
-        <v>94998502604.69609</v>
+        <v>94999794375.9511</v>
       </c>
       <c r="N9" t="n">
-        <v>94998536194.20079</v>
+        <v>94999999462.45239</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.032</v>
+        <v>1.034</v>
       </c>
       <c r="F10" t="n">
-        <v>24668780814</v>
+        <v>24775147900</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>296352257</v>
+        <v>121619596</v>
       </c>
       <c r="I10" t="n">
-        <v>1.047</v>
+        <v>1.037</v>
       </c>
       <c r="J10" t="n">
-        <v>1.018</v>
+        <v>1.031</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.004493841927478259</v>
+        <v>0.00301549</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.43365</v>
+        <v>0.29236</v>
       </c>
       <c r="M10" t="n">
-        <v>23908770801.868</v>
+        <v>23950374574.928</v>
       </c>
       <c r="N10" t="n">
-        <v>23908770801.868</v>
+        <v>23950374574.928</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1219.82</v>
+        <v>1166.97</v>
       </c>
       <c r="F11" t="n">
-        <v>20706838541</v>
+        <v>19827714621</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1478344830</v>
+        <v>690269906</v>
       </c>
       <c r="I11" t="n">
-        <v>1251.93</v>
+        <v>1225.97</v>
       </c>
       <c r="J11" t="n">
-        <v>1088.24</v>
+        <v>1132.57</v>
       </c>
       <c r="K11" t="n">
-        <v>124.57</v>
+        <v>-61.46120439908077</v>
       </c>
       <c r="L11" t="n">
-        <v>11.37416</v>
+        <v>-5.00325</v>
       </c>
       <c r="M11" t="n">
-        <v>16988150.1655448</v>
+        <v>16990836.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>16989311.1030448</v>
+        <v>16991045.4780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>81.16</v>
+        <v>78.87</v>
       </c>
       <c r="F12" t="n">
-        <v>18051336236</v>
+        <v>17545269792</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>767236220</v>
+        <v>569922776</v>
       </c>
       <c r="I12" t="n">
-        <v>82.51000000000001</v>
+        <v>81.41</v>
       </c>
       <c r="J12" t="n">
-        <v>77.68000000000001</v>
+        <v>78.45</v>
       </c>
       <c r="K12" t="n">
-        <v>3.1</v>
+        <v>-2.963128816302074</v>
       </c>
       <c r="L12" t="n">
-        <v>3.97762</v>
+        <v>-3.62075</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.081432</v>
+        <v>0.079914</v>
       </c>
       <c r="F13" t="n">
-        <v>12727417384</v>
+        <v>12495383033</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1040485472</v>
+        <v>582124621</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082757</v>
+        <v>0.082092</v>
       </c>
       <c r="J13" t="n">
-        <v>0.077935</v>
+        <v>0.07933</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0022734</v>
+        <v>-0.002242756669351878</v>
       </c>
       <c r="L13" t="n">
-        <v>2.87196</v>
+        <v>-2.72984</v>
       </c>
       <c r="M13" t="n">
-        <v>156343966383.7052</v>
+        <v>156359642864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156347892864.2343</v>
+        <v>156361352864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>555.01</v>
+        <v>554.96</v>
       </c>
       <c r="F14" t="n">
-        <v>10442877924</v>
+        <v>10443675706</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>103362764</v>
+        <v>90422267</v>
       </c>
       <c r="I14" t="n">
-        <v>569.8200000000001</v>
+        <v>562.85</v>
       </c>
       <c r="J14" t="n">
-        <v>527.91</v>
+        <v>545.3</v>
       </c>
       <c r="K14" t="n">
-        <v>21.44</v>
+        <v>-4.258181792300206</v>
       </c>
       <c r="L14" t="n">
-        <v>4.01878</v>
+        <v>-0.76145</v>
       </c>
       <c r="M14" t="n">
-        <v>18818330.21818927</v>
+        <v>18818720.21540879</v>
       </c>
       <c r="N14" t="n">
-        <v>18818342.81815135</v>
+        <v>18818777.21537256</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.999609</v>
       </c>
       <c r="F15" t="n">
-        <v>10234140103</v>
+        <v>10235487124</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>150420161</v>
+        <v>57842888</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.99962</v>
+        <v>0.999449</v>
       </c>
       <c r="K15" t="n">
-        <v>6.546e-05</v>
+        <v>-0.000377425924169117</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00655</v>
+        <v>-0.03774</v>
       </c>
       <c r="M15" t="n">
-        <v>10235146527.19681</v>
+        <v>10239494087.77727</v>
       </c>
       <c r="N15" t="n">
-        <v>10235846819.45149</v>
+        <v>10239031200.57358</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,144 +1409,144 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>12.58</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9642886168</v>
+        <v>9490701095</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>321698833</v>
+        <v>79074225</v>
       </c>
       <c r="I16" t="n">
-        <v>12.76</v>
+        <v>81.06999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>11.88</v>
+        <v>79.22</v>
       </c>
       <c r="K16" t="n">
-        <v>0.6705989999999999</v>
+        <v>-1.055372653202411</v>
       </c>
       <c r="L16" t="n">
-        <v>5.63208</v>
+        <v>-1.3037</v>
       </c>
       <c r="M16" t="n">
-        <v>766849970.424884</v>
+        <v>118786640</v>
       </c>
       <c r="N16" t="n">
-        <v>1000000000</v>
+        <v>293356139</v>
       </c>
       <c r="O16" t="n">
-        <v>52.7</v>
+        <v>87.91</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>80.52</v>
+        <v>12.1</v>
       </c>
       <c r="F17" t="n">
-        <v>9562869831</v>
+        <v>9281089290</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>123574619</v>
+        <v>230917864</v>
       </c>
       <c r="I17" t="n">
-        <v>81.48</v>
+        <v>12.65</v>
       </c>
       <c r="J17" t="n">
-        <v>78.34</v>
+        <v>12.15</v>
       </c>
       <c r="K17" t="n">
-        <v>1.96</v>
+        <v>-0.5438707483190797</v>
       </c>
       <c r="L17" t="n">
-        <v>2.50047</v>
+        <v>-4.30048</v>
       </c>
       <c r="M17" t="n">
-        <v>118786640</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N17" t="n">
-        <v>293356139</v>
+        <v>1000000000</v>
       </c>
       <c r="O17" t="n">
-        <v>87.91</v>
+        <v>52.7</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,31 +1565,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.228749</v>
+        <v>0.221951</v>
       </c>
       <c r="F18" t="n">
-        <v>8590157371</v>
+        <v>8336341265</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>327031124</v>
+        <v>236195583</v>
       </c>
       <c r="I18" t="n">
-        <v>0.233126</v>
+        <v>0.230141</v>
       </c>
       <c r="J18" t="n">
-        <v>0.218627</v>
+        <v>0.221358</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00908843</v>
+        <v>-0.008392773995036851</v>
       </c>
       <c r="L18" t="n">
-        <v>4.13748</v>
+        <v>-3.64359</v>
       </c>
       <c r="M18" t="n">
-        <v>37553537941.9088</v>
+        <v>37559424049.89742</v>
       </c>
       <c r="N18" t="n">
         <v>45000000000</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.039999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>8318634333</v>
+        <v>8323063758</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>148971</v>
+        <v>231160</v>
       </c>
       <c r="I19" t="n">
-        <v>9.050000000000001</v>
+        <v>9.08</v>
       </c>
       <c r="J19" t="n">
-        <v>9.029999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.03347744</v>
+        <v>0.00580984</v>
       </c>
       <c r="L19" t="n">
-        <v>0.37156</v>
+        <v>0.06425</v>
       </c>
       <c r="M19" t="n">
         <v>919857851.9</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.25</v>
+        <v>5.09</v>
       </c>
       <c r="F20" t="n">
-        <v>6868939868</v>
+        <v>6665307780</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>1346539922</v>
+        <v>791790203</v>
       </c>
       <c r="I20" t="n">
-        <v>5.43</v>
+        <v>5.28</v>
       </c>
       <c r="J20" t="n">
-        <v>4.57</v>
+        <v>4.93</v>
       </c>
       <c r="K20" t="n">
-        <v>0.625414</v>
+        <v>-0.1999578432107914</v>
       </c>
       <c r="L20" t="n">
-        <v>13.52871</v>
+        <v>-3.77912</v>
       </c>
       <c r="M20" t="n">
-        <v>1309110317</v>
+        <v>1309190001</v>
       </c>
       <c r="N20" t="n">
-        <v>1309110350</v>
+        <v>1309190000</v>
       </c>
       <c r="O20" t="n">
         <v>20.44</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261016T133536Z-dad102</t>
+          <t>20261017T123145Z-9ed0c1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.009155470000000001</v>
+        <v>0.178768</v>
       </c>
       <c r="F21" t="n">
-        <v>6496562156</v>
+        <v>6292924300</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>14600288</v>
+        <v>98974100</v>
       </c>
       <c r="I21" t="n">
-        <v>0.009755740000000001</v>
+        <v>0.184197</v>
       </c>
       <c r="J21" t="n">
-        <v>0.007951949999999999</v>
+        <v>0.178682</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0011497</v>
+        <v>-0.005027792137979131</v>
       </c>
       <c r="L21" t="n">
-        <v>14.3609</v>
+        <v>-2.73554</v>
       </c>
       <c r="M21" t="n">
-        <v>709252819526.8486</v>
+        <v>35201684158.68541</v>
       </c>
       <c r="N21" t="n">
-        <v>1142406063382.48</v>
+        <v>50001786839.69947</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-16T13:33:49.000Z</t>
+          <t>2026-10-17T12:30:51.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81449</v>
+        <v>81840</v>
       </c>
       <c r="F2" t="n">
-        <v>1637036303957</v>
+        <v>1644922349031</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>22285614325</v>
+        <v>15833623864</v>
       </c>
       <c r="I2" t="n">
-        <v>82385</v>
+        <v>82178</v>
       </c>
       <c r="J2" t="n">
-        <v>80761</v>
+        <v>80823</v>
       </c>
       <c r="K2" t="n">
-        <v>-793.1984415269108</v>
+        <v>429.43</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.96446</v>
+        <v>0.5274799999999999</v>
       </c>
       <c r="M2" t="n">
         <v>20098843</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2427.76</v>
+        <v>2412.63</v>
       </c>
       <c r="F3" t="n">
-        <v>296532252463</v>
+        <v>294692886941</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8860960660</v>
+        <v>6801447065</v>
       </c>
       <c r="I3" t="n">
-        <v>2477.01</v>
+        <v>2426.58</v>
       </c>
       <c r="J3" t="n">
-        <v>2392.9</v>
+        <v>2363.56</v>
       </c>
       <c r="K3" t="n">
-        <v>-43.75325902150735</v>
+        <v>-11.33853866394384</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.7703</v>
+        <v>-0.46777</v>
       </c>
       <c r="M3" t="n">
-        <v>122142460.7593166</v>
+        <v>122145416.4149071</v>
       </c>
       <c r="N3" t="n">
-        <v>122142460.7593166</v>
+        <v>122145416.4149071</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9988669999999999</v>
+        <v>0.999039</v>
       </c>
       <c r="F4" t="n">
-        <v>183456895114</v>
+        <v>183488869298</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>41563710771</v>
+        <v>30512158919</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999401</v>
+        <v>0.999176</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9988320000000001</v>
+        <v>0.998552</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000339479352379102</v>
+        <v>0.00020536</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.03397</v>
+        <v>0.02056</v>
       </c>
       <c r="M4" t="n">
         <v>183665036252.9821</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>719.37</v>
+        <v>721.97</v>
       </c>
       <c r="F5" t="n">
-        <v>95790328662</v>
+        <v>96127425589</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>550447004</v>
+        <v>552656071</v>
       </c>
       <c r="I5" t="n">
-        <v>730.23</v>
+        <v>723.42</v>
       </c>
       <c r="J5" t="n">
-        <v>718.12</v>
+        <v>710.41</v>
       </c>
       <c r="K5" t="n">
-        <v>-10.32157869100968</v>
+        <v>3.29</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.41451</v>
+        <v>0.45708</v>
       </c>
       <c r="M5" t="n">
-        <v>133158380.58</v>
+        <v>133158327.74</v>
       </c>
       <c r="N5" t="n">
-        <v>133158373.97</v>
+        <v>133158323.64</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="F6" t="n">
-        <v>82042442751</v>
+        <v>81688907343</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1101326585</v>
+        <v>1006840350</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.04065648424111967</v>
+        <v>-0.003320256036395852</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.03352</v>
+        <v>-0.25594</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99957</v>
+        <v>0.999706</v>
       </c>
       <c r="F7" t="n">
-        <v>72550189435</v>
+        <v>72339236080</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13466994831</v>
+        <v>8073738785</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.999837</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9995230000000001</v>
+        <v>0.99917</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000273425420727391</v>
+        <v>0.00014154</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.02735</v>
+        <v>0.01416</v>
       </c>
       <c r="M7" t="n">
-        <v>72581370791.43715</v>
+        <v>72360476009.2679</v>
       </c>
       <c r="N7" t="n">
-        <v>72581370791.43715</v>
+        <v>72529085859.26056</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.25</v>
+        <v>103.89</v>
       </c>
       <c r="F8" t="n">
-        <v>61445173307</v>
+        <v>61235859455</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2304642554</v>
+        <v>1974809978</v>
       </c>
       <c r="I8" t="n">
-        <v>106.46</v>
+        <v>104.6</v>
       </c>
       <c r="J8" t="n">
-        <v>102.51</v>
+        <v>101.41</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.093693293325174</v>
+        <v>-0.09840746130987554</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.96874</v>
+        <v>-0.09463000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>589385048.0487075</v>
+        <v>589438381.2948874</v>
       </c>
       <c r="N8" t="n">
-        <v>635967584.9728914</v>
+        <v>636029155.8538811</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.336684</v>
+        <v>0.332911</v>
       </c>
       <c r="F9" t="n">
-        <v>31984906743</v>
+        <v>31631025436</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>302031533</v>
+        <v>272287301</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336655</v>
+        <v>0.336808</v>
       </c>
       <c r="J9" t="n">
-        <v>0.333992</v>
+        <v>0.332764</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0015323</v>
+        <v>-0.003660915296187728</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4572</v>
+        <v>-1.08771</v>
       </c>
       <c r="M9" t="n">
         <v>94999794375.9511</v>
       </c>
       <c r="N9" t="n">
-        <v>94999999462.45239</v>
+        <v>95002158802.75867</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.034</v>
+        <v>1.068</v>
       </c>
       <c r="F10" t="n">
-        <v>24775147900</v>
+        <v>25631793251</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>121619596</v>
+        <v>2286530</v>
       </c>
       <c r="I10" t="n">
-        <v>1.037</v>
+        <v>1.068</v>
       </c>
       <c r="J10" t="n">
-        <v>1.031</v>
+        <v>1.014</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00301549</v>
+        <v>0.03307799</v>
       </c>
       <c r="L10" t="n">
-        <v>0.29236</v>
+        <v>3.19766</v>
       </c>
       <c r="M10" t="n">
-        <v>23950374574.928</v>
+        <v>24010566736.048</v>
       </c>
       <c r="N10" t="n">
-        <v>23950374574.928</v>
+        <v>24010566736.048</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T08:19:31.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1166.97</v>
+        <v>1125.28</v>
       </c>
       <c r="F11" t="n">
-        <v>19827714621</v>
+        <v>19116367374</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>690269906</v>
+        <v>700672715</v>
       </c>
       <c r="I11" t="n">
-        <v>1225.97</v>
+        <v>1176.06</v>
       </c>
       <c r="J11" t="n">
-        <v>1132.57</v>
+        <v>1104.15</v>
       </c>
       <c r="K11" t="n">
-        <v>-61.46120439908077</v>
+        <v>-33.3608363901451</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.00325</v>
+        <v>-2.8793</v>
       </c>
       <c r="M11" t="n">
         <v>16990836.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>16991045.4780448</v>
+        <v>16992856.4155448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.87</v>
+        <v>78.66</v>
       </c>
       <c r="F12" t="n">
-        <v>17545269792</v>
+        <v>17502730512</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>569922776</v>
+        <v>447279723</v>
       </c>
       <c r="I12" t="n">
-        <v>81.41</v>
+        <v>79.27</v>
       </c>
       <c r="J12" t="n">
-        <v>78.45</v>
+        <v>77.36</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.963128816302074</v>
+        <v>-0.08887658338404947</v>
       </c>
       <c r="L12" t="n">
-        <v>-3.62075</v>
+        <v>-0.11286</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.079914</v>
+        <v>0.079398</v>
       </c>
       <c r="F13" t="n">
-        <v>12495383033</v>
+        <v>12415213651</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>582124621</v>
+        <v>418332029</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082092</v>
+        <v>0.080335</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07933</v>
+        <v>0.07766199999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002242756669351878</v>
+        <v>-0.000268697157271555</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.72984</v>
+        <v>-0.33728</v>
       </c>
       <c r="M13" t="n">
         <v>156359642864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156361352864.2343</v>
+        <v>156375122864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>554.96</v>
+        <v>582.37</v>
       </c>
       <c r="F14" t="n">
-        <v>10443675706</v>
+        <v>10958932343</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>90422267</v>
+        <v>174146237</v>
       </c>
       <c r="I14" t="n">
-        <v>562.85</v>
+        <v>607.6799999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>545.3</v>
+        <v>545.52</v>
       </c>
       <c r="K14" t="n">
-        <v>-4.258181792300206</v>
+        <v>28.23</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.76145</v>
+        <v>5.09448</v>
       </c>
       <c r="M14" t="n">
-        <v>18818720.21540879</v>
+        <v>18819164.81130753</v>
       </c>
       <c r="N14" t="n">
-        <v>18818777.21537256</v>
+        <v>18819197.81127546</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999609</v>
+        <v>0.9997549999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>10235487124</v>
+        <v>10229787261</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>57842888</v>
+        <v>13338823</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999449</v>
+        <v>0.999098</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000377425924169117</v>
+        <v>0.00015895</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.03774</v>
+        <v>0.0159</v>
       </c>
       <c r="M15" t="n">
-        <v>10239494087.77727</v>
+        <v>10232232130.12299</v>
       </c>
       <c r="N15" t="n">
-        <v>10239031200.57358</v>
+        <v>10232785260.69191</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.90000000000001</v>
+        <v>80.06999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9490701095</v>
+        <v>9510702094</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>79074225</v>
+        <v>48340847</v>
       </c>
       <c r="I16" t="n">
-        <v>81.06999999999999</v>
+        <v>80.36</v>
       </c>
       <c r="J16" t="n">
-        <v>79.22</v>
+        <v>78.86</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.055372653202411</v>
+        <v>0.221375</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3037</v>
+        <v>0.27724</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.1</v>
+        <v>12.01</v>
       </c>
       <c r="F17" t="n">
-        <v>9281089290</v>
+        <v>9207915045</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>230917864</v>
+        <v>238503558</v>
       </c>
       <c r="I17" t="n">
-        <v>12.65</v>
+        <v>12.11</v>
       </c>
       <c r="J17" t="n">
-        <v>12.15</v>
+        <v>11.8</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.5438707483190797</v>
+        <v>-0.05240061057845402</v>
       </c>
       <c r="L17" t="n">
-        <v>-4.30048</v>
+        <v>-0.43458</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,267 +1539,267 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.221951</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8336341265</v>
+        <v>8314597738</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>236195583</v>
+        <v>244077</v>
       </c>
       <c r="I18" t="n">
-        <v>0.230141</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.221358</v>
+        <v>8.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.008392773995036851</v>
+        <v>-0.009145107502344985</v>
       </c>
       <c r="L18" t="n">
-        <v>-3.64359</v>
+        <v>-0.10107</v>
       </c>
       <c r="M18" t="n">
-        <v>37559424049.89742</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.050000000000001</v>
+        <v>0.220109</v>
       </c>
       <c r="F19" t="n">
-        <v>8323063758</v>
+        <v>8267418346</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>231160</v>
+        <v>234862689</v>
       </c>
       <c r="I19" t="n">
-        <v>9.08</v>
+        <v>0.223016</v>
       </c>
       <c r="J19" t="n">
-        <v>8.960000000000001</v>
+        <v>0.215662</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00580984</v>
+        <v>-0.001437609941457418</v>
       </c>
       <c r="L19" t="n">
-        <v>0.06425</v>
+        <v>-0.6489</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>37559424049.89742</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.09</v>
+        <v>0.00919641</v>
       </c>
       <c r="F20" t="n">
-        <v>6665307780</v>
+        <v>6522317480</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>791790203</v>
+        <v>10895094</v>
       </c>
       <c r="I20" t="n">
-        <v>5.28</v>
+        <v>0.00931416</v>
       </c>
       <c r="J20" t="n">
-        <v>4.93</v>
+        <v>0.00865176</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1999578432107914</v>
+        <v>0.0003836</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.77912</v>
+        <v>4.35276</v>
       </c>
       <c r="M20" t="n">
-        <v>1309190001</v>
+        <v>709252819141.0112</v>
       </c>
       <c r="N20" t="n">
-        <v>1309190000</v>
+        <v>1142406062934.849</v>
       </c>
       <c r="O20" t="n">
-        <v>20.44</v>
+        <v>0.01946402</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261017T123145Z-9ed0c1</t>
+          <t>20261018T125021Z-21dea0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.178768</v>
+        <v>4.91</v>
       </c>
       <c r="F21" t="n">
-        <v>6292924300</v>
+        <v>6432017945</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>98974100</v>
+        <v>570456860</v>
       </c>
       <c r="I21" t="n">
-        <v>0.184197</v>
+        <v>5.1</v>
       </c>
       <c r="J21" t="n">
-        <v>0.178682</v>
+        <v>4.79</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005027792137979131</v>
+        <v>-0.1570939046227666</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.73554</v>
+        <v>-3.09895</v>
       </c>
       <c r="M21" t="n">
-        <v>35201684158.68541</v>
+        <v>1309296211</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786839.69947</v>
+        <v>1309296217</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-17T12:30:51.000Z</t>
+          <t>2026-10-18T12:48:53.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81840</v>
+        <v>81999</v>
       </c>
       <c r="F2" t="n">
-        <v>1644922349031</v>
+        <v>1648343211145</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>15833623864</v>
+        <v>28096593748</v>
       </c>
       <c r="I2" t="n">
-        <v>82178</v>
+        <v>83035</v>
       </c>
       <c r="J2" t="n">
-        <v>80823</v>
+        <v>80672</v>
       </c>
       <c r="K2" t="n">
-        <v>429.43</v>
+        <v>950.08</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5274799999999999</v>
+        <v>1.1573</v>
       </c>
       <c r="M2" t="n">
         <v>20098843</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2412.63</v>
+        <v>2395.39</v>
       </c>
       <c r="F3" t="n">
-        <v>294692886941</v>
+        <v>292706556611</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>6801447065</v>
+        <v>10705337627</v>
       </c>
       <c r="I3" t="n">
-        <v>2426.58</v>
+        <v>2443.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2363.56</v>
+        <v>2329.53</v>
       </c>
       <c r="K3" t="n">
-        <v>-11.33853866394384</v>
+        <v>19.52</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.46777</v>
+        <v>0.80217</v>
       </c>
       <c r="M3" t="n">
-        <v>122145416.4149071</v>
+        <v>122148377.8600448</v>
       </c>
       <c r="N3" t="n">
-        <v>122145416.4149071</v>
+        <v>122148377.8600448</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999039</v>
+        <v>0.99927</v>
       </c>
       <c r="F4" t="n">
-        <v>183488869298</v>
+        <v>183531442789</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>30512158919</v>
+        <v>51145168747</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999176</v>
+        <v>0.999436</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998552</v>
+        <v>0.999011</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00020536</v>
+        <v>0.00025581</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02056</v>
+        <v>0.02894</v>
       </c>
       <c r="M4" t="n">
         <v>183665036252.9821</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>721.97</v>
+        <v>725.58</v>
       </c>
       <c r="F5" t="n">
-        <v>96127425589</v>
+        <v>95429616271</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>552656071</v>
+        <v>782018686</v>
       </c>
       <c r="I5" t="n">
-        <v>723.42</v>
+        <v>728.91</v>
       </c>
       <c r="J5" t="n">
-        <v>710.41</v>
+        <v>705.5599999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>3.29</v>
+        <v>13.72</v>
       </c>
       <c r="L5" t="n">
-        <v>0.45708</v>
+        <v>1.92571</v>
       </c>
       <c r="M5" t="n">
-        <v>133158327.74</v>
+        <v>131512078.46</v>
       </c>
       <c r="N5" t="n">
-        <v>133158323.64</v>
+        <v>131512066.19</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>81688907343</v>
+        <v>82006759085</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1006840350</v>
+        <v>1540830524</v>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003320256036395852</v>
+        <v>0.02565722</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.25594</v>
+        <v>2.00795</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999706</v>
+        <v>0.999915</v>
       </c>
       <c r="F7" t="n">
-        <v>72339236080</v>
+        <v>72284630181</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>8073738785</v>
+        <v>16636073066</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999837</v>
+        <v>0.99998</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99917</v>
+        <v>0.999636</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00014154</v>
+        <v>0.00027768</v>
       </c>
       <c r="L7" t="n">
-        <v>0.01416</v>
+        <v>0.02804</v>
       </c>
       <c r="M7" t="n">
-        <v>72360476009.2679</v>
+        <v>72290909944.32866</v>
       </c>
       <c r="N7" t="n">
-        <v>72529085859.26056</v>
+        <v>72217980798.60966</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103.89</v>
+        <v>104.23</v>
       </c>
       <c r="F8" t="n">
-        <v>61235859455</v>
+        <v>61448855944</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>1974809978</v>
+        <v>2853413683</v>
       </c>
       <c r="I8" t="n">
-        <v>104.6</v>
+        <v>106.05</v>
       </c>
       <c r="J8" t="n">
-        <v>101.41</v>
+        <v>100.48</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09840746130987554</v>
+        <v>2.16</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.09463000000000001</v>
+        <v>2.10656</v>
       </c>
       <c r="M8" t="n">
-        <v>589438381.2948874</v>
+        <v>589493939.5236186</v>
       </c>
       <c r="N8" t="n">
-        <v>636029155.8538811</v>
+        <v>636090538.8119909</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.332911</v>
+        <v>0.330931</v>
       </c>
       <c r="F9" t="n">
-        <v>31631025436</v>
+        <v>31442171966</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>272287301</v>
+        <v>348904063</v>
       </c>
       <c r="I9" t="n">
-        <v>0.336808</v>
+        <v>0.333133</v>
       </c>
       <c r="J9" t="n">
-        <v>0.332764</v>
+        <v>0.330453</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.003660915296187728</v>
+        <v>-0.000793434188158526</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.08771</v>
+        <v>-0.22421</v>
       </c>
       <c r="M9" t="n">
-        <v>94999794375.9511</v>
+        <v>95003907688.99457</v>
       </c>
       <c r="N9" t="n">
-        <v>95002158802.75867</v>
+        <v>95003926457.80727</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.068</v>
+        <v>1.033</v>
       </c>
       <c r="F10" t="n">
-        <v>25631793251</v>
+        <v>24804028407</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2286530</v>
+        <v>2367445</v>
       </c>
       <c r="I10" t="n">
-        <v>1.068</v>
+        <v>1.053</v>
       </c>
       <c r="J10" t="n">
-        <v>1.014</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.03307799</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.19766</v>
-      </c>
+        <v>1.017</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>24010566736.048</v>
+        <v>24018021967.488</v>
       </c>
       <c r="N10" t="n">
-        <v>24010566736.048</v>
+        <v>24018021967.488</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-18T08:19:31.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1125.28</v>
+        <v>1123.05</v>
       </c>
       <c r="F11" t="n">
-        <v>19116367374</v>
+        <v>19081137346</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>700672715</v>
+        <v>998059035</v>
       </c>
       <c r="I11" t="n">
-        <v>1176.06</v>
+        <v>1186.79</v>
       </c>
       <c r="J11" t="n">
-        <v>1104.15</v>
+        <v>1049.9</v>
       </c>
       <c r="K11" t="n">
-        <v>-33.3608363901451</v>
+        <v>40.23</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.8793</v>
+        <v>3.74434</v>
       </c>
       <c r="M11" t="n">
-        <v>16990836.1030448</v>
+        <v>16994573.6030448</v>
       </c>
       <c r="N11" t="n">
-        <v>16992856.4155448</v>
+        <v>16994836.1030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.66</v>
+        <v>78.84999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17502730512</v>
+        <v>17546276372</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>447279723</v>
+        <v>599752640</v>
       </c>
       <c r="I12" t="n">
-        <v>79.27</v>
+        <v>80.34</v>
       </c>
       <c r="J12" t="n">
-        <v>77.36</v>
+        <v>76.14</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.08887658338404947</v>
+        <v>1.37</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.11286</v>
+        <v>1.76027</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.079398</v>
+        <v>0.07919</v>
       </c>
       <c r="F13" t="n">
-        <v>12415213651</v>
+        <v>12386377234</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>418332029</v>
+        <v>543494855</v>
       </c>
       <c r="I13" t="n">
-        <v>0.080335</v>
+        <v>0.080146</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07766199999999999</v>
+        <v>0.076143</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.000268697157271555</v>
+        <v>0.0017975</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.33728</v>
+        <v>2.29975</v>
       </c>
       <c r="M13" t="n">
-        <v>156359642864.2343</v>
+        <v>156388292864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156375122864.2343</v>
+        <v>156390392864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>582.37</v>
+        <v>594.41</v>
       </c>
       <c r="F14" t="n">
-        <v>10958932343</v>
+        <v>11207952207</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>174146237</v>
+        <v>187415319</v>
       </c>
       <c r="I14" t="n">
-        <v>607.6799999999999</v>
+        <v>606.03</v>
       </c>
       <c r="J14" t="n">
-        <v>545.52</v>
+        <v>572.52</v>
       </c>
       <c r="K14" t="n">
-        <v>28.23</v>
+        <v>10.59</v>
       </c>
       <c r="L14" t="n">
-        <v>5.09448</v>
+        <v>1.89314</v>
       </c>
       <c r="M14" t="n">
-        <v>18819164.81130753</v>
+        <v>18819696.39820961</v>
       </c>
       <c r="N14" t="n">
-        <v>18819197.81127546</v>
+        <v>18819716.19763446</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.9997549999999999</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10229787261</v>
+        <v>10209850486</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>13338823</v>
+        <v>78877083</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999098</v>
+        <v>0.999591</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00015895</v>
+        <v>0.00053579</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0159</v>
+        <v>0.06188</v>
       </c>
       <c r="M15" t="n">
-        <v>10232232130.12299</v>
+        <v>10207126753.2636</v>
       </c>
       <c r="N15" t="n">
-        <v>10232785260.69191</v>
+        <v>10210497230.01631</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1431,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80.06999999999999</v>
+        <v>80.06</v>
       </c>
       <c r="F16" t="n">
-        <v>9510702094</v>
+        <v>9513334507</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>48340847</v>
+        <v>96879035</v>
       </c>
       <c r="I16" t="n">
-        <v>80.36</v>
+        <v>81.14</v>
       </c>
       <c r="J16" t="n">
-        <v>78.86</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.221375</v>
+        <v>0.873362</v>
       </c>
       <c r="L16" t="n">
-        <v>0.27724</v>
+        <v>1.09682</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.01</v>
+        <v>11.96</v>
       </c>
       <c r="F17" t="n">
-        <v>9207915045</v>
+        <v>9170302708</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>238503558</v>
+        <v>283998258</v>
       </c>
       <c r="I17" t="n">
-        <v>12.11</v>
+        <v>12.25</v>
       </c>
       <c r="J17" t="n">
-        <v>11.8</v>
+        <v>11.54</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.05240061057845402</v>
+        <v>0.203197</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.43458</v>
+        <v>1.72514</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1568,25 +1564,25 @@
         <v>9.039999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8314597738</v>
+        <v>8319062465</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>244077</v>
+        <v>230413</v>
       </c>
       <c r="I18" t="n">
-        <v>9.050000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>8.99</v>
+        <v>9</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.009145107502344985</v>
+        <v>0.00668027</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.10107</v>
+        <v>0.07367</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.220109</v>
+        <v>0.21742</v>
       </c>
       <c r="F19" t="n">
-        <v>8267418346</v>
+        <v>8167339300</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>234862689</v>
+        <v>267796416</v>
       </c>
       <c r="I19" t="n">
-        <v>0.223016</v>
+        <v>0.222543</v>
       </c>
       <c r="J19" t="n">
-        <v>0.215662</v>
+        <v>0.211289</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.001437609941457418</v>
+        <v>0.00140652</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6489</v>
+        <v>0.59861</v>
       </c>
       <c r="M19" t="n">
         <v>37559424049.89742</v>
@@ -1669,137 +1665,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.00919641</v>
+        <v>4.93</v>
       </c>
       <c r="F20" t="n">
-        <v>6522317480</v>
+        <v>6451215052</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>10895094</v>
+        <v>764111874</v>
       </c>
       <c r="I20" t="n">
-        <v>0.00931416</v>
+        <v>5.13</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00865176</v>
+        <v>4.63</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0003836</v>
+        <v>0.202766</v>
       </c>
       <c r="L20" t="n">
-        <v>4.35276</v>
+        <v>4.21362</v>
       </c>
       <c r="M20" t="n">
-        <v>709252819141.0112</v>
+        <v>1309375512</v>
       </c>
       <c r="N20" t="n">
-        <v>1142406062934.849</v>
+        <v>1309375550</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01946402</v>
+        <v>20.44</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261018T125021Z-21dea0</t>
+          <t>20261019T155721Z-bf5b4f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.91</v>
+        <v>0.00902215</v>
       </c>
       <c r="F21" t="n">
-        <v>6432017945</v>
+        <v>6403144123</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>570456860</v>
+        <v>18995561</v>
       </c>
       <c r="I21" t="n">
-        <v>5.1</v>
+        <v>0.00938874</v>
       </c>
       <c r="J21" t="n">
-        <v>4.79</v>
+        <v>0.00896216</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1570939046227666</v>
+        <v>-0.000209720018367648</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.09895</v>
+        <v>-2.19383</v>
       </c>
       <c r="M21" t="n">
-        <v>1309296211</v>
+        <v>709252818982.6709</v>
       </c>
       <c r="N21" t="n">
-        <v>1309296217</v>
+        <v>1142406062839.606</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>0.01946402</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-18T12:48:53.000Z</t>
+          <t>2026-10-19T15:54:54.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81999</v>
+        <v>81820</v>
       </c>
       <c r="F2" t="n">
-        <v>1648343211145</v>
+        <v>1643849661168</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>28096593748</v>
+        <v>23794376293</v>
       </c>
       <c r="I2" t="n">
-        <v>83035</v>
+        <v>82457</v>
       </c>
       <c r="J2" t="n">
-        <v>80672</v>
+        <v>81155</v>
       </c>
       <c r="K2" t="n">
-        <v>950.08</v>
+        <v>-277.0832016136119</v>
       </c>
       <c r="L2" t="n">
-        <v>1.1573</v>
+        <v>-0.40277</v>
       </c>
       <c r="M2" t="n">
         <v>20098843</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2395.39</v>
+        <v>2399.27</v>
       </c>
       <c r="F3" t="n">
-        <v>292706556611</v>
+        <v>292978105187</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>10705337627</v>
+        <v>8990307160</v>
       </c>
       <c r="I3" t="n">
-        <v>2443.8</v>
+        <v>2418.38</v>
       </c>
       <c r="J3" t="n">
-        <v>2329.53</v>
+        <v>2374.52</v>
       </c>
       <c r="K3" t="n">
-        <v>19.52</v>
+        <v>-2.522336619902489</v>
       </c>
       <c r="L3" t="n">
-        <v>0.80217</v>
+        <v>-0.18086</v>
       </c>
       <c r="M3" t="n">
-        <v>122148377.8600448</v>
+        <v>122151332.3949526</v>
       </c>
       <c r="N3" t="n">
-        <v>122148377.8600448</v>
+        <v>122151332.3949526</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99927</v>
+        <v>0.999086</v>
       </c>
       <c r="F4" t="n">
-        <v>183531442789</v>
+        <v>183006939791</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>51145168747</v>
+        <v>45480782171</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999436</v>
+        <v>0.999418</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999011</v>
+        <v>0.99908</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00025581</v>
+        <v>-0.000256184905119805</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02894</v>
+        <v>-0.02432</v>
       </c>
       <c r="M4" t="n">
-        <v>183665036252.9821</v>
+        <v>183176219727.9433</v>
       </c>
       <c r="N4" t="n">
-        <v>189131984703.7462</v>
+        <v>188643168191.5762</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>725.58</v>
+        <v>731.48</v>
       </c>
       <c r="F5" t="n">
-        <v>95429616271</v>
+        <v>96181005386</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>782018686</v>
+        <v>622890543</v>
       </c>
       <c r="I5" t="n">
-        <v>728.91</v>
+        <v>732.9</v>
       </c>
       <c r="J5" t="n">
-        <v>705.5599999999999</v>
+        <v>723.75</v>
       </c>
       <c r="K5" t="n">
-        <v>13.72</v>
+        <v>5.43</v>
       </c>
       <c r="L5" t="n">
-        <v>1.92571</v>
+        <v>0.71666</v>
       </c>
       <c r="M5" t="n">
-        <v>131512078.46</v>
+        <v>131512026.94</v>
       </c>
       <c r="N5" t="n">
-        <v>131512066.19</v>
+        <v>131512026.94</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>82006759085</v>
+        <v>82201354777</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1540830524</v>
+        <v>1172521983</v>
       </c>
       <c r="I6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02565722</v>
+        <v>0.00200376</v>
       </c>
       <c r="L6" t="n">
-        <v>2.00795</v>
+        <v>0.08273</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999915</v>
+        <v>0.999846</v>
       </c>
       <c r="F7" t="n">
-        <v>72284630181</v>
+        <v>72079818613</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16636073066</v>
+        <v>16202293212</v>
       </c>
       <c r="I7" t="n">
-        <v>0.99998</v>
+        <v>1.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999636</v>
+        <v>0.999321</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00027768</v>
+        <v>-2.9288340161138e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02804</v>
+        <v>-0.00104</v>
       </c>
       <c r="M7" t="n">
-        <v>72290909944.32866</v>
+        <v>72092031784.48212</v>
       </c>
       <c r="N7" t="n">
-        <v>72217980798.60966</v>
+        <v>72093444363.25397</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.23</v>
+        <v>104.57</v>
       </c>
       <c r="F8" t="n">
-        <v>61448855944</v>
+        <v>61623423608</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2853413683</v>
+        <v>2197448615</v>
       </c>
       <c r="I8" t="n">
-        <v>106.05</v>
+        <v>105.51</v>
       </c>
       <c r="J8" t="n">
-        <v>100.48</v>
+        <v>103.54</v>
       </c>
       <c r="K8" t="n">
-        <v>2.16</v>
+        <v>0.30799</v>
       </c>
       <c r="L8" t="n">
-        <v>2.10656</v>
+        <v>0.19838</v>
       </c>
       <c r="M8" t="n">
-        <v>589493939.5236186</v>
+        <v>589549805.1585578</v>
       </c>
       <c r="N8" t="n">
-        <v>636090538.8119909</v>
+        <v>636152130.5110345</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330931</v>
+        <v>0.330519</v>
       </c>
       <c r="F9" t="n">
-        <v>31442171966</v>
+        <v>31393768777</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>348904063</v>
+        <v>307024496</v>
       </c>
       <c r="I9" t="n">
-        <v>0.333133</v>
+        <v>0.33237</v>
       </c>
       <c r="J9" t="n">
-        <v>0.330453</v>
+        <v>0.33083</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000793434188158526</v>
+        <v>-0.001465281165272836</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.22421</v>
+        <v>-0.44701</v>
       </c>
       <c r="M9" t="n">
-        <v>95003907688.99457</v>
+        <v>95005283434.57567</v>
       </c>
       <c r="N9" t="n">
-        <v>95003926457.80727</v>
+        <v>95005306953.93657</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,25 +1045,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.033</v>
+        <v>1.021</v>
       </c>
       <c r="F10" t="n">
-        <v>24804028407</v>
+        <v>24524808341</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>2367445</v>
+        <v>19109939</v>
       </c>
       <c r="I10" t="n">
         <v>1.053</v>
       </c>
       <c r="J10" t="n">
-        <v>1.017</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.02</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00369969</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3616</v>
+      </c>
       <c r="M10" t="n">
         <v>24018021967.488</v>
       </c>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1123.05</v>
+        <v>1165.72</v>
       </c>
       <c r="F11" t="n">
-        <v>19081137346</v>
+        <v>19815688253</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>998059035</v>
+        <v>681324082</v>
       </c>
       <c r="I11" t="n">
-        <v>1186.79</v>
+        <v>1167.47</v>
       </c>
       <c r="J11" t="n">
-        <v>1049.9</v>
+        <v>1110.62</v>
       </c>
       <c r="K11" t="n">
-        <v>40.23</v>
+        <v>35.27</v>
       </c>
       <c r="L11" t="n">
-        <v>3.74434</v>
+        <v>3.08281</v>
       </c>
       <c r="M11" t="n">
-        <v>16994573.6030448</v>
+        <v>16995679.8530448</v>
       </c>
       <c r="N11" t="n">
-        <v>16994836.1030448</v>
+        <v>16996439.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.84999999999999</v>
+        <v>79.22</v>
       </c>
       <c r="F12" t="n">
-        <v>17546276372</v>
+        <v>17612551486</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>599752640</v>
+        <v>554739423</v>
       </c>
       <c r="I12" t="n">
-        <v>80.34</v>
+        <v>79.69</v>
       </c>
       <c r="J12" t="n">
-        <v>76.14</v>
+        <v>77.56999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>1.37</v>
+        <v>0.17247</v>
       </c>
       <c r="L12" t="n">
-        <v>1.76027</v>
+        <v>0.11026</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07919</v>
+        <v>0.07961500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12386377234</v>
+        <v>12447095005</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>543494855</v>
+        <v>321009717</v>
       </c>
       <c r="I13" t="n">
-        <v>0.080146</v>
+        <v>0.079957</v>
       </c>
       <c r="J13" t="n">
-        <v>0.076143</v>
+        <v>0.078486</v>
       </c>
       <c r="K13" t="n">
-        <v>0.0017975</v>
+        <v>0.00052291</v>
       </c>
       <c r="L13" t="n">
-        <v>2.29975</v>
+        <v>0.59559</v>
       </c>
       <c r="M13" t="n">
-        <v>156388292864.2343</v>
+        <v>156396942864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156390392864.2343</v>
+        <v>156402662864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>594.41</v>
+        <v>609.11</v>
       </c>
       <c r="F14" t="n">
-        <v>11207952207</v>
+        <v>11462504879</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>187415319</v>
+        <v>174355982</v>
       </c>
       <c r="I14" t="n">
-        <v>606.03</v>
+        <v>616.5599999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>572.52</v>
+        <v>583.67</v>
       </c>
       <c r="K14" t="n">
-        <v>10.59</v>
+        <v>13.5</v>
       </c>
       <c r="L14" t="n">
-        <v>1.89314</v>
+        <v>2.26053</v>
       </c>
       <c r="M14" t="n">
-        <v>18819696.39820961</v>
+        <v>18820082.89960967</v>
       </c>
       <c r="N14" t="n">
-        <v>18819716.19763446</v>
+        <v>18820082.89960967</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1369,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10209850486</v>
+        <v>10024386456</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>78877083</v>
+        <v>63843542</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999591</v>
+        <v>0.999852</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00053579</v>
+        <v>0.00024095</v>
       </c>
       <c r="L15" t="n">
-        <v>0.06188</v>
+        <v>0.01625</v>
       </c>
       <c r="M15" t="n">
-        <v>10207126753.2636</v>
+        <v>10022132246.0431</v>
       </c>
       <c r="N15" t="n">
-        <v>10210497230.01631</v>
+        <v>10022132246.0431</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>80.06</v>
+        <v>79.86</v>
       </c>
       <c r="F16" t="n">
-        <v>9513334507</v>
+        <v>9482614455</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>96879035</v>
+        <v>96281711</v>
       </c>
       <c r="I16" t="n">
-        <v>81.14</v>
+        <v>80.48999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>78.59999999999999</v>
+        <v>79.3</v>
       </c>
       <c r="K16" t="n">
-        <v>0.873362</v>
+        <v>-0.3093209300650983</v>
       </c>
       <c r="L16" t="n">
-        <v>1.09682</v>
+        <v>-0.47426</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1470,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.96</v>
+        <v>12.03</v>
       </c>
       <c r="F17" t="n">
-        <v>9170302708</v>
+        <v>9222393383</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>283998258</v>
+        <v>219380223</v>
       </c>
       <c r="I17" t="n">
-        <v>12.25</v>
+        <v>12.1</v>
       </c>
       <c r="J17" t="n">
-        <v>11.54</v>
+        <v>11.84</v>
       </c>
       <c r="K17" t="n">
-        <v>0.203197</v>
+        <v>0.052295</v>
       </c>
       <c r="L17" t="n">
-        <v>1.72514</v>
+        <v>0.3517</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1535,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.039999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8319062465</v>
+        <v>8304067361</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>230413</v>
+        <v>160599</v>
       </c>
       <c r="I18" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>9</v>
+        <v>9.01</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00668027</v>
+        <v>-0.01609306665198673</v>
       </c>
       <c r="L18" t="n">
-        <v>0.07367</v>
+        <v>-0.17868</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.21742</v>
+        <v>0.217535</v>
       </c>
       <c r="F19" t="n">
-        <v>8167339300</v>
+        <v>8169171075</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>267796416</v>
+        <v>213664084</v>
       </c>
       <c r="I19" t="n">
-        <v>0.222543</v>
+        <v>0.219528</v>
       </c>
       <c r="J19" t="n">
-        <v>0.211289</v>
+        <v>0.21468</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00140652</v>
+        <v>0.00034401</v>
       </c>
       <c r="L19" t="n">
-        <v>0.59861</v>
+        <v>0.10037</v>
       </c>
       <c r="M19" t="n">
         <v>37559424049.89742</v>
@@ -1665,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.93</v>
+        <v>0.009045879999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>6451215052</v>
+        <v>6412380430</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>764111874</v>
+        <v>16646992</v>
       </c>
       <c r="I20" t="n">
-        <v>5.13</v>
+        <v>0.009157449999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>4.63</v>
+        <v>0.00815956</v>
       </c>
       <c r="K20" t="n">
-        <v>0.202766</v>
+        <v>-4.2656012075308e-05</v>
       </c>
       <c r="L20" t="n">
-        <v>4.21362</v>
+        <v>-0.57721</v>
       </c>
       <c r="M20" t="n">
-        <v>1309375512</v>
+        <v>709252781589.0068</v>
       </c>
       <c r="N20" t="n">
-        <v>1309375550</v>
+        <v>1142406025446.552</v>
       </c>
       <c r="O20" t="n">
-        <v>20.44</v>
+        <v>0.01946402</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261019T155721Z-bf5b4f</t>
+          <t>20261020T135539Z-4fe15e</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.00902215</v>
+        <v>0.176519</v>
       </c>
       <c r="F21" t="n">
-        <v>6403144123</v>
+        <v>6213910300</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>18995561</v>
+        <v>98797071</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00938874</v>
+        <v>0.178101</v>
       </c>
       <c r="J21" t="n">
-        <v>0.00896216</v>
+        <v>0.17504</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.000209720018367648</v>
+        <v>-0.000142818662488553</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.19383</v>
+        <v>-0.09701</v>
       </c>
       <c r="M21" t="n">
-        <v>709252818982.6709</v>
+        <v>35208646793.51079</v>
       </c>
       <c r="N21" t="n">
-        <v>1142406062839.606</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-19T15:54:54.000Z</t>
+          <t>2026-10-20T13:54:48.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81820</v>
+        <v>83782</v>
       </c>
       <c r="F2" t="n">
-        <v>1643849661168</v>
+        <v>1683463864161</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>23794376293</v>
+        <v>27810620427</v>
       </c>
       <c r="I2" t="n">
-        <v>82457</v>
+        <v>83827</v>
       </c>
       <c r="J2" t="n">
-        <v>81155</v>
+        <v>82226</v>
       </c>
       <c r="K2" t="n">
-        <v>-277.0832016136119</v>
+        <v>817.78</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.40277</v>
+        <v>0.98571</v>
       </c>
       <c r="M2" t="n">
         <v>20098843</v>
       </c>
       <c r="N2" t="n">
-        <v>20098843</v>
+        <v>20099025</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2399.27</v>
+        <v>2467.29</v>
       </c>
       <c r="F3" t="n">
-        <v>292978105187</v>
+        <v>301341587294</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8990307160</v>
+        <v>13229514090</v>
       </c>
       <c r="I3" t="n">
-        <v>2418.38</v>
+        <v>2489.69</v>
       </c>
       <c r="J3" t="n">
-        <v>2374.52</v>
+        <v>2423.99</v>
       </c>
       <c r="K3" t="n">
-        <v>-2.522336619902489</v>
+        <v>18.67</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.18086</v>
+        <v>0.76241</v>
       </c>
       <c r="M3" t="n">
-        <v>122151332.3949526</v>
+        <v>122149509.8558182</v>
       </c>
       <c r="N3" t="n">
-        <v>122151332.3949526</v>
+        <v>122149509.8558182</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999086</v>
+        <v>0.998991</v>
       </c>
       <c r="F4" t="n">
-        <v>183006939791</v>
+        <v>182757891307</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>45480782171</v>
+        <v>52212332851</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999418</v>
+        <v>0.999326</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99908</v>
+        <v>0.9989170000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000256184905119805</v>
+        <v>-0.000196251266625036</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.02432</v>
+        <v>-0.01964</v>
       </c>
       <c r="M4" t="n">
-        <v>183176219727.9433</v>
+        <v>182942080919.1835</v>
       </c>
       <c r="N4" t="n">
-        <v>188643168191.5762</v>
+        <v>188409029385.2262</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>731.48</v>
+        <v>744.28</v>
       </c>
       <c r="F5" t="n">
-        <v>96181005386</v>
+        <v>97860915798</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>622890543</v>
+        <v>758599828</v>
       </c>
       <c r="I5" t="n">
-        <v>732.9</v>
+        <v>749.03</v>
       </c>
       <c r="J5" t="n">
-        <v>723.75</v>
+        <v>731.01</v>
       </c>
       <c r="K5" t="n">
-        <v>5.43</v>
+        <v>5.73</v>
       </c>
       <c r="L5" t="n">
-        <v>0.71666</v>
+        <v>0.77571</v>
       </c>
       <c r="M5" t="n">
-        <v>131512026.94</v>
+        <v>131511970.91</v>
       </c>
       <c r="N5" t="n">
-        <v>131512026.94</v>
+        <v>131511970.91</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="F6" t="n">
-        <v>82201354777</v>
+        <v>85724373277</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1172521983</v>
+        <v>1568317957</v>
       </c>
       <c r="I6" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="J6" t="n">
         <v>1.31</v>
       </c>
-      <c r="J6" t="n">
-        <v>1.29</v>
-      </c>
       <c r="K6" t="n">
-        <v>0.00200376</v>
+        <v>0.02668706</v>
       </c>
       <c r="L6" t="n">
-        <v>0.08273</v>
+        <v>2.00476</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999846</v>
+        <v>0.999404</v>
       </c>
       <c r="F7" t="n">
-        <v>72079818613</v>
+        <v>72050433910</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>16202293212</v>
+        <v>17320888874</v>
       </c>
       <c r="I7" t="n">
-        <v>1.001</v>
+        <v>0.999865</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999321</v>
+        <v>0.9982569999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-2.9288340161138e-05</v>
+        <v>-0.00043945887705088</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00104</v>
+        <v>-0.04395</v>
       </c>
       <c r="M7" t="n">
-        <v>72092031784.48212</v>
+        <v>72093698793.09575</v>
       </c>
       <c r="N7" t="n">
-        <v>72093444363.25397</v>
+        <v>72078358359.18475</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.57</v>
+        <v>106.51</v>
       </c>
       <c r="F8" t="n">
-        <v>61623423608</v>
+        <v>62766639454</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2197448615</v>
+        <v>2645967014</v>
       </c>
       <c r="I8" t="n">
-        <v>105.51</v>
+        <v>107.73</v>
       </c>
       <c r="J8" t="n">
-        <v>103.54</v>
+        <v>105.03</v>
       </c>
       <c r="K8" t="n">
-        <v>0.30799</v>
+        <v>-0.5101782287419354</v>
       </c>
       <c r="L8" t="n">
-        <v>0.19838</v>
+        <v>-0.47669</v>
       </c>
       <c r="M8" t="n">
-        <v>589549805.1585578</v>
+        <v>589548647.5300552</v>
       </c>
       <c r="N8" t="n">
-        <v>636152130.5110345</v>
+        <v>636150962.0157574</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330519</v>
+        <v>0.33147</v>
       </c>
       <c r="F9" t="n">
-        <v>31393768777</v>
+        <v>31499294319</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>307024496</v>
+        <v>324164813</v>
       </c>
       <c r="I9" t="n">
-        <v>0.33237</v>
+        <v>0.331681</v>
       </c>
       <c r="J9" t="n">
-        <v>0.33083</v>
+        <v>0.330199</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001465281165272836</v>
+        <v>0.00030584</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.44701</v>
+        <v>0.09235</v>
       </c>
       <c r="M9" t="n">
-        <v>95005283434.57567</v>
+        <v>95006507400.98915</v>
       </c>
       <c r="N9" t="n">
-        <v>95005306953.93657</v>
+        <v>95006511248.69714</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.021</v>
+        <v>1.026</v>
       </c>
       <c r="F10" t="n">
-        <v>24524808341</v>
+        <v>24736365007</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>19109939</v>
+        <v>118926237</v>
       </c>
       <c r="I10" t="n">
-        <v>1.053</v>
+        <v>1.055</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00369969</v>
+        <v>0.00539556</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3616</v>
+        <v>0.52864</v>
       </c>
       <c r="M10" t="n">
-        <v>24018021967.488</v>
+        <v>24108358660.328</v>
       </c>
       <c r="N10" t="n">
-        <v>24018021967.488</v>
+        <v>24108358660.328</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1165.72</v>
+        <v>1305.87</v>
       </c>
       <c r="F11" t="n">
-        <v>19815688253</v>
+        <v>22179713592</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>681324082</v>
+        <v>1129005884</v>
       </c>
       <c r="I11" t="n">
-        <v>1167.47</v>
+        <v>1323.04</v>
       </c>
       <c r="J11" t="n">
-        <v>1110.62</v>
+        <v>1175.52</v>
       </c>
       <c r="K11" t="n">
-        <v>35.27</v>
+        <v>79.69</v>
       </c>
       <c r="L11" t="n">
-        <v>3.08281</v>
+        <v>6.49931</v>
       </c>
       <c r="M11" t="n">
-        <v>16995679.8530448</v>
+        <v>16997331.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>16996439.2280448</v>
+        <v>16998273.6030448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>79.22</v>
+        <v>80.53</v>
       </c>
       <c r="F12" t="n">
-        <v>17612551486</v>
+        <v>17899703279</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>554739423</v>
+        <v>804087874</v>
       </c>
       <c r="I12" t="n">
-        <v>79.69</v>
+        <v>82.23</v>
       </c>
       <c r="J12" t="n">
-        <v>77.56999999999999</v>
+        <v>79.25</v>
       </c>
       <c r="K12" t="n">
-        <v>0.17247</v>
+        <v>-0.8254749271948896</v>
       </c>
       <c r="L12" t="n">
-        <v>0.11026</v>
+        <v>-1.01465</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07961500000000001</v>
+        <v>0.08199099999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>12447095005</v>
+        <v>12820096260</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>321009717</v>
+        <v>484870012</v>
       </c>
       <c r="I13" t="n">
-        <v>0.079957</v>
+        <v>0.082555</v>
       </c>
       <c r="J13" t="n">
-        <v>0.078486</v>
+        <v>0.080065</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00052291</v>
+        <v>0.00066966</v>
       </c>
       <c r="L13" t="n">
-        <v>0.59559</v>
+        <v>0.82347</v>
       </c>
       <c r="M13" t="n">
-        <v>156396942864.2343</v>
+        <v>156409352864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156402662864.2343</v>
+        <v>156416602864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>609.11</v>
+        <v>606.5599999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>11462504879</v>
+        <v>11399956352</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>174355982</v>
+        <v>240951337</v>
       </c>
       <c r="I14" t="n">
-        <v>616.5599999999999</v>
+        <v>625.37</v>
       </c>
       <c r="J14" t="n">
-        <v>583.67</v>
+        <v>570.4400000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>13.5</v>
+        <v>-1.620665057405631</v>
       </c>
       <c r="L14" t="n">
-        <v>2.26053</v>
+        <v>-0.26648</v>
       </c>
       <c r="M14" t="n">
-        <v>18820082.89960967</v>
+        <v>18820523.88535966</v>
       </c>
       <c r="N14" t="n">
-        <v>18820082.89960967</v>
+        <v>18820523.88535966</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10024386456</v>
+        <v>10018842396</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>63843542</v>
+        <v>144603442</v>
       </c>
       <c r="I15" t="n">
         <v>1.002</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999852</v>
+        <v>0.99878</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00024095</v>
+        <v>7.994e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.01625</v>
+        <v>0.007990000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>10022132246.0431</v>
+        <v>10013339652.00038</v>
       </c>
       <c r="N15" t="n">
-        <v>10022132246.0431</v>
+        <v>10013339652.00038</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.86</v>
+        <v>81.84</v>
       </c>
       <c r="F16" t="n">
-        <v>9482614455</v>
+        <v>9718380996</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>96281711</v>
+        <v>109664029</v>
       </c>
       <c r="I16" t="n">
-        <v>80.48999999999999</v>
+        <v>82.02</v>
       </c>
       <c r="J16" t="n">
-        <v>79.3</v>
+        <v>80.39</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.3093209300650983</v>
+        <v>0.775909</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.47426</v>
+        <v>0.9571499999999999</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.03</v>
+        <v>12.35</v>
       </c>
       <c r="F17" t="n">
-        <v>9222393383</v>
+        <v>9468996830</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>219380223</v>
+        <v>264479134</v>
       </c>
       <c r="I17" t="n">
-        <v>12.1</v>
+        <v>12.51</v>
       </c>
       <c r="J17" t="n">
-        <v>11.84</v>
+        <v>12.09</v>
       </c>
       <c r="K17" t="n">
-        <v>0.052295</v>
+        <v>0.02464098</v>
       </c>
       <c r="L17" t="n">
-        <v>0.3517</v>
+        <v>0.19993</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,267 +1539,267 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.029999999999999</v>
+        <v>0.224666</v>
       </c>
       <c r="F18" t="n">
-        <v>8304067361</v>
+        <v>8434666885</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>160599</v>
+        <v>288462732</v>
       </c>
       <c r="I18" t="n">
-        <v>9.039999999999999</v>
+        <v>0.227318</v>
       </c>
       <c r="J18" t="n">
-        <v>9.01</v>
+        <v>0.219776</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01609306665198673</v>
+        <v>0.00083715</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.17868</v>
+        <v>0.37401</v>
       </c>
       <c r="M18" t="n">
-        <v>919857851.9</v>
+        <v>37559424049.89742</v>
       </c>
       <c r="N18" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.217535</v>
+        <v>9.02</v>
       </c>
       <c r="F19" t="n">
-        <v>8169171075</v>
+        <v>8294491296</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>213664084</v>
+        <v>42783</v>
       </c>
       <c r="I19" t="n">
-        <v>0.219528</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.21468</v>
+        <v>9.02</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00034401</v>
+        <v>-0.009864146250500028</v>
       </c>
       <c r="L19" t="n">
-        <v>0.10037</v>
+        <v>-0.10927</v>
       </c>
       <c r="M19" t="n">
-        <v>37559424049.89742</v>
+        <v>919857851.9</v>
       </c>
       <c r="N19" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O19" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.009045879999999999</v>
+        <v>5.18</v>
       </c>
       <c r="F20" t="n">
-        <v>6412380430</v>
+        <v>6774703352</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>16646992</v>
+        <v>1400923570</v>
       </c>
       <c r="I20" t="n">
-        <v>0.009157449999999999</v>
+        <v>5.27</v>
       </c>
       <c r="J20" t="n">
-        <v>0.00815956</v>
+        <v>4.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.2656012075308e-05</v>
+        <v>0.259606</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.57721</v>
+        <v>5.27833</v>
       </c>
       <c r="M20" t="n">
-        <v>709252781589.0068</v>
+        <v>1309561659</v>
       </c>
       <c r="N20" t="n">
-        <v>1142406025446.552</v>
+        <v>1309561693</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01946402</v>
+        <v>20.44</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261020T135539Z-4fe15e</t>
+          <t>20261021T141209Z-227dcf</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Rain</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.176519</v>
+        <v>0.00920665</v>
       </c>
       <c r="F21" t="n">
-        <v>6213910300</v>
+        <v>6546503425</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>98797071</v>
+        <v>22581871</v>
       </c>
       <c r="I21" t="n">
-        <v>0.178101</v>
+        <v>0.00956691</v>
       </c>
       <c r="J21" t="n">
-        <v>0.17504</v>
+        <v>0.008797630000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.000142818662488553</v>
+        <v>1.322e-05</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.09701</v>
+        <v>0.14382</v>
       </c>
       <c r="M21" t="n">
-        <v>35208646793.51079</v>
+        <v>710830195080.5627</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786837.39717</v>
+        <v>1142406020597.705</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>0.01946402</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2026-08-25T19:53:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-20T13:54:48.000Z</t>
+          <t>2026-10-21T14:10:55.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>83782</v>
+        <v>81572</v>
       </c>
       <c r="F2" t="n">
-        <v>1683463864161</v>
+        <v>1639953831278</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>27810620427</v>
+        <v>38089870448</v>
       </c>
       <c r="I2" t="n">
-        <v>83827</v>
+        <v>84808</v>
       </c>
       <c r="J2" t="n">
-        <v>82226</v>
+        <v>81331</v>
       </c>
       <c r="K2" t="n">
-        <v>817.78</v>
+        <v>-2188.189196955354</v>
       </c>
       <c r="L2" t="n">
-        <v>0.98571</v>
+        <v>-2.61243</v>
       </c>
       <c r="M2" t="n">
-        <v>20098843</v>
+        <v>20101921</v>
       </c>
       <c r="N2" t="n">
-        <v>20099025</v>
+        <v>20101921</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2467.29</v>
+        <v>2404.2</v>
       </c>
       <c r="F3" t="n">
-        <v>301341587294</v>
+        <v>293805229186</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>13229514090</v>
+        <v>12875591137</v>
       </c>
       <c r="I3" t="n">
-        <v>2489.69</v>
+        <v>2518.86</v>
       </c>
       <c r="J3" t="n">
-        <v>2423.99</v>
+        <v>2394.86</v>
       </c>
       <c r="K3" t="n">
-        <v>18.67</v>
+        <v>-63.58853910244761</v>
       </c>
       <c r="L3" t="n">
-        <v>0.76241</v>
+        <v>-2.57674</v>
       </c>
       <c r="M3" t="n">
-        <v>122149509.8558182</v>
+        <v>122152451.8360052</v>
       </c>
       <c r="N3" t="n">
-        <v>122149509.8558182</v>
+        <v>122152451.8360052</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.998991</v>
+        <v>0.999251</v>
       </c>
       <c r="F4" t="n">
-        <v>182757891307</v>
+        <v>182689798743</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52212332851</v>
+        <v>60569021710</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999326</v>
+        <v>0.999519</v>
       </c>
       <c r="J4" t="n">
-        <v>0.9989170000000001</v>
+        <v>0.999039</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000196251266625036</v>
+        <v>0.00025633</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.01964</v>
+        <v>0.02566</v>
       </c>
       <c r="M4" t="n">
-        <v>182942080919.1835</v>
+        <v>182831230623.759</v>
       </c>
       <c r="N4" t="n">
-        <v>188409029385.2262</v>
+        <v>188298179099.2962</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>744.28</v>
+        <v>732.74</v>
       </c>
       <c r="F5" t="n">
-        <v>97860915798</v>
+        <v>96374736598</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>758599828</v>
+        <v>782296271</v>
       </c>
       <c r="I5" t="n">
-        <v>749.03</v>
+        <v>750.97</v>
       </c>
       <c r="J5" t="n">
-        <v>731.01</v>
+        <v>729.92</v>
       </c>
       <c r="K5" t="n">
-        <v>5.73</v>
+        <v>-11.61705748492932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.77571</v>
+        <v>-1.56068</v>
       </c>
       <c r="M5" t="n">
-        <v>131511970.91</v>
+        <v>131511918.93</v>
       </c>
       <c r="N5" t="n">
-        <v>131511970.91</v>
+        <v>131511918.93</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="F6" t="n">
-        <v>85724373277</v>
+        <v>83608896730</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1568317957</v>
+        <v>1830162390</v>
       </c>
       <c r="I6" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02668706</v>
+        <v>-0.03415134251471419</v>
       </c>
       <c r="L6" t="n">
-        <v>2.00476</v>
+        <v>-2.51473</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999404</v>
+        <v>0.999699</v>
       </c>
       <c r="F7" t="n">
-        <v>72050433910</v>
+        <v>72422463290</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>17320888874</v>
+        <v>14753634391</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999865</v>
+        <v>0.99985</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9982569999999999</v>
+        <v>0.999443</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.00043945887705088</v>
+        <v>0.00029433</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.04395</v>
+        <v>0.02945</v>
       </c>
       <c r="M7" t="n">
-        <v>72093698793.09575</v>
+        <v>72445468118.76578</v>
       </c>
       <c r="N7" t="n">
-        <v>72078358359.18475</v>
+        <v>72457324980.41069</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106.51</v>
+        <v>104.82</v>
       </c>
       <c r="F8" t="n">
-        <v>62766639454</v>
+        <v>61833825336</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2645967014</v>
+        <v>2825373209</v>
       </c>
       <c r="I8" t="n">
-        <v>107.73</v>
+        <v>109.08</v>
       </c>
       <c r="J8" t="n">
-        <v>105.03</v>
+        <v>103.55</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5101782287419354</v>
+        <v>-1.679224884064851</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.47669</v>
+        <v>-1.57673</v>
       </c>
       <c r="M8" t="n">
-        <v>589548647.5300552</v>
+        <v>589604429.4459344</v>
       </c>
       <c r="N8" t="n">
-        <v>636150962.0157574</v>
+        <v>636212474.9384301</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33147</v>
+        <v>0.330247</v>
       </c>
       <c r="F9" t="n">
-        <v>31499294319</v>
+        <v>31382558737</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>324164813</v>
+        <v>344295630</v>
       </c>
       <c r="I9" t="n">
-        <v>0.331681</v>
+        <v>0.333105</v>
       </c>
       <c r="J9" t="n">
-        <v>0.330199</v>
+        <v>0.329962</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00030584</v>
+        <v>-0.001261836252519355</v>
       </c>
       <c r="L9" t="n">
-        <v>0.09235</v>
+        <v>-0.38063</v>
       </c>
       <c r="M9" t="n">
-        <v>95006507400.98915</v>
+        <v>95007902278.38824</v>
       </c>
       <c r="N9" t="n">
-        <v>95006511248.69714</v>
+        <v>95007906674.41174</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.026</v>
+        <v>1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>24736365007</v>
+        <v>25696975084</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>118926237</v>
+        <v>65415850</v>
       </c>
       <c r="I10" t="n">
-        <v>1.055</v>
+        <v>1.035</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
+        <v>1.008</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00539556</v>
+        <v>0.00338754</v>
       </c>
       <c r="L10" t="n">
-        <v>0.52864</v>
+        <v>0.33015</v>
       </c>
       <c r="M10" t="n">
-        <v>24108358660.328</v>
+        <v>24961635873.278</v>
       </c>
       <c r="N10" t="n">
-        <v>24108358660.328</v>
+        <v>24961635873.278</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1305.87</v>
+        <v>1252.05</v>
       </c>
       <c r="F11" t="n">
-        <v>22179713592</v>
+        <v>21314492209</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1129005884</v>
+        <v>1365641372</v>
       </c>
       <c r="I11" t="n">
-        <v>1323.04</v>
+        <v>1367.63</v>
       </c>
       <c r="J11" t="n">
-        <v>1175.52</v>
+        <v>1227.03</v>
       </c>
       <c r="K11" t="n">
-        <v>79.69</v>
+        <v>-52.82248712633873</v>
       </c>
       <c r="L11" t="n">
-        <v>6.49931</v>
+        <v>-4.04809</v>
       </c>
       <c r="M11" t="n">
-        <v>16997331.4155448</v>
+        <v>17000109.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>16998273.6030448</v>
+        <v>17000109.5405448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>80.53</v>
+        <v>78.38</v>
       </c>
       <c r="F12" t="n">
-        <v>17899703279</v>
+        <v>17445257068</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>804087874</v>
+        <v>841819264</v>
       </c>
       <c r="I12" t="n">
-        <v>82.23</v>
+        <v>82.39</v>
       </c>
       <c r="J12" t="n">
-        <v>79.25</v>
+        <v>77.73</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.8254749271948896</v>
+        <v>-2.124107408167404</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.01465</v>
+        <v>-2.63844</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.08199099999999999</v>
+        <v>0.079585</v>
       </c>
       <c r="F13" t="n">
-        <v>12820096260</v>
+        <v>12454553873</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>484870012</v>
+        <v>627616674</v>
       </c>
       <c r="I13" t="n">
-        <v>0.082555</v>
+        <v>0.08371099999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.080065</v>
+        <v>0.078802</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00066966</v>
+        <v>-0.002398414333372498</v>
       </c>
       <c r="L13" t="n">
-        <v>0.82347</v>
+        <v>-2.92549</v>
       </c>
       <c r="M13" t="n">
-        <v>156409352864.2343</v>
+        <v>156430792864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156416602864.2343</v>
+        <v>156430792864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>606.5599999999999</v>
+        <v>625.46</v>
       </c>
       <c r="F14" t="n">
-        <v>11399956352</v>
+        <v>11768254559</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>240951337</v>
+        <v>250633046</v>
       </c>
       <c r="I14" t="n">
-        <v>625.37</v>
+        <v>656.3099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>570.4400000000001</v>
+        <v>594.3</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.620665057405631</v>
+        <v>20.36</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.26648</v>
+        <v>3.36507</v>
       </c>
       <c r="M14" t="n">
-        <v>18820523.88535966</v>
+        <v>18820987.07496451</v>
       </c>
       <c r="N14" t="n">
-        <v>18820523.88535966</v>
+        <v>18820987.07496451</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10018842396</v>
+        <v>10019517079</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>144603442</v>
+        <v>177595735</v>
       </c>
       <c r="I15" t="n">
-        <v>1.002</v>
+        <v>1.001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.99878</v>
+        <v>0.998405</v>
       </c>
       <c r="K15" t="n">
-        <v>7.994e-05</v>
+        <v>-0.000357428804759419</v>
       </c>
       <c r="L15" t="n">
-        <v>0.007990000000000001</v>
+        <v>-0.03572</v>
       </c>
       <c r="M15" t="n">
-        <v>10013339652.00038</v>
+        <v>10018807472.00808</v>
       </c>
       <c r="N15" t="n">
-        <v>10013339652.00038</v>
+        <v>10018807472.00808</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>81.84</v>
+        <v>79.22</v>
       </c>
       <c r="F16" t="n">
-        <v>9718380996</v>
+        <v>9411734322</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>109664029</v>
+        <v>110220815</v>
       </c>
       <c r="I16" t="n">
-        <v>82.02</v>
+        <v>83</v>
       </c>
       <c r="J16" t="n">
-        <v>80.39</v>
+        <v>78.98999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.775909</v>
+        <v>-2.614758174356709</v>
       </c>
       <c r="L16" t="n">
-        <v>0.9571499999999999</v>
+        <v>-3.19528</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.35</v>
+        <v>12.05</v>
       </c>
       <c r="F17" t="n">
-        <v>9468996830</v>
+        <v>9242868559</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>264479134</v>
+        <v>257677899</v>
       </c>
       <c r="I17" t="n">
-        <v>12.51</v>
+        <v>12.8</v>
       </c>
       <c r="J17" t="n">
-        <v>12.09</v>
+        <v>11.99</v>
       </c>
       <c r="K17" t="n">
-        <v>0.02464098</v>
+        <v>-0.3039280529180477</v>
       </c>
       <c r="L17" t="n">
-        <v>0.19993</v>
+        <v>-2.46013</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,144 +1539,144 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>cardano</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ada</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.224666</v>
+        <v>9.01</v>
       </c>
       <c r="F18" t="n">
-        <v>8434666885</v>
+        <v>8291844897</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>288462732</v>
+        <v>21401</v>
       </c>
       <c r="I18" t="n">
-        <v>0.227318</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>0.219776</v>
+        <v>9.01</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00083715</v>
+        <v>-0.002685112756767083</v>
       </c>
       <c r="L18" t="n">
-        <v>0.37401</v>
+        <v>-0.02978</v>
       </c>
       <c r="M18" t="n">
-        <v>37559424049.89742</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>45000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>3.09</v>
+        <v>10.61</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-09-01T22:00:10.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>cardano</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>ada</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>9.02</v>
+        <v>0.2165</v>
       </c>
       <c r="F19" t="n">
-        <v>8294491296</v>
+        <v>8135531249</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>42783</v>
+        <v>298035031</v>
       </c>
       <c r="I19" t="n">
-        <v>9.050000000000001</v>
+        <v>0.230254</v>
       </c>
       <c r="J19" t="n">
-        <v>9.02</v>
+        <v>0.214379</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.009864146250500028</v>
+        <v>-0.008140664042258855</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.10927</v>
+        <v>-3.62385</v>
       </c>
       <c r="M19" t="n">
-        <v>919857851.9</v>
+        <v>37565404869.05737</v>
       </c>
       <c r="N19" t="n">
-        <v>985239504</v>
+        <v>45000000000</v>
       </c>
       <c r="O19" t="n">
-        <v>10.61</v>
+        <v>3.09</v>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-09-01T22:00:10.000Z</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.18</v>
+        <v>5.02</v>
       </c>
       <c r="F20" t="n">
-        <v>6774703352</v>
+        <v>6579112434</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>1400923570</v>
+        <v>861668660</v>
       </c>
       <c r="I20" t="n">
-        <v>5.27</v>
+        <v>5.44</v>
       </c>
       <c r="J20" t="n">
-        <v>4.77</v>
+        <v>4.91</v>
       </c>
       <c r="K20" t="n">
-        <v>0.259606</v>
+        <v>-0.1522175663309753</v>
       </c>
       <c r="L20" t="n">
-        <v>5.27833</v>
+        <v>-2.94239</v>
       </c>
       <c r="M20" t="n">
-        <v>1309561659</v>
+        <v>1309640634</v>
       </c>
       <c r="N20" t="n">
-        <v>1309561693</v>
+        <v>1309640652</v>
       </c>
       <c r="O20" t="n">
         <v>20.44</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261021T141209Z-227dcf</t>
+          <t>20261022T140949Z-8578a2</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Rain</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.00920665</v>
+        <v>0.17773</v>
       </c>
       <c r="F21" t="n">
-        <v>6546503425</v>
+        <v>6261696093</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>22581871</v>
+        <v>122842073</v>
       </c>
       <c r="I21" t="n">
-        <v>0.00956691</v>
+        <v>0.186904</v>
       </c>
       <c r="J21" t="n">
-        <v>0.008797630000000001</v>
+        <v>0.176936</v>
       </c>
       <c r="K21" t="n">
-        <v>1.322e-05</v>
+        <v>-0.005842954321204852</v>
       </c>
       <c r="L21" t="n">
-        <v>0.14382</v>
+        <v>-3.1829</v>
       </c>
       <c r="M21" t="n">
-        <v>710830195080.5627</v>
+        <v>35224551930.82242</v>
       </c>
       <c r="N21" t="n">
-        <v>1142406020597.705</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01946402</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2026-08-25T19:53:00.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-21T14:10:55.000Z</t>
+          <t>2026-10-22T14:08:51.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81572</v>
+        <v>81854</v>
       </c>
       <c r="F2" t="n">
-        <v>1639953831278</v>
+        <v>1645054339158</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>38089870448</v>
+        <v>25037878787</v>
       </c>
       <c r="I2" t="n">
-        <v>84808</v>
+        <v>81912</v>
       </c>
       <c r="J2" t="n">
-        <v>81331</v>
+        <v>80989</v>
       </c>
       <c r="K2" t="n">
-        <v>-2188.189196955354</v>
+        <v>515.24</v>
       </c>
       <c r="L2" t="n">
-        <v>-2.61243</v>
+        <v>0.61892</v>
       </c>
       <c r="M2" t="n">
-        <v>20101921</v>
+        <v>20102287</v>
       </c>
       <c r="N2" t="n">
-        <v>20101921</v>
+        <v>20102381</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2404.2</v>
+        <v>2409.9</v>
       </c>
       <c r="F3" t="n">
-        <v>293805229186</v>
+        <v>294277775377</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>12875591137</v>
+        <v>11511892774</v>
       </c>
       <c r="I3" t="n">
-        <v>2518.86</v>
+        <v>2413.57</v>
       </c>
       <c r="J3" t="n">
-        <v>2394.86</v>
+        <v>2372.55</v>
       </c>
       <c r="K3" t="n">
-        <v>-63.58853910244761</v>
+        <v>13.42</v>
       </c>
       <c r="L3" t="n">
-        <v>-2.57674</v>
+        <v>0.5234799999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>122152451.8360052</v>
+        <v>122155364.9391704</v>
       </c>
       <c r="N3" t="n">
-        <v>122152451.8360052</v>
+        <v>122155364.9391704</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999251</v>
+        <v>0.998988</v>
       </c>
       <c r="F4" t="n">
-        <v>182689798743</v>
+        <v>182537859724</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>60569021710</v>
+        <v>44738466951</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999519</v>
+        <v>0.999366</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999039</v>
+        <v>0.998763</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00025633</v>
+        <v>-0.000282344574371152</v>
       </c>
       <c r="L4" t="n">
-        <v>0.02566</v>
+        <v>-0.03354</v>
       </c>
       <c r="M4" t="n">
-        <v>182831230623.759</v>
+        <v>182726130617.5043</v>
       </c>
       <c r="N4" t="n">
-        <v>188298179099.2962</v>
+        <v>188193079099.2962</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>732.74</v>
+        <v>746.89</v>
       </c>
       <c r="F5" t="n">
-        <v>96374736598</v>
+        <v>98196827734</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>782296271</v>
+        <v>776390888</v>
       </c>
       <c r="I5" t="n">
-        <v>750.97</v>
+        <v>748.17</v>
       </c>
       <c r="J5" t="n">
-        <v>729.92</v>
+        <v>726.86</v>
       </c>
       <c r="K5" t="n">
-        <v>-11.61705748492932</v>
+        <v>15.68</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.56068</v>
+        <v>2.1055</v>
       </c>
       <c r="M5" t="n">
-        <v>131511918.93</v>
+        <v>131511871.75</v>
       </c>
       <c r="N5" t="n">
-        <v>131511918.93</v>
+        <v>131511871.75</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.32</v>
       </c>
       <c r="F6" t="n">
-        <v>83608896730</v>
+        <v>83214755830</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1830162390</v>
+        <v>1294823660</v>
       </c>
       <c r="I6" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="J6" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.03415134251471419</v>
+        <v>-0.002701103874918731</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.51473</v>
+        <v>-0.25246</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999699</v>
+        <v>0.999549</v>
       </c>
       <c r="F7" t="n">
-        <v>72422463290</v>
+        <v>71912492920</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>14753634391</v>
+        <v>11101664437</v>
       </c>
       <c r="I7" t="n">
-        <v>0.99985</v>
+        <v>0.999753</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999443</v>
+        <v>0.999368</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00029433</v>
+        <v>-0.000131953782633643</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02945</v>
+        <v>-0.01822</v>
       </c>
       <c r="M7" t="n">
-        <v>72445468118.76578</v>
+        <v>71946451102.79054</v>
       </c>
       <c r="N7" t="n">
-        <v>72457324980.41069</v>
+        <v>72038993044.92058</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.82</v>
+        <v>104.86</v>
       </c>
       <c r="F8" t="n">
-        <v>61833825336</v>
+        <v>61791327165</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2825373209</v>
+        <v>2054485967</v>
       </c>
       <c r="I8" t="n">
-        <v>109.08</v>
+        <v>105.13</v>
       </c>
       <c r="J8" t="n">
-        <v>103.55</v>
+        <v>102.97</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.679224884064851</v>
+        <v>0.395399</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.57673</v>
+        <v>0.34272</v>
       </c>
       <c r="M8" t="n">
-        <v>589604429.4459344</v>
+        <v>589653232.69521</v>
       </c>
       <c r="N8" t="n">
-        <v>636212474.9384301</v>
+        <v>636273659.9485152</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330247</v>
+        <v>0.330133</v>
       </c>
       <c r="F9" t="n">
-        <v>31382558737</v>
+        <v>31357020226</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>344295630</v>
+        <v>342542982</v>
       </c>
       <c r="I9" t="n">
-        <v>0.333105</v>
+        <v>0.330748</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329962</v>
+        <v>0.327599</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001261836252519355</v>
+        <v>-0.000363687318418404</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.38063</v>
+        <v>-0.13658</v>
       </c>
       <c r="M9" t="n">
-        <v>95007902278.38824</v>
+        <v>95007901157.49394</v>
       </c>
       <c r="N9" t="n">
-        <v>95007906674.41174</v>
+        <v>95009334576.03865</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.029</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>25696975084</v>
+        <v>26163984058</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>65415850</v>
+        <v>142609078</v>
       </c>
       <c r="I10" t="n">
-        <v>1.035</v>
+        <v>1.041</v>
       </c>
       <c r="J10" t="n">
-        <v>1.008</v>
+        <v>1.019</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00338754</v>
+        <v>-0.002079342705535003</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33015</v>
+        <v>-0.1965</v>
       </c>
       <c r="M10" t="n">
-        <v>24961635873.278</v>
+        <v>25467283024.529</v>
       </c>
       <c r="N10" t="n">
-        <v>24961635873.278</v>
+        <v>25467283024.529</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1252.05</v>
+        <v>1241.51</v>
       </c>
       <c r="F11" t="n">
-        <v>21314492209</v>
+        <v>21076247981</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>1365641372</v>
+        <v>813179233</v>
       </c>
       <c r="I11" t="n">
-        <v>1367.63</v>
+        <v>1258.67</v>
       </c>
       <c r="J11" t="n">
-        <v>1227.03</v>
+        <v>1187.54</v>
       </c>
       <c r="K11" t="n">
-        <v>-52.82248712633873</v>
+        <v>-1.059418664697432</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.04809</v>
+        <v>-0.10778</v>
       </c>
       <c r="M11" t="n">
-        <v>17000109.5405448</v>
+        <v>17000534.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>17000109.5405448</v>
+        <v>17001828.2905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.38</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17445257068</v>
+        <v>17341041583</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>841819264</v>
+        <v>767814560</v>
       </c>
       <c r="I12" t="n">
-        <v>82.39</v>
+        <v>78.83</v>
       </c>
       <c r="J12" t="n">
-        <v>77.73</v>
+        <v>76.8</v>
       </c>
       <c r="K12" t="n">
-        <v>-2.124107408167404</v>
+        <v>0.054426</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.63844</v>
+        <v>0.014</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.079585</v>
+        <v>0.080225</v>
       </c>
       <c r="F13" t="n">
-        <v>12454553873</v>
+        <v>12546183691</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>627616674</v>
+        <v>512613281</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08371099999999999</v>
+        <v>0.08056000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.078802</v>
+        <v>0.07806100000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002398414333372498</v>
+        <v>0.00092616</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.92549</v>
+        <v>1.14277</v>
       </c>
       <c r="M13" t="n">
-        <v>156430792864.2343</v>
+        <v>156433972864.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156430792864.2343</v>
+        <v>156443892864.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>625.46</v>
+        <v>606.75</v>
       </c>
       <c r="F14" t="n">
-        <v>11768254559</v>
+        <v>11423484687</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>250633046</v>
+        <v>131502892</v>
       </c>
       <c r="I14" t="n">
-        <v>656.3099999999999</v>
+        <v>628.71</v>
       </c>
       <c r="J14" t="n">
-        <v>594.3</v>
+        <v>588.46</v>
       </c>
       <c r="K14" t="n">
-        <v>20.36</v>
+        <v>-20.30272762252298</v>
       </c>
       <c r="L14" t="n">
-        <v>3.36507</v>
+        <v>-3.1656</v>
       </c>
       <c r="M14" t="n">
-        <v>18820987.07496451</v>
+        <v>18821377.0702075</v>
       </c>
       <c r="N14" t="n">
-        <v>18820987.07496451</v>
+        <v>18821377.0702075</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10019517079</v>
+        <v>10078678645</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>177595735</v>
+        <v>106831580</v>
       </c>
       <c r="I15" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.998405</v>
+        <v>0.998779</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000357428804759419</v>
+        <v>1.097e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.03572</v>
+        <v>-0.00284</v>
       </c>
       <c r="M15" t="n">
-        <v>10018807472.00808</v>
+        <v>10078420114.57474</v>
       </c>
       <c r="N15" t="n">
-        <v>10018807472.00808</v>
+        <v>10078420114.57474</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.22</v>
+        <v>79.41</v>
       </c>
       <c r="F16" t="n">
-        <v>9411734322</v>
+        <v>9430446322</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>110220815</v>
+        <v>86376311</v>
       </c>
       <c r="I16" t="n">
-        <v>83</v>
+        <v>79.54000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>78.98999999999999</v>
+        <v>78.58</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.614758174356709</v>
+        <v>0.422486</v>
       </c>
       <c r="L16" t="n">
-        <v>-3.19528</v>
+        <v>0.50641</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1503,25 +1503,25 @@
         <v>12.05</v>
       </c>
       <c r="F17" t="n">
-        <v>9242868559</v>
+        <v>9238946506</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>257677899</v>
+        <v>230039528</v>
       </c>
       <c r="I17" t="n">
-        <v>12.8</v>
+        <v>12.25</v>
       </c>
       <c r="J17" t="n">
-        <v>11.99</v>
+        <v>11.85</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.3039280529180477</v>
+        <v>0.0538</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.46013</v>
+        <v>0.41419</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.01</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8291844897</v>
+        <v>8306114847</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>21401</v>
+        <v>149821</v>
       </c>
       <c r="I18" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>9.01</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.002685112756767083</v>
+        <v>0.01506055</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.02978</v>
+        <v>0.16434</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.2165</v>
+        <v>0.217207</v>
       </c>
       <c r="F19" t="n">
-        <v>8135531249</v>
+        <v>8155313244</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>298035031</v>
+        <v>260192278</v>
       </c>
       <c r="I19" t="n">
-        <v>0.230254</v>
+        <v>0.217257</v>
       </c>
       <c r="J19" t="n">
-        <v>0.214379</v>
+        <v>0.210308</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.008140664042258855</v>
+        <v>0.00187202</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.62385</v>
+        <v>0.798</v>
       </c>
       <c r="M19" t="n">
         <v>37565404869.05737</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5.02</v>
+        <v>4.93</v>
       </c>
       <c r="F20" t="n">
-        <v>6579112434</v>
+        <v>6461713988</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>861668660</v>
+        <v>566198987</v>
       </c>
       <c r="I20" t="n">
-        <v>5.44</v>
+        <v>5.06</v>
       </c>
       <c r="J20" t="n">
-        <v>4.91</v>
+        <v>4.83</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1522175663309753</v>
+        <v>-0.04498326141389697</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.94239</v>
+        <v>-0.83068</v>
       </c>
       <c r="M20" t="n">
-        <v>1309640634</v>
+        <v>1309719226</v>
       </c>
       <c r="N20" t="n">
-        <v>1309640652</v>
+        <v>1309719252</v>
       </c>
       <c r="O20" t="n">
         <v>20.44</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261022T140949Z-8578a2</t>
+          <t>20261023T135348Z-8fad73</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,31 +1760,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.17773</v>
+        <v>0.17672</v>
       </c>
       <c r="F21" t="n">
-        <v>6261696093</v>
+        <v>6220391012</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>122842073</v>
+        <v>98896533</v>
       </c>
       <c r="I21" t="n">
-        <v>0.186904</v>
+        <v>0.17869</v>
       </c>
       <c r="J21" t="n">
-        <v>0.176936</v>
+        <v>0.174723</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.005842954321204852</v>
+        <v>-0.000277282600367024</v>
       </c>
       <c r="L21" t="n">
-        <v>-3.1829</v>
+        <v>-0.1787</v>
       </c>
       <c r="M21" t="n">
-        <v>35224551930.82242</v>
+        <v>35210795482.03242</v>
       </c>
       <c r="N21" t="n">
         <v>50001786837.39717</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-22T14:08:51.000Z</t>
+          <t>2026-10-23T13:52:55.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81854</v>
+        <v>80734</v>
       </c>
       <c r="F2" t="n">
-        <v>1645054339158</v>
+        <v>1623022754152</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>25037878787</v>
+        <v>21739991094</v>
       </c>
       <c r="I2" t="n">
-        <v>81912</v>
+        <v>81939</v>
       </c>
       <c r="J2" t="n">
-        <v>80989</v>
+        <v>80410</v>
       </c>
       <c r="K2" t="n">
-        <v>515.24</v>
+        <v>-943.7766598456074</v>
       </c>
       <c r="L2" t="n">
-        <v>0.61892</v>
+        <v>-1.15549</v>
       </c>
       <c r="M2" t="n">
-        <v>20102287</v>
+        <v>20102809</v>
       </c>
       <c r="N2" t="n">
-        <v>20102381</v>
+        <v>20102837</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2409.9</v>
+        <v>2368.72</v>
       </c>
       <c r="F3" t="n">
-        <v>294277775377</v>
+        <v>289370949780</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11511892774</v>
+        <v>7973965344</v>
       </c>
       <c r="I3" t="n">
-        <v>2413.57</v>
+        <v>2413.74</v>
       </c>
       <c r="J3" t="n">
-        <v>2372.55</v>
+        <v>2353.51</v>
       </c>
       <c r="K3" t="n">
-        <v>13.42</v>
+        <v>-31.70884346880712</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5234799999999999</v>
+        <v>-1.32096</v>
       </c>
       <c r="M3" t="n">
-        <v>122155364.9391704</v>
+        <v>122158316.6661137</v>
       </c>
       <c r="N3" t="n">
-        <v>122155364.9391704</v>
+        <v>122158316.6661137</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.998988</v>
+        <v>0.999108</v>
       </c>
       <c r="F4" t="n">
-        <v>182537859724</v>
+        <v>182481542747</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>44738466951</v>
+        <v>37627547349</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999366</v>
+        <v>0.99926</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998763</v>
+        <v>0.998897</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.000282344574371152</v>
+        <v>6.886e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.03354</v>
+        <v>0.00689</v>
       </c>
       <c r="M4" t="n">
-        <v>182726130617.5043</v>
+        <v>182638997379.4458</v>
       </c>
       <c r="N4" t="n">
-        <v>188193079099.2962</v>
+        <v>188105945865.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>746.89</v>
+        <v>731.85</v>
       </c>
       <c r="F5" t="n">
-        <v>98196827734</v>
+        <v>96252186287</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>776390888</v>
+        <v>814354752</v>
       </c>
       <c r="I5" t="n">
-        <v>748.17</v>
+        <v>749.39</v>
       </c>
       <c r="J5" t="n">
-        <v>726.86</v>
+        <v>730.38</v>
       </c>
       <c r="K5" t="n">
-        <v>15.68</v>
+        <v>-13.24813718169003</v>
       </c>
       <c r="L5" t="n">
-        <v>2.1055</v>
+        <v>-1.77804</v>
       </c>
       <c r="M5" t="n">
-        <v>131511871.75</v>
+        <v>131511793.31</v>
       </c>
       <c r="N5" t="n">
-        <v>131511871.75</v>
+        <v>131511793.31</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="F6" t="n">
-        <v>83214755830</v>
+        <v>81127493031</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1294823660</v>
+        <v>1207303881</v>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.002701103874918731</v>
+        <v>-0.03179473411131628</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.25246</v>
+        <v>-2.41446</v>
       </c>
       <c r="M6" t="n">
         <v>63129671205</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999549</v>
+        <v>0.9996699999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>71912492920</v>
+        <v>71623799474</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>11101664437</v>
+        <v>8636181243</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999753</v>
+        <v>0.999989</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999368</v>
+        <v>0.9991679999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000131953782633643</v>
+        <v>9.865e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.01822</v>
+        <v>0.00987</v>
       </c>
       <c r="M7" t="n">
-        <v>71946451102.79054</v>
+        <v>71645467571.8607</v>
       </c>
       <c r="N7" t="n">
-        <v>72038993044.92058</v>
+        <v>71649512847.53479</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>104.86</v>
+        <v>101.56</v>
       </c>
       <c r="F8" t="n">
-        <v>61791327165</v>
+        <v>59891486073</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2054485967</v>
+        <v>2234848656</v>
       </c>
       <c r="I8" t="n">
-        <v>105.13</v>
+        <v>105.05</v>
       </c>
       <c r="J8" t="n">
-        <v>102.97</v>
+        <v>101.07</v>
       </c>
       <c r="K8" t="n">
-        <v>0.395399</v>
+        <v>-2.806623815400911</v>
       </c>
       <c r="L8" t="n">
-        <v>0.34272</v>
+        <v>-2.68919</v>
       </c>
       <c r="M8" t="n">
-        <v>589653232.69521</v>
+        <v>589708746.3112797</v>
       </c>
       <c r="N8" t="n">
-        <v>636273659.9485152</v>
+        <v>636334864.3185364</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330133</v>
+        <v>0.330204</v>
       </c>
       <c r="F9" t="n">
-        <v>31357020226</v>
+        <v>31374714243</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>342542982</v>
+        <v>255579707</v>
       </c>
       <c r="I9" t="n">
-        <v>0.330748</v>
+        <v>0.330302</v>
       </c>
       <c r="J9" t="n">
-        <v>0.327599</v>
+        <v>0.32921</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000363687318418404</v>
+        <v>0.00024503</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.13658</v>
+        <v>0.07426000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>95007901157.49394</v>
+        <v>95011001950.76335</v>
       </c>
       <c r="N9" t="n">
-        <v>95009334576.03865</v>
+        <v>95011055471.28934</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.027</v>
+        <v>1.021</v>
       </c>
       <c r="F10" t="n">
-        <v>26163984058</v>
+        <v>26024879876</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>142609078</v>
+        <v>70521515</v>
       </c>
       <c r="I10" t="n">
-        <v>1.041</v>
+        <v>1.028</v>
       </c>
       <c r="J10" t="n">
-        <v>1.019</v>
+        <v>1.021</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.002079342705535003</v>
+        <v>-0.006604316946325683</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.1965</v>
+        <v>-0.64274</v>
       </c>
       <c r="M10" t="n">
-        <v>25467283024.529</v>
+        <v>25492230658.569</v>
       </c>
       <c r="N10" t="n">
-        <v>25467283024.529</v>
+        <v>25492230658.569</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1241.51</v>
+        <v>1162.61</v>
       </c>
       <c r="F11" t="n">
-        <v>21076247981</v>
+        <v>19760961761</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>813179233</v>
+        <v>715482024</v>
       </c>
       <c r="I11" t="n">
-        <v>1258.67</v>
+        <v>1255.61</v>
       </c>
       <c r="J11" t="n">
-        <v>1187.54</v>
+        <v>1142.06</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.059418664697432</v>
+        <v>-69.00105632225109</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.10778</v>
+        <v>-5.60249</v>
       </c>
       <c r="M11" t="n">
-        <v>17000534.5405448</v>
+        <v>17003447.0405448</v>
       </c>
       <c r="N11" t="n">
-        <v>17001828.2905448</v>
+        <v>17003539.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>77.98999999999999</v>
+        <v>75.81999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17341041583</v>
+        <v>16866607324</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>767814560</v>
+        <v>797292837</v>
       </c>
       <c r="I12" t="n">
-        <v>78.83</v>
+        <v>78.69</v>
       </c>
       <c r="J12" t="n">
-        <v>76.8</v>
+        <v>75.13</v>
       </c>
       <c r="K12" t="n">
-        <v>0.054426</v>
+        <v>-1.905600851022427</v>
       </c>
       <c r="L12" t="n">
-        <v>0.014</v>
+        <v>-2.45165</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.080225</v>
+        <v>0.077593</v>
       </c>
       <c r="F13" t="n">
-        <v>12546183691</v>
+        <v>12140211703</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>512613281</v>
+        <v>408109296</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08056000000000001</v>
+        <v>0.080383</v>
       </c>
       <c r="J13" t="n">
-        <v>0.07806100000000001</v>
+        <v>0.076866</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00092616</v>
+        <v>-0.002592231899674266</v>
       </c>
       <c r="L13" t="n">
-        <v>1.14277</v>
+        <v>-3.2328</v>
       </c>
       <c r="M13" t="n">
-        <v>156433972864.2343</v>
+        <v>156456492863.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156443892864.2343</v>
+        <v>156457162863.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>606.75</v>
+        <v>594.9</v>
       </c>
       <c r="F14" t="n">
-        <v>11423484687</v>
+        <v>11194618420</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>131502892</v>
+        <v>109494588</v>
       </c>
       <c r="I14" t="n">
-        <v>628.71</v>
+        <v>611.47</v>
       </c>
       <c r="J14" t="n">
-        <v>588.46</v>
+        <v>564.87</v>
       </c>
       <c r="K14" t="n">
-        <v>-20.30272762252298</v>
+        <v>-12.94515818090179</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.1656</v>
+        <v>-2.1297</v>
       </c>
       <c r="M14" t="n">
-        <v>18821377.0702075</v>
+        <v>18821799.45734001</v>
       </c>
       <c r="N14" t="n">
-        <v>18821377.0702075</v>
+        <v>18821799.45734001</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10078678645</v>
+        <v>10051239108</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>106831580</v>
+        <v>89937225</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.998779</v>
+        <v>0.999331</v>
       </c>
       <c r="K15" t="n">
-        <v>1.097e-05</v>
+        <v>9.411000000000001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.00284</v>
+        <v>0.00941</v>
       </c>
       <c r="M15" t="n">
-        <v>10078420114.57474</v>
+        <v>10049312190.4542</v>
       </c>
       <c r="N15" t="n">
-        <v>10078420114.57474</v>
+        <v>10049312190.4542</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>79.41</v>
+        <v>78.3</v>
       </c>
       <c r="F16" t="n">
-        <v>9430446322</v>
+        <v>9301705471</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>86376311</v>
+        <v>80710690</v>
       </c>
       <c r="I16" t="n">
-        <v>79.54000000000001</v>
+        <v>79.55</v>
       </c>
       <c r="J16" t="n">
-        <v>78.58</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>0.422486</v>
+        <v>-0.9903175786374732</v>
       </c>
       <c r="L16" t="n">
-        <v>0.50641</v>
+        <v>-1.2489</v>
       </c>
       <c r="M16" t="n">
         <v>118786640</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>12.05</v>
+        <v>11.63</v>
       </c>
       <c r="F17" t="n">
-        <v>9238946506</v>
+        <v>8917953536</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>230039528</v>
+        <v>201490923</v>
       </c>
       <c r="I17" t="n">
-        <v>12.25</v>
+        <v>12.08</v>
       </c>
       <c r="J17" t="n">
-        <v>11.85</v>
+        <v>11.52</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0538</v>
+        <v>-0.4355623266983457</v>
       </c>
       <c r="L17" t="n">
-        <v>0.41419</v>
+        <v>-3.61033</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.029999999999999</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8306114847</v>
+        <v>8314128661</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>149821</v>
+        <v>140677</v>
       </c>
       <c r="I18" t="n">
-        <v>9.039999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="J18" t="n">
-        <v>8.960000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.01506055</v>
+        <v>0.00435588</v>
       </c>
       <c r="L18" t="n">
-        <v>0.16434</v>
+        <v>0.04822</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.217207</v>
+        <v>0.208673</v>
       </c>
       <c r="F19" t="n">
-        <v>8155313244</v>
+        <v>7840146416</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>260192278</v>
+        <v>239279833</v>
       </c>
       <c r="I19" t="n">
-        <v>0.217257</v>
+        <v>0.218299</v>
       </c>
       <c r="J19" t="n">
-        <v>0.210308</v>
+        <v>0.206396</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00187202</v>
+        <v>-0.007795653602053254</v>
       </c>
       <c r="L19" t="n">
-        <v>0.798</v>
+        <v>-3.60129</v>
       </c>
       <c r="M19" t="n">
         <v>37565404869.05737</v>
@@ -1669,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.93</v>
+        <v>0.170609</v>
       </c>
       <c r="F20" t="n">
-        <v>6461713988</v>
+        <v>6010035265</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>566198987</v>
+        <v>103284604</v>
       </c>
       <c r="I20" t="n">
-        <v>5.06</v>
+        <v>0.177437</v>
       </c>
       <c r="J20" t="n">
-        <v>4.83</v>
+        <v>0.168682</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.04498326141389697</v>
+        <v>-0.006155792497655688</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.83068</v>
+        <v>-3.48248</v>
       </c>
       <c r="M20" t="n">
-        <v>1309719226</v>
+        <v>35227385849.28918</v>
       </c>
       <c r="N20" t="n">
-        <v>1309719252</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O20" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261023T135348Z-8fad73</t>
+          <t>20261024T125831Z-3c1cd6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.17672</v>
+        <v>4.48</v>
       </c>
       <c r="F21" t="n">
-        <v>6220391012</v>
+        <v>5861619870</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>98896533</v>
+        <v>634081385</v>
       </c>
       <c r="I21" t="n">
-        <v>0.17869</v>
+        <v>4.97</v>
       </c>
       <c r="J21" t="n">
-        <v>0.174723</v>
+        <v>4.43</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.000277282600367024</v>
+        <v>-0.4701145786829377</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.1787</v>
+        <v>-9.506500000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>35210795482.03242</v>
+        <v>1309822139</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786837.39717</v>
+        <v>1309822181</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-23T13:52:55.000Z</t>
+          <t>2026-10-24T12:56:52.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80734</v>
+        <v>80307</v>
       </c>
       <c r="F2" t="n">
-        <v>1623022754152</v>
+        <v>1614459663111</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>21739991094</v>
+        <v>19204146100</v>
       </c>
       <c r="I2" t="n">
-        <v>81939</v>
+        <v>80949</v>
       </c>
       <c r="J2" t="n">
-        <v>80410</v>
+        <v>79263</v>
       </c>
       <c r="K2" t="n">
-        <v>-943.7766598456074</v>
+        <v>-365.0108296831022</v>
       </c>
       <c r="L2" t="n">
-        <v>-1.15549</v>
+        <v>-0.45262</v>
       </c>
       <c r="M2" t="n">
-        <v>20102809</v>
+        <v>20103303</v>
       </c>
       <c r="N2" t="n">
-        <v>20102837</v>
+        <v>20103303</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2368.72</v>
+        <v>2331.75</v>
       </c>
       <c r="F3" t="n">
-        <v>289370949780</v>
+        <v>284861381667</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>7973965344</v>
+        <v>9249778384</v>
       </c>
       <c r="I3" t="n">
-        <v>2413.74</v>
+        <v>2368.07</v>
       </c>
       <c r="J3" t="n">
-        <v>2353.51</v>
+        <v>2286.76</v>
       </c>
       <c r="K3" t="n">
-        <v>-31.70884346880712</v>
+        <v>-33.43268191229436</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.32096</v>
+        <v>-1.40156</v>
       </c>
       <c r="M3" t="n">
-        <v>122158316.6661137</v>
+        <v>122161274.5109022</v>
       </c>
       <c r="N3" t="n">
-        <v>122158316.6661137</v>
+        <v>122161274.5109022</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999108</v>
+        <v>0.9990790000000001</v>
       </c>
       <c r="F4" t="n">
-        <v>182481542747</v>
+        <v>182455328621</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>37627547349</v>
+        <v>33420602808</v>
       </c>
       <c r="I4" t="n">
-        <v>0.99926</v>
+        <v>0.999356</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998897</v>
+        <v>0.999001</v>
       </c>
       <c r="K4" t="n">
-        <v>6.886e-05</v>
+        <v>-3.9916113325211e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00689</v>
+        <v>-0.00439</v>
       </c>
       <c r="M4" t="n">
-        <v>182638997379.4458</v>
+        <v>182624397367.7578</v>
       </c>
       <c r="N4" t="n">
-        <v>188105945865.3062</v>
+        <v>188091345865.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>731.85</v>
+        <v>736.86</v>
       </c>
       <c r="F5" t="n">
-        <v>96252186287</v>
+        <v>96906470558</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>814354752</v>
+        <v>836975053</v>
       </c>
       <c r="I5" t="n">
-        <v>749.39</v>
+        <v>747.79</v>
       </c>
       <c r="J5" t="n">
-        <v>730.38</v>
+        <v>717.91</v>
       </c>
       <c r="K5" t="n">
-        <v>-13.24813718169003</v>
+        <v>5.9</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.77804</v>
+        <v>0.81558</v>
       </c>
       <c r="M5" t="n">
-        <v>131511793.31</v>
+        <v>131511734.35</v>
       </c>
       <c r="N5" t="n">
-        <v>131511793.31</v>
+        <v>131511734.35</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,31 +788,31 @@
         <v>1.29</v>
       </c>
       <c r="F6" t="n">
-        <v>81127493031</v>
+        <v>82031151715</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1207303881</v>
+        <v>1312871035</v>
       </c>
       <c r="I6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.03179473411131628</v>
+        <v>0.01132634</v>
       </c>
       <c r="L6" t="n">
-        <v>-2.41446</v>
+        <v>0.89412</v>
       </c>
       <c r="M6" t="n">
-        <v>63129671205</v>
+        <v>63351197653</v>
       </c>
       <c r="N6" t="n">
-        <v>99985607990</v>
+        <v>99985589443</v>
       </c>
       <c r="O6" t="n">
         <v>3.65</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9996699999999999</v>
+        <v>0.999596</v>
       </c>
       <c r="F7" t="n">
-        <v>71623799474</v>
+        <v>71563510970</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>8636181243</v>
+        <v>6497971915</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999989</v>
+        <v>0.999775</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9991679999999999</v>
+        <v>0.999497</v>
       </c>
       <c r="K7" t="n">
-        <v>9.865e-05</v>
+        <v>-8.126178266554301e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00987</v>
+        <v>-0.008370000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>71645467571.8607</v>
+        <v>71592884796.22005</v>
       </c>
       <c r="N7" t="n">
-        <v>71649512847.53479</v>
+        <v>71599000910.64632</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101.56</v>
+        <v>100.89</v>
       </c>
       <c r="F8" t="n">
-        <v>59891486073</v>
+        <v>59494169716</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2234848656</v>
+        <v>2064596483</v>
       </c>
       <c r="I8" t="n">
-        <v>105.05</v>
+        <v>102.63</v>
       </c>
       <c r="J8" t="n">
-        <v>101.07</v>
+        <v>98.81</v>
       </c>
       <c r="K8" t="n">
-        <v>-2.806623815400911</v>
+        <v>-0.438700018753579</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.68919</v>
+        <v>-0.42619</v>
       </c>
       <c r="M8" t="n">
-        <v>589708746.3112797</v>
+        <v>589764193.9488363</v>
       </c>
       <c r="N8" t="n">
-        <v>636334864.3185364</v>
+        <v>636395966.9091337</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330204</v>
+        <v>0.328823</v>
       </c>
       <c r="F9" t="n">
-        <v>31374714243</v>
+        <v>31233304436</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>255579707</v>
+        <v>233761709</v>
       </c>
       <c r="I9" t="n">
-        <v>0.330302</v>
+        <v>0.330015</v>
       </c>
       <c r="J9" t="n">
-        <v>0.32921</v>
+        <v>0.328407</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00024503</v>
+        <v>-0.001307707033394001</v>
       </c>
       <c r="L9" t="n">
-        <v>0.07426000000000001</v>
+        <v>-0.40637</v>
       </c>
       <c r="M9" t="n">
-        <v>95011001950.76335</v>
+        <v>95011335458.92464</v>
       </c>
       <c r="N9" t="n">
-        <v>95011055471.28934</v>
+        <v>95013154016.99425</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.021</v>
+        <v>1.056</v>
       </c>
       <c r="F10" t="n">
-        <v>26024879876</v>
+        <v>27000066134</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>70521515</v>
+        <v>101981</v>
       </c>
       <c r="I10" t="n">
-        <v>1.028</v>
+        <v>1.063</v>
       </c>
       <c r="J10" t="n">
-        <v>1.021</v>
+        <v>1.016</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.006604316946325683</v>
+        <v>0.03441566</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.64274</v>
+        <v>3.36879</v>
       </c>
       <c r="M10" t="n">
-        <v>25492230658.569</v>
+        <v>25568520111.869</v>
       </c>
       <c r="N10" t="n">
-        <v>25492230658.569</v>
+        <v>25568520111.869</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:14:38.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1162.61</v>
+        <v>1208.62</v>
       </c>
       <c r="F11" t="n">
-        <v>19760961761</v>
+        <v>20544867620</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>715482024</v>
+        <v>644907029</v>
       </c>
       <c r="I11" t="n">
-        <v>1255.61</v>
+        <v>1223.01</v>
       </c>
       <c r="J11" t="n">
-        <v>1142.06</v>
+        <v>1120.66</v>
       </c>
       <c r="K11" t="n">
-        <v>-69.00105632225109</v>
+        <v>49.66</v>
       </c>
       <c r="L11" t="n">
-        <v>-5.60249</v>
+        <v>4.30041</v>
       </c>
       <c r="M11" t="n">
-        <v>17003447.0405448</v>
+        <v>17004061.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>17003539.2280448</v>
+        <v>17005365.7905448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>75.81999999999999</v>
+        <v>76.55</v>
       </c>
       <c r="F12" t="n">
-        <v>16866607324</v>
+        <v>17031983044</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>797292837</v>
+        <v>585799238</v>
       </c>
       <c r="I12" t="n">
-        <v>78.69</v>
+        <v>76.81999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>75.13</v>
+        <v>74.53</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.905600851022427</v>
+        <v>0.804046</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.45165</v>
+        <v>1.14605</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.077593</v>
+        <v>0.07671500000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>12140211703</v>
+        <v>12004350556</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>408109296</v>
+        <v>515011723</v>
       </c>
       <c r="I13" t="n">
-        <v>0.080383</v>
+        <v>0.077935</v>
       </c>
       <c r="J13" t="n">
-        <v>0.076866</v>
+        <v>0.074965</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.002592231899674266</v>
+        <v>-0.00077416143468241</v>
       </c>
       <c r="L13" t="n">
-        <v>-3.2328</v>
+        <v>-0.96351</v>
       </c>
       <c r="M13" t="n">
-        <v>156456492863.2343</v>
+        <v>156461052863.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156457162863.2343</v>
+        <v>156471092863.2343</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>594.9</v>
+        <v>605.09</v>
       </c>
       <c r="F14" t="n">
-        <v>11194618420</v>
+        <v>11386969628</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>109494588</v>
+        <v>101901752</v>
       </c>
       <c r="I14" t="n">
-        <v>611.47</v>
+        <v>616.38</v>
       </c>
       <c r="J14" t="n">
-        <v>564.87</v>
+        <v>586.74</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.94515818090179</v>
+        <v>12.19</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.1297</v>
+        <v>2.04844</v>
       </c>
       <c r="M14" t="n">
-        <v>18821799.45734001</v>
+        <v>18822247.05399578</v>
       </c>
       <c r="N14" t="n">
-        <v>18821799.45734001</v>
+        <v>18822247.05399578</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>10051239108</v>
+        <v>9997651385</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>89937225</v>
+        <v>137327020</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999331</v>
+        <v>0.999843</v>
       </c>
       <c r="K15" t="n">
-        <v>9.411000000000001e-05</v>
+        <v>7.966000000000001e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00941</v>
+        <v>0.00739</v>
       </c>
       <c r="M15" t="n">
-        <v>10049312190.4542</v>
+        <v>9996148645.844257</v>
       </c>
       <c r="N15" t="n">
-        <v>10049312190.4542</v>
+        <v>9996148645.844257</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>78.3</v>
+        <v>77.34999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9301705471</v>
+        <v>9182827350</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>80710690</v>
+        <v>87881667</v>
       </c>
       <c r="I16" t="n">
-        <v>79.55</v>
+        <v>78.3</v>
       </c>
       <c r="J16" t="n">
-        <v>78.01000000000001</v>
+        <v>76.23</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9903175786374732</v>
+        <v>-0.9044494619347461</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.2489</v>
+        <v>-1.15101</v>
       </c>
       <c r="M16" t="n">
-        <v>118786640</v>
+        <v>118720983</v>
       </c>
       <c r="N16" t="n">
-        <v>293356139</v>
+        <v>293290482</v>
       </c>
       <c r="O16" t="n">
         <v>87.91</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.63</v>
+        <v>11.37</v>
       </c>
       <c r="F17" t="n">
-        <v>8917953536</v>
+        <v>8716633333</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>201490923</v>
+        <v>227835446</v>
       </c>
       <c r="I17" t="n">
-        <v>12.08</v>
+        <v>11.63</v>
       </c>
       <c r="J17" t="n">
-        <v>11.52</v>
+        <v>11.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.4355623266983457</v>
+        <v>-0.2403310280865867</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.61033</v>
+        <v>-2.06676</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.039999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="F18" t="n">
-        <v>8314128661</v>
+        <v>8270772045</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>140677</v>
+        <v>21977</v>
       </c>
       <c r="I18" t="n">
-        <v>9.07</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>8.869999999999999</v>
+        <v>8.99</v>
       </c>
       <c r="K18" t="n">
-        <v>0.00435588</v>
+        <v>-0.0479614351344928</v>
       </c>
       <c r="L18" t="n">
-        <v>0.04822</v>
+        <v>-0.5311399999999999</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.208673</v>
+        <v>0.204217</v>
       </c>
       <c r="F19" t="n">
-        <v>7840146416</v>
+        <v>7671658920</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>239279833</v>
+        <v>237391127</v>
       </c>
       <c r="I19" t="n">
-        <v>0.218299</v>
+        <v>0.209157</v>
       </c>
       <c r="J19" t="n">
-        <v>0.206396</v>
+        <v>0.200756</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.007795653602053254</v>
+        <v>-0.003526402062732137</v>
       </c>
       <c r="L19" t="n">
-        <v>-3.60129</v>
+        <v>-1.65502</v>
       </c>
       <c r="M19" t="n">
         <v>37565404869.05737</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.170609</v>
+        <v>0.168764</v>
       </c>
       <c r="F20" t="n">
-        <v>6010035265</v>
+        <v>5945248129</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>103284604</v>
+        <v>84125902</v>
       </c>
       <c r="I20" t="n">
-        <v>0.177437</v>
+        <v>0.172234</v>
       </c>
       <c r="J20" t="n">
-        <v>0.168682</v>
+        <v>0.166669</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.006155792497655688</v>
+        <v>-0.001593718464056815</v>
       </c>
       <c r="L20" t="n">
-        <v>-3.48248</v>
+        <v>-0.93953</v>
       </c>
       <c r="M20" t="n">
-        <v>35227385849.28918</v>
+        <v>35227380300.13435</v>
       </c>
       <c r="N20" t="n">
         <v>50001786837.39717</v>
@@ -1734,14 +1734,14 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261024T125831Z-3c1cd6</t>
+          <t>20261025T132516Z-760526</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1760,34 +1760,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.48</v>
+        <v>4.45</v>
       </c>
       <c r="F21" t="n">
-        <v>5861619870</v>
+        <v>5834799257</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>634081385</v>
+        <v>576511937</v>
       </c>
       <c r="I21" t="n">
-        <v>4.97</v>
+        <v>4.52</v>
       </c>
       <c r="J21" t="n">
-        <v>4.43</v>
+        <v>4.28</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.4701145786829377</v>
+        <v>0.02207731</v>
       </c>
       <c r="L21" t="n">
-        <v>-9.506500000000001</v>
+        <v>0.48394</v>
       </c>
       <c r="M21" t="n">
-        <v>1309822139</v>
+        <v>1309898726</v>
       </c>
       <c r="N21" t="n">
-        <v>1309822181</v>
+        <v>1309898756</v>
       </c>
       <c r="O21" t="n">
         <v>20.44</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-24T12:56:52.000Z</t>
+          <t>2026-10-25T13:23:48.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80307</v>
+        <v>80476</v>
       </c>
       <c r="F2" t="n">
-        <v>1614459663111</v>
+        <v>1617516797125</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>19204146100</v>
+        <v>26210543957</v>
       </c>
       <c r="I2" t="n">
-        <v>80949</v>
+        <v>80825</v>
       </c>
       <c r="J2" t="n">
-        <v>79263</v>
+        <v>79332</v>
       </c>
       <c r="K2" t="n">
-        <v>-365.0108296831022</v>
+        <v>-52.86693244088383</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.45262</v>
+        <v>-0.06565</v>
       </c>
       <c r="M2" t="n">
-        <v>20103303</v>
+        <v>20103596</v>
       </c>
       <c r="N2" t="n">
-        <v>20103303</v>
+        <v>20103868</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2331.75</v>
+        <v>2331.55</v>
       </c>
       <c r="F3" t="n">
-        <v>284861381667</v>
+        <v>284715101514</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9249778384</v>
+        <v>9967805761</v>
       </c>
       <c r="I3" t="n">
-        <v>2368.07</v>
+        <v>2359.75</v>
       </c>
       <c r="J3" t="n">
-        <v>2286.76</v>
+        <v>2293.2</v>
       </c>
       <c r="K3" t="n">
-        <v>-33.43268191229436</v>
+        <v>-6.041907954147518</v>
       </c>
       <c r="L3" t="n">
-        <v>-1.40156</v>
+        <v>-0.25847</v>
       </c>
       <c r="M3" t="n">
-        <v>122161274.5109022</v>
+        <v>122164245.2834002</v>
       </c>
       <c r="N3" t="n">
-        <v>122161274.5109022</v>
+        <v>122164245.2834002</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9990790000000001</v>
+        <v>0.99873</v>
       </c>
       <c r="F4" t="n">
-        <v>182455328621</v>
+        <v>182258804487</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>33420602808</v>
+        <v>42481667414</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999356</v>
+        <v>0.999465</v>
       </c>
       <c r="J4" t="n">
-        <v>0.999001</v>
+        <v>0.998636</v>
       </c>
       <c r="K4" t="n">
-        <v>-3.9916113325211e-05</v>
+        <v>-0.00032524802894307</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00439</v>
+        <v>-0.03256</v>
       </c>
       <c r="M4" t="n">
-        <v>182624397367.7578</v>
+        <v>182493797362.4195</v>
       </c>
       <c r="N4" t="n">
-        <v>188091345865.3062</v>
+        <v>187960745865.3062</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>736.86</v>
+        <v>744.24</v>
       </c>
       <c r="F5" t="n">
-        <v>96906470558</v>
+        <v>97848454897</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>836975053</v>
+        <v>776403042</v>
       </c>
       <c r="I5" t="n">
-        <v>747.79</v>
+        <v>744.77</v>
       </c>
       <c r="J5" t="n">
-        <v>717.91</v>
+        <v>731.99</v>
       </c>
       <c r="K5" t="n">
-        <v>5.9</v>
+        <v>3.46</v>
       </c>
       <c r="L5" t="n">
-        <v>0.81558</v>
+        <v>0.46719</v>
       </c>
       <c r="M5" t="n">
-        <v>131511734.35</v>
+        <v>131511658.44</v>
       </c>
       <c r="N5" t="n">
-        <v>131511734.35</v>
+        <v>131511658.44</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="F6" t="n">
-        <v>82031151715</v>
+        <v>82315740317</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1312871035</v>
+        <v>1296717706</v>
       </c>
       <c r="I6" t="n">
         <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01132634</v>
+        <v>0.00265805</v>
       </c>
       <c r="L6" t="n">
-        <v>0.89412</v>
+        <v>0.20501</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999596</v>
+        <v>0.999341</v>
       </c>
       <c r="F7" t="n">
-        <v>71563510970</v>
+        <v>71024815536</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>6497971915</v>
+        <v>10558902720</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999775</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999497</v>
+        <v>0.999434</v>
       </c>
       <c r="K7" t="n">
-        <v>-8.126178266554301e-05</v>
+        <v>-0.000285177055205477</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.008370000000000001</v>
+        <v>-0.02853</v>
       </c>
       <c r="M7" t="n">
-        <v>71592884796.22005</v>
+        <v>71073652364.31392</v>
       </c>
       <c r="N7" t="n">
-        <v>71599000910.64632</v>
+        <v>71199404861.60213</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.89</v>
+        <v>102.18</v>
       </c>
       <c r="F8" t="n">
-        <v>59494169716</v>
+        <v>60240758473</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2064596483</v>
+        <v>2177735176</v>
       </c>
       <c r="I8" t="n">
-        <v>102.63</v>
+        <v>102.06</v>
       </c>
       <c r="J8" t="n">
-        <v>98.81</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.438700018753579</v>
+        <v>0.796108</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.42619</v>
+        <v>0.78525</v>
       </c>
       <c r="M8" t="n">
-        <v>589764193.9488363</v>
+        <v>589819571.9737056</v>
       </c>
       <c r="N8" t="n">
-        <v>636395966.9091337</v>
+        <v>636457026.7801988</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.328823</v>
+        <v>0.33098</v>
       </c>
       <c r="F9" t="n">
-        <v>31233304436</v>
+        <v>31443000944</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>233761709</v>
+        <v>329389203</v>
       </c>
       <c r="I9" t="n">
-        <v>0.330015</v>
+        <v>0.331294</v>
       </c>
       <c r="J9" t="n">
-        <v>0.328407</v>
+        <v>0.329022</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.001307707033394001</v>
+        <v>0.00192432</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.40637</v>
+        <v>0.5848</v>
       </c>
       <c r="M9" t="n">
-        <v>95011335458.92464</v>
+        <v>95014985713.76654</v>
       </c>
       <c r="N9" t="n">
-        <v>95013154016.99425</v>
+        <v>95014988604.06955</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,30 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.056</v>
+        <v>1.044</v>
       </c>
       <c r="F10" t="n">
-        <v>27000066134</v>
+        <v>26718415567</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>101981</v>
+        <v>50049076</v>
       </c>
       <c r="I10" t="n">
-        <v>1.063</v>
+        <v>1.048</v>
       </c>
       <c r="J10" t="n">
-        <v>1.016</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0.03441566</v>
-      </c>
-      <c r="L10" t="n">
-        <v>3.36879</v>
-      </c>
+        <v>1.001</v>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
       <c r="M10" t="n">
-        <v>25568520111.869</v>
+        <v>25586557407.249</v>
       </c>
       <c r="N10" t="n">
-        <v>25568520111.869</v>
+        <v>25586557407.249</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1080,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-25T13:14:38.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1106,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1208.62</v>
+        <v>1251.53</v>
       </c>
       <c r="F11" t="n">
-        <v>20544867620</v>
+        <v>21256147493</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>644907029</v>
+        <v>829422802</v>
       </c>
       <c r="I11" t="n">
-        <v>1223.01</v>
+        <v>1250.88</v>
       </c>
       <c r="J11" t="n">
-        <v>1120.66</v>
+        <v>1177.73</v>
       </c>
       <c r="K11" t="n">
-        <v>49.66</v>
+        <v>36.44</v>
       </c>
       <c r="L11" t="n">
-        <v>4.30041</v>
+        <v>2.99937</v>
       </c>
       <c r="M11" t="n">
         <v>17004061.1030448</v>
       </c>
       <c r="N11" t="n">
-        <v>17005365.7905448</v>
+        <v>17007392.3530448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1145,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1171,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>76.55</v>
+        <v>78.34</v>
       </c>
       <c r="F12" t="n">
-        <v>17031983044</v>
+        <v>17422271729</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>585799238</v>
+        <v>781569659</v>
       </c>
       <c r="I12" t="n">
-        <v>76.81999999999999</v>
+        <v>78.2</v>
       </c>
       <c r="J12" t="n">
-        <v>74.53</v>
+        <v>74.92</v>
       </c>
       <c r="K12" t="n">
-        <v>0.804046</v>
+        <v>1.26</v>
       </c>
       <c r="L12" t="n">
-        <v>1.14605</v>
+        <v>1.63698</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1214,14 +1210,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1236,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.07671500000000001</v>
+        <v>0.077901</v>
       </c>
       <c r="F13" t="n">
-        <v>12004350556</v>
+        <v>12184761736</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>515011723</v>
+        <v>430708937</v>
       </c>
       <c r="I13" t="n">
-        <v>0.077935</v>
+        <v>0.077767</v>
       </c>
       <c r="J13" t="n">
-        <v>0.074965</v>
+        <v>0.075962</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.00077416143468241</v>
+        <v>0.00081374</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.96351</v>
+        <v>1.05561</v>
       </c>
       <c r="M13" t="n">
         <v>156461052863.2343</v>
       </c>
       <c r="N13" t="n">
-        <v>156471092863.2343</v>
+        <v>156486812860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1275,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1301,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>605.09</v>
+        <v>591.36</v>
       </c>
       <c r="F14" t="n">
-        <v>11386969628</v>
+        <v>11127529393</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>101901752</v>
+        <v>144859318</v>
       </c>
       <c r="I14" t="n">
-        <v>616.38</v>
+        <v>605.62</v>
       </c>
       <c r="J14" t="n">
-        <v>586.74</v>
+        <v>582.8200000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>12.19</v>
+        <v>-12.98980672562504</v>
       </c>
       <c r="L14" t="n">
-        <v>2.04844</v>
+        <v>-2.14938</v>
       </c>
       <c r="M14" t="n">
-        <v>18822247.05399578</v>
+        <v>18822731.84223136</v>
       </c>
       <c r="N14" t="n">
-        <v>18822247.05399578</v>
+        <v>18822731.84223136</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1340,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1366,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0.999718</v>
       </c>
       <c r="F15" t="n">
-        <v>9997651385</v>
+        <v>9971602809</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>137327020</v>
+        <v>201764725</v>
       </c>
       <c r="I15" t="n">
-        <v>1.001</v>
+        <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999843</v>
+        <v>0.998918</v>
       </c>
       <c r="K15" t="n">
-        <v>7.966000000000001e-05</v>
+        <v>-0.000416938398470457</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00739</v>
+        <v>-0.04169</v>
       </c>
       <c r="M15" t="n">
-        <v>9996148645.844257</v>
+        <v>9974742982.816563</v>
       </c>
       <c r="N15" t="n">
-        <v>9996148645.844257</v>
+        <v>9974742982.816563</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1405,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1431,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.34999999999999</v>
+        <v>77.31999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9182827350</v>
+        <v>9178743545</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>87881667</v>
+        <v>141905088</v>
       </c>
       <c r="I16" t="n">
-        <v>78.3</v>
+        <v>77.92</v>
       </c>
       <c r="J16" t="n">
-        <v>76.23</v>
+        <v>76.37</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.9044494619347461</v>
+        <v>-0.2463835791570688</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.15101</v>
+        <v>-0.31765</v>
       </c>
       <c r="M16" t="n">
         <v>118720983</v>
@@ -1474,14 +1470,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1496,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.37</v>
+        <v>11.57</v>
       </c>
       <c r="F17" t="n">
-        <v>8716633333</v>
+        <v>8873179239</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>227835446</v>
+        <v>262333003</v>
       </c>
       <c r="I17" t="n">
-        <v>11.63</v>
+        <v>11.56</v>
       </c>
       <c r="J17" t="n">
         <v>11.26</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.2403310280865867</v>
+        <v>0.177965</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.06676</v>
+        <v>1.56169</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1535,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1561,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>8.99</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8270772045</v>
+        <v>8308529865</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>21977</v>
+        <v>115883</v>
       </c>
       <c r="I18" t="n">
         <v>9.039999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>8.99</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.0479614351344928</v>
+        <v>0.04033454</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.5311399999999999</v>
+        <v>0.44857</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1600,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1626,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.204217</v>
+        <v>0.20706</v>
       </c>
       <c r="F19" t="n">
-        <v>7671658920</v>
+        <v>7775775935</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>237391127</v>
+        <v>231670427</v>
       </c>
       <c r="I19" t="n">
-        <v>0.209157</v>
+        <v>0.206733</v>
       </c>
       <c r="J19" t="n">
-        <v>0.200756</v>
+        <v>0.200505</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.003526402062732137</v>
+        <v>0.00211243</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.65502</v>
+        <v>1.03072</v>
       </c>
       <c r="M19" t="n">
         <v>37565404869.05737</v>
@@ -1669,137 +1665,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.168764</v>
+        <v>4.61</v>
       </c>
       <c r="F20" t="n">
-        <v>5945248129</v>
+        <v>6032426776</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>84125902</v>
+        <v>576868480</v>
       </c>
       <c r="I20" t="n">
-        <v>0.172234</v>
+        <v>4.69</v>
       </c>
       <c r="J20" t="n">
-        <v>0.166669</v>
+        <v>4.43</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001593718464056815</v>
+        <v>0.122392</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.93953</v>
+        <v>2.72856</v>
       </c>
       <c r="M20" t="n">
-        <v>35227380300.13435</v>
+        <v>1310001700</v>
       </c>
       <c r="N20" t="n">
-        <v>50001786837.39717</v>
+        <v>1310001727</v>
       </c>
       <c r="O20" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261025T132516Z-760526</t>
+          <t>20261026T153406Z-67835f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.45</v>
+        <v>0.170173</v>
       </c>
       <c r="F21" t="n">
-        <v>5834799257</v>
+        <v>5997065322</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>576511937</v>
+        <v>92318557</v>
       </c>
       <c r="I21" t="n">
-        <v>4.52</v>
+        <v>0.170306</v>
       </c>
       <c r="J21" t="n">
-        <v>4.28</v>
+        <v>0.166566</v>
       </c>
       <c r="K21" t="n">
-        <v>0.02207731</v>
+        <v>0.00105458</v>
       </c>
       <c r="L21" t="n">
-        <v>0.48394</v>
+        <v>0.62357</v>
       </c>
       <c r="M21" t="n">
-        <v>1309898726</v>
+        <v>35227372279.74623</v>
       </c>
       <c r="N21" t="n">
-        <v>1309898756</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-25T13:23:48.000Z</t>
+          <t>2026-10-26T15:32:47.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80476</v>
+        <v>80278</v>
       </c>
       <c r="F2" t="n">
-        <v>1617516797125</v>
+        <v>1613335588139</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>26210543957</v>
+        <v>24002048860</v>
       </c>
       <c r="I2" t="n">
-        <v>80825</v>
+        <v>80680</v>
       </c>
       <c r="J2" t="n">
-        <v>79332</v>
+        <v>79416</v>
       </c>
       <c r="K2" t="n">
-        <v>-52.86693244088383</v>
+        <v>61.31</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.06565</v>
+        <v>0.07643</v>
       </c>
       <c r="M2" t="n">
-        <v>20103596</v>
+        <v>20104350</v>
       </c>
       <c r="N2" t="n">
-        <v>20103868</v>
+        <v>20104350</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2331.55</v>
+        <v>2332.27</v>
       </c>
       <c r="F3" t="n">
-        <v>284715101514</v>
+        <v>284782021136</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9967805761</v>
+        <v>8384290560</v>
       </c>
       <c r="I3" t="n">
-        <v>2359.75</v>
+        <v>2338.49</v>
       </c>
       <c r="J3" t="n">
-        <v>2293.2</v>
+        <v>2295.57</v>
       </c>
       <c r="K3" t="n">
-        <v>-6.041907954147518</v>
+        <v>10.93</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.25847</v>
+        <v>0.47081</v>
       </c>
       <c r="M3" t="n">
-        <v>122164245.2834002</v>
+        <v>122167205.1116396</v>
       </c>
       <c r="N3" t="n">
-        <v>122164245.2834002</v>
+        <v>122167205.1116396</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,28 +655,28 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.99873</v>
+        <v>0.998777</v>
       </c>
       <c r="F4" t="n">
-        <v>182258804487</v>
+        <v>182272088699</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>42481667414</v>
+        <v>41050404824</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999465</v>
+        <v>0.998978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998636</v>
+        <v>0.998525</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.00032524802894307</v>
+        <v>-7.1685789360676e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.03256</v>
+        <v>-0.00718</v>
       </c>
       <c r="M4" t="n">
         <v>182493797362.4195</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>744.24</v>
+        <v>743.78</v>
       </c>
       <c r="F5" t="n">
-        <v>97848454897</v>
+        <v>97762334920</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>776403042</v>
+        <v>835909882</v>
       </c>
       <c r="I5" t="n">
-        <v>744.77</v>
+        <v>745.99</v>
       </c>
       <c r="J5" t="n">
-        <v>731.99</v>
+        <v>733.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.46</v>
+        <v>-0.529939267483428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.46719</v>
+        <v>-0.0712</v>
       </c>
       <c r="M5" t="n">
-        <v>131511658.44</v>
+        <v>131511597.49</v>
       </c>
       <c r="N5" t="n">
-        <v>131511658.44</v>
+        <v>131511597.49</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="F6" t="n">
-        <v>82315740317</v>
+        <v>83380218601</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1296717706</v>
+        <v>1408801009</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="J6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00265805</v>
+        <v>0.01725941</v>
       </c>
       <c r="L6" t="n">
-        <v>0.20501</v>
+        <v>1.32808</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999341</v>
+        <v>0.999426</v>
       </c>
       <c r="F7" t="n">
-        <v>71024815536</v>
+        <v>71007538466</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>10558902720</v>
+        <v>10764240440</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0.9995270000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999434</v>
+        <v>0.99924</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.000285177055205477</v>
+        <v>-5.0427716462687e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.02853</v>
+        <v>-0.00505</v>
       </c>
       <c r="M7" t="n">
-        <v>71073652364.31392</v>
+        <v>71047604364.11368</v>
       </c>
       <c r="N7" t="n">
-        <v>71199404861.60213</v>
+        <v>71060043349.80391</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.18</v>
+        <v>100.57</v>
       </c>
       <c r="F8" t="n">
-        <v>60240758473</v>
+        <v>59289467035</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2177735176</v>
+        <v>2297290366</v>
       </c>
       <c r="I8" t="n">
-        <v>102.06</v>
+        <v>102.48</v>
       </c>
       <c r="J8" t="n">
-        <v>99.81999999999999</v>
+        <v>99.09</v>
       </c>
       <c r="K8" t="n">
-        <v>0.796108</v>
+        <v>-1.229122118726593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.78525</v>
+        <v>-1.20735</v>
       </c>
       <c r="M8" t="n">
-        <v>589819571.9737056</v>
+        <v>589874555.009055</v>
       </c>
       <c r="N8" t="n">
-        <v>636457026.7801988</v>
+        <v>636517635.4621183</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.33098</v>
+        <v>0.327703</v>
       </c>
       <c r="F9" t="n">
-        <v>31443000944</v>
+        <v>31132907980</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>329389203</v>
+        <v>309598777</v>
       </c>
       <c r="I9" t="n">
-        <v>0.331294</v>
+        <v>0.331116</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329022</v>
+        <v>0.326958</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00192432</v>
+        <v>-0.002812133333927935</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5848</v>
+        <v>-0.85083</v>
       </c>
       <c r="M9" t="n">
-        <v>95014985713.76654</v>
+        <v>95016413026.10515</v>
       </c>
       <c r="N9" t="n">
-        <v>95014988604.06955</v>
+        <v>95016432541.01904</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,25 +1045,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.044</v>
+        <v>1.036</v>
       </c>
       <c r="F10" t="n">
-        <v>26718415567</v>
+        <v>26511629018</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>50049076</v>
+        <v>107261580</v>
       </c>
       <c r="I10" t="n">
-        <v>1.048</v>
+        <v>1.044</v>
       </c>
       <c r="J10" t="n">
-        <v>1.001</v>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+        <v>1.036</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.00038846</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.0375</v>
+      </c>
       <c r="M10" t="n">
         <v>25586557407.249</v>
       </c>
@@ -1080,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1106,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1251.53</v>
+        <v>1279.09</v>
       </c>
       <c r="F11" t="n">
-        <v>21256147493</v>
+        <v>21745245852</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>829422802</v>
+        <v>768791825</v>
       </c>
       <c r="I11" t="n">
-        <v>1250.88</v>
+        <v>1275.59</v>
       </c>
       <c r="J11" t="n">
-        <v>1177.73</v>
+        <v>1210.61</v>
       </c>
       <c r="K11" t="n">
-        <v>36.44</v>
+        <v>32.89</v>
       </c>
       <c r="L11" t="n">
-        <v>2.99937</v>
+        <v>2.63884</v>
       </c>
       <c r="M11" t="n">
-        <v>17004061.1030448</v>
+        <v>17007557.9780448</v>
       </c>
       <c r="N11" t="n">
-        <v>17007392.3530448</v>
+        <v>17009107.9780448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1145,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1171,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.34</v>
+        <v>78.81</v>
       </c>
       <c r="F12" t="n">
-        <v>17422271729</v>
+        <v>17522971167</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>781569659</v>
+        <v>756754252</v>
       </c>
       <c r="I12" t="n">
-        <v>78.2</v>
+        <v>80.47</v>
       </c>
       <c r="J12" t="n">
-        <v>74.92</v>
+        <v>77.11</v>
       </c>
       <c r="K12" t="n">
-        <v>1.26</v>
+        <v>0.846127</v>
       </c>
       <c r="L12" t="n">
-        <v>1.63698</v>
+        <v>1.08529</v>
       </c>
       <c r="M12" t="n">
         <v>222445714.0741414</v>
@@ -1210,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1236,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.077901</v>
+        <v>0.077889</v>
       </c>
       <c r="F13" t="n">
-        <v>12184761736</v>
+        <v>12183190448</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>430708937</v>
+        <v>380503951</v>
       </c>
       <c r="I13" t="n">
-        <v>0.077767</v>
+        <v>0.078068</v>
       </c>
       <c r="J13" t="n">
-        <v>0.075962</v>
+        <v>0.0766</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00081374</v>
+        <v>0.00024049</v>
       </c>
       <c r="L13" t="n">
-        <v>1.05561</v>
+        <v>0.30972</v>
       </c>
       <c r="M13" t="n">
-        <v>156461052863.2343</v>
+        <v>156488042860.1691</v>
       </c>
       <c r="N13" t="n">
-        <v>156486812860.1691</v>
+        <v>156499842860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1275,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1301,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>591.36</v>
+        <v>589.14</v>
       </c>
       <c r="F14" t="n">
-        <v>11127529393</v>
+        <v>11092832406</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>144859318</v>
+        <v>118100402</v>
       </c>
       <c r="I14" t="n">
-        <v>605.62</v>
+        <v>610.55</v>
       </c>
       <c r="J14" t="n">
-        <v>582.8200000000001</v>
+        <v>589.4</v>
       </c>
       <c r="K14" t="n">
-        <v>-12.98980672562504</v>
+        <v>-3.144494070428095</v>
       </c>
       <c r="L14" t="n">
-        <v>-2.14938</v>
+        <v>-0.53091</v>
       </c>
       <c r="M14" t="n">
-        <v>18822731.84223136</v>
+        <v>18823166.83063715</v>
       </c>
       <c r="N14" t="n">
-        <v>18822731.84223136</v>
+        <v>18823166.83063715</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1340,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1366,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999718</v>
+        <v>0.999784</v>
       </c>
       <c r="F15" t="n">
-        <v>9971602809</v>
+        <v>9970147347</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>201764725</v>
+        <v>113195964</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.998918</v>
+        <v>0.998874</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000416938398470457</v>
+        <v>0.00025762</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.04169</v>
+        <v>0.02577</v>
       </c>
       <c r="M15" t="n">
-        <v>9974742982.816563</v>
+        <v>9973213697.173923</v>
       </c>
       <c r="N15" t="n">
-        <v>9974742982.816563</v>
+        <v>9973213697.173923</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1405,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1431,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.31999999999999</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>9178743545</v>
+        <v>9146996059</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>141905088</v>
+        <v>88769461</v>
       </c>
       <c r="I16" t="n">
-        <v>77.92</v>
+        <v>77.52</v>
       </c>
       <c r="J16" t="n">
-        <v>76.37</v>
+        <v>76.26000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.2463835791570688</v>
+        <v>0.00052758</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.31765</v>
+        <v>0.00068</v>
       </c>
       <c r="M16" t="n">
         <v>118720983</v>
@@ -1470,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1496,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.57</v>
+        <v>11.4</v>
       </c>
       <c r="F17" t="n">
-        <v>8873179239</v>
+        <v>8730435138</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>262333003</v>
+        <v>274952980</v>
       </c>
       <c r="I17" t="n">
-        <v>11.56</v>
+        <v>11.61</v>
       </c>
       <c r="J17" t="n">
-        <v>11.26</v>
+        <v>11.22</v>
       </c>
       <c r="K17" t="n">
-        <v>0.177965</v>
+        <v>-0.1384343238299</v>
       </c>
       <c r="L17" t="n">
-        <v>1.56169</v>
+        <v>-1.20023</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1535,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1561,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.029999999999999</v>
+        <v>9.01</v>
       </c>
       <c r="F18" t="n">
-        <v>8308529865</v>
+        <v>8283756684</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>115883</v>
+        <v>27550</v>
       </c>
       <c r="I18" t="n">
-        <v>9.039999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>8.970000000000001</v>
+        <v>8.99</v>
       </c>
       <c r="K18" t="n">
-        <v>0.04033454</v>
+        <v>-0.02719253393909149</v>
       </c>
       <c r="L18" t="n">
-        <v>0.44857</v>
+        <v>-0.30105</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1600,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1626,31 +1630,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.20706</v>
+        <v>0.204719</v>
       </c>
       <c r="F19" t="n">
-        <v>7775775935</v>
+        <v>7684875173</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>231670427</v>
+        <v>197180899</v>
       </c>
       <c r="I19" t="n">
-        <v>0.206733</v>
+        <v>0.207755</v>
       </c>
       <c r="J19" t="n">
-        <v>0.200505</v>
+        <v>0.201113</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00211243</v>
+        <v>-0.001316062655271982</v>
       </c>
       <c r="L19" t="n">
-        <v>1.03072</v>
+        <v>-0.63876</v>
       </c>
       <c r="M19" t="n">
-        <v>37565404869.05737</v>
+        <v>37571497272.79388</v>
       </c>
       <c r="N19" t="n">
         <v>45000000000</v>
@@ -1665,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.61</v>
+        <v>0.168339</v>
       </c>
       <c r="F20" t="n">
-        <v>6032426776</v>
+        <v>5926669824</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>576868480</v>
+        <v>94702647</v>
       </c>
       <c r="I20" t="n">
-        <v>4.69</v>
+        <v>0.170855</v>
       </c>
       <c r="J20" t="n">
-        <v>4.43</v>
+        <v>0.166515</v>
       </c>
       <c r="K20" t="n">
-        <v>0.122392</v>
+        <v>-0.001702758184817771</v>
       </c>
       <c r="L20" t="n">
-        <v>2.72856</v>
+        <v>-1.00138</v>
       </c>
       <c r="M20" t="n">
-        <v>1310001700</v>
+        <v>35229195307.62386</v>
       </c>
       <c r="N20" t="n">
-        <v>1310001727</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O20" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261026T153406Z-67835f</t>
+          <t>20261027T145904Z-e5e534</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.170173</v>
+        <v>4.54</v>
       </c>
       <c r="F21" t="n">
-        <v>5997065322</v>
+        <v>5935412003</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>92318557</v>
+        <v>500749012</v>
       </c>
       <c r="I21" t="n">
-        <v>0.170306</v>
+        <v>4.65</v>
       </c>
       <c r="J21" t="n">
-        <v>0.166566</v>
+        <v>4.39</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00105458</v>
+        <v>-0.08357878804290575</v>
       </c>
       <c r="L21" t="n">
-        <v>0.62357</v>
+        <v>-1.80946</v>
       </c>
       <c r="M21" t="n">
-        <v>35227372279.74623</v>
+        <v>1310084611</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786837.39717</v>
+        <v>1310084620</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-26T15:32:47.000Z</t>
+          <t>2026-10-27T14:57:53.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80278</v>
+        <v>80497</v>
       </c>
       <c r="F2" t="n">
-        <v>1613335588139</v>
+        <v>1618831730277</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>24002048860</v>
+        <v>23399033951</v>
       </c>
       <c r="I2" t="n">
-        <v>80680</v>
+        <v>81636</v>
       </c>
       <c r="J2" t="n">
-        <v>79416</v>
+        <v>80360</v>
       </c>
       <c r="K2" t="n">
-        <v>61.31</v>
+        <v>182.87</v>
       </c>
       <c r="L2" t="n">
-        <v>0.07643</v>
+        <v>0.22769</v>
       </c>
       <c r="M2" t="n">
-        <v>20104350</v>
+        <v>20104859</v>
       </c>
       <c r="N2" t="n">
-        <v>20104350</v>
+        <v>20104859</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2332.27</v>
+        <v>2330.71</v>
       </c>
       <c r="F3" t="n">
-        <v>284782021136</v>
+        <v>284852803518</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>8384290560</v>
+        <v>9039137161</v>
       </c>
       <c r="I3" t="n">
-        <v>2338.49</v>
+        <v>2379.62</v>
       </c>
       <c r="J3" t="n">
-        <v>2295.57</v>
+        <v>2324.28</v>
       </c>
       <c r="K3" t="n">
-        <v>10.93</v>
+        <v>-8.01030517197114</v>
       </c>
       <c r="L3" t="n">
-        <v>0.47081</v>
+        <v>-0.34251</v>
       </c>
       <c r="M3" t="n">
-        <v>122167205.1116396</v>
+        <v>122170165.6206168</v>
       </c>
       <c r="N3" t="n">
-        <v>122167205.1116396</v>
+        <v>122170165.6206168</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.998777</v>
+        <v>0.9988</v>
       </c>
       <c r="F4" t="n">
-        <v>182272088699</v>
+        <v>181609862067</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>41050404824</v>
+        <v>41175904449</v>
       </c>
       <c r="I4" t="n">
-        <v>0.998978</v>
+        <v>0.999105</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998525</v>
+        <v>0.99863</v>
       </c>
       <c r="K4" t="n">
-        <v>-7.1685789360676e-05</v>
+        <v>-1.0761392450598e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00718</v>
+        <v>-0.00108</v>
       </c>
       <c r="M4" t="n">
-        <v>182493797362.4195</v>
+        <v>181828259330.4374</v>
       </c>
       <c r="N4" t="n">
-        <v>187960745865.3062</v>
+        <v>187295207855.8162</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>743.78</v>
+        <v>748.2</v>
       </c>
       <c r="F5" t="n">
-        <v>97762334920</v>
+        <v>98404965296</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>835909882</v>
+        <v>946017581</v>
       </c>
       <c r="I5" t="n">
-        <v>745.99</v>
+        <v>761.04</v>
       </c>
       <c r="J5" t="n">
-        <v>733.25</v>
+        <v>741.12</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.529939267483428</v>
+        <v>-0.2364925889006599</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0712</v>
+        <v>-0.0316</v>
       </c>
       <c r="M5" t="n">
-        <v>131511597.49</v>
+        <v>131511531.91</v>
       </c>
       <c r="N5" t="n">
-        <v>131511597.49</v>
+        <v>131511531.91</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="F6" t="n">
-        <v>83380218601</v>
+        <v>83059993495</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1408801009</v>
+        <v>1669267181</v>
       </c>
       <c r="I6" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="K6" t="n">
-        <v>0.01725941</v>
+        <v>-0.008811557372664147</v>
       </c>
       <c r="L6" t="n">
-        <v>1.32808</v>
+        <v>-0.6677999999999999</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999426</v>
+        <v>0.99932</v>
       </c>
       <c r="F7" t="n">
-        <v>71007538466</v>
+        <v>71006937126</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>10764240440</v>
+        <v>10849387838</v>
       </c>
       <c r="I7" t="n">
-        <v>0.9995270000000001</v>
+        <v>0.999598</v>
       </c>
       <c r="J7" t="n">
-        <v>0.99924</v>
+        <v>0.998902</v>
       </c>
       <c r="K7" t="n">
-        <v>-5.0427716462687e-05</v>
+        <v>-9.509290057618799e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.00505</v>
+        <v>-0.009509999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>71047604364.11368</v>
+        <v>71055245212.72014</v>
       </c>
       <c r="N7" t="n">
-        <v>71060043349.80391</v>
+        <v>71075718222.1992</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.57</v>
+        <v>100.87</v>
       </c>
       <c r="F8" t="n">
-        <v>59289467035</v>
+        <v>59522041964</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2297290366</v>
+        <v>2071864372</v>
       </c>
       <c r="I8" t="n">
-        <v>102.48</v>
+        <v>103.35</v>
       </c>
       <c r="J8" t="n">
-        <v>99.09</v>
+        <v>100.37</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.229122118726593</v>
+        <v>0.114285</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.20735</v>
+        <v>0.11343</v>
       </c>
       <c r="M8" t="n">
-        <v>589874555.009055</v>
+        <v>589928341.4213028</v>
       </c>
       <c r="N8" t="n">
-        <v>636517635.4621183</v>
+        <v>636578157.9389172</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.327703</v>
+        <v>0.330955</v>
       </c>
       <c r="F9" t="n">
-        <v>31132907980</v>
+        <v>31449912214</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>309598777</v>
+        <v>382139327</v>
       </c>
       <c r="I9" t="n">
-        <v>0.331116</v>
+        <v>0.332064</v>
       </c>
       <c r="J9" t="n">
-        <v>0.326958</v>
+        <v>0.327314</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.002812133333927935</v>
+        <v>0.00302693</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.85083</v>
+        <v>0.92305</v>
       </c>
       <c r="M9" t="n">
-        <v>95016413026.10515</v>
+        <v>95017831832.69115</v>
       </c>
       <c r="N9" t="n">
-        <v>95016432541.01904</v>
+        <v>95017844588.83205</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.036</v>
+        <v>1.03</v>
       </c>
       <c r="F10" t="n">
-        <v>26511629018</v>
+        <v>26539586270</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>107261580</v>
+        <v>96556152</v>
       </c>
       <c r="I10" t="n">
-        <v>1.044</v>
+        <v>1.032</v>
       </c>
       <c r="J10" t="n">
-        <v>1.036</v>
+        <v>1.02</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00038846</v>
+        <v>-0.00189471534651009</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0375</v>
+        <v>-0.18364</v>
       </c>
       <c r="M10" t="n">
-        <v>25586557407.249</v>
+        <v>25770229883.169</v>
       </c>
       <c r="N10" t="n">
-        <v>25586557407.249</v>
+        <v>25770229883.169</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1279.09</v>
+        <v>1270.32</v>
       </c>
       <c r="F11" t="n">
-        <v>21745245852</v>
+        <v>21623487276</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>768791825</v>
+        <v>761372593</v>
       </c>
       <c r="I11" t="n">
-        <v>1275.59</v>
+        <v>1327.53</v>
       </c>
       <c r="J11" t="n">
-        <v>1210.61</v>
+        <v>1268.68</v>
       </c>
       <c r="K11" t="n">
-        <v>32.89</v>
+        <v>-15.19412451718813</v>
       </c>
       <c r="L11" t="n">
-        <v>2.63884</v>
+        <v>-1.18195</v>
       </c>
       <c r="M11" t="n">
-        <v>17007557.9780448</v>
+        <v>17010609.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>17009107.9780448</v>
+        <v>17010962.6655448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,34 +1175,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>78.81</v>
+        <v>79.84999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>17522971167</v>
+        <v>19113464834</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>756754252</v>
+        <v>747645162</v>
       </c>
       <c r="I12" t="n">
-        <v>80.47</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>77.11</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.846127</v>
+        <v>0.6669659999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>1.08529</v>
+        <v>0.8423</v>
       </c>
       <c r="M12" t="n">
-        <v>222445714.0741414</v>
+        <v>239406814.3741415</v>
       </c>
       <c r="N12" t="n">
-        <v>955307079.4341414</v>
+        <v>951538272.9141414</v>
       </c>
       <c r="O12" t="n">
         <v>97.95999999999999</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.077889</v>
+        <v>0.079141</v>
       </c>
       <c r="F13" t="n">
-        <v>12183190448</v>
+        <v>12390157231</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>380503951</v>
+        <v>525489445</v>
       </c>
       <c r="I13" t="n">
-        <v>0.078068</v>
+        <v>0.080513</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0766</v>
+        <v>0.077963</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00024049</v>
+        <v>0.00110003</v>
       </c>
       <c r="L13" t="n">
-        <v>0.30972</v>
+        <v>1.40955</v>
       </c>
       <c r="M13" t="n">
-        <v>156488042860.1691</v>
+        <v>156511242860.1691</v>
       </c>
       <c r="N13" t="n">
-        <v>156499842860.1691</v>
+        <v>156513712860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>589.14</v>
+        <v>598.65</v>
       </c>
       <c r="F14" t="n">
-        <v>11092832406</v>
+        <v>11265075380</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>118100402</v>
+        <v>127115154</v>
       </c>
       <c r="I14" t="n">
-        <v>610.55</v>
+        <v>618.63</v>
       </c>
       <c r="J14" t="n">
-        <v>589.4</v>
+        <v>590.33</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.144494070428095</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.53091</v>
+        <v>1.60317</v>
       </c>
       <c r="M14" t="n">
-        <v>18823166.83063715</v>
+        <v>18823586.22203933</v>
       </c>
       <c r="N14" t="n">
-        <v>18823166.83063715</v>
+        <v>18823586.22203933</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999784</v>
+        <v>0.999644</v>
       </c>
       <c r="F15" t="n">
-        <v>9970147347</v>
+        <v>9850128426</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>113195964</v>
+        <v>141804000</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.998874</v>
+        <v>0.999492</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00025762</v>
+        <v>-0.000210757134774142</v>
       </c>
       <c r="L15" t="n">
-        <v>0.02577</v>
+        <v>-0.02108</v>
       </c>
       <c r="M15" t="n">
-        <v>9973213697.173923</v>
+        <v>9853620003.635508</v>
       </c>
       <c r="N15" t="n">
-        <v>9973213697.173923</v>
+        <v>9853620003.635508</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,34 +1435,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.06999999999999</v>
+        <v>77.27</v>
       </c>
       <c r="F16" t="n">
-        <v>9146996059</v>
+        <v>9173361449</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>88769461</v>
+        <v>53524476</v>
       </c>
       <c r="I16" t="n">
-        <v>77.52</v>
+        <v>78.47</v>
       </c>
       <c r="J16" t="n">
-        <v>76.26000000000001</v>
+        <v>77.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00052758</v>
+        <v>0.063406</v>
       </c>
       <c r="L16" t="n">
-        <v>0.00068</v>
+        <v>0.08212999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>118720983</v>
+        <v>118688311</v>
       </c>
       <c r="N16" t="n">
-        <v>293290482</v>
+        <v>293257810</v>
       </c>
       <c r="O16" t="n">
         <v>87.91</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.4</v>
+        <v>11.53</v>
       </c>
       <c r="F17" t="n">
-        <v>8730435138</v>
+        <v>8852544195</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>274952980</v>
+        <v>256310761</v>
       </c>
       <c r="I17" t="n">
-        <v>11.61</v>
+        <v>11.87</v>
       </c>
       <c r="J17" t="n">
-        <v>11.22</v>
+        <v>11.43</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.1384343238299</v>
+        <v>0.108897</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.20023</v>
+        <v>0.9531500000000001</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1565,28 +1565,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.01</v>
+        <v>9.41</v>
       </c>
       <c r="F18" t="n">
-        <v>8283756684</v>
+        <v>8659814701</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>27550</v>
+        <v>263835</v>
       </c>
       <c r="I18" t="n">
-        <v>9.050000000000001</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="J18" t="n">
         <v>8.99</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.02719253393909149</v>
+        <v>0.408527</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.30105</v>
+        <v>4.53628</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.204719</v>
+        <v>0.202754</v>
       </c>
       <c r="F19" t="n">
-        <v>7684875173</v>
+        <v>7622271986</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>197180899</v>
+        <v>204668452</v>
       </c>
       <c r="I19" t="n">
-        <v>0.207755</v>
+        <v>0.208034</v>
       </c>
       <c r="J19" t="n">
-        <v>0.201113</v>
+        <v>0.201198</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.001316062655271982</v>
+        <v>-0.002397892926596396</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.63876</v>
+        <v>-1.16884</v>
       </c>
       <c r="M19" t="n">
         <v>37571497272.79388</v>
@@ -1669,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.168339</v>
+        <v>4.62</v>
       </c>
       <c r="F20" t="n">
-        <v>5926669824</v>
+        <v>6054850857</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>94702647</v>
+        <v>513017571</v>
       </c>
       <c r="I20" t="n">
-        <v>0.170855</v>
+        <v>4.78</v>
       </c>
       <c r="J20" t="n">
-        <v>0.166515</v>
+        <v>4.54</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.001702758184817771</v>
+        <v>0.055934</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.00138</v>
+        <v>1.22561</v>
       </c>
       <c r="M20" t="n">
-        <v>35229195307.62386</v>
+        <v>1310187816</v>
       </c>
       <c r="N20" t="n">
-        <v>50001786837.39717</v>
+        <v>1310187869</v>
       </c>
       <c r="O20" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261027T145904Z-e5e534</t>
+          <t>20261028T153338Z-4a5dc7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.54</v>
+        <v>0.170683</v>
       </c>
       <c r="F21" t="n">
-        <v>5935412003</v>
+        <v>6012525569</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>500749012</v>
+        <v>102373004</v>
       </c>
       <c r="I21" t="n">
-        <v>4.65</v>
+        <v>0.172641</v>
       </c>
       <c r="J21" t="n">
-        <v>4.39</v>
+        <v>0.168749</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.08357878804290575</v>
+        <v>0.00181027</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.80946</v>
+        <v>1.07197</v>
       </c>
       <c r="M21" t="n">
-        <v>1310084611</v>
+        <v>35230412492.58374</v>
       </c>
       <c r="N21" t="n">
-        <v>1310084620</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-27T14:57:53.000Z</t>
+          <t>2026-10-28T15:32:55.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>80497</v>
+        <v>81570</v>
       </c>
       <c r="F2" t="n">
-        <v>1618831730277</v>
+        <v>1640213246630</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>23399033951</v>
+        <v>29783480231</v>
       </c>
       <c r="I2" t="n">
-        <v>81636</v>
+        <v>81698</v>
       </c>
       <c r="J2" t="n">
-        <v>80360</v>
+        <v>79636</v>
       </c>
       <c r="K2" t="n">
-        <v>182.87</v>
+        <v>1031.48</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22769</v>
+        <v>1.26739</v>
       </c>
       <c r="M2" t="n">
-        <v>20104859</v>
+        <v>20105281</v>
       </c>
       <c r="N2" t="n">
-        <v>20104859</v>
+        <v>20105290</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2330.71</v>
+        <v>2363.28</v>
       </c>
       <c r="F3" t="n">
-        <v>284852803518</v>
+        <v>288642974989</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>9039137161</v>
+        <v>11536237706</v>
       </c>
       <c r="I3" t="n">
-        <v>2379.62</v>
+        <v>2384.72</v>
       </c>
       <c r="J3" t="n">
-        <v>2324.28</v>
+        <v>2292.94</v>
       </c>
       <c r="K3" t="n">
-        <v>-8.01030517197114</v>
+        <v>31.86</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.34251</v>
+        <v>1.3717</v>
       </c>
       <c r="M3" t="n">
-        <v>122170165.6206168</v>
+        <v>122173130.0474278</v>
       </c>
       <c r="N3" t="n">
-        <v>122170165.6206168</v>
+        <v>122173130.0474278</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.9988</v>
+        <v>0.999178</v>
       </c>
       <c r="F4" t="n">
-        <v>181609862067</v>
+        <v>180881465815</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>41175904449</v>
+        <v>52073594926</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999105</v>
+        <v>0.9993610000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.99863</v>
+        <v>0.998797</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.0761392450598e-05</v>
+        <v>0.00036481</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.00108</v>
+        <v>0.0346</v>
       </c>
       <c r="M4" t="n">
-        <v>181828259330.4374</v>
+        <v>181029976505.8259</v>
       </c>
       <c r="N4" t="n">
-        <v>187295207855.8162</v>
+        <v>186496925031.8962</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>748.2</v>
+        <v>750.98</v>
       </c>
       <c r="F5" t="n">
-        <v>98404965296</v>
+        <v>98779279227</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>946017581</v>
+        <v>1796011630</v>
       </c>
       <c r="I5" t="n">
-        <v>761.04</v>
+        <v>760.02</v>
       </c>
       <c r="J5" t="n">
-        <v>741.12</v>
+        <v>737.63</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.2364925889006599</v>
+        <v>1.81</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0316</v>
+        <v>0.27051</v>
       </c>
       <c r="M5" t="n">
-        <v>131511531.91</v>
+        <v>131511473.63</v>
       </c>
       <c r="N5" t="n">
-        <v>131511531.91</v>
+        <v>131511473.63</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.31</v>
       </c>
       <c r="F6" t="n">
-        <v>83059993495</v>
+        <v>82873161991</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1669267181</v>
+        <v>1900085780</v>
       </c>
       <c r="I6" t="n">
         <v>1.34</v>
       </c>
       <c r="J6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.008811557372664147</v>
+        <v>-0.003546531219992488</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6677999999999999</v>
+        <v>-0.27275</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.99932</v>
+        <v>0.999578</v>
       </c>
       <c r="F7" t="n">
-        <v>71006937126</v>
+        <v>71154799596</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>10849387838</v>
+        <v>13839077472</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999598</v>
+        <v>0.999885</v>
       </c>
       <c r="J7" t="n">
-        <v>0.998902</v>
+        <v>0.999306</v>
       </c>
       <c r="K7" t="n">
-        <v>-9.509290057618799e-05</v>
+        <v>0.00023755</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.009509999999999999</v>
+        <v>0.02057</v>
       </c>
       <c r="M7" t="n">
-        <v>71055245212.72014</v>
+        <v>71184903122.78786</v>
       </c>
       <c r="N7" t="n">
-        <v>71075718222.1992</v>
+        <v>71208749615.19931</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100.87</v>
+        <v>102.29</v>
       </c>
       <c r="F8" t="n">
-        <v>59522041964</v>
+        <v>60344972135</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>2071864372</v>
+        <v>3083557287</v>
       </c>
       <c r="I8" t="n">
-        <v>103.35</v>
+        <v>103.65</v>
       </c>
       <c r="J8" t="n">
-        <v>100.37</v>
+        <v>99.23</v>
       </c>
       <c r="K8" t="n">
-        <v>0.114285</v>
+        <v>1.33</v>
       </c>
       <c r="L8" t="n">
-        <v>0.11343</v>
+        <v>1.35028</v>
       </c>
       <c r="M8" t="n">
-        <v>589928341.4213028</v>
+        <v>589983751.8910971</v>
       </c>
       <c r="N8" t="n">
-        <v>636578157.9389172</v>
+        <v>636639326.5744199</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.330955</v>
+        <v>0.331043</v>
       </c>
       <c r="F9" t="n">
-        <v>31449912214</v>
+        <v>31454816286</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>382139327</v>
+        <v>345770862</v>
       </c>
       <c r="I9" t="n">
-        <v>0.332064</v>
+        <v>0.331578</v>
       </c>
       <c r="J9" t="n">
-        <v>0.327314</v>
+        <v>0.329042</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00302693</v>
+        <v>-0.000117510005646249</v>
       </c>
       <c r="L9" t="n">
-        <v>0.92305</v>
+        <v>-0.02632</v>
       </c>
       <c r="M9" t="n">
-        <v>95017831832.69115</v>
+        <v>95019314311.45085</v>
       </c>
       <c r="N9" t="n">
-        <v>95017844588.83205</v>
+        <v>95019315933.56534</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.03</v>
+        <v>1.034</v>
       </c>
       <c r="F10" t="n">
-        <v>26539586270</v>
+        <v>26714650986</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>96556152</v>
+        <v>32169040</v>
       </c>
       <c r="I10" t="n">
-        <v>1.032</v>
+        <v>1.037</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>1.027</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.00189471534651009</v>
+        <v>0.00414</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.18364</v>
+        <v>0.40398</v>
       </c>
       <c r="M10" t="n">
-        <v>25770229883.169</v>
+        <v>25836537626.749</v>
       </c>
       <c r="N10" t="n">
-        <v>25770229883.169</v>
+        <v>25836537626.749</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,14 +1084,14 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1110,34 +1110,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1270.32</v>
+        <v>1342.66</v>
       </c>
       <c r="F11" t="n">
-        <v>21623487276</v>
+        <v>22812968315</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>761372593</v>
+        <v>959603723</v>
       </c>
       <c r="I11" t="n">
-        <v>1327.53</v>
+        <v>1316.81</v>
       </c>
       <c r="J11" t="n">
-        <v>1268.68</v>
+        <v>1230.65</v>
       </c>
       <c r="K11" t="n">
-        <v>-15.19412451718813</v>
+        <v>67.94</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.18195</v>
+        <v>5.21869</v>
       </c>
       <c r="M11" t="n">
         <v>17010609.5405448</v>
       </c>
       <c r="N11" t="n">
-        <v>17010962.6655448</v>
+        <v>17012739.2280448</v>
       </c>
       <c r="O11" t="n">
         <v>3191.93</v>
@@ -1149,14 +1149,14 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1175,28 +1175,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>79.84999999999999</v>
+        <v>93.48999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>19113464834</v>
+        <v>22368141802</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>747645162</v>
+        <v>1978474951</v>
       </c>
       <c r="I12" t="n">
-        <v>82.34999999999999</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>79.20999999999999</v>
+        <v>78.11</v>
       </c>
       <c r="K12" t="n">
-        <v>0.6669659999999999</v>
+        <v>13.63</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8423</v>
+        <v>17.14462</v>
       </c>
       <c r="M12" t="n">
         <v>239406814.3741415</v>
@@ -1214,14 +1214,14 @@
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.079141</v>
+        <v>0.080169</v>
       </c>
       <c r="F13" t="n">
-        <v>12390157231</v>
+        <v>12540115699</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>525489445</v>
+        <v>474427894</v>
       </c>
       <c r="I13" t="n">
-        <v>0.080513</v>
+        <v>0.08067299999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.077963</v>
+        <v>0.077427</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00110003</v>
+        <v>0.00092592</v>
       </c>
       <c r="L13" t="n">
-        <v>1.40955</v>
+        <v>1.13288</v>
       </c>
       <c r="M13" t="n">
         <v>156511242860.1691</v>
       </c>
       <c r="N13" t="n">
-        <v>156513712860.1691</v>
+        <v>156527552860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>598.65</v>
+        <v>602.0700000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>11265075380</v>
+        <v>11334011931</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>127115154</v>
+        <v>108224310</v>
       </c>
       <c r="I14" t="n">
-        <v>618.63</v>
+        <v>607.3099999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>590.33</v>
+        <v>583.11</v>
       </c>
       <c r="K14" t="n">
-        <v>9.449999999999999</v>
+        <v>1.68</v>
       </c>
       <c r="L14" t="n">
-        <v>1.60317</v>
+        <v>0.22529</v>
       </c>
       <c r="M14" t="n">
-        <v>18823586.22203933</v>
+        <v>18824003.212897</v>
       </c>
       <c r="N14" t="n">
-        <v>18823586.22203933</v>
+        <v>18824003.212897</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999644</v>
+        <v>0.999854</v>
       </c>
       <c r="F15" t="n">
-        <v>9850128426</v>
+        <v>9795890926</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>141804000</v>
+        <v>306793048</v>
       </c>
       <c r="I15" t="n">
         <v>1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999492</v>
+        <v>0.999007</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.000210757134774142</v>
+        <v>0.0002882</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.02108</v>
+        <v>0.00745</v>
       </c>
       <c r="M15" t="n">
-        <v>9853620003.635508</v>
+        <v>9797316019.576208</v>
       </c>
       <c r="N15" t="n">
-        <v>9853620003.635508</v>
+        <v>9797316019.576208</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>77.27</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9173361449</v>
+        <v>9291937027</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>53524476</v>
+        <v>120811642</v>
       </c>
       <c r="I16" t="n">
-        <v>78.47</v>
+        <v>78.52</v>
       </c>
       <c r="J16" t="n">
-        <v>77.09999999999999</v>
+        <v>76.34</v>
       </c>
       <c r="K16" t="n">
-        <v>0.063406</v>
+        <v>0.997934</v>
       </c>
       <c r="L16" t="n">
-        <v>0.08212999999999999</v>
+        <v>1.25165</v>
       </c>
       <c r="M16" t="n">
         <v>118688311</v>
@@ -1474,14 +1474,14 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1500,28 +1500,28 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.53</v>
+        <v>11.92</v>
       </c>
       <c r="F17" t="n">
-        <v>8852544195</v>
+        <v>9136803883</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>256310761</v>
+        <v>304163344</v>
       </c>
       <c r="I17" t="n">
-        <v>11.87</v>
+        <v>11.95</v>
       </c>
       <c r="J17" t="n">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="K17" t="n">
-        <v>0.108897</v>
+        <v>0.355988</v>
       </c>
       <c r="L17" t="n">
-        <v>0.9531500000000001</v>
+        <v>3.07058</v>
       </c>
       <c r="M17" t="n">
         <v>766849970.424884</v>
@@ -1539,14 +1539,14 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1568,25 +1568,25 @@
         <v>9.41</v>
       </c>
       <c r="F18" t="n">
-        <v>8659814701</v>
+        <v>8652448790</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>263835</v>
+        <v>31815</v>
       </c>
       <c r="I18" t="n">
-        <v>9.449999999999999</v>
+        <v>9.48</v>
       </c>
       <c r="J18" t="n">
-        <v>8.99</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>0.408527</v>
+        <v>-0.007796741756527226</v>
       </c>
       <c r="L18" t="n">
-        <v>4.53628</v>
+        <v>-0.08477</v>
       </c>
       <c r="M18" t="n">
         <v>919857851.9</v>
@@ -1604,14 +1604,14 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.202754</v>
+        <v>0.205125</v>
       </c>
       <c r="F19" t="n">
-        <v>7622271986</v>
+        <v>7703050635</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>204668452</v>
+        <v>339536560</v>
       </c>
       <c r="I19" t="n">
-        <v>0.208034</v>
+        <v>0.209247</v>
       </c>
       <c r="J19" t="n">
-        <v>0.201198</v>
+        <v>0.195778</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.002397892926596396</v>
+        <v>0.00208998</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.16884</v>
+        <v>1.02095</v>
       </c>
       <c r="M19" t="n">
         <v>37571497272.79388</v>
@@ -1669,137 +1669,137 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>stellar</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>xlm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4.62</v>
+        <v>0.172231</v>
       </c>
       <c r="F20" t="n">
-        <v>6054850857</v>
+        <v>6068378924</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>513017571</v>
+        <v>123035418</v>
       </c>
       <c r="I20" t="n">
-        <v>4.78</v>
+        <v>0.174678</v>
       </c>
       <c r="J20" t="n">
-        <v>4.54</v>
+        <v>0.166968</v>
       </c>
       <c r="K20" t="n">
-        <v>0.055934</v>
+        <v>0.00157995</v>
       </c>
       <c r="L20" t="n">
-        <v>1.22561</v>
+        <v>0.89549</v>
       </c>
       <c r="M20" t="n">
-        <v>1310187816</v>
+        <v>35246873561.44807</v>
       </c>
       <c r="N20" t="n">
-        <v>1310187869</v>
+        <v>50001786837.39717</v>
       </c>
       <c r="O20" t="n">
-        <v>20.44</v>
+        <v>0.875563</v>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2018-01-02T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261028T153338Z-4a5dc7</t>
+          <t>20261029T154130Z-582e69</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>stellar</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>xlm</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>0.170683</v>
+        <v>4.62</v>
       </c>
       <c r="F21" t="n">
-        <v>6012525569</v>
+        <v>6048873663</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>102373004</v>
+        <v>813830839</v>
       </c>
       <c r="I21" t="n">
-        <v>0.172641</v>
+        <v>4.79</v>
       </c>
       <c r="J21" t="n">
-        <v>0.168749</v>
+        <v>4.29</v>
       </c>
       <c r="K21" t="n">
-        <v>0.00181027</v>
+        <v>-0.006459180289605904</v>
       </c>
       <c r="L21" t="n">
-        <v>1.07197</v>
+        <v>-0.2298</v>
       </c>
       <c r="M21" t="n">
-        <v>35230412492.58374</v>
+        <v>1310265070</v>
       </c>
       <c r="N21" t="n">
-        <v>50001786837.39717</v>
+        <v>1310265103</v>
       </c>
       <c r="O21" t="n">
-        <v>0.875563</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2018-01-02T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-28T15:32:55.000Z</t>
+          <t>2026-10-29T15:39:49.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,34 +525,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>81570</v>
+        <v>77867</v>
       </c>
       <c r="F2" t="n">
-        <v>1640213246630</v>
+        <v>1565677316596</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>29783480231</v>
+        <v>177012877962</v>
       </c>
       <c r="I2" t="n">
-        <v>81698</v>
+        <v>81840</v>
       </c>
       <c r="J2" t="n">
-        <v>79636</v>
+        <v>76443</v>
       </c>
       <c r="K2" t="n">
-        <v>1031.48</v>
+        <v>-3618.897402665651</v>
       </c>
       <c r="L2" t="n">
-        <v>1.26739</v>
+        <v>-4.44113</v>
       </c>
       <c r="M2" t="n">
-        <v>20105281</v>
+        <v>20105365</v>
       </c>
       <c r="N2" t="n">
-        <v>20105290</v>
+        <v>20105365</v>
       </c>
       <c r="O2" t="n">
         <v>126080</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2363.28</v>
+        <v>2246.06</v>
       </c>
       <c r="F3" t="n">
-        <v>288642974989</v>
+        <v>274542341533</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>11536237706</v>
+        <v>26876131642</v>
       </c>
       <c r="I3" t="n">
-        <v>2384.72</v>
+        <v>2373.22</v>
       </c>
       <c r="J3" t="n">
-        <v>2292.94</v>
+        <v>2178.62</v>
       </c>
       <c r="K3" t="n">
-        <v>31.86</v>
+        <v>-111.4385119325175</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3717</v>
+        <v>-4.72699</v>
       </c>
       <c r="M3" t="n">
-        <v>122173130.0474278</v>
+        <v>122174495.4349656</v>
       </c>
       <c r="N3" t="n">
-        <v>122173130.0474278</v>
+        <v>122174495.4349656</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999178</v>
+        <v>0.999038</v>
       </c>
       <c r="F4" t="n">
-        <v>180881465815</v>
+        <v>180340041253</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>52073594926</v>
+        <v>101735897455</v>
       </c>
       <c r="I4" t="n">
-        <v>0.9993610000000001</v>
+        <v>0.999275</v>
       </c>
       <c r="J4" t="n">
-        <v>0.998797</v>
+        <v>0.997999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00036481</v>
+        <v>-9.9704670627143e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0346</v>
+        <v>-0.009979999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>181029976505.8259</v>
+        <v>180512752222.448</v>
       </c>
       <c r="N4" t="n">
-        <v>186496925031.8962</v>
+        <v>185979700787.3362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>750.98</v>
+        <v>702.9</v>
       </c>
       <c r="F5" t="n">
-        <v>98779279227</v>
+        <v>92462253882</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>1796011630</v>
+        <v>3117246162</v>
       </c>
       <c r="I5" t="n">
-        <v>760.02</v>
+        <v>753.04</v>
       </c>
       <c r="J5" t="n">
-        <v>737.63</v>
+        <v>682.36</v>
       </c>
       <c r="K5" t="n">
-        <v>1.81</v>
+        <v>-47.95799875427099</v>
       </c>
       <c r="L5" t="n">
-        <v>0.27051</v>
+        <v>-6.38713</v>
       </c>
       <c r="M5" t="n">
-        <v>131511473.63</v>
+        <v>131511405.81</v>
       </c>
       <c r="N5" t="n">
-        <v>131511473.63</v>
+        <v>131511404.17</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -785,28 +785,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="F6" t="n">
-        <v>82873161991</v>
+        <v>79556693251</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>1900085780</v>
+        <v>4027993113</v>
       </c>
       <c r="I6" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="J6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.003546531219992488</v>
+        <v>-0.05192871821432377</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.27275</v>
+        <v>-3.97367</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999578</v>
+        <v>0.999658</v>
       </c>
       <c r="F7" t="n">
-        <v>71154799596</v>
+        <v>71526328773</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>13839077472</v>
+        <v>24324739353</v>
       </c>
       <c r="I7" t="n">
-        <v>0.999885</v>
+        <v>1.002</v>
       </c>
       <c r="J7" t="n">
-        <v>0.999306</v>
+        <v>0.998694</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00023755</v>
+        <v>9.704000000000001e-05</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02057</v>
+        <v>0.00971</v>
       </c>
       <c r="M7" t="n">
-        <v>71184903122.78786</v>
+        <v>71550607655.88692</v>
       </c>
       <c r="N7" t="n">
-        <v>71208749615.19931</v>
+        <v>71544148463.41095</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102.29</v>
+        <v>95.27</v>
       </c>
       <c r="F8" t="n">
-        <v>60344972135</v>
+        <v>56245091312</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>3083557287</v>
+        <v>5885601978</v>
       </c>
       <c r="I8" t="n">
-        <v>103.65</v>
+        <v>102.94</v>
       </c>
       <c r="J8" t="n">
-        <v>99.23</v>
+        <v>92.64</v>
       </c>
       <c r="K8" t="n">
-        <v>1.33</v>
+        <v>-6.810177750522286</v>
       </c>
       <c r="L8" t="n">
-        <v>1.35028</v>
+        <v>-6.67156</v>
       </c>
       <c r="M8" t="n">
-        <v>589983751.8910971</v>
+        <v>590039849.0719869</v>
       </c>
       <c r="N8" t="n">
-        <v>636639326.5744199</v>
+        <v>636700254.1080314</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.331043</v>
+        <v>0.334486</v>
       </c>
       <c r="F9" t="n">
-        <v>31454816286</v>
+        <v>31784255585</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>345770862</v>
+        <v>2278880640</v>
       </c>
       <c r="I9" t="n">
-        <v>0.331578</v>
+        <v>0.366528</v>
       </c>
       <c r="J9" t="n">
-        <v>0.329042</v>
+        <v>0.328832</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.000117510005646249</v>
+        <v>0.00333713</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.02632</v>
+        <v>1.00774</v>
       </c>
       <c r="M9" t="n">
-        <v>95019314311.45085</v>
+        <v>95020243944.30574</v>
       </c>
       <c r="N9" t="n">
-        <v>95019315933.56534</v>
+        <v>95020275950.42404</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.034</v>
+        <v>1.029</v>
       </c>
       <c r="F10" t="n">
-        <v>26714650986</v>
+        <v>26597679566</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>32169040</v>
+        <v>367797937</v>
       </c>
       <c r="I10" t="n">
-        <v>1.037</v>
+        <v>1.061</v>
       </c>
       <c r="J10" t="n">
         <v>1.027</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00414</v>
+        <v>-0.004340902318732853</v>
       </c>
       <c r="L10" t="n">
-        <v>0.40398</v>
+        <v>-0.4199</v>
       </c>
       <c r="M10" t="n">
         <v>25836537626.749</v>
       </c>
       <c r="N10" t="n">
-        <v>25836537626.749</v>
+        <v>25890652588.459</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,144 +1084,144 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>hyperliquid</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1342.66</v>
+        <v>93.13</v>
       </c>
       <c r="F11" t="n">
-        <v>22812968315</v>
+        <v>22300176597</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>959603723</v>
+        <v>2904755669</v>
       </c>
       <c r="I11" t="n">
-        <v>1316.81</v>
+        <v>96.7</v>
       </c>
       <c r="J11" t="n">
-        <v>1230.65</v>
+        <v>88.67</v>
       </c>
       <c r="K11" t="n">
-        <v>67.94</v>
+        <v>-0.2206697577718586</v>
       </c>
       <c r="L11" t="n">
-        <v>5.21869</v>
+        <v>-0.2364</v>
       </c>
       <c r="M11" t="n">
-        <v>17010609.5405448</v>
+        <v>239406814.3741415</v>
       </c>
       <c r="N11" t="n">
-        <v>17012739.2280448</v>
+        <v>951538272.9141414</v>
       </c>
       <c r="O11" t="n">
-        <v>3191.93</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2016-10-28T16:00:00.000Z</t>
+          <t>2026-09-23T05:16:50.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hyperliquid</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hype</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>93.48999999999999</v>
+        <v>1250.33</v>
       </c>
       <c r="F12" t="n">
-        <v>22368141802</v>
+        <v>21254633959</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1978474951</v>
+        <v>1515646853</v>
       </c>
       <c r="I12" t="n">
-        <v>91.84999999999999</v>
+        <v>1392.21</v>
       </c>
       <c r="J12" t="n">
-        <v>78.11</v>
+        <v>1189.27</v>
       </c>
       <c r="K12" t="n">
-        <v>13.63</v>
+        <v>-69.38714946963682</v>
       </c>
       <c r="L12" t="n">
-        <v>17.14462</v>
+        <v>-5.25773</v>
       </c>
       <c r="M12" t="n">
-        <v>239406814.3741415</v>
+        <v>17010609.5405448</v>
       </c>
       <c r="N12" t="n">
-        <v>951538272.9141414</v>
+        <v>17014531.4155448</v>
       </c>
       <c r="O12" t="n">
-        <v>97.95999999999999</v>
+        <v>3191.93</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2026-09-23T05:16:50.000Z</t>
+          <t>2016-10-28T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.080169</v>
+        <v>0.076281</v>
       </c>
       <c r="F13" t="n">
-        <v>12540115699</v>
+        <v>11941642087</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>474427894</v>
+        <v>1044756240</v>
       </c>
       <c r="I13" t="n">
-        <v>0.08067299999999999</v>
+        <v>0.081219</v>
       </c>
       <c r="J13" t="n">
-        <v>0.077427</v>
+        <v>0.072687</v>
       </c>
       <c r="K13" t="n">
-        <v>0.00092592</v>
+        <v>-0.003684641734336594</v>
       </c>
       <c r="L13" t="n">
-        <v>1.13288</v>
+        <v>-4.60777</v>
       </c>
       <c r="M13" t="n">
         <v>156511242860.1691</v>
       </c>
       <c r="N13" t="n">
-        <v>156527552860.1691</v>
+        <v>156541172860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>602.0700000000001</v>
+        <v>599.35</v>
       </c>
       <c r="F14" t="n">
-        <v>11334011931</v>
+        <v>11291345186</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>108224310</v>
+        <v>225788953</v>
       </c>
       <c r="I14" t="n">
-        <v>607.3099999999999</v>
+        <v>646.2</v>
       </c>
       <c r="J14" t="n">
-        <v>583.11</v>
+        <v>574.24</v>
       </c>
       <c r="K14" t="n">
-        <v>1.68</v>
+        <v>-1.170031909041427</v>
       </c>
       <c r="L14" t="n">
-        <v>0.22529</v>
+        <v>-0.19484</v>
       </c>
       <c r="M14" t="n">
-        <v>18824003.212897</v>
+        <v>18824433.39824343</v>
       </c>
       <c r="N14" t="n">
-        <v>18824003.212897</v>
+        <v>18824443.59824343</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1370,34 +1370,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.999854</v>
+        <v>1.001</v>
       </c>
       <c r="F15" t="n">
-        <v>9795890926</v>
+        <v>9560023102</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>306793048</v>
+        <v>250103442</v>
       </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>1.008</v>
       </c>
       <c r="J15" t="n">
-        <v>0.999007</v>
+        <v>0.993682</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0002882</v>
+        <v>0.00072913</v>
       </c>
       <c r="L15" t="n">
-        <v>0.00745</v>
+        <v>0.07292999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>9797316019.576208</v>
+        <v>9553064925.561302</v>
       </c>
       <c r="N15" t="n">
-        <v>9797316019.576208</v>
+        <v>9553751663.605755</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,14 +1409,14 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1435,28 +1435,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>78.29000000000001</v>
+        <v>74.54000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>9291937027</v>
+        <v>8849925151</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>120811642</v>
+        <v>287779826</v>
       </c>
       <c r="I16" t="n">
-        <v>78.52</v>
+        <v>78.58</v>
       </c>
       <c r="J16" t="n">
-        <v>76.34</v>
+        <v>73.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.997934</v>
+        <v>-3.630967185801765</v>
       </c>
       <c r="L16" t="n">
-        <v>1.25165</v>
+        <v>-4.64471</v>
       </c>
       <c r="M16" t="n">
         <v>118688311</v>
@@ -1474,144 +1474,144 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>11.92</v>
+        <v>9.4</v>
       </c>
       <c r="F17" t="n">
-        <v>9136803883</v>
+        <v>8647156553</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>304163344</v>
+        <v>170782</v>
       </c>
       <c r="I17" t="n">
-        <v>11.95</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>11.29</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.355988</v>
+        <v>-0.005316334383755006</v>
       </c>
       <c r="L17" t="n">
-        <v>3.07058</v>
+        <v>-0.05652</v>
       </c>
       <c r="M17" t="n">
-        <v>766849970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N17" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O17" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>9.41</v>
+        <v>11.21</v>
       </c>
       <c r="F18" t="n">
-        <v>8652448790</v>
+        <v>8604497529</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>31815</v>
+        <v>909817447</v>
       </c>
       <c r="I18" t="n">
-        <v>9.48</v>
+        <v>11.99</v>
       </c>
       <c r="J18" t="n">
-        <v>9.369999999999999</v>
+        <v>10.3</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.007796741756527226</v>
+        <v>-0.6525340146184107</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.08477</v>
+        <v>-5.49862</v>
       </c>
       <c r="M18" t="n">
-        <v>919857851.9</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N18" t="n">
-        <v>985239504</v>
+        <v>1000000000</v>
       </c>
       <c r="O18" t="n">
-        <v>10.61</v>
+        <v>52.7</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.205125</v>
+        <v>0.193778</v>
       </c>
       <c r="F19" t="n">
-        <v>7703050635</v>
+        <v>7283224175</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>339536560</v>
+        <v>473983841</v>
       </c>
       <c r="I19" t="n">
-        <v>0.209247</v>
+        <v>0.208002</v>
       </c>
       <c r="J19" t="n">
-        <v>0.195778</v>
+        <v>0.183186</v>
       </c>
       <c r="K19" t="n">
-        <v>0.00208998</v>
+        <v>-0.01094488603445748</v>
       </c>
       <c r="L19" t="n">
-        <v>1.02095</v>
+        <v>-5.34619</v>
       </c>
       <c r="M19" t="n">
         <v>37571497272.79388</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,31 +1695,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.172231</v>
+        <v>0.169629</v>
       </c>
       <c r="F20" t="n">
-        <v>6068378924</v>
+        <v>5984185821</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>123035418</v>
+        <v>207868344</v>
       </c>
       <c r="I20" t="n">
-        <v>0.174678</v>
+        <v>0.17347</v>
       </c>
       <c r="J20" t="n">
-        <v>0.166968</v>
+        <v>0.158344</v>
       </c>
       <c r="K20" t="n">
-        <v>0.00157995</v>
+        <v>-0.002258901154111176</v>
       </c>
       <c r="L20" t="n">
-        <v>0.89549</v>
+        <v>-1.31417</v>
       </c>
       <c r="M20" t="n">
-        <v>35246873561.44807</v>
+        <v>35247503121.71093</v>
       </c>
       <c r="N20" t="n">
         <v>50001786837.39717</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261029T154130Z-582e69</t>
+          <t>20261030T152401Z-472100</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>bitcoin-cash</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>near</t>
+          <t>bch</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NEAR Protocol</t>
+          <t>Bitcoin Cash</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4.62</v>
+        <v>295.43</v>
       </c>
       <c r="F21" t="n">
-        <v>6048873663</v>
+        <v>5945285846</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>813830839</v>
+        <v>286323274</v>
       </c>
       <c r="I21" t="n">
-        <v>4.79</v>
+        <v>292.88</v>
       </c>
       <c r="J21" t="n">
-        <v>4.29</v>
+        <v>263.35</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.006459180289605904</v>
+        <v>12.27</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.2298</v>
+        <v>4.3351</v>
       </c>
       <c r="M21" t="n">
-        <v>1310265070</v>
+        <v>20109921.77165076</v>
       </c>
       <c r="N21" t="n">
-        <v>1310265103</v>
+        <v>20109996.77165076</v>
       </c>
       <c r="O21" t="n">
-        <v>20.44</v>
+        <v>3785.82</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2022-01-16T14:09:45.000Z</t>
+          <t>2017-12-19T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-29T15:39:49.000Z</t>
+          <t>2026-10-30T15:22:54.000Z</t>
         </is>
       </c>
     </row>

--- a/src/xlsx/ingestion.xlsx
+++ b/src/xlsx/ingestion.xlsx
@@ -506,7 +506,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -525,28 +525,28 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>77867</v>
+        <v>77470</v>
       </c>
       <c r="F2" t="n">
-        <v>1565677316596</v>
+        <v>1557527020395</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>177012877962</v>
+        <v>90415848477</v>
       </c>
       <c r="I2" t="n">
-        <v>81840</v>
+        <v>77932</v>
       </c>
       <c r="J2" t="n">
-        <v>76443</v>
+        <v>76338</v>
       </c>
       <c r="K2" t="n">
-        <v>-3618.897402665651</v>
+        <v>454.2</v>
       </c>
       <c r="L2" t="n">
-        <v>-4.44113</v>
+        <v>0.59306</v>
       </c>
       <c r="M2" t="n">
         <v>20105365</v>
@@ -564,14 +564,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,34 +590,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2246.06</v>
+        <v>2250.69</v>
       </c>
       <c r="F3" t="n">
-        <v>274542341533</v>
+        <v>274974840232</v>
       </c>
       <c r="G3" t="n">
         <v>2</v>
       </c>
       <c r="H3" t="n">
-        <v>26876131642</v>
+        <v>8368886232</v>
       </c>
       <c r="I3" t="n">
-        <v>2373.22</v>
+        <v>2257.45</v>
       </c>
       <c r="J3" t="n">
-        <v>2178.62</v>
+        <v>2218.44</v>
       </c>
       <c r="K3" t="n">
-        <v>-111.4385119325175</v>
+        <v>17.46</v>
       </c>
       <c r="L3" t="n">
-        <v>-4.72699</v>
+        <v>0.76872</v>
       </c>
       <c r="M3" t="n">
-        <v>122174495.4349656</v>
+        <v>122177241.1277333</v>
       </c>
       <c r="N3" t="n">
-        <v>122174495.4349656</v>
+        <v>122177241.1277333</v>
       </c>
       <c r="O3" t="n">
         <v>4946.05</v>
@@ -629,14 +629,14 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -655,34 +655,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.999038</v>
+        <v>0.99923</v>
       </c>
       <c r="F4" t="n">
-        <v>180340041253</v>
+        <v>179990851505</v>
       </c>
       <c r="G4" t="n">
         <v>3</v>
       </c>
       <c r="H4" t="n">
-        <v>101735897455</v>
+        <v>38621634949</v>
       </c>
       <c r="I4" t="n">
-        <v>0.999275</v>
+        <v>0.999348</v>
       </c>
       <c r="J4" t="n">
-        <v>0.997999</v>
+        <v>0.998936</v>
       </c>
       <c r="K4" t="n">
-        <v>-9.9704670627143e-05</v>
+        <v>0.00030877</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.009979999999999999</v>
+        <v>0.02821</v>
       </c>
       <c r="M4" t="n">
-        <v>180512752222.448</v>
+        <v>180123438776.854</v>
       </c>
       <c r="N4" t="n">
-        <v>185979700787.3362</v>
+        <v>185590387357.1362</v>
       </c>
       <c r="O4" t="n">
         <v>1.32</v>
@@ -694,14 +694,14 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -720,34 +720,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>702.9</v>
+        <v>706.23</v>
       </c>
       <c r="F5" t="n">
-        <v>92462253882</v>
+        <v>92859178773</v>
       </c>
       <c r="G5" t="n">
         <v>4</v>
       </c>
       <c r="H5" t="n">
-        <v>3117246162</v>
+        <v>851654941</v>
       </c>
       <c r="I5" t="n">
-        <v>753.04</v>
+        <v>709.72</v>
       </c>
       <c r="J5" t="n">
-        <v>682.36</v>
+        <v>695.25</v>
       </c>
       <c r="K5" t="n">
-        <v>-47.95799875427099</v>
+        <v>8.75</v>
       </c>
       <c r="L5" t="n">
-        <v>-6.38713</v>
+        <v>1.22583</v>
       </c>
       <c r="M5" t="n">
-        <v>131511405.81</v>
+        <v>131511361.63</v>
       </c>
       <c r="N5" t="n">
-        <v>131511404.17</v>
+        <v>131511361.63</v>
       </c>
       <c r="O5" t="n">
         <v>1369.99</v>
@@ -759,14 +759,14 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -788,25 +788,25 @@
         <v>1.25</v>
       </c>
       <c r="F6" t="n">
-        <v>79556693251</v>
+        <v>79067094412</v>
       </c>
       <c r="G6" t="n">
         <v>5</v>
       </c>
       <c r="H6" t="n">
-        <v>4027993113</v>
+        <v>1415790371</v>
       </c>
       <c r="I6" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="J6" t="n">
-        <v>1.2</v>
+        <v>1.23</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.05192871821432377</v>
+        <v>0.00744971</v>
       </c>
       <c r="L6" t="n">
-        <v>-3.97367</v>
+        <v>0.54795</v>
       </c>
       <c r="M6" t="n">
         <v>63351197653</v>
@@ -824,14 +824,14 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -850,34 +850,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.999658</v>
+        <v>0.999891</v>
       </c>
       <c r="F7" t="n">
-        <v>71526328773</v>
+        <v>71733868663</v>
       </c>
       <c r="G7" t="n">
         <v>6</v>
       </c>
       <c r="H7" t="n">
-        <v>24324739353</v>
+        <v>9868385249</v>
       </c>
       <c r="I7" t="n">
-        <v>1.002</v>
+        <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>0.998694</v>
+        <v>0.999489</v>
       </c>
       <c r="K7" t="n">
-        <v>9.704000000000001e-05</v>
+        <v>0.00033235</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00971</v>
+        <v>0.02844</v>
       </c>
       <c r="M7" t="n">
-        <v>71550607655.88692</v>
+        <v>71740657501.92535</v>
       </c>
       <c r="N7" t="n">
-        <v>71544148463.41095</v>
+        <v>71739435178.34438</v>
       </c>
       <c r="O7" t="n">
         <v>1.043</v>
@@ -889,14 +889,14 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -915,34 +915,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>95.27</v>
+        <v>95.8</v>
       </c>
       <c r="F8" t="n">
-        <v>56245091312</v>
+        <v>56515653732</v>
       </c>
       <c r="G8" t="n">
         <v>7</v>
       </c>
       <c r="H8" t="n">
-        <v>5885601978</v>
+        <v>2570602438</v>
       </c>
       <c r="I8" t="n">
-        <v>102.94</v>
+        <v>96.94</v>
       </c>
       <c r="J8" t="n">
-        <v>92.64</v>
+        <v>93.56999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>-6.810177750522286</v>
+        <v>1.075</v>
       </c>
       <c r="L8" t="n">
-        <v>-6.67156</v>
+        <v>1.08517</v>
       </c>
       <c r="M8" t="n">
-        <v>590039849.0719869</v>
+        <v>590095108.4572147</v>
       </c>
       <c r="N8" t="n">
-        <v>636700254.1080314</v>
+        <v>636761191.5751935</v>
       </c>
       <c r="O8" t="n">
         <v>293.31</v>
@@ -954,14 +954,14 @@
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -980,34 +980,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.334486</v>
+        <v>0.315719</v>
       </c>
       <c r="F9" t="n">
-        <v>31784255585</v>
+        <v>29992075766</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
       </c>
       <c r="H9" t="n">
-        <v>2278880640</v>
+        <v>639895621</v>
       </c>
       <c r="I9" t="n">
-        <v>0.366528</v>
+        <v>0.336755</v>
       </c>
       <c r="J9" t="n">
-        <v>0.328832</v>
+        <v>0.315621</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00333713</v>
+        <v>-0.02040460445639053</v>
       </c>
       <c r="L9" t="n">
-        <v>1.00774</v>
+        <v>-6.12514</v>
       </c>
       <c r="M9" t="n">
-        <v>95020243944.30574</v>
+        <v>95020228344.12474</v>
       </c>
       <c r="N9" t="n">
-        <v>95020275950.42404</v>
+        <v>95021695569.18364</v>
       </c>
       <c r="O9" t="n">
         <v>0.431288</v>
@@ -1019,14 +1019,14 @@
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1045,34 +1045,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1.029</v>
+        <v>1.027</v>
       </c>
       <c r="F10" t="n">
-        <v>26597679566</v>
+        <v>26687875468</v>
       </c>
       <c r="G10" t="n">
         <v>9</v>
       </c>
       <c r="H10" t="n">
-        <v>367797937</v>
+        <v>79723729</v>
       </c>
       <c r="I10" t="n">
-        <v>1.061</v>
+        <v>1.038</v>
       </c>
       <c r="J10" t="n">
-        <v>1.027</v>
+        <v>1.023</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.004340902318732853</v>
+        <v>-0.002135892355686897</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.4199</v>
+        <v>-0.20435</v>
       </c>
       <c r="M10" t="n">
-        <v>25836537626.749</v>
+        <v>25975658560.029</v>
       </c>
       <c r="N10" t="n">
-        <v>25890652588.459</v>
+        <v>25975658560.029</v>
       </c>
       <c r="O10" t="n">
         <v>1.075</v>
@@ -1084,144 +1084,144 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hyperliquid</t>
+          <t>zcash</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>hype</t>
+          <t>zec</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Hyperliquid</t>
+          <t>Zcash</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>93.13</v>
+        <v>1282.74</v>
       </c>
       <c r="F11" t="n">
-        <v>22300176597</v>
+        <v>21817527993</v>
       </c>
       <c r="G11" t="n">
         <v>10</v>
       </c>
       <c r="H11" t="n">
-        <v>2904755669</v>
+        <v>669295724</v>
       </c>
       <c r="I11" t="n">
-        <v>96.7</v>
+        <v>1296.49</v>
       </c>
       <c r="J11" t="n">
-        <v>88.67</v>
+        <v>1208.71</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.2206697577718586</v>
+        <v>45.15</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2364</v>
+        <v>3.60159</v>
       </c>
       <c r="M11" t="n">
-        <v>239406814.3741415</v>
+        <v>17014731.4155448</v>
       </c>
       <c r="N11" t="n">
-        <v>951538272.9141414</v>
+        <v>17016262.6655448</v>
       </c>
       <c r="O11" t="n">
-        <v>97.95999999999999</v>
+        <v>3191.93</v>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2026-09-23T05:16:50.000Z</t>
+          <t>2016-10-28T16:00:00.000Z</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>zcash</t>
+          <t>hyperliquid</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>zec</t>
+          <t>hype</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Zcash</t>
+          <t>Hyperliquid</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1250.33</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>21254633959</v>
+        <v>20784398822</v>
       </c>
       <c r="G12" t="n">
         <v>11</v>
       </c>
       <c r="H12" t="n">
-        <v>1515646853</v>
+        <v>1828903532</v>
       </c>
       <c r="I12" t="n">
-        <v>1392.21</v>
+        <v>93.84</v>
       </c>
       <c r="J12" t="n">
-        <v>1189.27</v>
+        <v>86.37</v>
       </c>
       <c r="K12" t="n">
-        <v>-69.38714946963682</v>
+        <v>-5.375216845563173</v>
       </c>
       <c r="L12" t="n">
-        <v>-5.25773</v>
+        <v>-5.90758</v>
       </c>
       <c r="M12" t="n">
-        <v>17010609.5405448</v>
+        <v>239406814.3741415</v>
       </c>
       <c r="N12" t="n">
-        <v>17014531.4155448</v>
+        <v>951538272.9141414</v>
       </c>
       <c r="O12" t="n">
-        <v>3191.93</v>
+        <v>97.95999999999999</v>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>2016-10-28T16:00:00.000Z</t>
+          <t>2026-09-23T05:16:50.000Z</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1240,34 +1240,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>0.076281</v>
+        <v>0.07546799999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>11941642087</v>
+        <v>11813111400</v>
       </c>
       <c r="G13" t="n">
         <v>12</v>
       </c>
       <c r="H13" t="n">
-        <v>1044756240</v>
+        <v>423755709</v>
       </c>
       <c r="I13" t="n">
-        <v>0.081219</v>
+        <v>0.076542</v>
       </c>
       <c r="J13" t="n">
-        <v>0.072687</v>
+        <v>0.07451000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.003684641734336594</v>
+        <v>-0.000143971648569025</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.60777</v>
+        <v>-0.21963</v>
       </c>
       <c r="M13" t="n">
-        <v>156511242860.1691</v>
+        <v>156543692860.1691</v>
       </c>
       <c r="N13" t="n">
-        <v>156541172860.1691</v>
+        <v>156554392860.1691</v>
       </c>
       <c r="O13" t="n">
         <v>0.731578</v>
@@ -1279,14 +1279,14 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1305,34 +1305,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>599.35</v>
+        <v>593.45</v>
       </c>
       <c r="F14" t="n">
-        <v>11291345186</v>
+        <v>11168957559</v>
       </c>
       <c r="G14" t="n">
         <v>13</v>
       </c>
       <c r="H14" t="n">
-        <v>225788953</v>
+        <v>91329173</v>
       </c>
       <c r="I14" t="n">
-        <v>646.2</v>
+        <v>600.79</v>
       </c>
       <c r="J14" t="n">
-        <v>574.24</v>
+        <v>586.42</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.170031909041427</v>
+        <v>-3.669873736796376</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.19484</v>
+        <v>-0.90298</v>
       </c>
       <c r="M14" t="n">
-        <v>18824433.39824343</v>
+        <v>18824860.59049213</v>
       </c>
       <c r="N14" t="n">
-        <v>18824443.59824343</v>
+        <v>18824860.59049213</v>
       </c>
       <c r="O14" t="n">
         <v>797.73</v>
@@ -1344,14 +1344,14 @@
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1373,31 +1373,31 @@
         <v>1.001</v>
       </c>
       <c r="F15" t="n">
-        <v>9560023102</v>
+        <v>9583597627</v>
       </c>
       <c r="G15" t="n">
         <v>14</v>
       </c>
       <c r="H15" t="n">
-        <v>250103442</v>
+        <v>301507150</v>
       </c>
       <c r="I15" t="n">
-        <v>1.008</v>
+        <v>1.001</v>
       </c>
       <c r="J15" t="n">
-        <v>0.993682</v>
+        <v>1</v>
       </c>
       <c r="K15" t="n">
-        <v>0.00072913</v>
+        <v>-5.1156484117465e-05</v>
       </c>
       <c r="L15" t="n">
-        <v>0.07292999999999999</v>
+        <v>-0.00715</v>
       </c>
       <c r="M15" t="n">
-        <v>9553064925.561302</v>
+        <v>9578492212.845774</v>
       </c>
       <c r="N15" t="n">
-        <v>9553751663.605755</v>
+        <v>9578492212.845774</v>
       </c>
       <c r="O15" t="n">
         <v>1.057</v>
@@ -1409,209 +1409,209 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>whitebit</t>
+          <t>chainlink</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>wbt</t>
+          <t>link</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>WhiteBIT Coin</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>74.54000000000001</v>
+        <v>11.54</v>
       </c>
       <c r="F16" t="n">
-        <v>8849925151</v>
+        <v>8851595759</v>
       </c>
       <c r="G16" t="n">
         <v>15</v>
       </c>
       <c r="H16" t="n">
-        <v>287779826</v>
+        <v>387235303</v>
       </c>
       <c r="I16" t="n">
-        <v>78.58</v>
+        <v>11.72</v>
       </c>
       <c r="J16" t="n">
-        <v>73.06999999999999</v>
+        <v>11.01</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.630967185801765</v>
+        <v>0.436301</v>
       </c>
       <c r="L16" t="n">
-        <v>-4.64471</v>
+        <v>3.95052</v>
       </c>
       <c r="M16" t="n">
-        <v>118688311</v>
+        <v>766849970.424884</v>
       </c>
       <c r="N16" t="n">
-        <v>293257810</v>
+        <v>1000000000</v>
       </c>
       <c r="O16" t="n">
-        <v>87.91</v>
+        <v>52.7</v>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>2026-09-21T20:29:10.000Z</t>
+          <t>2021-05-09T16:13:57.000Z</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>leo-token</t>
+          <t>whitebit</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>leo</t>
+          <t>wbt</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LEO Token</t>
+          <t>WhiteBIT Coin</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>9.4</v>
+        <v>74.37</v>
       </c>
       <c r="F17" t="n">
-        <v>8647156553</v>
+        <v>8825450143</v>
       </c>
       <c r="G17" t="n">
         <v>16</v>
       </c>
       <c r="H17" t="n">
-        <v>170782</v>
+        <v>93580707</v>
       </c>
       <c r="I17" t="n">
-        <v>9.470000000000001</v>
+        <v>74.84</v>
       </c>
       <c r="J17" t="n">
-        <v>9.210000000000001</v>
+        <v>73.28</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.005316334383755006</v>
+        <v>0.405336</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.05652</v>
+        <v>0.53829</v>
       </c>
       <c r="M17" t="n">
-        <v>919857851.9</v>
+        <v>118688311</v>
       </c>
       <c r="N17" t="n">
-        <v>985239504</v>
+        <v>293257810</v>
       </c>
       <c r="O17" t="n">
-        <v>10.61</v>
+        <v>87.91</v>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>2026-05-04T09:35:00.000Z</t>
+          <t>2026-09-21T20:29:10.000Z</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>chainlink</t>
+          <t>leo-token</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>link</t>
+          <t>leo</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>LEO Token</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>11.21</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>8604497529</v>
+        <v>8623243550</v>
       </c>
       <c r="G18" t="n">
         <v>17</v>
       </c>
       <c r="H18" t="n">
-        <v>909817447</v>
+        <v>160226</v>
       </c>
       <c r="I18" t="n">
-        <v>11.99</v>
+        <v>9.48</v>
       </c>
       <c r="J18" t="n">
-        <v>10.3</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6525340146184107</v>
+        <v>-0.03027727341055275</v>
       </c>
       <c r="L18" t="n">
-        <v>-5.49862</v>
+        <v>-0.32071</v>
       </c>
       <c r="M18" t="n">
-        <v>766849970.424884</v>
+        <v>919857851.9</v>
       </c>
       <c r="N18" t="n">
-        <v>1000000000</v>
+        <v>985239504</v>
       </c>
       <c r="O18" t="n">
-        <v>52.7</v>
+        <v>10.61</v>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2021-05-09T16:13:57.000Z</t>
+          <t>2026-05-04T09:35:00.000Z</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1630,28 +1630,28 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.193778</v>
+        <v>0.192664</v>
       </c>
       <c r="F19" t="n">
-        <v>7283224175</v>
+        <v>7235674173</v>
       </c>
       <c r="G19" t="n">
         <v>18</v>
       </c>
       <c r="H19" t="n">
-        <v>473983841</v>
+        <v>173533018</v>
       </c>
       <c r="I19" t="n">
-        <v>0.208002</v>
+        <v>0.196663</v>
       </c>
       <c r="J19" t="n">
-        <v>0.183186</v>
+        <v>0.19001</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.01094488603445748</v>
+        <v>0.0006743400000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>-5.34619</v>
+        <v>0.29524</v>
       </c>
       <c r="M19" t="n">
         <v>37571497272.79388</v>
@@ -1669,14 +1669,14 @@
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1695,34 +1695,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>0.169629</v>
+        <v>0.16936</v>
       </c>
       <c r="F20" t="n">
-        <v>5984185821</v>
+        <v>5970126218</v>
       </c>
       <c r="G20" t="n">
         <v>19</v>
       </c>
       <c r="H20" t="n">
-        <v>207868344</v>
+        <v>112342738</v>
       </c>
       <c r="I20" t="n">
-        <v>0.17347</v>
+        <v>0.172249</v>
       </c>
       <c r="J20" t="n">
-        <v>0.158344</v>
+        <v>0.166006</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.002258901154111176</v>
+        <v>0.00292816</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.31417</v>
+        <v>1.67394</v>
       </c>
       <c r="M20" t="n">
-        <v>35247503121.71093</v>
+        <v>35251445970.0695</v>
       </c>
       <c r="N20" t="n">
-        <v>50001786837.39717</v>
+        <v>50001786837.39707</v>
       </c>
       <c r="O20" t="n">
         <v>0.875563</v>
@@ -1734,72 +1734,72 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>20261030T152401Z-472100</t>
+          <t>20261031T145308Z-eb0b43</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>bitcoin-cash</t>
+          <t>near</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>bch</t>
+          <t>near</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Bitcoin Cash</t>
+          <t>NEAR Protocol</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>295.43</v>
+        <v>4.45</v>
       </c>
       <c r="F21" t="n">
-        <v>5945285846</v>
+        <v>5827366245</v>
       </c>
       <c r="G21" t="n">
         <v>20</v>
       </c>
       <c r="H21" t="n">
-        <v>286323274</v>
+        <v>534486585</v>
       </c>
       <c r="I21" t="n">
-        <v>292.88</v>
+        <v>4.45</v>
       </c>
       <c r="J21" t="n">
-        <v>263.35</v>
+        <v>4.24</v>
       </c>
       <c r="K21" t="n">
-        <v>12.27</v>
+        <v>0.114342</v>
       </c>
       <c r="L21" t="n">
-        <v>4.3351</v>
+        <v>2.5763</v>
       </c>
       <c r="M21" t="n">
-        <v>20109921.77165076</v>
+        <v>1310446865</v>
       </c>
       <c r="N21" t="n">
-        <v>20109996.77165076</v>
+        <v>1310446891</v>
       </c>
       <c r="O21" t="n">
-        <v>3785.82</v>
+        <v>20.44</v>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>2017-12-19T16:00:00.000Z</t>
+          <t>2022-01-16T14:09:45.000Z</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2026-10-30T15:22:54.000Z</t>
+          <t>2026-10-31T14:51:57.000Z</t>
         </is>
       </c>
     </row>
